--- a/research/traditional_assets/database/data/finland/finland_air_transport.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_air_transport.xlsx
@@ -588,121 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.256</v>
-      </c>
-      <c r="F2">
-        <v>-0.182</v>
+        <v>-0.0353</v>
       </c>
       <c r="G2">
-        <v>-0.4935320124447355</v>
+        <v>-0.1642675283979632</v>
       </c>
       <c r="H2">
-        <v>-0.4935320124447355</v>
+        <v>-0.1642675283979632</v>
       </c>
       <c r="I2">
-        <v>-0.7599796456443126</v>
+        <v>-0.1357475944772303</v>
       </c>
       <c r="J2">
-        <v>-0.7599796456443126</v>
+        <v>-0.1357475944772303</v>
       </c>
       <c r="K2">
-        <v>-451.7</v>
+        <v>-601.2</v>
       </c>
       <c r="L2">
-        <v>-0.7396430325855575</v>
+        <v>-0.2943595769682726</v>
       </c>
       <c r="M2">
-        <v>79.59999999999999</v>
+        <v>20.1</v>
       </c>
       <c r="N2">
-        <v>0.08401055408970975</v>
+        <v>0.03443549768716807</v>
       </c>
       <c r="O2">
-        <v>-0.1762231569625858</v>
+        <v>-0.03343313373253493</v>
       </c>
       <c r="P2">
-        <v>29.4</v>
+        <v>20.1</v>
       </c>
       <c r="Q2">
-        <v>0.03102902374670185</v>
+        <v>0.03443549768716807</v>
       </c>
       <c r="R2">
-        <v>-0.06508744742085455</v>
+        <v>-0.03343313373253493</v>
       </c>
       <c r="S2">
-        <v>50.2</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.6306532663316583</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>940.1</v>
+        <v>804.5</v>
       </c>
       <c r="V2">
-        <v>0.9921899736147758</v>
+        <v>1.378276511906801</v>
       </c>
       <c r="W2">
-        <v>-0.4090744430356819</v>
+        <v>-0.9460267505900866</v>
       </c>
       <c r="X2">
-        <v>0.1670977616735161</v>
+        <v>0.2818190703261046</v>
       </c>
       <c r="Y2">
-        <v>-0.5761722047091981</v>
+        <v>-1.227845820916191</v>
       </c>
       <c r="Z2">
-        <v>0.2122477519766753</v>
+        <v>0.7136381960398591</v>
       </c>
       <c r="AA2">
-        <v>-0.1613039713360357</v>
+        <v>-0.09687466843948099</v>
       </c>
       <c r="AB2">
-        <v>0.05774886208395079</v>
+        <v>0.08866301344141819</v>
       </c>
       <c r="AC2">
-        <v>-0.2190528334199864</v>
+        <v>-0.1855376818808992</v>
       </c>
       <c r="AD2">
-        <v>3150.7</v>
+        <v>2750.8</v>
       </c>
       <c r="AE2">
-        <v>20.09784797490893</v>
+        <v>15.85443480147612</v>
       </c>
       <c r="AF2">
-        <v>3170.797847974909</v>
+        <v>2766.654434801476</v>
       </c>
       <c r="AG2">
-        <v>2230.697847974909</v>
+        <v>1962.154434801476</v>
       </c>
       <c r="AH2">
-        <v>0.7699292195522199</v>
+        <v>0.8257796267950417</v>
       </c>
       <c r="AI2">
-        <v>0.8330398656694432</v>
+        <v>0.8875292321069942</v>
       </c>
       <c r="AJ2">
-        <v>0.7018750734465036</v>
+        <v>0.7707253046282213</v>
       </c>
       <c r="AK2">
-        <v>0.7782776927109174</v>
+        <v>0.8484058684638973</v>
       </c>
       <c r="AL2">
-        <v>21.7</v>
+        <v>114.2</v>
       </c>
       <c r="AM2">
-        <v>-74.2</v>
+        <v>114.2</v>
       </c>
       <c r="AN2">
-        <v>-13.34476916560779</v>
+        <v>-20.22944550669216</v>
       </c>
       <c r="AO2">
-        <v>-21.40552995391705</v>
+        <v>-2.437828371278459</v>
       </c>
       <c r="AP2">
-        <v>-9.448106090533285</v>
+        <v>-14.42972815709278</v>
       </c>
       <c r="AQ2">
-        <v>6.26010781671159</v>
+        <v>-2.437828371278459</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +719,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.256</v>
-      </c>
-      <c r="F3">
-        <v>-0.182</v>
+        <v>-0.0353</v>
       </c>
       <c r="G3">
-        <v>-0.4935320124447355</v>
+        <v>-0.1642675283979632</v>
       </c>
       <c r="H3">
-        <v>-0.4935320124447355</v>
+        <v>-0.1642675283979632</v>
       </c>
       <c r="I3">
-        <v>-0.7599796456443126</v>
+        <v>-0.1357475944772303</v>
       </c>
       <c r="J3">
-        <v>-0.7599796456443126</v>
+        <v>-0.1357475944772303</v>
       </c>
       <c r="K3">
-        <v>-451.7</v>
+        <v>-601.2</v>
       </c>
       <c r="L3">
-        <v>-0.7396430325855575</v>
+        <v>-0.2943595769682726</v>
       </c>
       <c r="M3">
-        <v>79.59999999999999</v>
+        <v>20.1</v>
       </c>
       <c r="N3">
-        <v>0.08401055408970975</v>
+        <v>0.03443549768716807</v>
       </c>
       <c r="O3">
-        <v>-0.1762231569625858</v>
+        <v>-0.03343313373253493</v>
       </c>
       <c r="P3">
-        <v>29.4</v>
+        <v>20.1</v>
       </c>
       <c r="Q3">
-        <v>0.03102902374670185</v>
+        <v>0.03443549768716807</v>
       </c>
       <c r="R3">
-        <v>-0.06508744742085455</v>
+        <v>-0.03343313373253493</v>
       </c>
       <c r="S3">
-        <v>50.2</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.6306532663316583</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>940.1</v>
+        <v>804.5</v>
       </c>
       <c r="V3">
-        <v>0.9921899736147758</v>
+        <v>1.378276511906801</v>
       </c>
       <c r="W3">
-        <v>-0.4090744430356819</v>
+        <v>-0.9460267505900866</v>
       </c>
       <c r="X3">
-        <v>0.1670977616735161</v>
+        <v>0.2818190703261046</v>
       </c>
       <c r="Y3">
-        <v>-0.5761722047091981</v>
+        <v>-1.227845820916191</v>
       </c>
       <c r="Z3">
-        <v>0.2122477519766753</v>
+        <v>0.7136381960398591</v>
       </c>
       <c r="AA3">
-        <v>-0.1613039713360357</v>
+        <v>-0.09687466843948099</v>
       </c>
       <c r="AB3">
-        <v>0.05774886208395079</v>
+        <v>0.08866301344141819</v>
       </c>
       <c r="AC3">
-        <v>-0.2190528334199864</v>
+        <v>-0.1855376818808992</v>
       </c>
       <c r="AD3">
-        <v>3150.7</v>
+        <v>2750.8</v>
       </c>
       <c r="AE3">
-        <v>20.09784797490893</v>
+        <v>15.85443480147612</v>
       </c>
       <c r="AF3">
-        <v>3170.797847974909</v>
+        <v>2766.654434801476</v>
       </c>
       <c r="AG3">
-        <v>2230.697847974909</v>
+        <v>1962.154434801476</v>
       </c>
       <c r="AH3">
-        <v>0.7699292195522199</v>
+        <v>0.8257796267950417</v>
       </c>
       <c r="AI3">
-        <v>0.8330398656694432</v>
+        <v>0.8875292321069942</v>
       </c>
       <c r="AJ3">
-        <v>0.7018750734465036</v>
+        <v>0.7707253046282213</v>
       </c>
       <c r="AK3">
-        <v>0.7782776927109174</v>
+        <v>0.8484058684638973</v>
       </c>
       <c r="AL3">
-        <v>21.7</v>
+        <v>114.2</v>
       </c>
       <c r="AM3">
-        <v>-74.2</v>
+        <v>114.2</v>
       </c>
       <c r="AN3">
-        <v>-13.34476916560779</v>
+        <v>-20.22944550669216</v>
       </c>
       <c r="AO3">
-        <v>-21.40552995391705</v>
+        <v>-2.437828371278459</v>
       </c>
       <c r="AP3">
-        <v>-9.448106090533285</v>
+        <v>-14.42972815709278</v>
       </c>
       <c r="AQ3">
-        <v>6.26010781671159</v>
+        <v>-2.437828371278459</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/finland/finland_air_transport.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_air_transport.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="hlse_fia1s" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,118 +590,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0353</v>
+        <v>0.00957</v>
+      </c>
+      <c r="E2">
+        <v>0.237</v>
       </c>
       <c r="G2">
-        <v>-0.1642675283979632</v>
+        <v>-0.01108654554775866</v>
       </c>
       <c r="H2">
-        <v>-0.1642675283979632</v>
+        <v>-0.01108654554775866</v>
       </c>
       <c r="I2">
-        <v>-0.1357475944772303</v>
+        <v>0.06876157556214076</v>
       </c>
       <c r="J2">
-        <v>-0.1357475944772303</v>
+        <v>0.06876157556214076</v>
       </c>
       <c r="K2">
-        <v>-601.2</v>
+        <v>261.9</v>
       </c>
       <c r="L2">
-        <v>-0.2943595769682726</v>
+        <v>0.08391810054791886</v>
       </c>
       <c r="M2">
-        <v>20.1</v>
+        <v>233.3</v>
       </c>
       <c r="N2">
-        <v>0.03443549768716807</v>
+        <v>0.2589345172031076</v>
       </c>
       <c r="O2">
-        <v>-0.03343313373253493</v>
+        <v>0.8907980145093547</v>
       </c>
       <c r="P2">
-        <v>20.1</v>
+        <v>21.6</v>
       </c>
       <c r="Q2">
-        <v>0.03443549768716807</v>
+        <v>0.02397336293007769</v>
       </c>
       <c r="R2">
-        <v>-0.03343313373253493</v>
+        <v>0.08247422680412372</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>211.7</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.9074153450492928</v>
       </c>
       <c r="U2">
-        <v>804.5</v>
+        <v>347.3</v>
       </c>
       <c r="V2">
-        <v>1.378276511906801</v>
+        <v>0.3854605993340733</v>
       </c>
       <c r="W2">
-        <v>-0.9460267505900866</v>
+        <v>0.7470051340559041</v>
       </c>
       <c r="X2">
-        <v>0.2818190703261046</v>
+        <v>0.1745836736320732</v>
       </c>
       <c r="Y2">
-        <v>-1.227845820916191</v>
+        <v>0.5724214604238309</v>
       </c>
       <c r="Z2">
-        <v>0.7136381960398591</v>
+        <v>1.350302435862688</v>
       </c>
       <c r="AA2">
-        <v>-0.09687466843948099</v>
+        <v>0.09284892297531495</v>
       </c>
       <c r="AB2">
-        <v>0.08866301344141819</v>
+        <v>0.07987638259285476</v>
       </c>
       <c r="AC2">
-        <v>-0.1855376818808992</v>
+        <v>0.01297254038246019</v>
       </c>
       <c r="AD2">
-        <v>2750.8</v>
+        <v>2527.2</v>
       </c>
       <c r="AE2">
-        <v>15.85443480147612</v>
+        <v>14.35999414057445</v>
       </c>
       <c r="AF2">
-        <v>2766.654434801476</v>
+        <v>2541.559994140574</v>
       </c>
       <c r="AG2">
-        <v>1962.154434801476</v>
+        <v>2194.259994140574</v>
       </c>
       <c r="AH2">
-        <v>0.8257796267950417</v>
+        <v>0.7382761661282443</v>
       </c>
       <c r="AI2">
-        <v>0.8875292321069942</v>
+        <v>0.8382564410652764</v>
       </c>
       <c r="AJ2">
-        <v>0.7707253046282213</v>
+        <v>0.7089097517799404</v>
       </c>
       <c r="AK2">
-        <v>0.8484058684638973</v>
+        <v>0.8173325482294493</v>
       </c>
       <c r="AL2">
-        <v>114.2</v>
+        <v>122.5</v>
       </c>
       <c r="AM2">
-        <v>114.2</v>
+        <v>76</v>
       </c>
       <c r="AN2">
-        <v>-20.22944550669216</v>
+        <v>6.763186769074317</v>
       </c>
       <c r="AO2">
-        <v>-2.437828371278459</v>
+        <v>1.740408163265306</v>
       </c>
       <c r="AP2">
-        <v>-14.42972815709278</v>
+        <v>5.872186673108825</v>
       </c>
       <c r="AQ2">
-        <v>-2.437828371278459</v>
+        <v>2.805263157894737</v>
       </c>
     </row>
     <row r="3">
@@ -719,118 +724,8893 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0353</v>
+        <v>0.00957</v>
+      </c>
+      <c r="E3">
+        <v>0.237</v>
       </c>
       <c r="G3">
-        <v>-0.1642675283979632</v>
+        <v>-0.01108654554775866</v>
       </c>
       <c r="H3">
-        <v>-0.1642675283979632</v>
+        <v>-0.01108654554775866</v>
       </c>
       <c r="I3">
-        <v>-0.1357475944772303</v>
+        <v>0.06876157556214076</v>
       </c>
       <c r="J3">
-        <v>-0.1357475944772303</v>
+        <v>0.06876157556214076</v>
       </c>
       <c r="K3">
-        <v>-601.2</v>
+        <v>261.9</v>
       </c>
       <c r="L3">
-        <v>-0.2943595769682726</v>
+        <v>0.08391810054791886</v>
       </c>
       <c r="M3">
-        <v>20.1</v>
+        <v>233.3</v>
       </c>
       <c r="N3">
-        <v>0.03443549768716807</v>
+        <v>0.2589345172031076</v>
       </c>
       <c r="O3">
-        <v>-0.03343313373253493</v>
+        <v>0.8907980145093547</v>
       </c>
       <c r="P3">
-        <v>20.1</v>
+        <v>21.6</v>
       </c>
       <c r="Q3">
-        <v>0.03443549768716807</v>
+        <v>0.02397336293007769</v>
       </c>
       <c r="R3">
-        <v>-0.03343313373253493</v>
+        <v>0.08247422680412372</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>211.7</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.9074153450492928</v>
       </c>
       <c r="U3">
-        <v>804.5</v>
+        <v>347.3</v>
       </c>
       <c r="V3">
-        <v>1.378276511906801</v>
+        <v>0.3854605993340733</v>
       </c>
       <c r="W3">
-        <v>-0.9460267505900866</v>
+        <v>0.7470051340559041</v>
       </c>
       <c r="X3">
-        <v>0.2818190703261046</v>
+        <v>0.1745836736320732</v>
       </c>
       <c r="Y3">
-        <v>-1.227845820916191</v>
+        <v>0.5724214604238309</v>
       </c>
       <c r="Z3">
-        <v>0.7136381960398591</v>
+        <v>1.350302435862688</v>
       </c>
       <c r="AA3">
-        <v>-0.09687466843948099</v>
+        <v>0.09284892297531495</v>
       </c>
       <c r="AB3">
-        <v>0.08866301344141819</v>
+        <v>0.07987638259285476</v>
       </c>
       <c r="AC3">
-        <v>-0.1855376818808992</v>
+        <v>0.01297254038246019</v>
       </c>
       <c r="AD3">
-        <v>2750.8</v>
+        <v>2527.2</v>
       </c>
       <c r="AE3">
-        <v>15.85443480147612</v>
+        <v>14.35999414057445</v>
       </c>
       <c r="AF3">
-        <v>2766.654434801476</v>
+        <v>2541.559994140574</v>
       </c>
       <c r="AG3">
-        <v>1962.154434801476</v>
+        <v>2194.259994140574</v>
       </c>
       <c r="AH3">
-        <v>0.8257796267950417</v>
+        <v>0.7382761661282443</v>
       </c>
       <c r="AI3">
-        <v>0.8875292321069942</v>
+        <v>0.8382564410652764</v>
       </c>
       <c r="AJ3">
-        <v>0.7707253046282213</v>
+        <v>0.7089097517799404</v>
       </c>
       <c r="AK3">
-        <v>0.8484058684638973</v>
+        <v>0.8173325482294493</v>
       </c>
       <c r="AL3">
-        <v>114.2</v>
+        <v>122.5</v>
       </c>
       <c r="AM3">
-        <v>114.2</v>
+        <v>76</v>
       </c>
       <c r="AN3">
-        <v>-20.22944550669216</v>
+        <v>6.763186769074317</v>
       </c>
       <c r="AO3">
-        <v>-2.437828371278459</v>
+        <v>1.740408163265306</v>
       </c>
       <c r="AP3">
-        <v>-14.42972815709278</v>
+        <v>5.872186673108825</v>
       </c>
       <c r="AQ3">
-        <v>-2.437828371278459</v>
+        <v>2.805263157894737</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Finnair Oyj (HLSE:FIA1S)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HLSE:FIA1S</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Air Transport</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.204653061224489</v>
+      </c>
+      <c r="F2">
+        <v>4.74391824571103</v>
+      </c>
+      <c r="G2">
+        <v>6.80161638381613</v>
+      </c>
+      <c r="H2">
+        <v>1.65831027094844</v>
+      </c>
+      <c r="I2">
+        <v>0.738276166128244</v>
+      </c>
+      <c r="J2">
+        <v>0.18</v>
+      </c>
+      <c r="K2">
+        <v>901</v>
+      </c>
+      <c r="L2">
+        <v>2850.41372745303</v>
+      </c>
+      <c r="M2">
+        <v>3095.25999414057</v>
+      </c>
+      <c r="N2">
+        <v>3122.77452639833</v>
+      </c>
+      <c r="O2">
+        <v>2541.55999414057</v>
+      </c>
+      <c r="P2">
+        <v>619.660798945303</v>
+      </c>
+      <c r="Q2">
+        <v>0.0798763825928548</v>
+      </c>
+      <c r="R2">
+        <v>0.0793387980163147</v>
+      </c>
+      <c r="S2">
+        <v>0.0463020151086867</v>
+      </c>
+      <c r="T2">
+        <v>0.04072</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.174583673632073</v>
+      </c>
+      <c r="X2">
+        <v>0.0878160951418471</v>
+      </c>
+      <c r="Y2">
+        <v>2.61906475924476</v>
+      </c>
+      <c r="Z2">
+        <v>0.94544744583694</v>
+      </c>
+      <c r="AA2">
+        <v>2527.2</v>
+      </c>
+      <c r="AB2">
+        <v>0.05787751888585833</v>
+      </c>
+      <c r="AC2">
+        <v>0.2046530612244893</v>
+      </c>
+      <c r="AD2">
+        <v>2541.559994140574</v>
+      </c>
+      <c r="AE2">
+        <v>122.5</v>
+      </c>
+      <c r="AF2">
+        <v>348.6</v>
+      </c>
+      <c r="AG2">
+        <v>373.67</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>901</v>
+      </c>
+      <c r="AK2">
+        <v>0.0518443360947012</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.2</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>183.3000000000001</v>
+      </c>
+      <c r="AR2">
+        <v>122.5</v>
+      </c>
+      <c r="AS2">
+        <v>2527.2</v>
+      </c>
+      <c r="AT2">
+        <v>347.3</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08049418881360441</v>
+      </c>
+      <c r="C2">
+        <v>3411.532358881308</v>
+      </c>
+      <c r="D2">
+        <v>3064.232358881308</v>
+      </c>
+      <c r="E2">
+        <v>-2541.559994140574</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>347.3</v>
+      </c>
+      <c r="H2">
+        <v>901</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K2">
+        <v>348.6</v>
+      </c>
+      <c r="L2">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="O2">
+        <v>29.92533333333332</v>
+      </c>
+      <c r="P2">
+        <v>119.7013333333333</v>
+      </c>
+      <c r="Q2">
+        <v>468.3013333333333</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08049418881360441</v>
+      </c>
+      <c r="T2">
+        <v>0.8042187817285176</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.2</v>
+      </c>
+      <c r="W2">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.0803804004359772</v>
+      </c>
+      <c r="C3">
+        <v>3382.774649232968</v>
+      </c>
+      <c r="D3">
+        <v>3069.900249174374</v>
+      </c>
+      <c r="E3">
+        <v>-2507.134394199169</v>
+      </c>
+      <c r="F3">
+        <v>34.42559994140574</v>
+      </c>
+      <c r="G3">
+        <v>347.3</v>
+      </c>
+      <c r="H3">
+        <v>901</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K3">
+        <v>348.6</v>
+      </c>
+      <c r="L3">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M3">
+        <v>1.538824317380837</v>
+      </c>
+      <c r="N3">
+        <v>148.0878423492858</v>
+      </c>
+      <c r="O3">
+        <v>29.61756846985716</v>
+      </c>
+      <c r="P3">
+        <v>118.4702738794286</v>
+      </c>
+      <c r="Q3">
+        <v>467.0702738794287</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08083111155149213</v>
+      </c>
+      <c r="T3">
+        <v>0.810717519358647</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.2</v>
+      </c>
+      <c r="W3">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>97.23440484833212</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08026661205834999</v>
+      </c>
+      <c r="C4">
+        <v>3354.037946158596</v>
+      </c>
+      <c r="D4">
+        <v>3075.589146041408</v>
+      </c>
+      <c r="E4">
+        <v>-2472.708794257763</v>
+      </c>
+      <c r="F4">
+        <v>68.85119988281149</v>
+      </c>
+      <c r="G4">
+        <v>347.3</v>
+      </c>
+      <c r="H4">
+        <v>901</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K4">
+        <v>348.6</v>
+      </c>
+      <c r="L4">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M4">
+        <v>3.077648634761674</v>
+      </c>
+      <c r="N4">
+        <v>146.5490180319049</v>
+      </c>
+      <c r="O4">
+        <v>29.30980360638099</v>
+      </c>
+      <c r="P4">
+        <v>117.2392144255239</v>
+      </c>
+      <c r="Q4">
+        <v>465.8392144255239</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08117491026362245</v>
+      </c>
+      <c r="T4">
+        <v>0.8173488842873505</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.2</v>
+      </c>
+      <c r="W4">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>48.61720242416605</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.08015282368072278</v>
+      </c>
+      <c r="C5">
+        <v>3325.322366658185</v>
+      </c>
+      <c r="D5">
+        <v>3081.299166482402</v>
+      </c>
+      <c r="E5">
+        <v>-2438.283194316357</v>
+      </c>
+      <c r="F5">
+        <v>103.2767998242172</v>
+      </c>
+      <c r="G5">
+        <v>347.3</v>
+      </c>
+      <c r="H5">
+        <v>901</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K5">
+        <v>348.6</v>
+      </c>
+      <c r="L5">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M5">
+        <v>4.616472952142511</v>
+      </c>
+      <c r="N5">
+        <v>145.0101937145241</v>
+      </c>
+      <c r="O5">
+        <v>29.00203874290482</v>
+      </c>
+      <c r="P5">
+        <v>116.0081549716193</v>
+      </c>
+      <c r="Q5">
+        <v>464.6081549716193</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08152579760899256</v>
+      </c>
+      <c r="T5">
+        <v>0.8241169783898417</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.2</v>
+      </c>
+      <c r="W5">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>32.41146828277738</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08003903530309557</v>
+      </c>
+      <c r="C6">
+        <v>3296.628028602209</v>
+      </c>
+      <c r="D6">
+        <v>3087.030428367832</v>
+      </c>
+      <c r="E6">
+        <v>-2403.857594374952</v>
+      </c>
+      <c r="F6">
+        <v>137.702399765623</v>
+      </c>
+      <c r="G6">
+        <v>347.3</v>
+      </c>
+      <c r="H6">
+        <v>901</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K6">
+        <v>348.6</v>
+      </c>
+      <c r="L6">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M6">
+        <v>6.155297269523348</v>
+      </c>
+      <c r="N6">
+        <v>143.4713693971433</v>
+      </c>
+      <c r="O6">
+        <v>28.69427387942865</v>
+      </c>
+      <c r="P6">
+        <v>114.7770955177146</v>
+      </c>
+      <c r="Q6">
+        <v>463.3770955177146</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08188399510739122</v>
+      </c>
+      <c r="T6">
+        <v>0.8310260744528015</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.2</v>
+      </c>
+      <c r="W6">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>24.30860121208303</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.07992524692546836</v>
+      </c>
+      <c r="C7">
+        <v>3267.955050739744</v>
+      </c>
+      <c r="D7">
+        <v>3092.783050446773</v>
+      </c>
+      <c r="E7">
+        <v>-2369.431994433546</v>
+      </c>
+      <c r="F7">
+        <v>172.1279997070287</v>
+      </c>
+      <c r="G7">
+        <v>347.3</v>
+      </c>
+      <c r="H7">
+        <v>901</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K7">
+        <v>348.6</v>
+      </c>
+      <c r="L7">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M7">
+        <v>7.694121586904185</v>
+      </c>
+      <c r="N7">
+        <v>141.9325450797624</v>
+      </c>
+      <c r="O7">
+        <v>28.38650901595249</v>
+      </c>
+      <c r="P7">
+        <v>113.54603606381</v>
+      </c>
+      <c r="Q7">
+        <v>462.14603606381</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08224973360575617</v>
+      </c>
+      <c r="T7">
+        <v>0.8380806251697183</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.2</v>
+      </c>
+      <c r="W7">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>19.44688096966642</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.07981145854784115</v>
+      </c>
+      <c r="C8">
+        <v>3239.303552706665</v>
+      </c>
+      <c r="D8">
+        <v>3098.557152355099</v>
+      </c>
+      <c r="E8">
+        <v>-2335.00639449214</v>
+      </c>
+      <c r="F8">
+        <v>206.5535996484345</v>
+      </c>
+      <c r="G8">
+        <v>347.3</v>
+      </c>
+      <c r="H8">
+        <v>901</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K8">
+        <v>348.6</v>
+      </c>
+      <c r="L8">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M8">
+        <v>9.232945904285021</v>
+      </c>
+      <c r="N8">
+        <v>140.3937207623816</v>
+      </c>
+      <c r="O8">
+        <v>28.07874415247632</v>
+      </c>
+      <c r="P8">
+        <v>112.3149766099053</v>
+      </c>
+      <c r="Q8">
+        <v>460.9149766099053</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.0826232537742991</v>
+      </c>
+      <c r="T8">
+        <v>0.8452852727103993</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.2</v>
+      </c>
+      <c r="W8">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>16.20573414138869</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.07969767017021395</v>
+      </c>
+      <c r="C9">
+        <v>3210.673655033936</v>
+      </c>
+      <c r="D9">
+        <v>3104.352854623776</v>
+      </c>
+      <c r="E9">
+        <v>-2300.580794550734</v>
+      </c>
+      <c r="F9">
+        <v>240.9791995898402</v>
+      </c>
+      <c r="G9">
+        <v>347.3</v>
+      </c>
+      <c r="H9">
+        <v>901</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K9">
+        <v>348.6</v>
+      </c>
+      <c r="L9">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M9">
+        <v>10.77177022166586</v>
+      </c>
+      <c r="N9">
+        <v>138.8548964450007</v>
+      </c>
+      <c r="O9">
+        <v>27.77097928900015</v>
+      </c>
+      <c r="P9">
+        <v>111.0839171560006</v>
+      </c>
+      <c r="Q9">
+        <v>459.6839171560006</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08300480663463866</v>
+      </c>
+      <c r="T9">
+        <v>0.8526448589078692</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.2</v>
+      </c>
+      <c r="W9">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>13.89062926404744</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.07965428179258674</v>
+      </c>
+      <c r="C10">
+        <v>3178.463714485656</v>
+      </c>
+      <c r="D10">
+        <v>3106.568514016902</v>
+      </c>
+      <c r="E10">
+        <v>-2266.155194609329</v>
+      </c>
+      <c r="F10">
+        <v>275.4047995312459</v>
+      </c>
+      <c r="G10">
+        <v>347.3</v>
+      </c>
+      <c r="H10">
+        <v>901</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K10">
+        <v>348.6</v>
+      </c>
+      <c r="L10">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M10">
+        <v>12.61353981853106</v>
+      </c>
+      <c r="N10">
+        <v>137.0131268481356</v>
+      </c>
+      <c r="O10">
+        <v>27.40262536962711</v>
+      </c>
+      <c r="P10">
+        <v>109.6105014785084</v>
+      </c>
+      <c r="Q10">
+        <v>458.2105014785085</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.0833946541223769</v>
+      </c>
+      <c r="T10">
+        <v>0.8601644361096319</v>
+      </c>
+      <c r="U10">
+        <v>0.0458</v>
+      </c>
+      <c r="V10">
+        <v>0.2</v>
+      </c>
+      <c r="W10">
+        <v>0.03664</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>11.86238508930253</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.07954929341495953</v>
+      </c>
+      <c r="C11">
+        <v>3149.412531497194</v>
+      </c>
+      <c r="D11">
+        <v>3111.942930969845</v>
+      </c>
+      <c r="E11">
+        <v>-2231.729594667923</v>
+      </c>
+      <c r="F11">
+        <v>309.8303994726517</v>
+      </c>
+      <c r="G11">
+        <v>347.3</v>
+      </c>
+      <c r="H11">
+        <v>901</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K11">
+        <v>348.6</v>
+      </c>
+      <c r="L11">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M11">
+        <v>14.19023229584745</v>
+      </c>
+      <c r="N11">
+        <v>135.4364343708192</v>
+      </c>
+      <c r="O11">
+        <v>27.08728687416384</v>
+      </c>
+      <c r="P11">
+        <v>108.3491474966553</v>
+      </c>
+      <c r="Q11">
+        <v>456.9491474966554</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08379306968676872</v>
+      </c>
+      <c r="T11">
+        <v>0.8678492787444002</v>
+      </c>
+      <c r="U11">
+        <v>0.0458</v>
+      </c>
+      <c r="V11">
+        <v>0.2</v>
+      </c>
+      <c r="W11">
+        <v>0.03664</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>10.54434230160225</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.07962030503733232</v>
+      </c>
+      <c r="C12">
+        <v>3111.349771899335</v>
+      </c>
+      <c r="D12">
+        <v>3108.305771313392</v>
+      </c>
+      <c r="E12">
+        <v>-2197.303994726517</v>
+      </c>
+      <c r="F12">
+        <v>344.2559994140574</v>
+      </c>
+      <c r="G12">
+        <v>347.3</v>
+      </c>
+      <c r="H12">
+        <v>901</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K12">
+        <v>348.6</v>
+      </c>
+      <c r="L12">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M12">
+        <v>16.52428797187476</v>
+      </c>
+      <c r="N12">
+        <v>133.1023786947919</v>
+      </c>
+      <c r="O12">
+        <v>26.62047573895838</v>
+      </c>
+      <c r="P12">
+        <v>106.4819029558335</v>
+      </c>
+      <c r="Q12">
+        <v>455.0819029558335</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.08420033893036925</v>
+      </c>
+      <c r="T12">
+        <v>0.8757048956599415</v>
+      </c>
+      <c r="U12">
+        <v>0.048</v>
+      </c>
+      <c r="V12">
+        <v>0.2</v>
+      </c>
+      <c r="W12">
+        <v>0.0384</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>9.054953951500931</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.07953291665970512</v>
+      </c>
+      <c r="C13">
+        <v>3081.401344392118</v>
+      </c>
+      <c r="D13">
+        <v>3112.782943747581</v>
+      </c>
+      <c r="E13">
+        <v>-2162.878394785111</v>
+      </c>
+      <c r="F13">
+        <v>378.6815993554632</v>
+      </c>
+      <c r="G13">
+        <v>347.3</v>
+      </c>
+      <c r="H13">
+        <v>901</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K13">
+        <v>348.6</v>
+      </c>
+      <c r="L13">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M13">
+        <v>18.17671676906223</v>
+      </c>
+      <c r="N13">
+        <v>131.4499498976044</v>
+      </c>
+      <c r="O13">
+        <v>26.28998997952088</v>
+      </c>
+      <c r="P13">
+        <v>105.1599599180835</v>
+      </c>
+      <c r="Q13">
+        <v>453.7599599180835</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.0846167602918035</v>
+      </c>
+      <c r="T13">
+        <v>0.8837370432926855</v>
+      </c>
+      <c r="U13">
+        <v>0.048</v>
+      </c>
+      <c r="V13">
+        <v>0.2</v>
+      </c>
+      <c r="W13">
+        <v>0.0384</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>8.231776319546299</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.07958952828207792</v>
+      </c>
+      <c r="C14">
+        <v>3044.073888874546</v>
+      </c>
+      <c r="D14">
+        <v>3109.881088171415</v>
+      </c>
+      <c r="E14">
+        <v>-2128.452794843705</v>
+      </c>
+      <c r="F14">
+        <v>413.1071992968689</v>
+      </c>
+      <c r="G14">
+        <v>347.3</v>
+      </c>
+      <c r="H14">
+        <v>901</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K14">
+        <v>348.6</v>
+      </c>
+      <c r="L14">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M14">
+        <v>20.44880636519501</v>
+      </c>
+      <c r="N14">
+        <v>129.1778603014716</v>
+      </c>
+      <c r="O14">
+        <v>25.83557206029432</v>
+      </c>
+      <c r="P14">
+        <v>103.3422882411773</v>
+      </c>
+      <c r="Q14">
+        <v>451.9422882411773</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.08504264577508854</v>
+      </c>
+      <c r="T14">
+        <v>0.891951739735265</v>
+      </c>
+      <c r="U14">
+        <v>0.0495</v>
+      </c>
+      <c r="V14">
+        <v>0.2</v>
+      </c>
+      <c r="W14">
+        <v>0.0396</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>7.317134506263375</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.07951413990445071</v>
+      </c>
+      <c r="C15">
+        <v>3013.513818691567</v>
+      </c>
+      <c r="D15">
+        <v>3113.746617929841</v>
+      </c>
+      <c r="E15">
+        <v>-2094.0271949023</v>
+      </c>
+      <c r="F15">
+        <v>447.5327992382747</v>
+      </c>
+      <c r="G15">
+        <v>347.3</v>
+      </c>
+      <c r="H15">
+        <v>901</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K15">
+        <v>348.6</v>
+      </c>
+      <c r="L15">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M15">
+        <v>22.1528735622946</v>
+      </c>
+      <c r="N15">
+        <v>127.473793104372</v>
+      </c>
+      <c r="O15">
+        <v>25.4947586208744</v>
+      </c>
+      <c r="P15">
+        <v>101.9790344834976</v>
+      </c>
+      <c r="Q15">
+        <v>450.5790344834976</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.08547832172925368</v>
+      </c>
+      <c r="T15">
+        <v>0.9003552797742254</v>
+      </c>
+      <c r="U15">
+        <v>0.0495</v>
+      </c>
+      <c r="V15">
+        <v>0.2</v>
+      </c>
+      <c r="W15">
+        <v>0.0396</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>6.754278005781578</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.07943875152682349</v>
+      </c>
+      <c r="C16">
+        <v>2982.963370044625</v>
+      </c>
+      <c r="D16">
+        <v>3117.621769224305</v>
+      </c>
+      <c r="E16">
+        <v>-2059.601594960894</v>
+      </c>
+      <c r="F16">
+        <v>481.9583991796804</v>
+      </c>
+      <c r="G16">
+        <v>347.3</v>
+      </c>
+      <c r="H16">
+        <v>901</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K16">
+        <v>348.6</v>
+      </c>
+      <c r="L16">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M16">
+        <v>23.85694075939418</v>
+      </c>
+      <c r="N16">
+        <v>125.7697259072724</v>
+      </c>
+      <c r="O16">
+        <v>25.15394518145449</v>
+      </c>
+      <c r="P16">
+        <v>100.6157807258179</v>
+      </c>
+      <c r="Q16">
+        <v>449.215780725818</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.08592412968235288</v>
+      </c>
+      <c r="T16">
+        <v>0.9089542509768826</v>
+      </c>
+      <c r="U16">
+        <v>0.0495</v>
+      </c>
+      <c r="V16">
+        <v>0.2</v>
+      </c>
+      <c r="W16">
+        <v>0.0396</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>6.271829576797179</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.07953136314919627</v>
+      </c>
+      <c r="C17">
+        <v>2943.778652379041</v>
+      </c>
+      <c r="D17">
+        <v>3112.862651500127</v>
+      </c>
+      <c r="E17">
+        <v>-2025.175995019488</v>
+      </c>
+      <c r="F17">
+        <v>516.3839991210862</v>
+      </c>
+      <c r="G17">
+        <v>347.3</v>
+      </c>
+      <c r="H17">
+        <v>901</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K17">
+        <v>348.6</v>
+      </c>
+      <c r="L17">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M17">
+        <v>26.28394555526329</v>
+      </c>
+      <c r="N17">
+        <v>123.3427211114033</v>
+      </c>
+      <c r="O17">
+        <v>24.66854422228067</v>
+      </c>
+      <c r="P17">
+        <v>98.67417688912266</v>
+      </c>
+      <c r="Q17">
+        <v>447.2741768891227</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.08638042723434856</v>
+      </c>
+      <c r="T17">
+        <v>0.91775555091372</v>
+      </c>
+      <c r="U17">
+        <v>0.0509</v>
+      </c>
+      <c r="V17">
+        <v>0.2</v>
+      </c>
+      <c r="W17">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>5.692701894853236</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.07946717477156907</v>
+      </c>
+      <c r="C18">
+        <v>2912.650012023501</v>
+      </c>
+      <c r="D18">
+        <v>3116.159611085993</v>
+      </c>
+      <c r="E18">
+        <v>-1990.750395078082</v>
+      </c>
+      <c r="F18">
+        <v>550.8095990624919</v>
+      </c>
+      <c r="G18">
+        <v>347.3</v>
+      </c>
+      <c r="H18">
+        <v>901</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K18">
+        <v>348.6</v>
+      </c>
+      <c r="L18">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M18">
+        <v>28.03620859228084</v>
+      </c>
+      <c r="N18">
+        <v>121.5904580743858</v>
+      </c>
+      <c r="O18">
+        <v>24.31809161487715</v>
+      </c>
+      <c r="P18">
+        <v>97.27236645950862</v>
+      </c>
+      <c r="Q18">
+        <v>445.8723664595086</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.08684758901377271</v>
+      </c>
+      <c r="T18">
+        <v>0.9267664056109582</v>
+      </c>
+      <c r="U18">
+        <v>0.0509</v>
+      </c>
+      <c r="V18">
+        <v>0.2</v>
+      </c>
+      <c r="W18">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>5.33690802642491</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.07940298639394185</v>
+      </c>
+      <c r="C19">
+        <v>2881.528362961016</v>
+      </c>
+      <c r="D19">
+        <v>3119.463561964914</v>
+      </c>
+      <c r="E19">
+        <v>-1956.324795136677</v>
+      </c>
+      <c r="F19">
+        <v>585.2351990038977</v>
+      </c>
+      <c r="G19">
+        <v>347.3</v>
+      </c>
+      <c r="H19">
+        <v>901</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K19">
+        <v>348.6</v>
+      </c>
+      <c r="L19">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M19">
+        <v>29.7884716292984</v>
+      </c>
+      <c r="N19">
+        <v>119.8381950373682</v>
+      </c>
+      <c r="O19">
+        <v>23.96763900747364</v>
+      </c>
+      <c r="P19">
+        <v>95.87055602989457</v>
+      </c>
+      <c r="Q19">
+        <v>444.4705560298946</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.0873260077035444</v>
+      </c>
+      <c r="T19">
+        <v>0.9359943893370457</v>
+      </c>
+      <c r="U19">
+        <v>0.0509</v>
+      </c>
+      <c r="V19">
+        <v>0.2</v>
+      </c>
+      <c r="W19">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>5.022972260164619</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.07933879801631466</v>
+      </c>
+      <c r="C20">
+        <v>2850.41372745303</v>
+      </c>
+      <c r="D20">
+        <v>3122.774526398333</v>
+      </c>
+      <c r="E20">
+        <v>-1921.899195195271</v>
+      </c>
+      <c r="F20">
+        <v>619.6607989453033</v>
+      </c>
+      <c r="G20">
+        <v>347.3</v>
+      </c>
+      <c r="H20">
+        <v>901</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K20">
+        <v>348.6</v>
+      </c>
+      <c r="L20">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M20">
+        <v>31.54073466631594</v>
+      </c>
+      <c r="N20">
+        <v>118.0859320003507</v>
+      </c>
+      <c r="O20">
+        <v>23.61718640007014</v>
+      </c>
+      <c r="P20">
+        <v>94.46874560028053</v>
+      </c>
+      <c r="Q20">
+        <v>443.0687456002805</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.08781609514184713</v>
+      </c>
+      <c r="T20">
+        <v>0.9454474458369401</v>
+      </c>
+      <c r="U20">
+        <v>0.0509</v>
+      </c>
+      <c r="V20">
+        <v>0.2</v>
+      </c>
+      <c r="W20">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>4.743918245711031</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.07966980963868746</v>
+      </c>
+      <c r="C21">
+        <v>2798.988810946033</v>
+      </c>
+      <c r="D21">
+        <v>3105.775209832741</v>
+      </c>
+      <c r="E21">
+        <v>-1887.473595253865</v>
+      </c>
+      <c r="F21">
+        <v>654.0863988867092</v>
+      </c>
+      <c r="G21">
+        <v>347.3</v>
+      </c>
+      <c r="H21">
+        <v>901</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K21">
+        <v>348.6</v>
+      </c>
+      <c r="L21">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M21">
+        <v>34.99362234043894</v>
+      </c>
+      <c r="N21">
+        <v>114.6330443262277</v>
+      </c>
+      <c r="O21">
+        <v>22.92660886524553</v>
+      </c>
+      <c r="P21">
+        <v>91.70643546098214</v>
+      </c>
+      <c r="Q21">
+        <v>440.3064354609821</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.08831828350455241</v>
+      </c>
+      <c r="T21">
+        <v>0.9551339111393012</v>
+      </c>
+      <c r="U21">
+        <v>0.0535</v>
+      </c>
+      <c r="V21">
+        <v>0.2</v>
+      </c>
+      <c r="W21">
+        <v>0.0428</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>4.275826755258677</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.07962642126106025</v>
+      </c>
+      <c r="C22">
+        <v>2766.78090193377</v>
+      </c>
+      <c r="D22">
+        <v>3107.992900761884</v>
+      </c>
+      <c r="E22">
+        <v>-1853.04799531246</v>
+      </c>
+      <c r="F22">
+        <v>688.5119988281149</v>
+      </c>
+      <c r="G22">
+        <v>347.3</v>
+      </c>
+      <c r="H22">
+        <v>901</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K22">
+        <v>348.6</v>
+      </c>
+      <c r="L22">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M22">
+        <v>36.83539193730414</v>
+      </c>
+      <c r="N22">
+        <v>112.7912747293625</v>
+      </c>
+      <c r="O22">
+        <v>22.55825494587249</v>
+      </c>
+      <c r="P22">
+        <v>90.23301978348998</v>
+      </c>
+      <c r="Q22">
+        <v>438.83301978349</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.0888330265763253</v>
+      </c>
+      <c r="T22">
+        <v>0.965062538074221</v>
+      </c>
+      <c r="U22">
+        <v>0.0535</v>
+      </c>
+      <c r="V22">
+        <v>0.2</v>
+      </c>
+      <c r="W22">
+        <v>0.0428</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>4.062035417495744</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.08003663288343303</v>
+      </c>
+      <c r="C23">
+        <v>2711.514063845798</v>
+      </c>
+      <c r="D23">
+        <v>3087.151662615318</v>
+      </c>
+      <c r="E23">
+        <v>-1818.622395371054</v>
+      </c>
+      <c r="F23">
+        <v>722.9375987695206</v>
+      </c>
+      <c r="G23">
+        <v>347.3</v>
+      </c>
+      <c r="H23">
+        <v>901</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K23">
+        <v>348.6</v>
+      </c>
+      <c r="L23">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M23">
+        <v>40.62909305084706</v>
+      </c>
+      <c r="N23">
+        <v>108.9975736158195</v>
+      </c>
+      <c r="O23">
+        <v>21.79951472316391</v>
+      </c>
+      <c r="P23">
+        <v>87.19805889265564</v>
+      </c>
+      <c r="Q23">
+        <v>435.7980588926557</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.08936080111826966</v>
+      </c>
+      <c r="T23">
+        <v>0.9752425226530631</v>
+      </c>
+      <c r="U23">
+        <v>0.0562</v>
+      </c>
+      <c r="V23">
+        <v>0.2</v>
+      </c>
+      <c r="W23">
+        <v>0.04496</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>3.682746904525035</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.08001484450580583</v>
+      </c>
+      <c r="C24">
+        <v>2678.188414319005</v>
+      </c>
+      <c r="D24">
+        <v>3088.251613029931</v>
+      </c>
+      <c r="E24">
+        <v>-1784.196795429648</v>
+      </c>
+      <c r="F24">
+        <v>757.3631987109263</v>
+      </c>
+      <c r="G24">
+        <v>347.3</v>
+      </c>
+      <c r="H24">
+        <v>901</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K24">
+        <v>348.6</v>
+      </c>
+      <c r="L24">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M24">
+        <v>42.56381176755406</v>
+      </c>
+      <c r="N24">
+        <v>107.0628548991126</v>
+      </c>
+      <c r="O24">
+        <v>21.41257097982251</v>
+      </c>
+      <c r="P24">
+        <v>85.65028391929005</v>
+      </c>
+      <c r="Q24">
+        <v>434.25028391929</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.08990210834077669</v>
+      </c>
+      <c r="T24">
+        <v>0.9856835324775165</v>
+      </c>
+      <c r="U24">
+        <v>0.0562</v>
+      </c>
+      <c r="V24">
+        <v>0.2</v>
+      </c>
+      <c r="W24">
+        <v>0.04496</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>3.515349317955716</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.08085785612817861</v>
+      </c>
+      <c r="C25">
+        <v>2601.768509705137</v>
+      </c>
+      <c r="D25">
+        <v>3046.257308357469</v>
+      </c>
+      <c r="E25">
+        <v>-1749.771195488242</v>
+      </c>
+      <c r="F25">
+        <v>791.7887986523322</v>
+      </c>
+      <c r="G25">
+        <v>347.3</v>
+      </c>
+      <c r="H25">
+        <v>901</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K25">
+        <v>348.6</v>
+      </c>
+      <c r="L25">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M25">
+        <v>48.21993783792703</v>
+      </c>
+      <c r="N25">
+        <v>101.4067288287396</v>
+      </c>
+      <c r="O25">
+        <v>20.28134576574791</v>
+      </c>
+      <c r="P25">
+        <v>81.12538306299166</v>
+      </c>
+      <c r="Q25">
+        <v>429.7253830629917</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09045747549114105</v>
+      </c>
+      <c r="T25">
+        <v>0.9963957373623452</v>
+      </c>
+      <c r="U25">
+        <v>0.0609</v>
+      </c>
+      <c r="V25">
+        <v>0.2</v>
+      </c>
+      <c r="W25">
+        <v>0.04872000000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>3.103004138445381</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.08265926775055141</v>
+      </c>
+      <c r="C26">
+        <v>2481.32594973363</v>
+      </c>
+      <c r="D26">
+        <v>2960.240348327367</v>
+      </c>
+      <c r="E26">
+        <v>-1715.345595546837</v>
+      </c>
+      <c r="F26">
+        <v>826.2143985937379</v>
+      </c>
+      <c r="G26">
+        <v>347.3</v>
+      </c>
+      <c r="H26">
+        <v>901</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K26">
+        <v>348.6</v>
+      </c>
+      <c r="L26">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M26">
+        <v>58.0002507812804</v>
+      </c>
+      <c r="N26">
+        <v>91.62641588538621</v>
+      </c>
+      <c r="O26">
+        <v>18.32528317707724</v>
+      </c>
+      <c r="P26">
+        <v>73.30113270830897</v>
+      </c>
+      <c r="Q26">
+        <v>421.901132708309</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09102745756651501</v>
+      </c>
+      <c r="T26">
+        <v>1.007389842375722</v>
+      </c>
+      <c r="U26">
+        <v>0.0702</v>
+      </c>
+      <c r="V26">
+        <v>0.2</v>
+      </c>
+      <c r="W26">
+        <v>0.05616</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>2.579758960541575</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.08368947937292417</v>
+      </c>
+      <c r="C27">
+        <v>2399.856722254143</v>
+      </c>
+      <c r="D27">
+        <v>2913.196720789286</v>
+      </c>
+      <c r="E27">
+        <v>-1680.919995605431</v>
+      </c>
+      <c r="F27">
+        <v>860.6399985351436</v>
+      </c>
+      <c r="G27">
+        <v>347.3</v>
+      </c>
+      <c r="H27">
+        <v>901</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K27">
+        <v>348.6</v>
+      </c>
+      <c r="L27">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M27">
+        <v>64.46193589028225</v>
+      </c>
+      <c r="N27">
+        <v>85.16473077638436</v>
+      </c>
+      <c r="O27">
+        <v>17.03294615527687</v>
+      </c>
+      <c r="P27">
+        <v>68.13178462110749</v>
+      </c>
+      <c r="Q27">
+        <v>416.7317846211075</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.09161263916389892</v>
+      </c>
+      <c r="T27">
+        <v>1.018677123522789</v>
+      </c>
+      <c r="U27">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V27">
+        <v>0.2</v>
+      </c>
+      <c r="W27">
+        <v>0.05992</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>2.321163095711854</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.08381729099529699</v>
+      </c>
+      <c r="C28">
+        <v>2359.698779772512</v>
+      </c>
+      <c r="D28">
+        <v>2907.464378249061</v>
+      </c>
+      <c r="E28">
+        <v>-1646.494395664025</v>
+      </c>
+      <c r="F28">
+        <v>895.0655984765493</v>
+      </c>
+      <c r="G28">
+        <v>347.3</v>
+      </c>
+      <c r="H28">
+        <v>901</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K28">
+        <v>348.6</v>
+      </c>
+      <c r="L28">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M28">
+        <v>67.04041332589354</v>
+      </c>
+      <c r="N28">
+        <v>82.58625334077307</v>
+      </c>
+      <c r="O28">
+        <v>16.51725066815461</v>
+      </c>
+      <c r="P28">
+        <v>66.06900267261845</v>
+      </c>
+      <c r="Q28">
+        <v>414.6690026726185</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09221363648013106</v>
+      </c>
+      <c r="T28">
+        <v>1.030269466322479</v>
+      </c>
+      <c r="U28">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V28">
+        <v>0.2</v>
+      </c>
+      <c r="W28">
+        <v>0.05992</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>2.231887592030628</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.08394510261766977</v>
+      </c>
+      <c r="C29">
+        <v>2319.563352227207</v>
+      </c>
+      <c r="D29">
+        <v>2901.754550645162</v>
+      </c>
+      <c r="E29">
+        <v>-1612.068795722619</v>
+      </c>
+      <c r="F29">
+        <v>929.4911984179552</v>
+      </c>
+      <c r="G29">
+        <v>347.3</v>
+      </c>
+      <c r="H29">
+        <v>901</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K29">
+        <v>348.6</v>
+      </c>
+      <c r="L29">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M29">
+        <v>69.61889076150483</v>
+      </c>
+      <c r="N29">
+        <v>80.00777590516178</v>
+      </c>
+      <c r="O29">
+        <v>16.00155518103236</v>
+      </c>
+      <c r="P29">
+        <v>64.00622072412942</v>
+      </c>
+      <c r="Q29">
+        <v>412.6062207241295</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.09283109947625998</v>
+      </c>
+      <c r="T29">
+        <v>1.042179407555038</v>
+      </c>
+      <c r="U29">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V29">
+        <v>0.2</v>
+      </c>
+      <c r="W29">
+        <v>0.05992</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>2.149225088622087</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.08407291424004257</v>
+      </c>
+      <c r="C30">
+        <v>2279.450307230258</v>
+      </c>
+      <c r="D30">
+        <v>2896.067105589618</v>
+      </c>
+      <c r="E30">
+        <v>-1577.643195781214</v>
+      </c>
+      <c r="F30">
+        <v>963.9167983593609</v>
+      </c>
+      <c r="G30">
+        <v>347.3</v>
+      </c>
+      <c r="H30">
+        <v>901</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K30">
+        <v>348.6</v>
+      </c>
+      <c r="L30">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M30">
+        <v>72.19736819711612</v>
+      </c>
+      <c r="N30">
+        <v>77.42929846955049</v>
+      </c>
+      <c r="O30">
+        <v>15.4858596939101</v>
+      </c>
+      <c r="P30">
+        <v>61.94343877564039</v>
+      </c>
+      <c r="Q30">
+        <v>410.5434387756404</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.09346571422228134</v>
+      </c>
+      <c r="T30">
+        <v>1.054420180488501</v>
+      </c>
+      <c r="U30">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V30">
+        <v>0.2</v>
+      </c>
+      <c r="W30">
+        <v>0.05992</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>2.072467049742727</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.08420072586241535</v>
+      </c>
+      <c r="C31">
+        <v>2239.359513429589</v>
+      </c>
+      <c r="D31">
+        <v>2890.401911730355</v>
+      </c>
+      <c r="E31">
+        <v>-1543.217595839808</v>
+      </c>
+      <c r="F31">
+        <v>998.3423983007665</v>
+      </c>
+      <c r="G31">
+        <v>347.3</v>
+      </c>
+      <c r="H31">
+        <v>901</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K31">
+        <v>348.6</v>
+      </c>
+      <c r="L31">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M31">
+        <v>74.77584563272741</v>
+      </c>
+      <c r="N31">
+        <v>74.8508210339392</v>
+      </c>
+      <c r="O31">
+        <v>14.97016420678784</v>
+      </c>
+      <c r="P31">
+        <v>59.88065682715136</v>
+      </c>
+      <c r="Q31">
+        <v>408.4806568271514</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.09411820544002163</v>
+      </c>
+      <c r="T31">
+        <v>1.067005763927132</v>
+      </c>
+      <c r="U31">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V31">
+        <v>0.2</v>
+      </c>
+      <c r="W31">
+        <v>0.05992</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>2.001002668717115</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.08824053748478815</v>
+      </c>
+      <c r="C32">
+        <v>2036.627641084407</v>
+      </c>
+      <c r="D32">
+        <v>2722.095639326579</v>
+      </c>
+      <c r="E32">
+        <v>-1508.791995898402</v>
+      </c>
+      <c r="F32">
+        <v>1032.767998242172</v>
+      </c>
+      <c r="G32">
+        <v>347.3</v>
+      </c>
+      <c r="H32">
+        <v>901</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K32">
+        <v>348.6</v>
+      </c>
+      <c r="L32">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M32">
+        <v>94.18844143968612</v>
+      </c>
+      <c r="N32">
+        <v>55.43822522698049</v>
+      </c>
+      <c r="O32">
+        <v>11.0876450453961</v>
+      </c>
+      <c r="P32">
+        <v>44.35058018158439</v>
+      </c>
+      <c r="Q32">
+        <v>392.9505801815844</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.09478933926398307</v>
+      </c>
+      <c r="T32">
+        <v>1.079950935464009</v>
+      </c>
+      <c r="U32">
+        <v>0.0912</v>
+      </c>
+      <c r="V32">
+        <v>0.2</v>
+      </c>
+      <c r="W32">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>1.588588412544023</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.08849874910716093</v>
+      </c>
+      <c r="C33">
+        <v>1992.108425872095</v>
+      </c>
+      <c r="D33">
+        <v>2712.002024055673</v>
+      </c>
+      <c r="E33">
+        <v>-1474.366395956996</v>
+      </c>
+      <c r="F33">
+        <v>1067.193598183578</v>
+      </c>
+      <c r="G33">
+        <v>347.3</v>
+      </c>
+      <c r="H33">
+        <v>901</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K33">
+        <v>348.6</v>
+      </c>
+      <c r="L33">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M33">
+        <v>97.32805615434233</v>
+      </c>
+      <c r="N33">
+        <v>52.29861051232427</v>
+      </c>
+      <c r="O33">
+        <v>10.45972210246486</v>
+      </c>
+      <c r="P33">
+        <v>41.83888840985942</v>
+      </c>
+      <c r="Q33">
+        <v>390.4388884098594</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.09547992624226223</v>
+      </c>
+      <c r="T33">
+        <v>1.093271329364275</v>
+      </c>
+      <c r="U33">
+        <v>0.0912</v>
+      </c>
+      <c r="V33">
+        <v>0.2</v>
+      </c>
+      <c r="W33">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>1.537343625042602</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1071830179412218</v>
+      </c>
+      <c r="C34">
+        <v>1383.953781365124</v>
+      </c>
+      <c r="D34">
+        <v>2138.272979490107</v>
+      </c>
+      <c r="E34">
+        <v>-1439.940796015591</v>
+      </c>
+      <c r="F34">
+        <v>1101.619198124984</v>
+      </c>
+      <c r="G34">
+        <v>347.3</v>
+      </c>
+      <c r="H34">
+        <v>901</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K34">
+        <v>348.6</v>
+      </c>
+      <c r="L34">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M34">
+        <v>172.5135664263725</v>
+      </c>
+      <c r="N34">
+        <v>-22.88689975970587</v>
+      </c>
+      <c r="O34">
+        <v>-4.577379951941174</v>
+      </c>
+      <c r="P34">
+        <v>-18.30951980776469</v>
+      </c>
+      <c r="Q34">
+        <v>330.2904801922353</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.09671143196273921</v>
+      </c>
+      <c r="T34">
+        <v>1.117025239882628</v>
+      </c>
+      <c r="U34">
+        <v>0.1566</v>
+      </c>
+      <c r="V34">
+        <v>0.173466550795037</v>
+      </c>
+      <c r="W34">
+        <v>0.1294351381454972</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.8673327539751847</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1083610179412218</v>
+      </c>
+      <c r="C35">
+        <v>1321.383593722362</v>
+      </c>
+      <c r="D35">
+        <v>2110.128391788752</v>
+      </c>
+      <c r="E35">
+        <v>-1405.515196074185</v>
+      </c>
+      <c r="F35">
+        <v>1136.04479806639</v>
+      </c>
+      <c r="G35">
+        <v>347.3</v>
+      </c>
+      <c r="H35">
+        <v>901</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K35">
+        <v>348.6</v>
+      </c>
+      <c r="L35">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M35">
+        <v>177.9046153771966</v>
+      </c>
+      <c r="N35">
+        <v>-28.27794871053001</v>
+      </c>
+      <c r="O35">
+        <v>-5.655589742106002</v>
+      </c>
+      <c r="P35">
+        <v>-22.62235896842401</v>
+      </c>
+      <c r="Q35">
+        <v>325.977641031576</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.09757578169352638</v>
+      </c>
+      <c r="T35">
+        <v>1.133697258388339</v>
+      </c>
+      <c r="U35">
+        <v>0.1566</v>
+      </c>
+      <c r="V35">
+        <v>0.1682099886497328</v>
+      </c>
+      <c r="W35">
+        <v>0.1302583157774519</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.841049943248664</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1095390179412218</v>
+      </c>
+      <c r="C36">
+        <v>1259.544675830064</v>
+      </c>
+      <c r="D36">
+        <v>2082.71507383786</v>
+      </c>
+      <c r="E36">
+        <v>-1371.089596132779</v>
+      </c>
+      <c r="F36">
+        <v>1170.470398007795</v>
+      </c>
+      <c r="G36">
+        <v>347.3</v>
+      </c>
+      <c r="H36">
+        <v>901</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K36">
+        <v>348.6</v>
+      </c>
+      <c r="L36">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M36">
+        <v>183.2956643280208</v>
+      </c>
+      <c r="N36">
+        <v>-33.66899766135418</v>
+      </c>
+      <c r="O36">
+        <v>-6.733799532270837</v>
+      </c>
+      <c r="P36">
+        <v>-26.93519812908335</v>
+      </c>
+      <c r="Q36">
+        <v>321.6648018709167</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.09846632384039797</v>
+      </c>
+      <c r="T36">
+        <v>1.150874489576041</v>
+      </c>
+      <c r="U36">
+        <v>0.1566</v>
+      </c>
+      <c r="V36">
+        <v>0.1632626360423877</v>
+      </c>
+      <c r="W36">
+        <v>0.1310330711957621</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.8163131802119384</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1295656217109572</v>
+      </c>
+      <c r="C37">
+        <v>848.3466128710832</v>
+      </c>
+      <c r="D37">
+        <v>1705.942610820284</v>
+      </c>
+      <c r="E37">
+        <v>-1336.663996191373</v>
+      </c>
+      <c r="F37">
+        <v>1204.895997949201</v>
+      </c>
+      <c r="G37">
+        <v>347.3</v>
+      </c>
+      <c r="H37">
+        <v>901</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K37">
+        <v>348.6</v>
+      </c>
+      <c r="L37">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M37">
+        <v>251.5822843717932</v>
+      </c>
+      <c r="N37">
+        <v>-101.9556177051266</v>
+      </c>
+      <c r="O37">
+        <v>-20.39112354102533</v>
+      </c>
+      <c r="P37">
+        <v>-81.5644941641013</v>
+      </c>
+      <c r="Q37">
+        <v>267.0355058358987</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1002744269298432</v>
+      </c>
+      <c r="T37">
+        <v>1.18575010426503</v>
+      </c>
+      <c r="U37">
+        <v>0.2088</v>
+      </c>
+      <c r="V37">
+        <v>0.1189484919737396</v>
+      </c>
+      <c r="W37">
+        <v>0.1839635548758832</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.594742459868698</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1312656217109572</v>
+      </c>
+      <c r="C38">
+        <v>788.1199977726824</v>
+      </c>
+      <c r="D38">
+        <v>1680.141595663289</v>
+      </c>
+      <c r="E38">
+        <v>-1302.238396249968</v>
+      </c>
+      <c r="F38">
+        <v>1239.321597890607</v>
+      </c>
+      <c r="G38">
+        <v>347.3</v>
+      </c>
+      <c r="H38">
+        <v>901</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K38">
+        <v>348.6</v>
+      </c>
+      <c r="L38">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M38">
+        <v>258.7703496395587</v>
+      </c>
+      <c r="N38">
+        <v>-109.1436829728921</v>
+      </c>
+      <c r="O38">
+        <v>-21.82873659457842</v>
+      </c>
+      <c r="P38">
+        <v>-87.31494637831365</v>
+      </c>
+      <c r="Q38">
+        <v>261.2850536216864</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.101234964850622</v>
+      </c>
+      <c r="T38">
+        <v>1.204277449644171</v>
+      </c>
+      <c r="U38">
+        <v>0.2088</v>
+      </c>
+      <c r="V38">
+        <v>0.1156443671966913</v>
+      </c>
+      <c r="W38">
+        <v>0.1846534561293308</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.5782218359834566</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1329656217109572</v>
+      </c>
+      <c r="C39">
+        <v>728.6621943772902</v>
+      </c>
+      <c r="D39">
+        <v>1655.109392209303</v>
+      </c>
+      <c r="E39">
+        <v>-1267.812796308562</v>
+      </c>
+      <c r="F39">
+        <v>1273.747197832012</v>
+      </c>
+      <c r="G39">
+        <v>347.3</v>
+      </c>
+      <c r="H39">
+        <v>901</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K39">
+        <v>348.6</v>
+      </c>
+      <c r="L39">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M39">
+        <v>265.9584149073242</v>
+      </c>
+      <c r="N39">
+        <v>-116.3317482406576</v>
+      </c>
+      <c r="O39">
+        <v>-23.26634964813152</v>
+      </c>
+      <c r="P39">
+        <v>-93.06539859252607</v>
+      </c>
+      <c r="Q39">
+        <v>255.534601407474</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1022259960387271</v>
+      </c>
+      <c r="T39">
+        <v>1.223392964717888</v>
+      </c>
+      <c r="U39">
+        <v>0.2088</v>
+      </c>
+      <c r="V39">
+        <v>0.1125188437589429</v>
+      </c>
+      <c r="W39">
+        <v>0.1853060654231327</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.5625942187947145</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1346656217109572</v>
+      </c>
+      <c r="C40">
+        <v>669.9393438765374</v>
+      </c>
+      <c r="D40">
+        <v>1630.812141649956</v>
+      </c>
+      <c r="E40">
+        <v>-1233.387196367156</v>
+      </c>
+      <c r="F40">
+        <v>1308.172797773418</v>
+      </c>
+      <c r="G40">
+        <v>347.3</v>
+      </c>
+      <c r="H40">
+        <v>901</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K40">
+        <v>348.6</v>
+      </c>
+      <c r="L40">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M40">
+        <v>273.1464801750898</v>
+      </c>
+      <c r="N40">
+        <v>-123.5198135084232</v>
+      </c>
+      <c r="O40">
+        <v>-24.70396270168463</v>
+      </c>
+      <c r="P40">
+        <v>-98.81585080673854</v>
+      </c>
+      <c r="Q40">
+        <v>249.7841491932615</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1032489959748357</v>
+      </c>
+      <c r="T40">
+        <v>1.243125109310113</v>
+      </c>
+      <c r="U40">
+        <v>0.2088</v>
+      </c>
+      <c r="V40">
+        <v>0.1095578215547602</v>
+      </c>
+      <c r="W40">
+        <v>0.1859243268593661</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.5477891077738009</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1363656217109572</v>
+      </c>
+      <c r="C41">
+        <v>611.9195469063698</v>
+      </c>
+      <c r="D41">
+        <v>1607.217944621194</v>
+      </c>
+      <c r="E41">
+        <v>-1198.96159642575</v>
+      </c>
+      <c r="F41">
+        <v>1342.598397714824</v>
+      </c>
+      <c r="G41">
+        <v>347.3</v>
+      </c>
+      <c r="H41">
+        <v>901</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K41">
+        <v>348.6</v>
+      </c>
+      <c r="L41">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M41">
+        <v>280.3345454428553</v>
+      </c>
+      <c r="N41">
+        <v>-130.7078787761887</v>
+      </c>
+      <c r="O41">
+        <v>-26.14157575523774</v>
+      </c>
+      <c r="P41">
+        <v>-104.566303020951</v>
+      </c>
+      <c r="Q41">
+        <v>244.0336969790491</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1043055368924559</v>
+      </c>
+      <c r="T41">
+        <v>1.263504209462737</v>
+      </c>
+      <c r="U41">
+        <v>0.2088</v>
+      </c>
+      <c r="V41">
+        <v>0.1067486466430996</v>
+      </c>
+      <c r="W41">
+        <v>0.1865108825809208</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.5337432332154983</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1380656217109572</v>
+      </c>
+      <c r="C42">
+        <v>554.5727238246814</v>
+      </c>
+      <c r="D42">
+        <v>1584.296721480911</v>
+      </c>
+      <c r="E42">
+        <v>-1164.535996484345</v>
+      </c>
+      <c r="F42">
+        <v>1377.02399765623</v>
+      </c>
+      <c r="G42">
+        <v>347.3</v>
+      </c>
+      <c r="H42">
+        <v>901</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K42">
+        <v>348.6</v>
+      </c>
+      <c r="L42">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M42">
+        <v>287.5226107106208</v>
+      </c>
+      <c r="N42">
+        <v>-137.8959440439542</v>
+      </c>
+      <c r="O42">
+        <v>-27.57918880879083</v>
+      </c>
+      <c r="P42">
+        <v>-110.3167552351633</v>
+      </c>
+      <c r="Q42">
+        <v>238.2832447648367</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1053972958406635</v>
+      </c>
+      <c r="T42">
+        <v>1.284562612953783</v>
+      </c>
+      <c r="U42">
+        <v>0.2088</v>
+      </c>
+      <c r="V42">
+        <v>0.1040799304770222</v>
+      </c>
+      <c r="W42">
+        <v>0.1870681105163978</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.5203996523851109</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1397656217109572</v>
+      </c>
+      <c r="C43">
+        <v>497.8704867766719</v>
+      </c>
+      <c r="D43">
+        <v>1562.020084374308</v>
+      </c>
+      <c r="E43">
+        <v>-1130.110396542939</v>
+      </c>
+      <c r="F43">
+        <v>1411.449597597636</v>
+      </c>
+      <c r="G43">
+        <v>347.3</v>
+      </c>
+      <c r="H43">
+        <v>901</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K43">
+        <v>348.6</v>
+      </c>
+      <c r="L43">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M43">
+        <v>294.7106759783863</v>
+      </c>
+      <c r="N43">
+        <v>-145.0840093117197</v>
+      </c>
+      <c r="O43">
+        <v>-29.01680186234395</v>
+      </c>
+      <c r="P43">
+        <v>-116.0672074493758</v>
+      </c>
+      <c r="Q43">
+        <v>232.5327925506242</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1065260635667764</v>
+      </c>
+      <c r="T43">
+        <v>1.306334860630966</v>
+      </c>
+      <c r="U43">
+        <v>0.2088</v>
+      </c>
+      <c r="V43">
+        <v>0.1015413955873387</v>
+      </c>
+      <c r="W43">
+        <v>0.1875981566013637</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.5077069779366934</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1542836884583449</v>
+      </c>
+      <c r="C44">
+        <v>295.9851905890243</v>
+      </c>
+      <c r="D44">
+        <v>1394.560388128066</v>
+      </c>
+      <c r="E44">
+        <v>-1095.684796601533</v>
+      </c>
+      <c r="F44">
+        <v>1445.875197539041</v>
+      </c>
+      <c r="G44">
+        <v>347.3</v>
+      </c>
+      <c r="H44">
+        <v>901</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K44">
+        <v>348.6</v>
+      </c>
+      <c r="L44">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M44">
+        <v>345.2749971723231</v>
+      </c>
+      <c r="N44">
+        <v>-195.6483305056565</v>
+      </c>
+      <c r="O44">
+        <v>-39.1296661011313</v>
+      </c>
+      <c r="P44">
+        <v>-156.5186644045252</v>
+      </c>
+      <c r="Q44">
+        <v>192.0813355954749</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1080697314685962</v>
+      </c>
+      <c r="T44">
+        <v>1.336109914534638</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.08667101173965952</v>
+      </c>
+      <c r="W44">
+        <v>0.2181029623965693</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.4333550586982976</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1562836884583449</v>
+      </c>
+      <c r="C45">
+        <v>241.2633727838299</v>
+      </c>
+      <c r="D45">
+        <v>1374.264170264277</v>
+      </c>
+      <c r="E45">
+        <v>-1061.259196660127</v>
+      </c>
+      <c r="F45">
+        <v>1480.300797480447</v>
+      </c>
+      <c r="G45">
+        <v>347.3</v>
+      </c>
+      <c r="H45">
+        <v>901</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K45">
+        <v>348.6</v>
+      </c>
+      <c r="L45">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M45">
+        <v>353.4958304383308</v>
+      </c>
+      <c r="N45">
+        <v>-203.8691637716641</v>
+      </c>
+      <c r="O45">
+        <v>-40.77383275433283</v>
+      </c>
+      <c r="P45">
+        <v>-163.0953310173313</v>
+      </c>
+      <c r="Q45">
+        <v>185.5046689826687</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1092849899154137</v>
+      </c>
+      <c r="T45">
+        <v>1.359550439351035</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.08465540681548139</v>
+      </c>
+      <c r="W45">
+        <v>0.218584288852463</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.423277034077407</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.158283688458345</v>
+      </c>
+      <c r="C46">
+        <v>187.1238563338827</v>
+      </c>
+      <c r="D46">
+        <v>1354.550253755735</v>
+      </c>
+      <c r="E46">
+        <v>-1026.833596718722</v>
+      </c>
+      <c r="F46">
+        <v>1514.726397421853</v>
+      </c>
+      <c r="G46">
+        <v>347.3</v>
+      </c>
+      <c r="H46">
+        <v>901</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K46">
+        <v>348.6</v>
+      </c>
+      <c r="L46">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M46">
+        <v>361.7166637043384</v>
+      </c>
+      <c r="N46">
+        <v>-212.0899970376718</v>
+      </c>
+      <c r="O46">
+        <v>-42.41799940753437</v>
+      </c>
+      <c r="P46">
+        <v>-169.6719976301375</v>
+      </c>
+      <c r="Q46">
+        <v>178.9280023698626</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1105436504496175</v>
+      </c>
+      <c r="T46">
+        <v>1.383828125768017</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.08273142029694774</v>
+      </c>
+      <c r="W46">
+        <v>0.2190437368330889</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.4136571014847387</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1602836884583449</v>
+      </c>
+      <c r="C47">
+        <v>133.5419361729926</v>
+      </c>
+      <c r="D47">
+        <v>1335.393933536251</v>
+      </c>
+      <c r="E47">
+        <v>-992.4079967773159</v>
+      </c>
+      <c r="F47">
+        <v>1549.151997363258</v>
+      </c>
+      <c r="G47">
+        <v>347.3</v>
+      </c>
+      <c r="H47">
+        <v>901</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K47">
+        <v>348.6</v>
+      </c>
+      <c r="L47">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M47">
+        <v>369.9374969703462</v>
+      </c>
+      <c r="N47">
+        <v>-220.3108303036796</v>
+      </c>
+      <c r="O47">
+        <v>-44.06216606073591</v>
+      </c>
+      <c r="P47">
+        <v>-176.2486642429436</v>
+      </c>
+      <c r="Q47">
+        <v>172.3513357570564</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1118480804577924</v>
+      </c>
+      <c r="T47">
+        <v>1.408988637145618</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.08089294429034889</v>
+      </c>
+      <c r="W47">
+        <v>0.2194827649034647</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.4044647214517444</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.162283688458345</v>
+      </c>
+      <c r="C48">
+        <v>80.49428528227008</v>
+      </c>
+      <c r="D48">
+        <v>1316.771882586934</v>
+      </c>
+      <c r="E48">
+        <v>-957.9823968359101</v>
+      </c>
+      <c r="F48">
+        <v>1583.577597304664</v>
+      </c>
+      <c r="G48">
+        <v>347.3</v>
+      </c>
+      <c r="H48">
+        <v>901</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K48">
+        <v>348.6</v>
+      </c>
+      <c r="L48">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M48">
+        <v>378.1583302363538</v>
+      </c>
+      <c r="N48">
+        <v>-228.5316635696872</v>
+      </c>
+      <c r="O48">
+        <v>-45.70633271393745</v>
+      </c>
+      <c r="P48">
+        <v>-182.8253308557498</v>
+      </c>
+      <c r="Q48">
+        <v>165.7746691442503</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1132008226884923</v>
+      </c>
+      <c r="T48">
+        <v>1.435081019314981</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.07913440202316741</v>
+      </c>
+      <c r="W48">
+        <v>0.2199027047968676</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.395672010115837</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.164283688458345</v>
+      </c>
+      <c r="C49">
+        <v>27.95885992733497</v>
+      </c>
+      <c r="D49">
+        <v>1298.662057173405</v>
+      </c>
+      <c r="E49">
+        <v>-923.5567968945043</v>
+      </c>
+      <c r="F49">
+        <v>1618.00319724607</v>
+      </c>
+      <c r="G49">
+        <v>347.3</v>
+      </c>
+      <c r="H49">
+        <v>901</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K49">
+        <v>348.6</v>
+      </c>
+      <c r="L49">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M49">
+        <v>386.3791635023616</v>
+      </c>
+      <c r="N49">
+        <v>-236.752496835695</v>
+      </c>
+      <c r="O49">
+        <v>-47.35049936713899</v>
+      </c>
+      <c r="P49">
+        <v>-189.401997468556</v>
+      </c>
+      <c r="Q49">
+        <v>159.198002531444</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1146046117958223</v>
+      </c>
+      <c r="T49">
+        <v>1.462158019679415</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.0774506913418234</v>
+      </c>
+      <c r="W49">
+        <v>0.2203047749075726</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.387253456709117</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.166283688458345</v>
+      </c>
+      <c r="C50">
+        <v>-24.08518739081501</v>
+      </c>
+      <c r="D50">
+        <v>1281.043609796661</v>
+      </c>
+      <c r="E50">
+        <v>-889.1311969530987</v>
+      </c>
+      <c r="F50">
+        <v>1652.428797187476</v>
+      </c>
+      <c r="G50">
+        <v>347.3</v>
+      </c>
+      <c r="H50">
+        <v>901</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K50">
+        <v>348.6</v>
+      </c>
+      <c r="L50">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M50">
+        <v>394.5999967683692</v>
+      </c>
+      <c r="N50">
+        <v>-244.9733301017026</v>
+      </c>
+      <c r="O50">
+        <v>-48.99466602034053</v>
+      </c>
+      <c r="P50">
+        <v>-195.9786640813621</v>
+      </c>
+      <c r="Q50">
+        <v>152.6213359186379</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1160623927918958</v>
+      </c>
+      <c r="T50">
+        <v>1.490276443134788</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.07583713527220209</v>
+      </c>
+      <c r="W50">
+        <v>0.2206900920969982</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.3791856763610104</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.168283688458345</v>
+      </c>
+      <c r="C51">
+        <v>-75.65758799400714</v>
+      </c>
+      <c r="D51">
+        <v>1263.896809134874</v>
+      </c>
+      <c r="E51">
+        <v>-854.705597011693</v>
+      </c>
+      <c r="F51">
+        <v>1686.854397128881</v>
+      </c>
+      <c r="G51">
+        <v>347.3</v>
+      </c>
+      <c r="H51">
+        <v>901</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K51">
+        <v>348.6</v>
+      </c>
+      <c r="L51">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M51">
+        <v>402.8208300343769</v>
+      </c>
+      <c r="N51">
+        <v>-253.1941633677103</v>
+      </c>
+      <c r="O51">
+        <v>-50.63883267354206</v>
+      </c>
+      <c r="P51">
+        <v>-202.5553306941682</v>
+      </c>
+      <c r="Q51">
+        <v>146.0446693058318</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1175773416701683</v>
+      </c>
+      <c r="T51">
+        <v>1.519497549862921</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.07428943863399388</v>
+      </c>
+      <c r="W51">
+        <v>0.2210596820542023</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.3714471931699694</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1702836884583449</v>
+      </c>
+      <c r="C52">
+        <v>-126.7770307405299</v>
+      </c>
+      <c r="D52">
+        <v>1247.202966329757</v>
+      </c>
+      <c r="E52">
+        <v>-820.2799970702872</v>
+      </c>
+      <c r="F52">
+        <v>1721.279997070287</v>
+      </c>
+      <c r="G52">
+        <v>347.3</v>
+      </c>
+      <c r="H52">
+        <v>901</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K52">
+        <v>348.6</v>
+      </c>
+      <c r="L52">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M52">
+        <v>411.0416633003846</v>
+      </c>
+      <c r="N52">
+        <v>-261.414996633718</v>
+      </c>
+      <c r="O52">
+        <v>-52.2829993267436</v>
+      </c>
+      <c r="P52">
+        <v>-209.1319973069744</v>
+      </c>
+      <c r="Q52">
+        <v>139.4680026930257</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1191528885035717</v>
+      </c>
+      <c r="T52">
+        <v>1.54988750086018</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.072803649861314</v>
+      </c>
+      <c r="W52">
+        <v>0.2214144884131182</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.36401824930657</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1722836884583449</v>
+      </c>
+      <c r="C53">
+        <v>-177.4612299731637</v>
+      </c>
+      <c r="D53">
+        <v>1230.944367038529</v>
+      </c>
+      <c r="E53">
+        <v>-785.8543971288814</v>
+      </c>
+      <c r="F53">
+        <v>1755.705597011693</v>
+      </c>
+      <c r="G53">
+        <v>347.3</v>
+      </c>
+      <c r="H53">
+        <v>901</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K53">
+        <v>348.6</v>
+      </c>
+      <c r="L53">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M53">
+        <v>419.2624965663923</v>
+      </c>
+      <c r="N53">
+        <v>-269.6358298997257</v>
+      </c>
+      <c r="O53">
+        <v>-53.92716597994514</v>
+      </c>
+      <c r="P53">
+        <v>-215.7086639197806</v>
+      </c>
+      <c r="Q53">
+        <v>132.8913360802194</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1207927433709915</v>
+      </c>
+      <c r="T53">
+        <v>1.581517858020592</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.07137612731501373</v>
+      </c>
+      <c r="W53">
+        <v>0.2217553807971747</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.3568806365750686</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.174283688458345</v>
+      </c>
+      <c r="C54">
+        <v>-227.7269882209575</v>
+      </c>
+      <c r="D54">
+        <v>1215.104208732141</v>
+      </c>
+      <c r="E54">
+        <v>-751.4287971874758</v>
+      </c>
+      <c r="F54">
+        <v>1790.131196953099</v>
+      </c>
+      <c r="G54">
+        <v>347.3</v>
+      </c>
+      <c r="H54">
+        <v>901</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K54">
+        <v>348.6</v>
+      </c>
+      <c r="L54">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M54">
+        <v>427.4833298324</v>
+      </c>
+      <c r="N54">
+        <v>-277.8566631657334</v>
+      </c>
+      <c r="O54">
+        <v>-55.57133263314668</v>
+      </c>
+      <c r="P54">
+        <v>-222.2853305325867</v>
+      </c>
+      <c r="Q54">
+        <v>126.3146694674133</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1225009255245538</v>
+      </c>
+      <c r="T54">
+        <v>1.614466146729354</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.0700035094820327</v>
+      </c>
+      <c r="W54">
+        <v>0.2220831619356906</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.3500175474101634</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1762836884583449</v>
+      </c>
+      <c r="C55">
+        <v>-277.5902541213241</v>
+      </c>
+      <c r="D55">
+        <v>1199.66654277318</v>
+      </c>
+      <c r="E55">
+        <v>-717.0031972460699</v>
+      </c>
+      <c r="F55">
+        <v>1824.556796894504</v>
+      </c>
+      <c r="G55">
+        <v>347.3</v>
+      </c>
+      <c r="H55">
+        <v>901</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K55">
+        <v>348.6</v>
+      </c>
+      <c r="L55">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M55">
+        <v>435.7041630984077</v>
+      </c>
+      <c r="N55">
+        <v>-286.0774964317411</v>
+      </c>
+      <c r="O55">
+        <v>-57.21549928634823</v>
+      </c>
+      <c r="P55">
+        <v>-228.8619971453929</v>
+      </c>
+      <c r="Q55">
+        <v>119.7380028546071</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1242817962803954</v>
+      </c>
+      <c r="T55">
+        <v>1.648816490276787</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.06868268854840943</v>
+      </c>
+      <c r="W55">
+        <v>0.2223985739746398</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.3434134427420471</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1782836884583449</v>
+      </c>
+      <c r="C56">
+        <v>-327.0661759821867</v>
+      </c>
+      <c r="D56">
+        <v>1184.616220853724</v>
+      </c>
+      <c r="E56">
+        <v>-682.5775973046641</v>
+      </c>
+      <c r="F56">
+        <v>1858.98239683591</v>
+      </c>
+      <c r="G56">
+        <v>347.3</v>
+      </c>
+      <c r="H56">
+        <v>901</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K56">
+        <v>348.6</v>
+      </c>
+      <c r="L56">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M56">
+        <v>443.9249963644154</v>
+      </c>
+      <c r="N56">
+        <v>-294.2983296977488</v>
+      </c>
+      <c r="O56">
+        <v>-58.85966593954976</v>
+      </c>
+      <c r="P56">
+        <v>-235.438663758199</v>
+      </c>
+      <c r="Q56">
+        <v>113.161336241801</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1261400961995344</v>
+      </c>
+      <c r="T56">
+        <v>1.684660327021934</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.06741078690862408</v>
+      </c>
+      <c r="W56">
+        <v>0.2227023040862206</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.3370539345431204</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1802836884583449</v>
+      </c>
+      <c r="C57">
+        <v>-376.1691513623293</v>
+      </c>
+      <c r="D57">
+        <v>1169.938845414987</v>
+      </c>
+      <c r="E57">
+        <v>-648.1519973632583</v>
+      </c>
+      <c r="F57">
+        <v>1893.407996777316</v>
+      </c>
+      <c r="G57">
+        <v>347.3</v>
+      </c>
+      <c r="H57">
+        <v>901</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K57">
+        <v>348.6</v>
+      </c>
+      <c r="L57">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M57">
+        <v>452.1458296304231</v>
+      </c>
+      <c r="N57">
+        <v>-302.5191629637565</v>
+      </c>
+      <c r="O57">
+        <v>-60.50383259275131</v>
+      </c>
+      <c r="P57">
+        <v>-242.0153303710052</v>
+      </c>
+      <c r="Q57">
+        <v>106.5846696289948</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1280809872261907</v>
+      </c>
+      <c r="T57">
+        <v>1.722097223177978</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.06618513623755817</v>
+      </c>
+      <c r="W57">
+        <v>0.2229949894664711</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.3309256811877909</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1822836884583449</v>
+      </c>
+      <c r="C58">
+        <v>-424.9128730110494</v>
+      </c>
+      <c r="D58">
+        <v>1155.620723707672</v>
+      </c>
+      <c r="E58">
+        <v>-613.7263974218527</v>
+      </c>
+      <c r="F58">
+        <v>1927.833596718722</v>
+      </c>
+      <c r="G58">
+        <v>347.3</v>
+      </c>
+      <c r="H58">
+        <v>901</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K58">
+        <v>348.6</v>
+      </c>
+      <c r="L58">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M58">
+        <v>460.3666628964308</v>
+      </c>
+      <c r="N58">
+        <v>-310.7399962297642</v>
+      </c>
+      <c r="O58">
+        <v>-62.14799924595284</v>
+      </c>
+      <c r="P58">
+        <v>-248.5919969838114</v>
+      </c>
+      <c r="Q58">
+        <v>100.0080030161887</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1301101005722405</v>
+      </c>
+      <c r="T58">
+        <v>1.761235796432022</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.06500325880474464</v>
+      </c>
+      <c r="W58">
+        <v>0.223277221797427</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.3250162940237232</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1842836884583449</v>
+      </c>
+      <c r="C59">
+        <v>-473.310371475246</v>
+      </c>
+      <c r="D59">
+        <v>1141.648825184882</v>
+      </c>
+      <c r="E59">
+        <v>-579.3007974804468</v>
+      </c>
+      <c r="F59">
+        <v>1962.259196660128</v>
+      </c>
+      <c r="G59">
+        <v>347.3</v>
+      </c>
+      <c r="H59">
+        <v>901</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K59">
+        <v>348.6</v>
+      </c>
+      <c r="L59">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M59">
+        <v>468.5874961624385</v>
+      </c>
+      <c r="N59">
+        <v>-318.9608294957719</v>
+      </c>
+      <c r="O59">
+        <v>-63.79216589915438</v>
+      </c>
+      <c r="P59">
+        <v>-255.1686635966175</v>
+      </c>
+      <c r="Q59">
+        <v>93.43133640338255</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1322335912832229</v>
+      </c>
+      <c r="T59">
+        <v>1.80219476844207</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.06386285075553859</v>
+      </c>
+      <c r="W59">
+        <v>0.2235495512395774</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.319314253777693</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1862836884583449</v>
+      </c>
+      <c r="C60">
+        <v>-521.3740546526137</v>
+      </c>
+      <c r="D60">
+        <v>1128.010741948919</v>
+      </c>
+      <c r="E60">
+        <v>-544.8751975390414</v>
+      </c>
+      <c r="F60">
+        <v>1996.684796601533</v>
+      </c>
+      <c r="G60">
+        <v>347.3</v>
+      </c>
+      <c r="H60">
+        <v>901</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K60">
+        <v>348.6</v>
+      </c>
+      <c r="L60">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M60">
+        <v>476.8083294284461</v>
+      </c>
+      <c r="N60">
+        <v>-327.1816627617795</v>
+      </c>
+      <c r="O60">
+        <v>-65.43633255235589</v>
+      </c>
+      <c r="P60">
+        <v>-261.7453302094236</v>
+      </c>
+      <c r="Q60">
+        <v>86.85466979057645</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.13445820059949</v>
+      </c>
+      <c r="T60">
+        <v>1.84510416769069</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.06276176712182242</v>
+      </c>
+      <c r="W60">
+        <v>0.2238124900113088</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.3138088356091121</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1882836884583449</v>
+      </c>
+      <c r="C61">
+        <v>-569.1157445433012</v>
+      </c>
+      <c r="D61">
+        <v>1114.694651999638</v>
+      </c>
+      <c r="E61">
+        <v>-510.4495975976356</v>
+      </c>
+      <c r="F61">
+        <v>2031.110396542939</v>
+      </c>
+      <c r="G61">
+        <v>347.3</v>
+      </c>
+      <c r="H61">
+        <v>901</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K61">
+        <v>348.6</v>
+      </c>
+      <c r="L61">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M61">
+        <v>485.0291626944538</v>
+      </c>
+      <c r="N61">
+        <v>-335.4024960277872</v>
+      </c>
+      <c r="O61">
+        <v>-67.08049920555744</v>
+      </c>
+      <c r="P61">
+        <v>-268.3219968222298</v>
+      </c>
+      <c r="Q61">
+        <v>80.27800317777024</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1367913274433801</v>
+      </c>
+      <c r="T61">
+        <v>1.890106708366073</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.06169800835704577</v>
+      </c>
+      <c r="W61">
+        <v>0.2240665156043375</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.3084900417852289</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.190283688458345</v>
+      </c>
+      <c r="C62">
+        <v>-616.5467114288308</v>
+      </c>
+      <c r="D62">
+        <v>1101.689285055514</v>
+      </c>
+      <c r="E62">
+        <v>-476.0239976562298</v>
+      </c>
+      <c r="F62">
+        <v>2065.535996484345</v>
+      </c>
+      <c r="G62">
+        <v>347.3</v>
+      </c>
+      <c r="H62">
+        <v>901</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K62">
+        <v>348.6</v>
+      </c>
+      <c r="L62">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M62">
+        <v>493.2499959604615</v>
+      </c>
+      <c r="N62">
+        <v>-343.6233292937949</v>
+      </c>
+      <c r="O62">
+        <v>-68.724665858759</v>
+      </c>
+      <c r="P62">
+        <v>-274.8986634350359</v>
+      </c>
+      <c r="Q62">
+        <v>73.70133656496409</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1392411106294645</v>
+      </c>
+      <c r="T62">
+        <v>1.937359376075224</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.06066970821776167</v>
+      </c>
+      <c r="W62">
+        <v>0.2243120736775985</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.3033485410888084</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.192283688458345</v>
+      </c>
+      <c r="C63">
+        <v>-663.6777056859839</v>
+      </c>
+      <c r="D63">
+        <v>1088.983890739767</v>
+      </c>
+      <c r="E63">
+        <v>-441.5983977148239</v>
+      </c>
+      <c r="F63">
+        <v>2099.96159642575</v>
+      </c>
+      <c r="G63">
+        <v>347.3</v>
+      </c>
+      <c r="H63">
+        <v>901</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K63">
+        <v>348.6</v>
+      </c>
+      <c r="L63">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M63">
+        <v>501.4708292264692</v>
+      </c>
+      <c r="N63">
+        <v>-351.8441625598026</v>
+      </c>
+      <c r="O63">
+        <v>-70.36883251196052</v>
+      </c>
+      <c r="P63">
+        <v>-281.4753300478421</v>
+      </c>
+      <c r="Q63">
+        <v>67.12466995215794</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1418165237225278</v>
+      </c>
+      <c r="T63">
+        <v>1.987035257513051</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.05967512283714263</v>
+      </c>
+      <c r="W63">
+        <v>0.2245495806664904</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.2983756141857131</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.194283688458345</v>
+      </c>
+      <c r="C64">
+        <v>-710.5189874243915</v>
+      </c>
+      <c r="D64">
+        <v>1076.568208942765</v>
+      </c>
+      <c r="E64">
+        <v>-407.1727977734181</v>
+      </c>
+      <c r="F64">
+        <v>2134.387196367156</v>
+      </c>
+      <c r="G64">
+        <v>347.3</v>
+      </c>
+      <c r="H64">
+        <v>901</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K64">
+        <v>348.6</v>
+      </c>
+      <c r="L64">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M64">
+        <v>509.691662492477</v>
+      </c>
+      <c r="N64">
+        <v>-360.0649958258103</v>
+      </c>
+      <c r="O64">
+        <v>-72.01299916516207</v>
+      </c>
+      <c r="P64">
+        <v>-288.0519966606483</v>
+      </c>
+      <c r="Q64">
+        <v>60.54800333935174</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1445274848731206</v>
+      </c>
+      <c r="T64">
+        <v>2.039325659026552</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.05871262085589838</v>
+      </c>
+      <c r="W64">
+        <v>0.2247794261396115</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.2935631042794919</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.196283688458345</v>
+      </c>
+      <c r="C65">
+        <v>-757.0803541195608</v>
+      </c>
+      <c r="D65">
+        <v>1064.432442189001</v>
+      </c>
+      <c r="E65">
+        <v>-372.7471978320127</v>
+      </c>
+      <c r="F65">
+        <v>2168.812796308562</v>
+      </c>
+      <c r="G65">
+        <v>347.3</v>
+      </c>
+      <c r="H65">
+        <v>901</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K65">
+        <v>348.6</v>
+      </c>
+      <c r="L65">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M65">
+        <v>517.9124957584845</v>
+      </c>
+      <c r="N65">
+        <v>-368.2858290918179</v>
+      </c>
+      <c r="O65">
+        <v>-73.65716581836358</v>
+      </c>
+      <c r="P65">
+        <v>-294.6286632734543</v>
+      </c>
+      <c r="Q65">
+        <v>53.9713367265457</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.147384984464286</v>
+      </c>
+      <c r="T65">
+        <v>2.094442568729972</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.05778067449310636</v>
+      </c>
+      <c r="W65">
+        <v>0.2250019749310462</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.2889033724655318</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.198283688458345</v>
+      </c>
+      <c r="C66">
+        <v>-803.3711663977549</v>
+      </c>
+      <c r="D66">
+        <v>1052.567229852213</v>
+      </c>
+      <c r="E66">
+        <v>-338.3215978906069</v>
+      </c>
+      <c r="F66">
+        <v>2203.238396249968</v>
+      </c>
+      <c r="G66">
+        <v>347.3</v>
+      </c>
+      <c r="H66">
+        <v>901</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K66">
+        <v>348.6</v>
+      </c>
+      <c r="L66">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M66">
+        <v>526.1333290244922</v>
+      </c>
+      <c r="N66">
+        <v>-376.5066623578256</v>
+      </c>
+      <c r="O66">
+        <v>-75.30133247156513</v>
+      </c>
+      <c r="P66">
+        <v>-301.2053298862605</v>
+      </c>
+      <c r="Q66">
+        <v>47.39467011373949</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1504012340327384</v>
+      </c>
+      <c r="T66">
+        <v>2.152621528972472</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.05687785145415158</v>
+      </c>
+      <c r="W66">
+        <v>0.2252175690727486</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.2843892572707578</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.200283688458345</v>
+      </c>
+      <c r="C67">
+        <v>-849.4003721153381</v>
+      </c>
+      <c r="D67">
+        <v>1040.963624076035</v>
+      </c>
+      <c r="E67">
+        <v>-303.895997949201</v>
+      </c>
+      <c r="F67">
+        <v>2237.663996191373</v>
+      </c>
+      <c r="G67">
+        <v>347.3</v>
+      </c>
+      <c r="H67">
+        <v>901</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K67">
+        <v>348.6</v>
+      </c>
+      <c r="L67">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M67">
+        <v>534.3541622905</v>
+      </c>
+      <c r="N67">
+        <v>-384.7274956238334</v>
+      </c>
+      <c r="O67">
+        <v>-76.94549912476668</v>
+      </c>
+      <c r="P67">
+        <v>-307.7819964990667</v>
+      </c>
+      <c r="Q67">
+        <v>40.81800350093334</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1535898407193881</v>
+      </c>
+      <c r="T67">
+        <v>2.214125001228828</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.05600280758562616</v>
+      </c>
+      <c r="W67">
+        <v>0.2254265295485525</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.2800140379281307</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2022836884583449</v>
+      </c>
+      <c r="C68">
+        <v>-895.1765288627726</v>
+      </c>
+      <c r="D68">
+        <v>1029.613067270007</v>
+      </c>
+      <c r="E68">
+        <v>-269.4703980077952</v>
+      </c>
+      <c r="F68">
+        <v>2272.089596132779</v>
+      </c>
+      <c r="G68">
+        <v>347.3</v>
+      </c>
+      <c r="H68">
+        <v>901</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K68">
+        <v>348.6</v>
+      </c>
+      <c r="L68">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M68">
+        <v>542.5749955565077</v>
+      </c>
+      <c r="N68">
+        <v>-392.9483288898411</v>
+      </c>
+      <c r="O68">
+        <v>-78.58966577796822</v>
+      </c>
+      <c r="P68">
+        <v>-314.3586631118729</v>
+      </c>
+      <c r="Q68">
+        <v>34.24133688812714</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1569660125052524</v>
+      </c>
+      <c r="T68">
+        <v>2.279246324794382</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.05515428019796514</v>
+      </c>
+      <c r="W68">
+        <v>0.2256291578887259</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.2757714009898258</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.204283688458345</v>
+      </c>
+      <c r="C69">
+        <v>-940.7078250122081</v>
+      </c>
+      <c r="D69">
+        <v>1018.507371061977</v>
+      </c>
+      <c r="E69">
+        <v>-235.0447980663894</v>
+      </c>
+      <c r="F69">
+        <v>2306.515196074185</v>
+      </c>
+      <c r="G69">
+        <v>347.3</v>
+      </c>
+      <c r="H69">
+        <v>901</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K69">
+        <v>348.6</v>
+      </c>
+      <c r="L69">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M69">
+        <v>550.7958288225154</v>
+      </c>
+      <c r="N69">
+        <v>-401.1691621558488</v>
+      </c>
+      <c r="O69">
+        <v>-80.23383243116977</v>
+      </c>
+      <c r="P69">
+        <v>-320.935329724679</v>
+      </c>
+      <c r="Q69">
+        <v>27.66467027532099</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1605468007629874</v>
+      </c>
+      <c r="T69">
+        <v>2.348314395242697</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.05433108198605522</v>
+      </c>
+      <c r="W69">
+        <v>0.22582573762173</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.271655409930276</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.206283688458345</v>
+      </c>
+      <c r="C70">
+        <v>-986.0020994174545</v>
+      </c>
+      <c r="D70">
+        <v>1007.638696598136</v>
+      </c>
+      <c r="E70">
+        <v>-200.6191981249835</v>
+      </c>
+      <c r="F70">
+        <v>2340.940796015591</v>
+      </c>
+      <c r="G70">
+        <v>347.3</v>
+      </c>
+      <c r="H70">
+        <v>901</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K70">
+        <v>348.6</v>
+      </c>
+      <c r="L70">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M70">
+        <v>559.0166620885232</v>
+      </c>
+      <c r="N70">
+        <v>-409.3899954218566</v>
+      </c>
+      <c r="O70">
+        <v>-81.87799908437131</v>
+      </c>
+      <c r="P70">
+        <v>-327.5119963374852</v>
+      </c>
+      <c r="Q70">
+        <v>21.08800366251478</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1643513882868307</v>
+      </c>
+      <c r="T70">
+        <v>2.421699220094031</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.05353209548626029</v>
+      </c>
+      <c r="W70">
+        <v>0.2260165355978811</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.2676604774313014</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2082836884583449</v>
+      </c>
+      <c r="C71">
+        <v>-1031.066859865941</v>
+      </c>
+      <c r="D71">
+        <v>996.9995360910555</v>
+      </c>
+      <c r="E71">
+        <v>-166.1935981835777</v>
+      </c>
+      <c r="F71">
+        <v>2375.366395956997</v>
+      </c>
+      <c r="G71">
+        <v>347.3</v>
+      </c>
+      <c r="H71">
+        <v>901</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K71">
+        <v>348.6</v>
+      </c>
+      <c r="L71">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M71">
+        <v>567.2374953545309</v>
+      </c>
+      <c r="N71">
+        <v>-417.6108286878643</v>
+      </c>
+      <c r="O71">
+        <v>-83.52216573757286</v>
+      </c>
+      <c r="P71">
+        <v>-334.0886629502915</v>
+      </c>
+      <c r="Q71">
+        <v>14.51133704970857</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1684014330702769</v>
+      </c>
+      <c r="T71">
+        <v>2.499818549774484</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.05275626801544492</v>
+      </c>
+      <c r="W71">
+        <v>0.2262018031979117</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.2637813400772245</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.210283688458345</v>
+      </c>
+      <c r="C72">
+        <v>-1075.909300373941</v>
+      </c>
+      <c r="D72">
+        <v>986.5826955244613</v>
+      </c>
+      <c r="E72">
+        <v>-131.7679982421719</v>
+      </c>
+      <c r="F72">
+        <v>2409.791995898403</v>
+      </c>
+      <c r="G72">
+        <v>347.3</v>
+      </c>
+      <c r="H72">
+        <v>901</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K72">
+        <v>348.6</v>
+      </c>
+      <c r="L72">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M72">
+        <v>575.4583286205385</v>
+      </c>
+      <c r="N72">
+        <v>-425.8316619538719</v>
+      </c>
+      <c r="O72">
+        <v>-85.16633239077439</v>
+      </c>
+      <c r="P72">
+        <v>-340.6653295630975</v>
+      </c>
+      <c r="Q72">
+        <v>7.934670436902479</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1727214808392861</v>
+      </c>
+      <c r="T72">
+        <v>2.583145834766967</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.05200260704379572</v>
+      </c>
+      <c r="W72">
+        <v>0.2263817774379416</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.2600130352189786</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2122836884583449</v>
+      </c>
+      <c r="C73">
+        <v>-1120.536317408779</v>
+      </c>
+      <c r="D73">
+        <v>976.3812784310293</v>
+      </c>
+      <c r="E73">
+        <v>-97.34239830076649</v>
+      </c>
+      <c r="F73">
+        <v>2444.217595839808</v>
+      </c>
+      <c r="G73">
+        <v>347.3</v>
+      </c>
+      <c r="H73">
+        <v>901</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K73">
+        <v>348.6</v>
+      </c>
+      <c r="L73">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M73">
+        <v>583.6791618865461</v>
+      </c>
+      <c r="N73">
+        <v>-434.0524952198795</v>
+      </c>
+      <c r="O73">
+        <v>-86.81049904397591</v>
+      </c>
+      <c r="P73">
+        <v>-347.2419961759036</v>
+      </c>
+      <c r="Q73">
+        <v>1.358003824096386</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1773394629371925</v>
+      </c>
+      <c r="T73">
+        <v>2.672219829069275</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.05127017595867184</v>
+      </c>
+      <c r="W73">
+        <v>0.2265566819810692</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.2563508797933591</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2142836884583449</v>
+      </c>
+      <c r="C74">
+        <v>-1164.954525114903</v>
+      </c>
+      <c r="D74">
+        <v>966.3886706663106</v>
+      </c>
+      <c r="E74">
+        <v>-62.91679835936111</v>
+      </c>
+      <c r="F74">
+        <v>2478.643195781213</v>
+      </c>
+      <c r="G74">
+        <v>347.3</v>
+      </c>
+      <c r="H74">
+        <v>901</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K74">
+        <v>348.6</v>
+      </c>
+      <c r="L74">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M74">
+        <v>591.8999951525537</v>
+      </c>
+      <c r="N74">
+        <v>-442.2733284858871</v>
+      </c>
+      <c r="O74">
+        <v>-88.45466569717743</v>
+      </c>
+      <c r="P74">
+        <v>-353.8186627887097</v>
+      </c>
+      <c r="Q74">
+        <v>-5.218662788709707</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1822873008992351</v>
+      </c>
+      <c r="T74">
+        <v>2.767656251536035</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.05055809018146806</v>
+      </c>
+      <c r="W74">
+        <v>0.2267267280646654</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.2527904509073403</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2162836884583449</v>
+      </c>
+      <c r="C75">
+        <v>-1209.170269614454</v>
+      </c>
+      <c r="D75">
+        <v>956.5985261081654</v>
+      </c>
+      <c r="E75">
+        <v>-28.49119841795527</v>
+      </c>
+      <c r="F75">
+        <v>2513.068795722619</v>
+      </c>
+      <c r="G75">
+        <v>347.3</v>
+      </c>
+      <c r="H75">
+        <v>901</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K75">
+        <v>348.6</v>
+      </c>
+      <c r="L75">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M75">
+        <v>600.1208284185615</v>
+      </c>
+      <c r="N75">
+        <v>-450.4941617518949</v>
+      </c>
+      <c r="O75">
+        <v>-90.09883235037898</v>
+      </c>
+      <c r="P75">
+        <v>-360.3953294015159</v>
+      </c>
+      <c r="Q75">
+        <v>-11.79532940151586</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1876016453769845</v>
+      </c>
+      <c r="T75">
+        <v>2.870162038629962</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.04986551360363974</v>
+      </c>
+      <c r="W75">
+        <v>0.2268921153514508</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.2493275680181987</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2182836884583449</v>
+      </c>
+      <c r="C76">
+        <v>-1253.18964244731</v>
+      </c>
+      <c r="D76">
+        <v>947.0047532167155</v>
+      </c>
+      <c r="E76">
+        <v>5.93440152345056</v>
+      </c>
+      <c r="F76">
+        <v>2547.494395664025</v>
+      </c>
+      <c r="G76">
+        <v>347.3</v>
+      </c>
+      <c r="H76">
+        <v>901</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K76">
+        <v>348.6</v>
+      </c>
+      <c r="L76">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M76">
+        <v>608.3416616845692</v>
+      </c>
+      <c r="N76">
+        <v>-458.7149950179026</v>
+      </c>
+      <c r="O76">
+        <v>-91.74299900358052</v>
+      </c>
+      <c r="P76">
+        <v>-366.9719960143221</v>
+      </c>
+      <c r="Q76">
+        <v>-18.37199601432206</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1933247855837916</v>
+      </c>
+      <c r="T76">
+        <v>2.980552886269576</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.04919165531169865</v>
+      </c>
+      <c r="W76">
+        <v>0.2270530327115664</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.2459582765584932</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.220283688458345</v>
+      </c>
+      <c r="C77">
+        <v>-1297.018493210411</v>
+      </c>
+      <c r="D77">
+        <v>937.6015023950195</v>
+      </c>
+      <c r="E77">
+        <v>40.3600014648564</v>
+      </c>
+      <c r="F77">
+        <v>2581.919995605431</v>
+      </c>
+      <c r="G77">
+        <v>347.3</v>
+      </c>
+      <c r="H77">
+        <v>901</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K77">
+        <v>348.6</v>
+      </c>
+      <c r="L77">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M77">
+        <v>616.5624949505769</v>
+      </c>
+      <c r="N77">
+        <v>-466.9358282839103</v>
+      </c>
+      <c r="O77">
+        <v>-93.38716565678207</v>
+      </c>
+      <c r="P77">
+        <v>-373.5486626271282</v>
+      </c>
+      <c r="Q77">
+        <v>-24.94866262712821</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.1995057770071433</v>
+      </c>
+      <c r="T77">
+        <v>3.099775001720359</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.04853576657420933</v>
+      </c>
+      <c r="W77">
+        <v>0.2272096589420788</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.2426788328710466</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.222283688458345</v>
+      </c>
+      <c r="C78">
+        <v>-1340.662441451488</v>
+      </c>
+      <c r="D78">
+        <v>928.3831540953485</v>
+      </c>
+      <c r="E78">
+        <v>74.78560140626223</v>
+      </c>
+      <c r="F78">
+        <v>2616.345595546837</v>
+      </c>
+      <c r="G78">
+        <v>347.3</v>
+      </c>
+      <c r="H78">
+        <v>901</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K78">
+        <v>348.6</v>
+      </c>
+      <c r="L78">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M78">
+        <v>624.7833282165847</v>
+      </c>
+      <c r="N78">
+        <v>-475.1566615499181</v>
+      </c>
+      <c r="O78">
+        <v>-95.03133230998361</v>
+      </c>
+      <c r="P78">
+        <v>-380.1253292399344</v>
+      </c>
+      <c r="Q78">
+        <v>-31.52532923993442</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2062018510491077</v>
+      </c>
+      <c r="T78">
+        <v>3.228932293458708</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.04789713806665395</v>
+      </c>
+      <c r="W78">
+        <v>0.227362163429683</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.2394856903332697</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.224283688458345</v>
+      </c>
+      <c r="C79">
+        <v>-1384.126887867985</v>
+      </c>
+      <c r="D79">
+        <v>919.344307620257</v>
+      </c>
+      <c r="E79">
+        <v>109.2112013476681</v>
+      </c>
+      <c r="F79">
+        <v>2650.771195488242</v>
+      </c>
+      <c r="G79">
+        <v>347.3</v>
+      </c>
+      <c r="H79">
+        <v>901</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K79">
+        <v>348.6</v>
+      </c>
+      <c r="L79">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M79">
+        <v>633.0041614825924</v>
+      </c>
+      <c r="N79">
+        <v>-483.3774948159258</v>
+      </c>
+      <c r="O79">
+        <v>-96.67549896318516</v>
+      </c>
+      <c r="P79">
+        <v>-386.7019958527407</v>
+      </c>
+      <c r="Q79">
+        <v>-38.10199585274063</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2134801923990688</v>
+      </c>
+      <c r="T79">
+        <v>3.369320654043868</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.04727509731254156</v>
+      </c>
+      <c r="W79">
+        <v>0.2275107067617651</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.2363754865627078</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.226283688458345</v>
+      </c>
+      <c r="C80">
+        <v>-1427.417024858097</v>
+      </c>
+      <c r="D80">
+        <v>910.4797705715512</v>
+      </c>
+      <c r="E80">
+        <v>143.6368012890739</v>
+      </c>
+      <c r="F80">
+        <v>2685.196795429648</v>
+      </c>
+      <c r="G80">
+        <v>347.3</v>
+      </c>
+      <c r="H80">
+        <v>901</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K80">
+        <v>348.6</v>
+      </c>
+      <c r="L80">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M80">
+        <v>641.2249947486</v>
+      </c>
+      <c r="N80">
+        <v>-491.5983280819334</v>
+      </c>
+      <c r="O80">
+        <v>-98.31966561638669</v>
+      </c>
+      <c r="P80">
+        <v>-393.2786624655467</v>
+      </c>
+      <c r="Q80">
+        <v>-44.67866246554672</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.221420201144481</v>
+      </c>
+      <c r="T80">
+        <v>3.522471592864045</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.04666900632135513</v>
+      </c>
+      <c r="W80">
+        <v>0.2276554412904604</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.2333450316067757</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.228283688458345</v>
+      </c>
+      <c r="C81">
+        <v>-1470.537846467216</v>
+      </c>
+      <c r="D81">
+        <v>901.7845489038377</v>
+      </c>
+      <c r="E81">
+        <v>178.0624012304793</v>
+      </c>
+      <c r="F81">
+        <v>2719.622395371054</v>
+      </c>
+      <c r="G81">
+        <v>347.3</v>
+      </c>
+      <c r="H81">
+        <v>901</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K81">
+        <v>348.6</v>
+      </c>
+      <c r="L81">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M81">
+        <v>649.4458280146076</v>
+      </c>
+      <c r="N81">
+        <v>-499.819161347941</v>
+      </c>
+      <c r="O81">
+        <v>-99.96383226958821</v>
+      </c>
+      <c r="P81">
+        <v>-399.8553290783528</v>
+      </c>
+      <c r="Q81">
+        <v>-51.25532907835282</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2301164011989801</v>
+      </c>
+      <c r="T81">
+        <v>3.69020833538138</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.04607825940589494</v>
+      </c>
+      <c r="W81">
+        <v>0.2277965116538723</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.2303912970294747</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.230283688458345</v>
+      </c>
+      <c r="C82">
+        <v>-1513.494157769834</v>
+      </c>
+      <c r="D82">
+        <v>893.2538375426253</v>
+      </c>
+      <c r="E82">
+        <v>212.4880011718851</v>
+      </c>
+      <c r="F82">
+        <v>2754.04799531246</v>
+      </c>
+      <c r="G82">
+        <v>347.3</v>
+      </c>
+      <c r="H82">
+        <v>901</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K82">
+        <v>348.6</v>
+      </c>
+      <c r="L82">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M82">
+        <v>657.6666612806154</v>
+      </c>
+      <c r="N82">
+        <v>-508.0399946139487</v>
+      </c>
+      <c r="O82">
+        <v>-101.6079989227898</v>
+      </c>
+      <c r="P82">
+        <v>-406.431995691159</v>
+      </c>
+      <c r="Q82">
+        <v>-57.83199569115897</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2396822212589292</v>
+      </c>
+      <c r="T82">
+        <v>3.87471875215045</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.04550228116332125</v>
+      </c>
+      <c r="W82">
+        <v>0.2279340552581989</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.2275114058166062</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.232283688458345</v>
+      </c>
+      <c r="C83">
+        <v>-1556.290583723926</v>
+      </c>
+      <c r="D83">
+        <v>884.8830115299395</v>
+      </c>
+      <c r="E83">
+        <v>246.913601113291</v>
+      </c>
+      <c r="F83">
+        <v>2788.473595253865</v>
+      </c>
+      <c r="G83">
+        <v>347.3</v>
+      </c>
+      <c r="H83">
+        <v>901</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K83">
+        <v>348.6</v>
+      </c>
+      <c r="L83">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M83">
+        <v>665.8874945466231</v>
+      </c>
+      <c r="N83">
+        <v>-516.2608278799564</v>
+      </c>
+      <c r="O83">
+        <v>-103.2521655759913</v>
+      </c>
+      <c r="P83">
+        <v>-413.0086623039651</v>
+      </c>
+      <c r="Q83">
+        <v>-64.40866230396512</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2502549697462413</v>
+      </c>
+      <c r="T83">
+        <v>4.078651318053105</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.04494052460574938</v>
+      </c>
+      <c r="W83">
+        <v>0.2280682027241471</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.224702623028747</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.234283688458345</v>
+      </c>
+      <c r="C84">
+        <v>-1598.931577532099</v>
+      </c>
+      <c r="D84">
+        <v>876.6676176631726</v>
+      </c>
+      <c r="E84">
+        <v>281.3392010546968</v>
+      </c>
+      <c r="F84">
+        <v>2822.899195195271</v>
+      </c>
+      <c r="G84">
+        <v>347.3</v>
+      </c>
+      <c r="H84">
+        <v>901</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K84">
+        <v>348.6</v>
+      </c>
+      <c r="L84">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M84">
+        <v>674.1083278126308</v>
+      </c>
+      <c r="N84">
+        <v>-524.4816611459642</v>
+      </c>
+      <c r="O84">
+        <v>-104.8963322291928</v>
+      </c>
+      <c r="P84">
+        <v>-419.5853289167713</v>
+      </c>
+      <c r="Q84">
+        <v>-70.98532891677132</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2620024680654769</v>
+      </c>
+      <c r="T84">
+        <v>4.305243057944945</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.04439246942763048</v>
+      </c>
+      <c r="W84">
+        <v>0.2281990783006818</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.2219623471381525</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2362836884583449</v>
+      </c>
+      <c r="C85">
+        <v>-1641.421428541274</v>
+      </c>
+      <c r="D85">
+        <v>868.603366595403</v>
+      </c>
+      <c r="E85">
+        <v>315.7648009961026</v>
+      </c>
+      <c r="F85">
+        <v>2857.324795136677</v>
+      </c>
+      <c r="G85">
+        <v>347.3</v>
+      </c>
+      <c r="H85">
+        <v>901</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K85">
+        <v>348.6</v>
+      </c>
+      <c r="L85">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M85">
+        <v>682.3291610786385</v>
+      </c>
+      <c r="N85">
+        <v>-532.7024944119719</v>
+      </c>
+      <c r="O85">
+        <v>-106.5404988823944</v>
+      </c>
+      <c r="P85">
+        <v>-426.1619955295775</v>
+      </c>
+      <c r="Q85">
+        <v>-77.56199552957747</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2751320250105049</v>
+      </c>
+      <c r="T85">
+        <v>4.558492649588765</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.04385762039838192</v>
+      </c>
+      <c r="W85">
+        <v>0.2283268002488664</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.2192881019919097</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.238283688458345</v>
+      </c>
+      <c r="C86">
+        <v>-1683.764269710332</v>
+      </c>
+      <c r="D86">
+        <v>860.68612536775</v>
+      </c>
+      <c r="E86">
+        <v>350.190400937508</v>
+      </c>
+      <c r="F86">
+        <v>2891.750395078082</v>
+      </c>
+      <c r="G86">
+        <v>347.3</v>
+      </c>
+      <c r="H86">
+        <v>901</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K86">
+        <v>348.6</v>
+      </c>
+      <c r="L86">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M86">
+        <v>690.5499943446462</v>
+      </c>
+      <c r="N86">
+        <v>-540.9233276779796</v>
+      </c>
+      <c r="O86">
+        <v>-108.1846655355959</v>
+      </c>
+      <c r="P86">
+        <v>-432.7386621423837</v>
+      </c>
+      <c r="Q86">
+        <v>-84.13866214238368</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2899027765736614</v>
+      </c>
+      <c r="T86">
+        <v>4.843398440188061</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.04333550586982976</v>
+      </c>
+      <c r="W86">
+        <v>0.2284514811982847</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.2166775293491487</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2402836884583449</v>
+      </c>
+      <c r="C87">
+        <v>-1725.964084673053</v>
+      </c>
+      <c r="D87">
+        <v>852.9119103464349</v>
+      </c>
+      <c r="E87">
+        <v>384.6160008789138</v>
+      </c>
+      <c r="F87">
+        <v>2926.175995019488</v>
+      </c>
+      <c r="G87">
+        <v>347.3</v>
+      </c>
+      <c r="H87">
+        <v>901</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K87">
+        <v>348.6</v>
+      </c>
+      <c r="L87">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M87">
+        <v>698.7708276106538</v>
+      </c>
+      <c r="N87">
+        <v>-549.1441609439871</v>
+      </c>
+      <c r="O87">
+        <v>-109.8288321887974</v>
+      </c>
+      <c r="P87">
+        <v>-439.3153287551897</v>
+      </c>
+      <c r="Q87">
+        <v>-90.71532875518966</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3066429616785721</v>
+      </c>
+      <c r="T87">
+        <v>5.166291669533932</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.04282567638900824</v>
+      </c>
+      <c r="W87">
+        <v>0.2285732284783048</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.2141283819450412</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.242283688458345</v>
+      </c>
+      <c r="C88">
+        <v>-1768.024714421697</v>
+      </c>
+      <c r="D88">
+        <v>845.2768805391974</v>
+      </c>
+      <c r="E88">
+        <v>419.0416008203197</v>
+      </c>
+      <c r="F88">
+        <v>2960.601594960894</v>
+      </c>
+      <c r="G88">
+        <v>347.3</v>
+      </c>
+      <c r="H88">
+        <v>901</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K88">
+        <v>348.6</v>
+      </c>
+      <c r="L88">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M88">
+        <v>706.9916608766615</v>
+      </c>
+      <c r="N88">
+        <v>-557.3649942099948</v>
+      </c>
+      <c r="O88">
+        <v>-111.472998841999</v>
+      </c>
+      <c r="P88">
+        <v>-445.8919953679959</v>
+      </c>
+      <c r="Q88">
+        <v>-97.29199536799587</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3257746017984702</v>
+      </c>
+      <c r="T88">
+        <v>5.53531250307207</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.0423277034077407</v>
+      </c>
+      <c r="W88">
+        <v>0.2286921444262315</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.2116385170387036</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.244283688458345</v>
+      </c>
+      <c r="C89">
+        <v>-1809.949863634794</v>
+      </c>
+      <c r="D89">
+        <v>837.7773312675062</v>
+      </c>
+      <c r="E89">
+        <v>453.4672007617255</v>
+      </c>
+      <c r="F89">
+        <v>2995.0271949023</v>
+      </c>
+      <c r="G89">
+        <v>347.3</v>
+      </c>
+      <c r="H89">
+        <v>901</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K89">
+        <v>348.6</v>
+      </c>
+      <c r="L89">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M89">
+        <v>715.2124941426692</v>
+      </c>
+      <c r="N89">
+        <v>-565.5858274760026</v>
+      </c>
+      <c r="O89">
+        <v>-113.1171654952005</v>
+      </c>
+      <c r="P89">
+        <v>-452.468661980802</v>
+      </c>
+      <c r="Q89">
+        <v>-103.868661980802</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3478495711675833</v>
+      </c>
+      <c r="T89">
+        <v>5.961105772539153</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.04184117808121494</v>
+      </c>
+      <c r="W89">
+        <v>0.2288083266742059</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.2092058904060747</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2462836884583449</v>
+      </c>
+      <c r="C90">
+        <v>-1851.743106671048</v>
+      </c>
+      <c r="D90">
+        <v>830.4096881726572</v>
+      </c>
+      <c r="E90">
+        <v>487.8928007031309</v>
+      </c>
+      <c r="F90">
+        <v>3029.452794843705</v>
+      </c>
+      <c r="G90">
+        <v>347.3</v>
+      </c>
+      <c r="H90">
+        <v>901</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K90">
+        <v>348.6</v>
+      </c>
+      <c r="L90">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M90">
+        <v>723.4333274086769</v>
+      </c>
+      <c r="N90">
+        <v>-573.8066607420103</v>
+      </c>
+      <c r="O90">
+        <v>-114.7613321484021</v>
+      </c>
+      <c r="P90">
+        <v>-459.0453285936082</v>
+      </c>
+      <c r="Q90">
+        <v>-110.4453285936082</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3736037020982152</v>
+      </c>
+      <c r="T90">
+        <v>6.457864586917415</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.04136571014847387</v>
+      </c>
+      <c r="W90">
+        <v>0.2289218684165444</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.2068285507423693</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2482836884583449</v>
+      </c>
+      <c r="C91">
+        <v>-1893.407893249725</v>
+      </c>
+      <c r="D91">
+        <v>823.1705015353856</v>
+      </c>
+      <c r="E91">
+        <v>522.3184006445367</v>
+      </c>
+      <c r="F91">
+        <v>3063.878394785111</v>
+      </c>
+      <c r="G91">
+        <v>347.3</v>
+      </c>
+      <c r="H91">
+        <v>901</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K91">
+        <v>348.6</v>
+      </c>
+      <c r="L91">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M91">
+        <v>731.6541606746846</v>
+      </c>
+      <c r="N91">
+        <v>-582.027494008018</v>
+      </c>
+      <c r="O91">
+        <v>-116.4054988016036</v>
+      </c>
+      <c r="P91">
+        <v>-465.6219952064145</v>
+      </c>
+      <c r="Q91">
+        <v>-117.0219952064144</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4040404022889621</v>
+      </c>
+      <c r="T91">
+        <v>7.04494318572809</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.04090092688837865</v>
+      </c>
+      <c r="W91">
+        <v>0.2290328586590552</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2045046344418932</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2502836884583449</v>
+      </c>
+      <c r="C92">
+        <v>-1934.947553836487</v>
+      </c>
+      <c r="D92">
+        <v>816.0564408900304</v>
+      </c>
+      <c r="E92">
+        <v>556.7440005859426</v>
+      </c>
+      <c r="F92">
+        <v>3098.303994726517</v>
+      </c>
+      <c r="G92">
+        <v>347.3</v>
+      </c>
+      <c r="H92">
+        <v>901</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K92">
+        <v>348.6</v>
+      </c>
+      <c r="L92">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M92">
+        <v>739.8749939406923</v>
+      </c>
+      <c r="N92">
+        <v>-590.2483272740258</v>
+      </c>
+      <c r="O92">
+        <v>-118.0496654548052</v>
+      </c>
+      <c r="P92">
+        <v>-472.1986618192206</v>
+      </c>
+      <c r="Q92">
+        <v>-123.5986618192206</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4405644425178584</v>
+      </c>
+      <c r="T92">
+        <v>7.7494375043009</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.04044647214517445</v>
+      </c>
+      <c r="W92">
+        <v>0.2291413824517324</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2022323607258721</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.252283688458345</v>
+      </c>
+      <c r="C93">
+        <v>-1976.365304752344</v>
+      </c>
+      <c r="D93">
+        <v>809.0642899155788</v>
+      </c>
+      <c r="E93">
+        <v>591.1696005273484</v>
+      </c>
+      <c r="F93">
+        <v>3132.729594667923</v>
+      </c>
+      <c r="G93">
+        <v>347.3</v>
+      </c>
+      <c r="H93">
+        <v>901</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K93">
+        <v>348.6</v>
+      </c>
+      <c r="L93">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M93">
+        <v>748.0958272067001</v>
+      </c>
+      <c r="N93">
+        <v>-598.4691605400335</v>
+      </c>
+      <c r="O93">
+        <v>-119.6938321080067</v>
+      </c>
+      <c r="P93">
+        <v>-478.7753284320268</v>
+      </c>
+      <c r="Q93">
+        <v>-130.1753284320268</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.4852049361309538</v>
+      </c>
+      <c r="T93">
+        <v>8.61048611588989</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.0400020054183044</v>
+      </c>
+      <c r="W93">
+        <v>0.2292475211061089</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2000100270915219</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.254283688458345</v>
+      </c>
+      <c r="C94">
+        <v>-2017.664253022203</v>
+      </c>
+      <c r="D94">
+        <v>802.190941587126</v>
+      </c>
+      <c r="E94">
+        <v>625.5952004687542</v>
+      </c>
+      <c r="F94">
+        <v>3167.155194609329</v>
+      </c>
+      <c r="G94">
+        <v>347.3</v>
+      </c>
+      <c r="H94">
+        <v>901</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K94">
+        <v>348.6</v>
+      </c>
+      <c r="L94">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M94">
+        <v>756.3166604727077</v>
+      </c>
+      <c r="N94">
+        <v>-606.689993806041</v>
+      </c>
+      <c r="O94">
+        <v>-121.3379987612082</v>
+      </c>
+      <c r="P94">
+        <v>-485.3519950448328</v>
+      </c>
+      <c r="Q94">
+        <v>-136.7519950448328</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.541005553147323</v>
+      </c>
+      <c r="T94">
+        <v>9.686796880376127</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.0395672010115837</v>
+      </c>
+      <c r="W94">
+        <v>0.2293513523984338</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1978360050579185</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2562836884583449</v>
+      </c>
+      <c r="C95">
+        <v>-2058.847400978336</v>
+      </c>
+      <c r="D95">
+        <v>795.4333935723981</v>
+      </c>
+      <c r="E95">
+        <v>660.0208004101601</v>
+      </c>
+      <c r="F95">
+        <v>3201.580794550734</v>
+      </c>
+      <c r="G95">
+        <v>347.3</v>
+      </c>
+      <c r="H95">
+        <v>901</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K95">
+        <v>348.6</v>
+      </c>
+      <c r="L95">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M95">
+        <v>764.5374937387154</v>
+      </c>
+      <c r="N95">
+        <v>-614.9108270720487</v>
+      </c>
+      <c r="O95">
+        <v>-122.9821654144097</v>
+      </c>
+      <c r="P95">
+        <v>-491.928661657639</v>
+      </c>
+      <c r="Q95">
+        <v>-143.328661657639</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.6127492035969409</v>
+      </c>
+      <c r="T95">
+        <v>11.07062500614415</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.03914174723726559</v>
+      </c>
+      <c r="W95">
+        <v>0.229452950759741</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.195708736186328</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.258283688458345</v>
+      </c>
+      <c r="C96">
+        <v>-2099.917650633137</v>
+      </c>
+      <c r="D96">
+        <v>788.7887438590037</v>
+      </c>
+      <c r="E96">
+        <v>694.4464003515659</v>
+      </c>
+      <c r="F96">
+        <v>3236.00639449214</v>
+      </c>
+      <c r="G96">
+        <v>347.3</v>
+      </c>
+      <c r="H96">
+        <v>901</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K96">
+        <v>348.6</v>
+      </c>
+      <c r="L96">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M96">
+        <v>772.7583270047231</v>
+      </c>
+      <c r="N96">
+        <v>-623.1316603380565</v>
+      </c>
+      <c r="O96">
+        <v>-124.6263320676113</v>
+      </c>
+      <c r="P96">
+        <v>-498.5053282704451</v>
+      </c>
+      <c r="Q96">
+        <v>-149.9053282704451</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.7084074041964312</v>
+      </c>
+      <c r="T96">
+        <v>12.91572917383484</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.0387253456709117</v>
+      </c>
+      <c r="W96">
+        <v>0.2295523874537863</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1936267283545585</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.260283688458345</v>
+      </c>
+      <c r="C97">
+        <v>-2140.877807834507</v>
+      </c>
+      <c r="D97">
+        <v>782.2541865990393</v>
+      </c>
+      <c r="E97">
+        <v>728.8720002929717</v>
+      </c>
+      <c r="F97">
+        <v>3270.431994433546</v>
+      </c>
+      <c r="G97">
+        <v>347.3</v>
+      </c>
+      <c r="H97">
+        <v>901</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K97">
+        <v>348.6</v>
+      </c>
+      <c r="L97">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M97">
+        <v>780.9791602707309</v>
+      </c>
+      <c r="N97">
+        <v>-631.3524936040642</v>
+      </c>
+      <c r="O97">
+        <v>-126.2704987208128</v>
+      </c>
+      <c r="P97">
+        <v>-505.0819948832514</v>
+      </c>
+      <c r="Q97">
+        <v>-156.4819948832513</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.8423288850357178</v>
+      </c>
+      <c r="T97">
+        <v>15.49887500860182</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.03831771045332315</v>
+      </c>
+      <c r="W97">
+        <v>0.2296497307437464</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1915885522666159</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.262283688458345</v>
+      </c>
+      <c r="C98">
+        <v>-2181.730586216411</v>
+      </c>
+      <c r="D98">
+        <v>775.82700815854</v>
+      </c>
+      <c r="E98">
+        <v>763.2976002343771</v>
+      </c>
+      <c r="F98">
+        <v>3304.857594374952</v>
+      </c>
+      <c r="G98">
+        <v>347.3</v>
+      </c>
+      <c r="H98">
+        <v>901</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K98">
+        <v>348.6</v>
+      </c>
+      <c r="L98">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M98">
+        <v>789.1999935367385</v>
+      </c>
+      <c r="N98">
+        <v>-639.5733268700719</v>
+      </c>
+      <c r="O98">
+        <v>-127.9146653740144</v>
+      </c>
+      <c r="P98">
+        <v>-511.6586614960576</v>
+      </c>
+      <c r="Q98">
+        <v>-163.0586614960575</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.043211106294645</v>
+      </c>
+      <c r="T98">
+        <v>19.37359376075223</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.03791856763610105</v>
+      </c>
+      <c r="W98">
+        <v>0.2297450460484991</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1895928381805051</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.264283688458345</v>
+      </c>
+      <c r="C99">
+        <v>-2222.478610956256</v>
+      </c>
+      <c r="D99">
+        <v>769.5045833601004</v>
+      </c>
+      <c r="E99">
+        <v>797.7232001757825</v>
+      </c>
+      <c r="F99">
+        <v>3339.283194316357</v>
+      </c>
+      <c r="G99">
+        <v>347.3</v>
+      </c>
+      <c r="H99">
+        <v>901</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K99">
+        <v>348.6</v>
+      </c>
+      <c r="L99">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M99">
+        <v>797.4208268027461</v>
+      </c>
+      <c r="N99">
+        <v>-647.7941601360794</v>
+      </c>
+      <c r="O99">
+        <v>-129.5588320272159</v>
+      </c>
+      <c r="P99">
+        <v>-518.2353281088635</v>
+      </c>
+      <c r="Q99">
+        <v>-169.6353281088635</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.37801480839286</v>
+      </c>
+      <c r="T99">
+        <v>25.83145834766964</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.03752765456768763</v>
+      </c>
+      <c r="W99">
+        <v>0.2298383960892362</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1876382728384383</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2662836884583449</v>
+      </c>
+      <c r="C100">
+        <v>-2263.124422350039</v>
+      </c>
+      <c r="D100">
+        <v>763.2843719077237</v>
+      </c>
+      <c r="E100">
+        <v>832.1488001171883</v>
+      </c>
+      <c r="F100">
+        <v>3373.708794257763</v>
+      </c>
+      <c r="G100">
+        <v>347.3</v>
+      </c>
+      <c r="H100">
+        <v>901</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K100">
+        <v>348.6</v>
+      </c>
+      <c r="L100">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M100">
+        <v>805.6416600687538</v>
+      </c>
+      <c r="N100">
+        <v>-656.0149934020872</v>
+      </c>
+      <c r="O100">
+        <v>-131.2029986804174</v>
+      </c>
+      <c r="P100">
+        <v>-524.8119947216697</v>
+      </c>
+      <c r="Q100">
+        <v>-176.2119947216697</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.04762221258929</v>
+      </c>
+      <c r="T100">
+        <v>38.74718752150446</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.03714471931699694</v>
+      </c>
+      <c r="W100">
+        <v>0.2299298410271012</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1857235965849847</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2682836884583449</v>
+      </c>
+      <c r="C101">
+        <v>-2303.670479215486</v>
+      </c>
+      <c r="D101">
+        <v>757.163914983682</v>
+      </c>
+      <c r="E101">
+        <v>866.5744000585942</v>
+      </c>
+      <c r="F101">
+        <v>3408.134394199169</v>
+      </c>
+      <c r="G101">
+        <v>347.3</v>
+      </c>
+      <c r="H101">
+        <v>901</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>498.2266666666666</v>
+      </c>
+      <c r="K101">
+        <v>348.6</v>
+      </c>
+      <c r="L101">
+        <v>149.6266666666666</v>
+      </c>
+      <c r="M101">
+        <v>813.8624933347616</v>
+      </c>
+      <c r="N101">
+        <v>-664.2358266680949</v>
+      </c>
+      <c r="O101">
+        <v>-132.847165333619</v>
+      </c>
+      <c r="P101">
+        <v>-531.388661334476</v>
+      </c>
+      <c r="Q101">
+        <v>-182.7886613344759</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.056444425178579</v>
+      </c>
+      <c r="T101">
+        <v>77.49437504300892</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.03676952013197677</v>
+      </c>
+      <c r="W101">
+        <v>0.230019438592484</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1838476006598839</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/finland/finland_air_transport.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_air_transport.xlsx
@@ -647,10 +647,10 @@
         <v>0.2400081566068516</v>
       </c>
       <c r="X2">
-        <v>0.2178511732000565</v>
+        <v>0.2177618412088314</v>
       </c>
       <c r="Y2">
-        <v>0.02215698340679509</v>
+        <v>0.02224631539802022</v>
       </c>
       <c r="Z2">
         <v>1.249655864934507</v>
@@ -659,10 +659,10 @@
         <v>0.06150985897488783</v>
       </c>
       <c r="AB2">
-        <v>0.08378422869052542</v>
+        <v>0.08376719872306614</v>
       </c>
       <c r="AC2">
-        <v>-0.02227436971563759</v>
+        <v>-0.02225733974817831</v>
       </c>
       <c r="AD2">
         <v>1974.7</v>
@@ -781,10 +781,10 @@
         <v>0.2400081566068516</v>
       </c>
       <c r="X3">
-        <v>0.2178511732000565</v>
+        <v>0.2177618412088314</v>
       </c>
       <c r="Y3">
-        <v>0.02215698340679509</v>
+        <v>0.02224631539802022</v>
       </c>
       <c r="Z3">
         <v>1.249655864934507</v>
@@ -793,10 +793,10 @@
         <v>0.06150985897488783</v>
       </c>
       <c r="AB3">
-        <v>0.08378422869052542</v>
+        <v>0.08376719872306614</v>
       </c>
       <c r="AC3">
-        <v>-0.02227436971563759</v>
+        <v>-0.02225733974817831</v>
       </c>
       <c r="AD3">
         <v>1974.7</v>
@@ -1133,7 +1133,7 @@
         <v>-0.0433463796477496</v>
       </c>
       <c r="F2">
-        <v>4.52736971949773</v>
+        <v>4.72601314377246</v>
       </c>
       <c r="G2">
         <v>5.4598806706927</v>
@@ -1151,13 +1151,13 @@
         <v>468.2</v>
       </c>
       <c r="L2">
-        <v>2012.32572907086</v>
+        <v>2033.15363739899</v>
       </c>
       <c r="M2">
         <v>2252.67875577909</v>
       </c>
       <c r="N2">
-        <v>2226.5421175533</v>
+        <v>2247.37002588144</v>
       </c>
       <c r="O2">
         <v>1987.77875577909</v>
@@ -1166,16 +1166,16 @@
         <v>417.516388482446</v>
       </c>
       <c r="Q2">
-        <v>0.0837842286905254</v>
+        <v>0.08376719872306609</v>
       </c>
       <c r="R2">
-        <v>0.0842301129321677</v>
+        <v>0.0838568847118753</v>
       </c>
       <c r="S2">
         <v>0.0522061955533515</v>
       </c>
       <c r="T2">
-        <v>0.0494861955533515</v>
+        <v>0.0474061955533515</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.217851173200056</v>
+        <v>0.217761841208831</v>
       </c>
       <c r="X2">
-        <v>0.091346336973612</v>
+        <v>0.09132268851542839</v>
       </c>
       <c r="Y2">
         <v>3.53571644822743</v>
@@ -1230,7 +1230,7 @@
         <v>468.2</v>
       </c>
       <c r="AK2">
-        <v>0.0486609081127847</v>
+        <v>0.04863564251455781</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08493401624026704</v>
+        <v>0.08491369717164138</v>
       </c>
       <c r="C2">
-        <v>2389.793318254353</v>
+        <v>2389.948365266387</v>
       </c>
       <c r="D2">
-        <v>2186.493318254353</v>
+        <v>2186.648365266386</v>
       </c>
       <c r="E2">
         <v>-1987.778755779091</v>
@@ -1469,19 +1469,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08493401624026704</v>
+        <v>0.08491369717164138</v>
       </c>
       <c r="T2">
         <v>0.8042187817285175</v>
       </c>
       <c r="U2">
-        <v>0.05565774444168939</v>
+        <v>0.05425774444168939</v>
       </c>
       <c r="V2">
         <v>0.2</v>
       </c>
       <c r="W2">
-        <v>0.04452619555335151</v>
+        <v>0.04340619555335151</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1500,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08484301016332002</v>
+        <v>0.0848115317328316</v>
       </c>
       <c r="C3">
-        <v>2370.330068548865</v>
+        <v>2371.115086764689</v>
       </c>
       <c r="D3">
-        <v>2191.589856106656</v>
+        <v>2192.37487432248</v>
       </c>
       <c r="E3">
         <v>-1963.2189682213</v>
@@ -1533,37 +1533,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M3">
-        <v>1.366942379433709</v>
+        <v>1.332558676852802</v>
       </c>
       <c r="N3">
-        <v>115.559724287233</v>
+        <v>115.5941079898139</v>
       </c>
       <c r="O3">
-        <v>23.11194485744659</v>
+        <v>23.11882159796278</v>
       </c>
       <c r="P3">
-        <v>92.44777942978638</v>
+        <v>92.4752863918511</v>
       </c>
       <c r="Q3">
-        <v>460.9477794297864</v>
+        <v>460.9752863918511</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08525025071493586</v>
+        <v>0.08522976745181625</v>
       </c>
       <c r="T3">
         <v>0.8107175193586469</v>
       </c>
       <c r="U3">
-        <v>0.05565774444168939</v>
+        <v>0.05425774444168939</v>
       </c>
       <c r="V3">
         <v>0.2</v>
       </c>
       <c r="W3">
-        <v>0.04452619555335151</v>
+        <v>0.04340619555335151</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>85.5388408654844</v>
+        <v>87.74597974388688</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1582,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08475200408637301</v>
+        <v>0.08470936629402183</v>
       </c>
       <c r="C4">
-        <v>2350.890633582917</v>
+        <v>2352.311880781065</v>
       </c>
       <c r="D4">
-        <v>2196.710208698499</v>
+        <v>2198.131455896646</v>
       </c>
       <c r="E4">
         <v>-1938.659180663509</v>
@@ -1615,37 +1615,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M4">
-        <v>2.733884758867419</v>
+        <v>2.665117353705604</v>
       </c>
       <c r="N4">
-        <v>114.1927819077993</v>
+        <v>114.2615493129611</v>
       </c>
       <c r="O4">
-        <v>22.83855638155985</v>
+        <v>22.85230986259221</v>
       </c>
       <c r="P4">
-        <v>91.3542255262394</v>
+        <v>91.40923945036886</v>
       </c>
       <c r="Q4">
-        <v>459.8542255262394</v>
+        <v>459.9092394503689</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08557293895439386</v>
+        <v>0.08555228814587225</v>
       </c>
       <c r="T4">
         <v>0.8173488842873504</v>
       </c>
       <c r="U4">
-        <v>0.05565774444168939</v>
+        <v>0.05425774444168939</v>
       </c>
       <c r="V4">
         <v>0.2</v>
       </c>
       <c r="W4">
-        <v>0.04452619555335151</v>
+        <v>0.04340619555335151</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>42.7694204327422</v>
+        <v>43.87298987194344</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1664,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08466099800942599</v>
+        <v>0.08460720085521205</v>
       </c>
       <c r="C5">
-        <v>2331.47518066714</v>
+        <v>2333.538984825972</v>
       </c>
       <c r="D5">
-        <v>2201.854543340513</v>
+        <v>2203.918347499345</v>
       </c>
       <c r="E5">
         <v>-1914.099393105718</v>
@@ -1697,37 +1697,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M5">
-        <v>4.100827138301128</v>
+        <v>3.997676030558405</v>
       </c>
       <c r="N5">
-        <v>112.8258395283655</v>
+        <v>112.9289906361083</v>
       </c>
       <c r="O5">
-        <v>22.56516790567311</v>
+        <v>22.58579812722165</v>
       </c>
       <c r="P5">
-        <v>90.26067162269244</v>
+        <v>90.34319250888662</v>
       </c>
       <c r="Q5">
-        <v>458.7606716226924</v>
+        <v>458.8431925088866</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08590228055961385</v>
+        <v>0.08588145875114589</v>
       </c>
       <c r="T5">
         <v>0.8241169783898415</v>
       </c>
       <c r="U5">
-        <v>0.05565774444168939</v>
+        <v>0.05425774444168939</v>
       </c>
       <c r="V5">
         <v>0.2</v>
       </c>
       <c r="W5">
-        <v>0.04452619555335151</v>
+        <v>0.04340619555335151</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>28.51294695516147</v>
+        <v>29.24865991462897</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1746,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08456999193247897</v>
+        <v>0.08450503541640231</v>
       </c>
       <c r="C6">
-        <v>2312.083878683099</v>
+        <v>2314.796638917587</v>
       </c>
       <c r="D6">
-        <v>2207.023028914262</v>
+        <v>2209.735789148751</v>
       </c>
       <c r="E6">
         <v>-1889.539605547927</v>
@@ -1779,37 +1779,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M6">
-        <v>5.467769517734838</v>
+        <v>5.330234707411209</v>
       </c>
       <c r="N6">
-        <v>111.4588971489318</v>
+        <v>111.5964319592555</v>
       </c>
       <c r="O6">
-        <v>22.29177942978637</v>
+        <v>22.31928639185109</v>
       </c>
       <c r="P6">
-        <v>89.16711771914547</v>
+        <v>89.27714556740438</v>
       </c>
       <c r="Q6">
-        <v>457.6671177191455</v>
+        <v>457.7771455674044</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08623848344827595</v>
+        <v>0.08621748707736275</v>
       </c>
       <c r="T6">
         <v>0.8310260744528014</v>
       </c>
       <c r="U6">
-        <v>0.05565774444168939</v>
+        <v>0.05425774444168939</v>
       </c>
       <c r="V6">
         <v>0.2</v>
       </c>
       <c r="W6">
-        <v>0.04452619555335151</v>
+        <v>0.04340619555335151</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>21.3847102163711</v>
+        <v>21.93649493597172</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1828,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08447898585553196</v>
+        <v>0.08440286997759253</v>
       </c>
       <c r="C7">
-        <v>2292.716898101773</v>
+        <v>2296.085085614999</v>
       </c>
       <c r="D7">
-        <v>2212.215835890727</v>
+        <v>2215.584023403953</v>
       </c>
       <c r="E7">
         <v>-1864.979817990136</v>
@@ -1861,37 +1861,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M7">
-        <v>6.834711897168547</v>
+        <v>6.662793384264011</v>
       </c>
       <c r="N7">
-        <v>110.0919547694981</v>
+        <v>110.2638732824027</v>
       </c>
       <c r="O7">
-        <v>22.01839095389963</v>
+        <v>22.05277465648054</v>
       </c>
       <c r="P7">
-        <v>88.0735638155985</v>
+        <v>88.21109862592213</v>
       </c>
       <c r="Q7">
-        <v>456.5735638155985</v>
+        <v>456.7110986259221</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08658176429248882</v>
+        <v>0.08656058968413152</v>
       </c>
       <c r="T7">
         <v>0.8380806251697182</v>
       </c>
       <c r="U7">
-        <v>0.05565774444168939</v>
+        <v>0.05425774444168939</v>
       </c>
       <c r="V7">
         <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.04452619555335151</v>
+        <v>0.04340619555335151</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>17.10776817309688</v>
+        <v>17.54919594877738</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +1910,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08438797977858493</v>
+        <v>0.08430070453878276</v>
       </c>
       <c r="C8">
-        <v>2273.374411002303</v>
+        <v>2277.404570051905</v>
       </c>
       <c r="D8">
-        <v>2217.433136349048</v>
+        <v>2221.46329539865</v>
       </c>
       <c r="E8">
         <v>-1840.420030432346</v>
@@ -1943,37 +1943,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M8">
-        <v>8.201654276602255</v>
+        <v>7.995352061116811</v>
       </c>
       <c r="N8">
-        <v>108.7250123900644</v>
+        <v>108.9313146055499</v>
       </c>
       <c r="O8">
-        <v>21.74500247801289</v>
+        <v>21.78626292110998</v>
       </c>
       <c r="P8">
-        <v>86.98000991205154</v>
+        <v>87.14505168443989</v>
       </c>
       <c r="Q8">
-        <v>455.4800099120515</v>
+        <v>455.6450516844399</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.0869323489844509</v>
+        <v>0.08691099234636349</v>
       </c>
       <c r="T8">
         <v>0.8452852727103992</v>
       </c>
       <c r="U8">
-        <v>0.05565774444168939</v>
+        <v>0.05425774444168939</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.04452619555335151</v>
+        <v>0.04340619555335151</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>14.25647347758074</v>
+        <v>14.62432995731448</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08435857370163791</v>
+        <v>0.08428253909997301</v>
       </c>
       <c r="C9">
-        <v>2250.505713211912</v>
+        <v>2253.893410170574</v>
       </c>
       <c r="D9">
-        <v>2219.124226116448</v>
+        <v>2222.51192307511</v>
       </c>
       <c r="E9">
         <v>-1815.860242874555</v>
@@ -2025,37 +2025,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M9">
-        <v>9.757707020230955</v>
+        <v>9.585788507326418</v>
       </c>
       <c r="N9">
-        <v>107.1689596464357</v>
+        <v>107.3408781593403</v>
       </c>
       <c r="O9">
-        <v>21.43379192928715</v>
+        <v>21.46817563186805</v>
       </c>
       <c r="P9">
-        <v>85.73516771714858</v>
+        <v>85.87270252747221</v>
       </c>
       <c r="Q9">
-        <v>454.2351677171486</v>
+        <v>454.3727025274722</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.0872904731321541</v>
+        <v>0.08726893054971871</v>
       </c>
       <c r="T9">
         <v>0.8526448589078691</v>
       </c>
       <c r="U9">
-        <v>0.05675774444168939</v>
+        <v>0.05575774444168938</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.04540619555335151</v>
+        <v>0.04460619555335151</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.9830065018594</v>
+        <v>12.19791846829289</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2074,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.0842763676246909</v>
+        <v>0.08419237366116322</v>
       </c>
       <c r="C10">
-        <v>2230.687160550994</v>
+        <v>2234.553246816606</v>
       </c>
       <c r="D10">
-        <v>2223.865461013321</v>
+        <v>2227.731547278933</v>
       </c>
       <c r="E10">
         <v>-1791.300455316764</v>
@@ -2107,37 +2107,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M10">
-        <v>11.15166516597823</v>
+        <v>10.95518686551591</v>
       </c>
       <c r="N10">
-        <v>105.7750015006884</v>
+        <v>105.9714798011508</v>
       </c>
       <c r="O10">
-        <v>21.15500030013769</v>
+        <v>21.19429596023015</v>
       </c>
       <c r="P10">
-        <v>84.62000120055076</v>
+        <v>84.77718384092061</v>
       </c>
       <c r="Q10">
-        <v>453.1200012005507</v>
+        <v>453.2771838409206</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.08765638258741607</v>
+        <v>0.08763465001836425</v>
       </c>
       <c r="T10">
         <v>0.8601644361096318</v>
       </c>
       <c r="U10">
-        <v>0.05675774444168939</v>
+        <v>0.05575774444168938</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.04540619555335151</v>
+        <v>0.04460619555335151</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>10.48513068912698</v>
+        <v>10.67317865975628</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08435256154774387</v>
+        <v>0.08422460822235346</v>
       </c>
       <c r="C11">
-        <v>2201.732203722627</v>
+        <v>2208.124606141026</v>
       </c>
       <c r="D11">
-        <v>2219.470291742745</v>
+        <v>2225.862694161144</v>
       </c>
       <c r="E11">
         <v>-1766.740667758973</v>
@@ -2189,37 +2189,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M11">
-        <v>13.03190710536977</v>
+        <v>12.70034997333959</v>
       </c>
       <c r="N11">
-        <v>103.8947595612969</v>
+        <v>104.2263166933271</v>
       </c>
       <c r="O11">
-        <v>20.77895191225938</v>
+        <v>20.84526333866542</v>
       </c>
       <c r="P11">
-        <v>83.11580764903752</v>
+        <v>83.38105335466166</v>
       </c>
       <c r="Q11">
-        <v>451.6158076490375</v>
+        <v>451.8810533546617</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08803033400872773</v>
+        <v>0.08800840727752948</v>
       </c>
       <c r="T11">
         <v>0.8678492787444001</v>
       </c>
       <c r="U11">
-        <v>0.05895774444168939</v>
+        <v>0.05745774444168938</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.04716619555335151</v>
+        <v>0.04596619555335151</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>8.972337334916029</v>
+        <v>9.206570441926212</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08428795547079687</v>
+        <v>0.08414804278354371</v>
       </c>
       <c r="C12">
-        <v>2180.898030235418</v>
+        <v>2188.008960748994</v>
       </c>
       <c r="D12">
-        <v>2223.195905813327</v>
+        <v>2230.306836326904</v>
       </c>
       <c r="E12">
         <v>-1742.180880201182</v>
@@ -2271,37 +2271,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M12">
-        <v>14.47989678374419</v>
+        <v>14.11149997037733</v>
       </c>
       <c r="N12">
-        <v>102.4467698829225</v>
+        <v>102.8151666962894</v>
       </c>
       <c r="O12">
-        <v>20.4893539765845</v>
+        <v>20.56303333925787</v>
       </c>
       <c r="P12">
-        <v>81.95741590633799</v>
+        <v>82.25213335703148</v>
       </c>
       <c r="Q12">
-        <v>450.457415906338</v>
+        <v>450.7521333570315</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.08841259546162412</v>
+        <v>0.08839047025356506</v>
       </c>
       <c r="T12">
         <v>0.8757048956599414</v>
       </c>
       <c r="U12">
-        <v>0.05895774444168939</v>
+        <v>0.05745774444168938</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.04716619555335151</v>
+        <v>0.04596619555335151</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>8.075103601424424</v>
+        <v>8.285913397733591</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08435534939384984</v>
+        <v>0.08414187734473391</v>
       </c>
       <c r="C13">
-        <v>2152.452143960753</v>
+        <v>2163.807810307555</v>
       </c>
       <c r="D13">
-        <v>2219.309807096453</v>
+        <v>2230.665473443255</v>
       </c>
       <c r="E13">
         <v>-1717.621092643391</v>
@@ -2353,37 +2353,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M13">
-        <v>16.33312295682216</v>
+        <v>15.73877609792362</v>
       </c>
       <c r="N13">
-        <v>100.5935437098445</v>
+        <v>101.1878905687431</v>
       </c>
       <c r="O13">
-        <v>20.1187087419689</v>
+        <v>20.23757811374861</v>
       </c>
       <c r="P13">
-        <v>80.47483496787561</v>
+        <v>80.95031245499445</v>
       </c>
       <c r="Q13">
-        <v>448.9748349678756</v>
+        <v>449.4503124549944</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.0888034470595294</v>
+        <v>0.08878111891445534</v>
       </c>
       <c r="T13">
         <v>0.8837370432926854</v>
       </c>
       <c r="U13">
-        <v>0.06045774444168939</v>
+        <v>0.05825774444168939</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.04836619555335151</v>
+        <v>0.04660619555335151</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>7.158867717813127</v>
+        <v>7.429209611927354</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08430274331690284</v>
+        <v>0.08407171190592415</v>
       </c>
       <c r="C14">
-        <v>2130.924586639661</v>
+        <v>2143.33761304995</v>
       </c>
       <c r="D14">
-        <v>2222.342037333152</v>
+        <v>2234.755063743441</v>
       </c>
       <c r="E14">
         <v>-1693.0613050856</v>
@@ -2435,37 +2435,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M14">
-        <v>17.81795231653327</v>
+        <v>17.16957392500758</v>
       </c>
       <c r="N14">
-        <v>99.10871435013341</v>
+        <v>99.75709274165909</v>
       </c>
       <c r="O14">
-        <v>19.82174287002668</v>
+        <v>19.95141854833182</v>
       </c>
       <c r="P14">
-        <v>79.28697148010673</v>
+        <v>79.80567419332728</v>
       </c>
       <c r="Q14">
-        <v>447.7869714801067</v>
+        <v>448.3056741933273</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.08920318164829619</v>
+        <v>0.08918064595400224</v>
       </c>
       <c r="T14">
         <v>0.8919517397352649</v>
       </c>
       <c r="U14">
-        <v>0.06045774444168939</v>
+        <v>0.05825774444168939</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.04836619555335151</v>
+        <v>0.04660619555335151</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>6.562295407995368</v>
+        <v>6.81010881093341</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2484,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08439573723995579</v>
+        <v>0.08400154646711439</v>
       </c>
       <c r="C15">
-        <v>2101.010210228385</v>
+        <v>2122.882438634323</v>
       </c>
       <c r="D15">
-        <v>2216.987448479667</v>
+        <v>2238.859676885604</v>
       </c>
       <c r="E15">
         <v>-1668.501517527809</v>
@@ -2517,45 +2517,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M15">
-        <v>19.74976980979617</v>
+        <v>18.60037175209155</v>
       </c>
       <c r="N15">
-        <v>97.17689685687051</v>
+        <v>98.32629491457513</v>
       </c>
       <c r="O15">
-        <v>19.4353793713741</v>
+        <v>19.66525898291503</v>
       </c>
       <c r="P15">
-        <v>77.74151748549642</v>
+        <v>78.66103593166011</v>
       </c>
       <c r="Q15">
-        <v>446.2415174854964</v>
+        <v>447.1610359316601</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.08961210553795414</v>
+        <v>0.0895893575231939</v>
       </c>
       <c r="T15">
         <v>0.9003552797742252</v>
       </c>
       <c r="U15">
-        <v>0.06185774444168939</v>
+        <v>0.05825774444168939</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.04948619555335151</v>
+        <v>0.04660619555335151</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y15">
-        <v>5.92040655626626</v>
+        <v>6.286254287015454</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2566,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08435433116300879</v>
+        <v>0.08404338102830462</v>
       </c>
       <c r="C16">
-        <v>2078.831393889993</v>
+        <v>2095.873555059637</v>
       </c>
       <c r="D16">
-        <v>2219.368419699065</v>
+        <v>2236.410580868709</v>
       </c>
       <c r="E16">
         <v>-1643.941729970018</v>
@@ -2599,37 +2599,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M16">
-        <v>21.26898287208818</v>
+        <v>20.37500660498459</v>
       </c>
       <c r="N16">
-        <v>95.6576837945785</v>
+        <v>96.55166006168209</v>
       </c>
       <c r="O16">
-        <v>19.1315367589157</v>
+        <v>19.31033201233642</v>
       </c>
       <c r="P16">
-        <v>76.5261470356628</v>
+        <v>77.24132804934567</v>
       </c>
       <c r="Q16">
-        <v>445.0261470356628</v>
+        <v>445.7413280493457</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09003053928551114</v>
+        <v>0.09000757401259932</v>
       </c>
       <c r="T16">
         <v>0.9089542509768825</v>
       </c>
       <c r="U16">
-        <v>0.06185774444168939</v>
+        <v>0.05925774444168939</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.04948619555335151</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.497520373675813</v>
+        <v>5.738730246009415</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2648,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08431292508606177</v>
+        <v>0.08398121558949485</v>
       </c>
       <c r="C17">
-        <v>2056.65769721869</v>
+        <v>2074.955019959946</v>
       </c>
       <c r="D17">
-        <v>2221.754510585553</v>
+        <v>2240.05183332681</v>
       </c>
       <c r="E17">
         <v>-1619.381942412227</v>
@@ -2681,37 +2681,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M17">
-        <v>22.78819593438019</v>
+        <v>21.83036421962635</v>
       </c>
       <c r="N17">
-        <v>94.13847073228649</v>
+        <v>95.09630244704033</v>
       </c>
       <c r="O17">
-        <v>18.8276941464573</v>
+        <v>19.01926048940807</v>
       </c>
       <c r="P17">
-        <v>75.31077658582919</v>
+        <v>76.07704195763226</v>
       </c>
       <c r="Q17">
-        <v>443.8107765858292</v>
+        <v>444.5770419576323</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09045881853301063</v>
+        <v>0.09043563088999074</v>
       </c>
       <c r="T17">
         <v>0.9177555509137199</v>
       </c>
       <c r="U17">
-        <v>0.06185774444168939</v>
+        <v>0.05925774444168939</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.04948619555335151</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.131019015430759</v>
+        <v>5.356148229608787</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08427151900911474</v>
+        <v>0.0839190501506851</v>
       </c>
       <c r="C18">
-        <v>2034.489136745042</v>
+        <v>2054.048361339652</v>
       </c>
       <c r="D18">
-        <v>2224.145737669696</v>
+        <v>2243.704962264306</v>
       </c>
       <c r="E18">
         <v>-1594.822154854436</v>
@@ -2763,37 +2763,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M18">
-        <v>24.30740899667221</v>
+        <v>23.28572183426811</v>
       </c>
       <c r="N18">
-        <v>92.61925766999447</v>
+        <v>93.64094483239857</v>
       </c>
       <c r="O18">
-        <v>18.52385153399889</v>
+        <v>18.72818896647972</v>
       </c>
       <c r="P18">
-        <v>74.09540613599557</v>
+        <v>74.91275586591885</v>
       </c>
       <c r="Q18">
-        <v>442.5954061359956</v>
+        <v>443.4127558659188</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09089729490545059</v>
+        <v>0.09087387959779625</v>
       </c>
       <c r="T18">
         <v>0.9267664056109581</v>
       </c>
       <c r="U18">
-        <v>0.06185774444168939</v>
+        <v>0.05925774444168939</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.04948619555335151</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.810330326966335</v>
+        <v>5.021388965258238</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2812,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08423011293216771</v>
+        <v>0.08385688471187532</v>
       </c>
       <c r="C19">
-        <v>2012.325729070857</v>
+        <v>2033.153637398992</v>
       </c>
       <c r="D19">
-        <v>2226.542117553302</v>
+        <v>2247.370025881437</v>
       </c>
       <c r="E19">
         <v>-1570.262367296645</v>
@@ -2845,37 +2845,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M19">
-        <v>25.82662205896422</v>
+        <v>24.74107944890986</v>
       </c>
       <c r="N19">
-        <v>91.10004460770246</v>
+        <v>92.18558721775682</v>
       </c>
       <c r="O19">
-        <v>18.22000892154049</v>
+        <v>18.43711744355137</v>
       </c>
       <c r="P19">
-        <v>72.88003568616196</v>
+        <v>73.74846977420546</v>
       </c>
       <c r="Q19">
-        <v>441.3800356861619</v>
+        <v>442.2484697742054</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.091346336973612</v>
+        <v>0.09132268851542838</v>
       </c>
       <c r="T19">
         <v>0.9359943893370456</v>
       </c>
       <c r="U19">
-        <v>0.06185774444168939</v>
+        <v>0.05925774444168939</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.04948619555335151</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>4.527369719497728</v>
+        <v>4.726013143772459</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +2894,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.0845631068552207</v>
+        <v>0.08415471927306556</v>
       </c>
       <c r="C20">
-        <v>1968.63886283653</v>
+        <v>1991.142425917978</v>
       </c>
       <c r="D20">
-        <v>2207.415038876766</v>
+        <v>2229.918601958214</v>
       </c>
       <c r="E20">
         <v>-1545.702579738855</v>
@@ -2927,37 +2927,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M20">
-        <v>28.49523317896085</v>
+        <v>27.30162750365221</v>
       </c>
       <c r="N20">
-        <v>88.43143348770583</v>
+        <v>89.62503916301446</v>
       </c>
       <c r="O20">
-        <v>17.68628669754117</v>
+        <v>17.92500783260289</v>
       </c>
       <c r="P20">
-        <v>70.74514679016467</v>
+        <v>71.70003133041158</v>
       </c>
       <c r="Q20">
-        <v>439.2451467901647</v>
+        <v>440.2000313304115</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09180633128733832</v>
+        <v>0.09178244399202717</v>
       </c>
       <c r="T20">
         <v>0.94544744583694</v>
       </c>
       <c r="U20">
-        <v>0.06445774444168939</v>
+        <v>0.06175774444168938</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.05156619555335151</v>
+        <v>0.04940619555335151</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>4.103376376403835</v>
+        <v>4.282772763309627</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +2976,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08495290077827369</v>
+        <v>0.0841125538342558</v>
       </c>
       <c r="C21">
-        <v>1922.102747836676</v>
+        <v>1969.036807736846</v>
       </c>
       <c r="D21">
-        <v>2185.438711434703</v>
+        <v>2232.372771334873</v>
       </c>
       <c r="E21">
         <v>-1521.142792181064</v>
@@ -3009,45 +3009,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M21">
-        <v>31.33821879061779</v>
+        <v>28.81838458718844</v>
       </c>
       <c r="N21">
-        <v>85.58844787604889</v>
+        <v>88.10828207947824</v>
       </c>
       <c r="O21">
-        <v>17.11768957520978</v>
+        <v>17.62165641589565</v>
       </c>
       <c r="P21">
-        <v>68.47075830083911</v>
+        <v>70.4866256635826</v>
       </c>
       <c r="Q21">
-        <v>436.9707583008391</v>
+        <v>438.9866256635826</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.0922776834853542</v>
+        <v>0.09225355145570246</v>
       </c>
       <c r="T21">
         <v>0.9551339111393011</v>
       </c>
       <c r="U21">
-        <v>0.06715774444168938</v>
+        <v>0.06175774444168938</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.05372619555335151</v>
+        <v>0.04940619555335151</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>3.731120375663241</v>
+        <v>4.057363670503857</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3058,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08495389470132667</v>
+        <v>0.08463038839544601</v>
       </c>
       <c r="C22">
-        <v>1897.487482837044</v>
+        <v>1914.706527989161</v>
       </c>
       <c r="D22">
-        <v>2185.383233992862</v>
+        <v>2202.602279144979</v>
       </c>
       <c r="E22">
         <v>-1496.583004623273</v>
@@ -3091,37 +3091,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M22">
-        <v>32.9875987269661</v>
+        <v>32.05432679977004</v>
       </c>
       <c r="N22">
-        <v>83.93906793970058</v>
+        <v>84.87233986689664</v>
       </c>
       <c r="O22">
-        <v>16.78781358794012</v>
+        <v>16.97446797337933</v>
       </c>
       <c r="P22">
-        <v>67.15125435176046</v>
+        <v>67.8978718935173</v>
       </c>
       <c r="Q22">
-        <v>435.6512543517605</v>
+        <v>436.3978718935173</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09276081948832046</v>
+        <v>0.09273643660596964</v>
       </c>
       <c r="T22">
         <v>0.9650625380742209</v>
       </c>
       <c r="U22">
-        <v>0.06715774444168938</v>
+        <v>0.06525774444168939</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.05372619555335151</v>
+        <v>0.05220619555335151</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.544564356880078</v>
+        <v>3.647765476313342</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3140,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08574448862437965</v>
+        <v>0.08508662295663624</v>
       </c>
       <c r="C23">
-        <v>1829.673900729931</v>
+        <v>1864.567975735521</v>
       </c>
       <c r="D23">
-        <v>2142.12943944354</v>
+        <v>2177.02351444913</v>
       </c>
       <c r="E23">
         <v>-1472.023217065482</v>
@@ -3173,37 +3173,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M23">
-        <v>37.06102969526836</v>
+        <v>35.10115864815664</v>
       </c>
       <c r="N23">
-        <v>79.86563697139832</v>
+        <v>81.82550801851004</v>
       </c>
       <c r="O23">
-        <v>15.97312739427966</v>
+        <v>16.36510160370201</v>
       </c>
       <c r="P23">
-        <v>63.89250957711865</v>
+        <v>65.46040641480803</v>
       </c>
       <c r="Q23">
-        <v>432.3925095771186</v>
+        <v>433.9604064148081</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09325618678250105</v>
+        <v>0.09323154669674991</v>
       </c>
       <c r="T23">
         <v>0.975242522653063</v>
       </c>
       <c r="U23">
-        <v>0.07185774444168938</v>
+        <v>0.06805774444168938</v>
       </c>
       <c r="V23">
         <v>0.2</v>
       </c>
       <c r="W23">
-        <v>0.05748619555335151</v>
+        <v>0.05444619555335151</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.154976200825713</v>
+        <v>3.331134104110468</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3222,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08578308254743264</v>
+        <v>0.08509485751782649</v>
       </c>
       <c r="C24">
-        <v>1803.046409196156</v>
+        <v>1839.551974961174</v>
       </c>
       <c r="D24">
-        <v>2140.061735467556</v>
+        <v>2176.567301232574</v>
       </c>
       <c r="E24">
         <v>-1447.463429507691</v>
@@ -3255,37 +3255,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M24">
-        <v>38.82584063313828</v>
+        <v>36.77264239330697</v>
       </c>
       <c r="N24">
-        <v>78.10082603352839</v>
+        <v>80.15402427335971</v>
       </c>
       <c r="O24">
-        <v>15.62016520670568</v>
+        <v>16.03080485467194</v>
       </c>
       <c r="P24">
-        <v>62.48066082682271</v>
+        <v>64.12321941868777</v>
       </c>
       <c r="Q24">
-        <v>430.9806608268227</v>
+        <v>432.6232194186878</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09376425580217346</v>
+        <v>0.09373935191806301</v>
       </c>
       <c r="T24">
         <v>0.9856835324775164</v>
       </c>
       <c r="U24">
-        <v>0.07185774444168938</v>
+        <v>0.06805774444168938</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.05748619555335151</v>
+        <v>0.05444619555335151</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.011568191697271</v>
+        <v>3.179718917559991</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3304,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08753287647048562</v>
+        <v>0.08510309207901672</v>
       </c>
       <c r="C25">
-        <v>1688.757196389481</v>
+        <v>1814.536165353245</v>
       </c>
       <c r="D25">
-        <v>2050.332310218672</v>
+        <v>2176.111279182435</v>
       </c>
       <c r="E25">
         <v>-1422.9036419499</v>
@@ -3337,45 +3337,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M25">
-        <v>45.84399012961968</v>
+        <v>38.44412613845728</v>
       </c>
       <c r="N25">
-        <v>71.08267653704701</v>
+        <v>78.4825405282094</v>
       </c>
       <c r="O25">
-        <v>14.2165353074094</v>
+        <v>15.69650810564188</v>
       </c>
       <c r="P25">
-        <v>56.86614122963761</v>
+        <v>62.78603242256752</v>
       </c>
       <c r="Q25">
-        <v>425.3661412296376</v>
+        <v>431.2860324225675</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09428552141975943</v>
+        <v>0.09426034688538425</v>
       </c>
       <c r="T25">
         <v>0.9963957373623451</v>
       </c>
       <c r="U25">
-        <v>0.08115774444168938</v>
+        <v>0.06805774444168938</v>
       </c>
       <c r="V25">
         <v>0.2</v>
       </c>
       <c r="W25">
-        <v>0.06492619555335151</v>
+        <v>0.05444619555335151</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.550534243115996</v>
+        <v>3.041470268970427</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3386,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08854827039353859</v>
+        <v>0.08660892664020695</v>
       </c>
       <c r="C26">
-        <v>1615.49614094718</v>
+        <v>1709.678662492149</v>
       </c>
       <c r="D26">
-        <v>2001.631042334162</v>
+        <v>2095.81356387913</v>
       </c>
       <c r="E26">
         <v>-1398.343854392109</v>
@@ -3419,45 +3419,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M26">
-        <v>50.60755112829587</v>
+        <v>44.71320211442605</v>
       </c>
       <c r="N26">
-        <v>66.31911553837081</v>
+        <v>72.21346455224062</v>
       </c>
       <c r="O26">
-        <v>13.26382310767416</v>
+        <v>14.44269291044812</v>
       </c>
       <c r="P26">
-        <v>53.05529243069665</v>
+        <v>57.7707716417925</v>
       </c>
       <c r="Q26">
-        <v>421.5552924306966</v>
+        <v>426.2707716417925</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09482050455359767</v>
+        <v>0.09479505224658233</v>
       </c>
       <c r="T26">
         <v>1.007389842375722</v>
       </c>
       <c r="U26">
-        <v>0.08585774444168939</v>
+        <v>0.07585774444168938</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.06868619555335152</v>
+        <v>0.06068619555335151</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.310458895160612</v>
+        <v>2.615036748373296</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3468,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08869886431659157</v>
+        <v>0.08667956120139718</v>
       </c>
       <c r="C27">
-        <v>1583.909746135986</v>
+        <v>1681.49758187077</v>
       </c>
       <c r="D27">
-        <v>1994.604435080758</v>
+        <v>2092.192270815543</v>
       </c>
       <c r="E27">
         <v>-1373.784066834318</v>
@@ -3501,45 +3501,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M27">
-        <v>52.71619909197487</v>
+        <v>46.57625220252714</v>
       </c>
       <c r="N27">
-        <v>64.2104675746918</v>
+        <v>70.35041446413953</v>
       </c>
       <c r="O27">
-        <v>12.84209351493836</v>
+        <v>14.07008289282791</v>
       </c>
       <c r="P27">
-        <v>51.36837405975344</v>
+        <v>56.28033157131163</v>
       </c>
       <c r="Q27">
-        <v>419.8683740597534</v>
+        <v>424.7803315713116</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.09536975390433824</v>
+        <v>0.0953440164174124</v>
       </c>
       <c r="T27">
         <v>1.018677123522789</v>
       </c>
       <c r="U27">
-        <v>0.08585774444168939</v>
+        <v>0.07585774444168938</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.06868619555335152</v>
+        <v>0.06068619555335151</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.218040539354187</v>
+        <v>2.510435278438364</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3550,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08884945823964455</v>
+        <v>0.08756139576258741</v>
       </c>
       <c r="C28">
-        <v>1552.372511727515</v>
+        <v>1612.759015817432</v>
       </c>
       <c r="D28">
-        <v>1987.626988230079</v>
+        <v>2048.013492319996</v>
       </c>
       <c r="E28">
         <v>-1349.224279276527</v>
@@ -3583,37 +3583,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M28">
-        <v>54.82484705565387</v>
+        <v>50.92966474898822</v>
       </c>
       <c r="N28">
-        <v>62.10181961101281</v>
+        <v>65.99700191767846</v>
       </c>
       <c r="O28">
-        <v>12.42036392220256</v>
+        <v>13.19940038353569</v>
       </c>
       <c r="P28">
-        <v>49.68145568881025</v>
+        <v>52.79760153414277</v>
       </c>
       <c r="Q28">
-        <v>418.1814556888103</v>
+        <v>421.2976015341428</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09593384783212588</v>
+        <v>0.09590781745772435</v>
       </c>
       <c r="T28">
         <v>1.030269466322479</v>
       </c>
       <c r="U28">
-        <v>0.08585774444168939</v>
+        <v>0.07975774444168938</v>
       </c>
       <c r="V28">
         <v>0.2</v>
       </c>
       <c r="W28">
-        <v>0.06868619555335152</v>
+        <v>0.06380619555335151</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.132731287840565</v>
+        <v>2.295845991583708</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08900005216269755</v>
+        <v>0.08766323032377765</v>
       </c>
       <c r="C29">
-        <v>1520.883923607255</v>
+        <v>1583.217325198432</v>
       </c>
       <c r="D29">
-        <v>1980.69818766761</v>
+        <v>2043.031589258787</v>
       </c>
       <c r="E29">
         <v>-1324.664491718736</v>
@@ -3665,37 +3665,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M29">
-        <v>56.93349501933286</v>
+        <v>52.88849800856469</v>
       </c>
       <c r="N29">
-        <v>59.99317164733382</v>
+        <v>64.03816865810199</v>
       </c>
       <c r="O29">
-        <v>11.99863432946676</v>
+        <v>12.8076337316204</v>
       </c>
       <c r="P29">
-        <v>47.99453731786706</v>
+        <v>51.2305349264816</v>
       </c>
       <c r="Q29">
-        <v>416.4945373178671</v>
+        <v>419.7305349264816</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.09651339638807209</v>
+        <v>0.09648706510188046</v>
       </c>
       <c r="T29">
         <v>1.042179407555038</v>
       </c>
       <c r="U29">
-        <v>0.08585774444168939</v>
+        <v>0.07975774444168938</v>
       </c>
       <c r="V29">
         <v>0.2</v>
       </c>
       <c r="W29">
-        <v>0.06868619555335152</v>
+        <v>0.06380619555335151</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.053741240142767</v>
+        <v>2.210814658562089</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3714,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.09280184608575051</v>
+        <v>0.08776506488496788</v>
       </c>
       <c r="C30">
-        <v>1336.113272851909</v>
+        <v>1553.699813258224</v>
       </c>
       <c r="D30">
-        <v>1820.487324470054</v>
+        <v>2038.07386487637</v>
       </c>
       <c r="E30">
         <v>-1300.104704160945</v>
@@ -3747,45 +3747,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M30">
-        <v>70.25123002438762</v>
+        <v>54.84733126814117</v>
       </c>
       <c r="N30">
-        <v>46.67543664227905</v>
+        <v>62.07933539852551</v>
       </c>
       <c r="O30">
-        <v>9.335087328455812</v>
+        <v>12.4158670797051</v>
       </c>
       <c r="P30">
-        <v>37.34034931382324</v>
+        <v>49.66346831882041</v>
       </c>
       <c r="Q30">
-        <v>405.8403493138233</v>
+        <v>418.1634683188204</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.09710904351501679</v>
+        <v>0.09708240295837424</v>
       </c>
       <c r="T30">
         <v>1.054420180488501</v>
       </c>
       <c r="U30">
-        <v>0.1021577444416894</v>
+        <v>0.07975774444168938</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.08172619555335152</v>
+        <v>0.06380619555335151</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y30">
-        <v>1.664407393665218</v>
+        <v>2.131856992184871</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3796,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.09308284000880349</v>
+        <v>0.08786689944615809</v>
       </c>
       <c r="C31">
-        <v>1300.734636953455</v>
+        <v>1524.206304403275</v>
       </c>
       <c r="D31">
-        <v>1809.668476129392</v>
+        <v>2033.140143579211</v>
       </c>
       <c r="E31">
         <v>-1275.544916603155</v>
@@ -3829,45 +3829,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M31">
-        <v>72.76020252525859</v>
+        <v>56.80616452771763</v>
       </c>
       <c r="N31">
-        <v>44.16646414140808</v>
+        <v>60.12050213894905</v>
       </c>
       <c r="O31">
-        <v>8.833292828281618</v>
+        <v>12.02410042778981</v>
       </c>
       <c r="P31">
-        <v>35.33317131312647</v>
+        <v>48.09640171115924</v>
       </c>
       <c r="Q31">
-        <v>403.8331713131265</v>
+        <v>416.5964017111592</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.09772146943426979</v>
+        <v>0.09769451089533263</v>
       </c>
       <c r="T31">
         <v>1.067005763927132</v>
       </c>
       <c r="U31">
-        <v>0.1021577444416894</v>
+        <v>0.07975774444168938</v>
       </c>
       <c r="V31">
         <v>0.2</v>
       </c>
       <c r="W31">
-        <v>0.08172619555335152</v>
+        <v>0.06380619555335151</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y31">
-        <v>1.607014035262969</v>
+        <v>2.058344682109531</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +3878,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.09336383393185649</v>
+        <v>0.09137673400734835</v>
       </c>
       <c r="C32">
-        <v>1265.483830558506</v>
+        <v>1343.075720383256</v>
       </c>
       <c r="D32">
-        <v>1798.977457292233</v>
+        <v>1876.569347116984</v>
       </c>
       <c r="E32">
         <v>-1250.985129045364</v>
@@ -3911,37 +3911,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M32">
-        <v>75.26917502612959</v>
+        <v>69.22746728691303</v>
       </c>
       <c r="N32">
-        <v>41.65749164053709</v>
+        <v>47.69919937975365</v>
       </c>
       <c r="O32">
-        <v>8.331498328107418</v>
+        <v>9.539839875950731</v>
       </c>
       <c r="P32">
-        <v>33.32599331242967</v>
+        <v>38.15935950380292</v>
       </c>
       <c r="Q32">
-        <v>401.8259933124297</v>
+        <v>406.6593595038029</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.09835139323693004</v>
+        <v>0.09832410763048985</v>
       </c>
       <c r="T32">
         <v>1.079950935464009</v>
       </c>
       <c r="U32">
-        <v>0.1021577444416894</v>
+        <v>0.09395774444168939</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.08172619555335152</v>
+        <v>0.07516619555335152</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>1.553446900754203</v>
+        <v>1.689021298180164</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.09364482785490946</v>
+        <v>0.09159216856853858</v>
       </c>
       <c r="C33">
-        <v>1230.358601429029</v>
+        <v>1309.687394966768</v>
       </c>
       <c r="D33">
-        <v>1788.412015720548</v>
+        <v>1867.740809258286</v>
       </c>
       <c r="E33">
         <v>-1226.425341487573</v>
@@ -3993,37 +3993,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M33">
-        <v>77.77814752700058</v>
+        <v>71.53504952981014</v>
       </c>
       <c r="N33">
-        <v>39.14851913966609</v>
+        <v>45.39161713685654</v>
       </c>
       <c r="O33">
-        <v>7.829703827933219</v>
+        <v>9.078323427371307</v>
       </c>
       <c r="P33">
-        <v>31.31881531173287</v>
+        <v>36.31329370948523</v>
       </c>
       <c r="Q33">
-        <v>399.8188153117329</v>
+        <v>404.8132937094852</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.09899957570053694</v>
+        <v>0.09897195354637624</v>
       </c>
       <c r="T33">
         <v>1.093271329364274</v>
       </c>
       <c r="U33">
-        <v>0.1021577444416894</v>
+        <v>0.09395774444168939</v>
       </c>
       <c r="V33">
         <v>0.2</v>
       </c>
       <c r="W33">
-        <v>0.08172619555335152</v>
+        <v>0.07516619555335152</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.503335710407293</v>
+        <v>1.634536740174352</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4042,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1121508292451908</v>
+        <v>0.0918076031297288</v>
       </c>
       <c r="C34">
-        <v>706.9903494432037</v>
+        <v>1276.381750326942</v>
       </c>
       <c r="D34">
-        <v>1289.603551292513</v>
+        <v>1858.994952176251</v>
       </c>
       <c r="E34">
         <v>-1201.865553929782</v>
@@ -4075,45 +4075,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M34">
-        <v>131.6858434288164</v>
+        <v>73.84263177270724</v>
       </c>
       <c r="N34">
-        <v>-14.75917676214971</v>
+        <v>43.08403489395944</v>
       </c>
       <c r="O34">
-        <v>-2.951835352429942</v>
+        <v>8.616806978791889</v>
       </c>
       <c r="P34">
-        <v>-11.80734140971976</v>
+        <v>34.46722791516756</v>
       </c>
       <c r="Q34">
-        <v>356.6926585902802</v>
+        <v>402.9672279151675</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1000796307548664</v>
+        <v>0.09963885375390635</v>
       </c>
       <c r="T34">
-        <v>1.115466867758794</v>
+        <v>1.106983499555724</v>
       </c>
       <c r="U34">
-        <v>0.1675577444416894</v>
+        <v>0.09395774444168939</v>
       </c>
       <c r="V34">
-        <v>0.1775842620924885</v>
+        <v>0.2</v>
       </c>
       <c r="W34">
-        <v>0.1378021260371302</v>
+        <v>0.07516619555335152</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>0.8879213104624426</v>
+        <v>1.583457467043904</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4124,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1133684066896078</v>
+        <v>0.09202303769091903</v>
       </c>
       <c r="C35">
-        <v>659.1920059800358</v>
+        <v>1243.157630397598</v>
       </c>
       <c r="D35">
-        <v>1266.364995387136</v>
+        <v>1850.330619804698</v>
       </c>
       <c r="E35">
         <v>-1177.305766371991</v>
@@ -4157,45 +4157,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M35">
-        <v>135.8010260359669</v>
+        <v>76.15021401560433</v>
       </c>
       <c r="N35">
-        <v>-18.87435936930024</v>
+        <v>40.77645265106234</v>
       </c>
       <c r="O35">
-        <v>-3.774871873860048</v>
+        <v>8.155290530212469</v>
       </c>
       <c r="P35">
-        <v>-15.09948749544019</v>
+        <v>32.62116212084987</v>
       </c>
       <c r="Q35">
-        <v>353.4005125045598</v>
+        <v>401.1211621208499</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1008897744974764</v>
+        <v>0.100325661430318</v>
       </c>
       <c r="T35">
-        <v>1.132115626979075</v>
+        <v>1.121104988260351</v>
       </c>
       <c r="U35">
-        <v>0.1675577444416894</v>
+        <v>0.09395774444168939</v>
       </c>
       <c r="V35">
-        <v>0.1722029208169585</v>
+        <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.138703811443329</v>
+        <v>0.07516619555335152</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.8610146040847927</v>
+        <v>1.535473907436513</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4206,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1145859841340247</v>
+        <v>0.1086071271700107</v>
       </c>
       <c r="C36">
-        <v>612.2163516698228</v>
+        <v>730.0219447306455</v>
       </c>
       <c r="D36">
-        <v>1243.949128634714</v>
+        <v>1361.754721695537</v>
       </c>
       <c r="E36">
         <v>-1152.7459788142</v>
@@ -4239,37 +4239,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M36">
-        <v>139.9162086431174</v>
+        <v>125.8876579901073</v>
       </c>
       <c r="N36">
-        <v>-22.98954197645074</v>
+        <v>-8.960991323440595</v>
       </c>
       <c r="O36">
-        <v>-4.597908395290148</v>
+        <v>-1.792198264688119</v>
       </c>
       <c r="P36">
-        <v>-18.39163358116059</v>
+        <v>-7.168793058752476</v>
       </c>
       <c r="Q36">
-        <v>350.1083664188394</v>
+        <v>361.3312069412475</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1017244680504685</v>
+        <v>0.101320139317114</v>
       </c>
       <c r="T36">
-        <v>1.149268894054516</v>
+        <v>1.14155250031899</v>
       </c>
       <c r="U36">
-        <v>0.1675577444416894</v>
+        <v>0.1507577444416894</v>
       </c>
       <c r="V36">
-        <v>0.1671381290282245</v>
+        <v>0.1857635109485558</v>
       </c>
       <c r="W36">
-        <v>0.139552456531516</v>
+        <v>0.1227524565315161</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8356906451411223</v>
+        <v>0.9288175547427788</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4288,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1158035615784415</v>
+        <v>0.1096567046144276</v>
       </c>
       <c r="C37">
-        <v>566.0204592214187</v>
+        <v>683.0797456571044</v>
       </c>
       <c r="D37">
-        <v>1222.313023744101</v>
+        <v>1339.372310179786</v>
       </c>
       <c r="E37">
         <v>-1128.186191256409</v>
@@ -4321,37 +4321,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M37">
-        <v>144.0313912502679</v>
+        <v>129.5902361662869</v>
       </c>
       <c r="N37">
-        <v>-27.10472458360127</v>
+        <v>-12.66356949962022</v>
       </c>
       <c r="O37">
-        <v>-5.420944916720254</v>
+        <v>-2.532713899924045</v>
       </c>
       <c r="P37">
-        <v>-21.68377966688102</v>
+        <v>-10.13085559969618</v>
       </c>
       <c r="Q37">
-        <v>346.816220333119</v>
+        <v>358.3691444003038</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1025848444820141</v>
+        <v>0.1021742953066081</v>
       </c>
       <c r="T37">
-        <v>1.166949953963047</v>
+        <v>1.159114846477743</v>
       </c>
       <c r="U37">
-        <v>0.1675577444416894</v>
+        <v>0.1507577444416894</v>
       </c>
       <c r="V37">
-        <v>0.1623627539131323</v>
+        <v>0.1804559820643113</v>
       </c>
       <c r="W37">
-        <v>0.1403526076146638</v>
+        <v>0.1235526076146639</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8118137695656616</v>
+        <v>0.9022799103215565</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4370,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1363413837714662</v>
+        <v>0.1107062820588445</v>
       </c>
       <c r="C38">
-        <v>264.1990869584696</v>
+        <v>636.861423334269</v>
       </c>
       <c r="D38">
-        <v>945.0514390389424</v>
+        <v>1317.713775414742</v>
       </c>
       <c r="E38">
         <v>-1103.626403698618</v>
@@ -4403,45 +4403,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M38">
-        <v>194.2993266360191</v>
+        <v>133.2928143424665</v>
       </c>
       <c r="N38">
-        <v>-77.37265996935244</v>
+        <v>-16.36614767579982</v>
       </c>
       <c r="O38">
-        <v>-15.47453199387049</v>
+        <v>-3.273229535159965</v>
       </c>
       <c r="P38">
-        <v>-61.89812797548196</v>
+        <v>-13.09291814063986</v>
       </c>
       <c r="Q38">
-        <v>306.6018720245181</v>
+        <v>355.4070818593601</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1042974900967452</v>
+        <v>0.1030551436707738</v>
       </c>
       <c r="T38">
-        <v>1.202145466771018</v>
+        <v>1.177226015953958</v>
       </c>
       <c r="U38">
-        <v>0.2197577444416894</v>
+        <v>0.1507577444416894</v>
       </c>
       <c r="V38">
-        <v>0.1203572536159175</v>
+        <v>0.1754433158958583</v>
       </c>
       <c r="W38">
-        <v>0.193308305859859</v>
+        <v>0.124308305859859</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.6017862680795871</v>
+        <v>0.8772165794792912</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1380809612158831</v>
+        <v>0.1117558595032614</v>
       </c>
       <c r="C39">
-        <v>221.8242469185105</v>
+        <v>591.3324198904453</v>
       </c>
       <c r="D39">
-        <v>927.2363865567742</v>
+        <v>1296.744559528709</v>
       </c>
       <c r="E39">
         <v>-1079.066616140827</v>
@@ -4485,45 +4485,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M39">
-        <v>199.6965301536863</v>
+        <v>136.9953925186461</v>
       </c>
       <c r="N39">
-        <v>-82.76986348701965</v>
+        <v>-20.06872585197945</v>
       </c>
       <c r="O39">
-        <v>-16.55397269740393</v>
+        <v>-4.01374517039589</v>
       </c>
       <c r="P39">
-        <v>-66.21589078961571</v>
+        <v>-16.05498068158356</v>
       </c>
       <c r="Q39">
-        <v>302.2841092103843</v>
+        <v>352.4450193184164</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1052260216855824</v>
+        <v>0.1039639554750718</v>
       </c>
       <c r="T39">
-        <v>1.221227140846748</v>
+        <v>1.195912143191322</v>
       </c>
       <c r="U39">
-        <v>0.2197577444416894</v>
+        <v>0.1507577444416894</v>
       </c>
       <c r="V39">
-        <v>0.1171043548695413</v>
+        <v>0.1707016046554297</v>
       </c>
       <c r="W39">
-        <v>0.1940231555512598</v>
+        <v>0.1250231555512598</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y39">
-        <v>0.5855217743477064</v>
+        <v>0.8535080232771483</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4534,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1398205386602999</v>
+        <v>0.1128054369476783</v>
       </c>
       <c r="C40">
-        <v>180.1086386572813</v>
+        <v>546.4603427207767</v>
       </c>
       <c r="D40">
-        <v>910.0805658533359</v>
+        <v>1276.432269916831</v>
       </c>
       <c r="E40">
         <v>-1054.506828583036</v>
@@ -4567,45 +4567,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M40">
-        <v>205.0937336713535</v>
+        <v>140.6979706948258</v>
       </c>
       <c r="N40">
-        <v>-88.16706700468686</v>
+        <v>-23.77130402815908</v>
       </c>
       <c r="O40">
-        <v>-17.63341340093737</v>
+        <v>-4.754260805631816</v>
       </c>
       <c r="P40">
-        <v>-70.53365360374949</v>
+        <v>-19.01704322252726</v>
       </c>
       <c r="Q40">
-        <v>297.9663463962505</v>
+        <v>349.4829567774727</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1061845059063176</v>
+        <v>0.1049020837891859</v>
       </c>
       <c r="T40">
-        <v>1.240924352795889</v>
+        <v>1.215201048726666</v>
       </c>
       <c r="U40">
-        <v>0.2197577444416894</v>
+        <v>0.1507577444416894</v>
       </c>
       <c r="V40">
-        <v>0.1140226613203428</v>
+        <v>0.1662094571644973</v>
       </c>
       <c r="W40">
-        <v>0.1947003815746922</v>
+        <v>0.1257003815746922</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y40">
-        <v>0.5701133066017141</v>
+        <v>0.8310472858224864</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4616,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1415601161047169</v>
+        <v>0.1138550143920952</v>
       </c>
       <c r="C41">
-        <v>139.0163353783378</v>
+        <v>502.2147975182677</v>
       </c>
       <c r="D41">
-        <v>893.5480501321832</v>
+        <v>1256.746512272113</v>
       </c>
       <c r="E41">
         <v>-1029.947041025245</v>
@@ -4649,45 +4649,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M41">
-        <v>210.4909371890207</v>
+        <v>144.4005488710054</v>
       </c>
       <c r="N41">
-        <v>-93.56427052235406</v>
+        <v>-27.47388220433871</v>
       </c>
       <c r="O41">
-        <v>-18.71285410447081</v>
+        <v>-5.494776440867742</v>
       </c>
       <c r="P41">
-        <v>-74.85141641788326</v>
+        <v>-21.97910576347097</v>
       </c>
       <c r="Q41">
-        <v>293.6485835821168</v>
+        <v>346.520894236529</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1071744158392081</v>
+        <v>0.1058709704086807</v>
       </c>
       <c r="T41">
-        <v>1.261267374972871</v>
+        <v>1.235122377394317</v>
       </c>
       <c r="U41">
-        <v>0.2197577444416894</v>
+        <v>0.1507577444416894</v>
       </c>
       <c r="V41">
-        <v>0.1110990033377699</v>
+        <v>0.1619476762115615</v>
       </c>
       <c r="W41">
-        <v>0.1953428780584614</v>
+        <v>0.1263428780584614</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y41">
-        <v>0.5554950166888497</v>
+        <v>0.8097383810578073</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4698,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1432996935491337</v>
+        <v>0.1371561026370947</v>
       </c>
       <c r="C42">
-        <v>98.51397429102758</v>
+        <v>157.1119861367199</v>
       </c>
       <c r="D42">
-        <v>877.6054766026641</v>
+        <v>936.2034884483563</v>
       </c>
       <c r="E42">
         <v>-1005.387253467454</v>
@@ -4731,37 +4731,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M42">
-        <v>215.8881407066879</v>
+        <v>201.1522681720134</v>
       </c>
       <c r="N42">
-        <v>-98.96147404002127</v>
+        <v>-84.2256015053467</v>
       </c>
       <c r="O42">
-        <v>-19.79229480800426</v>
+        <v>-16.84512030106934</v>
       </c>
       <c r="P42">
-        <v>-79.16917923201702</v>
+        <v>-67.38048120427736</v>
       </c>
       <c r="Q42">
-        <v>289.330820767983</v>
+        <v>301.1195187957226</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1081973227698615</v>
+        <v>0.1079580045831297</v>
       </c>
       <c r="T42">
-        <v>1.282288497889086</v>
+        <v>1.278033996662517</v>
       </c>
       <c r="U42">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V42">
-        <v>0.1083215282543257</v>
+        <v>0.1162568712043336</v>
       </c>
       <c r="W42">
-        <v>0.1959532497180421</v>
+        <v>0.1809532497180421</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5416076412716284</v>
+        <v>0.5812843560216681</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4780,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1450392709935506</v>
+        <v>0.1387456800815116</v>
       </c>
       <c r="C43">
-        <v>58.57053188661928</v>
+        <v>116.5410408003553</v>
       </c>
       <c r="D43">
-        <v>862.2218217560467</v>
+        <v>920.1923306697826</v>
       </c>
       <c r="E43">
         <v>-980.8274659096636</v>
@@ -4813,37 +4813,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M43">
-        <v>221.2853442243551</v>
+        <v>206.1810748763137</v>
       </c>
       <c r="N43">
-        <v>-104.3586775576885</v>
+        <v>-89.25440820964704</v>
       </c>
       <c r="O43">
-        <v>-20.87173551153769</v>
+        <v>-17.85088164192941</v>
       </c>
       <c r="P43">
-        <v>-83.48694204615076</v>
+        <v>-71.40352656771763</v>
       </c>
       <c r="Q43">
-        <v>285.0130579538492</v>
+        <v>297.0964734322824</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1092549045117236</v>
+        <v>0.1090115300845387</v>
       </c>
       <c r="T43">
-        <v>1.304022201243138</v>
+        <v>1.299695589826288</v>
       </c>
       <c r="U43">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V43">
-        <v>0.1056795397603177</v>
+        <v>0.1134213377603255</v>
       </c>
       <c r="W43">
-        <v>0.1965338471503262</v>
+        <v>0.1815338471503261</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5283976988015887</v>
+        <v>0.5671066888016274</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4862,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1467788484379675</v>
+        <v>0.1403352575259285</v>
       </c>
       <c r="C44">
-        <v>19.15712244253541</v>
+        <v>76.50853955204616</v>
       </c>
       <c r="D44">
-        <v>847.3681998697537</v>
+        <v>904.7196169792643</v>
       </c>
       <c r="E44">
         <v>-956.2676783518727</v>
@@ -4895,37 +4895,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M44">
-        <v>226.6825477420223</v>
+        <v>211.209881580614</v>
       </c>
       <c r="N44">
-        <v>-109.7558810753556</v>
+        <v>-94.28321491394735</v>
       </c>
       <c r="O44">
-        <v>-21.95117621507113</v>
+        <v>-18.85664298278947</v>
       </c>
       <c r="P44">
-        <v>-87.8047048602845</v>
+        <v>-75.42657193115788</v>
       </c>
       <c r="Q44">
-        <v>280.6952951397155</v>
+        <v>293.0734280688421</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1103489545895119</v>
+        <v>0.1101013840515135</v>
       </c>
       <c r="T44">
-        <v>1.326505342643882</v>
+        <v>1.322104134478466</v>
       </c>
       <c r="U44">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V44">
-        <v>0.103163360242215</v>
+        <v>0.110720829718413</v>
       </c>
       <c r="W44">
-        <v>0.1970867970858348</v>
+        <v>0.1820867970858348</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5158168012110746</v>
+        <v>0.5536041485920649</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1485184258823844</v>
+        <v>0.1419248349703454</v>
       </c>
       <c r="C45">
-        <v>-19.75318299894479</v>
+        <v>36.98777029670123</v>
       </c>
       <c r="D45">
-        <v>833.0176819860644</v>
+        <v>889.7586352817103</v>
       </c>
       <c r="E45">
         <v>-931.7078907940818</v>
@@ -4977,37 +4977,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M45">
-        <v>232.0797512596895</v>
+        <v>216.2386882849144</v>
       </c>
       <c r="N45">
-        <v>-115.1530845930228</v>
+        <v>-99.31202161824771</v>
       </c>
       <c r="O45">
-        <v>-23.03061691860457</v>
+        <v>-19.86240432364954</v>
       </c>
       <c r="P45">
-        <v>-92.12246767441827</v>
+        <v>-79.44961729459817</v>
       </c>
       <c r="Q45">
-        <v>276.3775323255817</v>
+        <v>289.0503827054018</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1114813923893279</v>
+        <v>0.1112294785085576</v>
       </c>
       <c r="T45">
-        <v>1.349777366199038</v>
+        <v>1.345298943855281</v>
       </c>
       <c r="U45">
-        <v>0.2197577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V45">
-        <v>0.1007642123296053</v>
+        <v>0.1081459267017057</v>
       </c>
       <c r="W45">
-        <v>0.1976140284196919</v>
+        <v>0.1826140284196918</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5038210616480265</v>
+        <v>0.5407296335085284</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5026,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1636616753989696</v>
+        <v>0.1435144124147623</v>
       </c>
       <c r="C46">
-        <v>-151.3417784142614</v>
+        <v>-2.046240895732581</v>
       </c>
       <c r="D46">
-        <v>725.9888741285388</v>
+        <v>875.2844116470676</v>
       </c>
       <c r="E46">
         <v>-907.1481032362908</v>
@@ -5059,45 +5059,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M46">
-        <v>269.8958743536407</v>
+        <v>221.2674949892147</v>
       </c>
       <c r="N46">
-        <v>-152.9692076869741</v>
+        <v>-104.340828322548</v>
       </c>
       <c r="O46">
-        <v>-30.59384153739482</v>
+        <v>-20.86816566450961</v>
       </c>
       <c r="P46">
-        <v>-122.3753661495793</v>
+        <v>-83.47266265803844</v>
       </c>
       <c r="Q46">
-        <v>246.1246338504207</v>
+        <v>285.0273373419616</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1130179745251521</v>
+        <v>0.1123978620533533</v>
       </c>
       <c r="T46">
-        <v>1.381354708164434</v>
+        <v>1.369322139281268</v>
       </c>
       <c r="U46">
-        <v>0.2497577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V46">
-        <v>0.08664576066358044</v>
+        <v>0.1056880647312124</v>
       </c>
       <c r="W46">
-        <v>0.2281172946929191</v>
+        <v>0.1831172946929191</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y46">
-        <v>0.4332288033179023</v>
+        <v>0.5284403236560619</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5108,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1657012528433864</v>
+        <v>0.1451039898591791</v>
       </c>
       <c r="C47">
-        <v>-188.2509826583332</v>
+        <v>-40.616868905925</v>
       </c>
       <c r="D47">
-        <v>713.6394574422576</v>
+        <v>861.2735711946659</v>
       </c>
       <c r="E47">
         <v>-882.5883156785001</v>
@@ -5141,45 +5141,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M47">
-        <v>276.0298714980416</v>
+        <v>226.296301693515</v>
       </c>
       <c r="N47">
-        <v>-159.103204831375</v>
+        <v>-109.3696350268484</v>
       </c>
       <c r="O47">
-        <v>-31.82064096627499</v>
+        <v>-21.87392700536967</v>
       </c>
       <c r="P47">
-        <v>-127.2825638651</v>
+        <v>-87.49570802147869</v>
       </c>
       <c r="Q47">
-        <v>241.2174361349</v>
+        <v>281.0042919785213</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1142401195165185</v>
+        <v>0.1136087322725051</v>
       </c>
       <c r="T47">
-        <v>1.406470248312878</v>
+        <v>1.394218905450018</v>
       </c>
       <c r="U47">
-        <v>0.2497577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V47">
-        <v>0.0847202993155009</v>
+        <v>0.1033394410705188</v>
       </c>
       <c r="W47">
-        <v>0.2285981935762251</v>
+        <v>0.1835981935762251</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y47">
-        <v>0.4236014965775045</v>
+        <v>0.5166972053525939</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5190,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1677408302878033</v>
+        <v>0.146693567303596</v>
       </c>
       <c r="C48">
-        <v>-224.7470752044521</v>
+        <v>-78.74601553022444</v>
       </c>
       <c r="D48">
-        <v>701.7031524539296</v>
+        <v>847.7042121281575</v>
       </c>
       <c r="E48">
         <v>-858.0285281207091</v>
@@ -5223,45 +5223,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M48">
-        <v>282.1638686424425</v>
+        <v>231.3251083978154</v>
       </c>
       <c r="N48">
-        <v>-165.2372019757759</v>
+        <v>-114.3984417311487</v>
       </c>
       <c r="O48">
-        <v>-33.04744039515517</v>
+        <v>-22.87968834622974</v>
       </c>
       <c r="P48">
-        <v>-132.1897615806207</v>
+        <v>-91.51875338491895</v>
       </c>
       <c r="Q48">
-        <v>236.3102384193793</v>
+        <v>276.981246615081</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1155075291371947</v>
+        <v>0.1148644495368108</v>
       </c>
       <c r="T48">
-        <v>1.432515993652006</v>
+        <v>1.420037774069463</v>
       </c>
       <c r="U48">
-        <v>0.2497577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V48">
-        <v>0.0828785536782074</v>
+        <v>0.1010929314820292</v>
       </c>
       <c r="W48">
-        <v>0.2290581838124308</v>
+        <v>0.1840581838124308</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.414392768391037</v>
+        <v>0.5054646574101462</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5272,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1697804077322203</v>
+        <v>0.1649986682034073</v>
       </c>
       <c r="C49">
-        <v>-260.850444111906</v>
+        <v>-233.4860422641891</v>
       </c>
       <c r="D49">
-        <v>690.1595711042668</v>
+        <v>717.5239729519838</v>
       </c>
       <c r="E49">
         <v>-833.4687405629181</v>
@@ -5305,37 +5305,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M49">
-        <v>288.2978657868435</v>
+        <v>276.7547656346817</v>
       </c>
       <c r="N49">
-        <v>-171.3711991201768</v>
+        <v>-159.8280989680151</v>
       </c>
       <c r="O49">
-        <v>-34.27423982403536</v>
+        <v>-31.96561979360301</v>
       </c>
       <c r="P49">
-        <v>-137.0969592961414</v>
+        <v>-127.8624791744121</v>
       </c>
       <c r="Q49">
-        <v>231.4030407038586</v>
+        <v>240.637520825588</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1168227655360097</v>
+        <v>0.1166685400099476</v>
       </c>
       <c r="T49">
-        <v>1.459544597305817</v>
+        <v>1.457131773035279</v>
       </c>
       <c r="U49">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V49">
-        <v>0.08111518019569235</v>
+        <v>0.08449839438068482</v>
       </c>
       <c r="W49">
-        <v>0.2294985999960321</v>
+        <v>0.2194985999960321</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.4055759009784617</v>
+        <v>0.4224919719034241</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5354,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1718199851766371</v>
+        <v>0.1669382456478242</v>
       </c>
       <c r="C50">
-        <v>-296.5801575532751</v>
+        <v>-269.534301578555</v>
       </c>
       <c r="D50">
-        <v>678.9896452206884</v>
+        <v>706.0355011954085</v>
       </c>
       <c r="E50">
         <v>-808.9089530051274</v>
@@ -5387,37 +5387,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M50">
-        <v>294.4318629312444</v>
+        <v>282.6431649035047</v>
       </c>
       <c r="N50">
-        <v>-177.5051962645777</v>
+        <v>-165.716498236838</v>
       </c>
       <c r="O50">
-        <v>-35.50103925291554</v>
+        <v>-33.14329964736761</v>
       </c>
       <c r="P50">
-        <v>-142.0041570116622</v>
+        <v>-132.5731985894705</v>
       </c>
       <c r="Q50">
-        <v>226.4958429883378</v>
+        <v>235.9268014105295</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1181885879501637</v>
+        <v>0.1180313965486005</v>
       </c>
       <c r="T50">
-        <v>1.487612762638621</v>
+        <v>1.485153537901342</v>
       </c>
       <c r="U50">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V50">
-        <v>0.07942528060828209</v>
+        <v>0.08273801116442056</v>
       </c>
       <c r="W50">
-        <v>0.2299206655053166</v>
+        <v>0.2199206655053166</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3971264030414104</v>
+        <v>0.4136900558221028</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5436,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.173859562621054</v>
+        <v>0.1688778230922411</v>
       </c>
       <c r="C51">
-        <v>-331.9540689222081</v>
+        <v>-305.2204683545569</v>
       </c>
       <c r="D51">
-        <v>668.1755214095464</v>
+        <v>694.9091219771975</v>
       </c>
       <c r="E51">
         <v>-784.3491654473364</v>
@@ -5469,37 +5469,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M51">
-        <v>300.5658600756453</v>
+        <v>288.5315641723278</v>
       </c>
       <c r="N51">
-        <v>-183.6391934089787</v>
+        <v>-171.6048975056611</v>
       </c>
       <c r="O51">
-        <v>-36.72783868179573</v>
+        <v>-34.32097950113222</v>
       </c>
       <c r="P51">
-        <v>-146.9113547271829</v>
+        <v>-137.2839180045289</v>
       </c>
       <c r="Q51">
-        <v>221.5886452728171</v>
+        <v>231.2160819954711</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1196079720276179</v>
+        <v>0.1194476984417103</v>
       </c>
       <c r="T51">
-        <v>1.516781640337418</v>
+        <v>1.514274195507251</v>
       </c>
       <c r="U51">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V51">
-        <v>0.07780435651423551</v>
+        <v>0.08104948032433035</v>
       </c>
       <c r="W51">
-        <v>0.2303255038509569</v>
+        <v>0.2203255038509569</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3890217825711776</v>
+        <v>0.4052474016216517</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5518,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1758991400654709</v>
+        <v>0.170817400536658</v>
       </c>
       <c r="C52">
-        <v>-366.9889120544831</v>
+        <v>-340.5613956026691</v>
       </c>
       <c r="D52">
-        <v>657.7004658350623</v>
+        <v>684.1279822868763</v>
       </c>
       <c r="E52">
         <v>-759.7893778895454</v>
@@ -5551,37 +5551,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M52">
-        <v>306.6998572200463</v>
+        <v>294.4199634411508</v>
       </c>
       <c r="N52">
-        <v>-189.7731905533796</v>
+        <v>-177.4932967744841</v>
       </c>
       <c r="O52">
-        <v>-37.95463811067592</v>
+        <v>-35.49865935489682</v>
       </c>
       <c r="P52">
-        <v>-151.8185524427037</v>
+        <v>-141.9946374195873</v>
       </c>
       <c r="Q52">
-        <v>216.6814475572963</v>
+        <v>226.5053625804127</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1210841314681703</v>
+        <v>0.1209206524105445</v>
       </c>
       <c r="T52">
-        <v>1.547117273144166</v>
+        <v>1.544559679417396</v>
       </c>
       <c r="U52">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V52">
-        <v>0.0762482693839508</v>
+        <v>0.07942849071784373</v>
       </c>
       <c r="W52">
-        <v>0.2307141486627715</v>
+        <v>0.2207141486627715</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.381241346919754</v>
+        <v>0.3971424535892186</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5600,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1779387175098878</v>
+        <v>0.1727569779810749</v>
       </c>
       <c r="C53">
-        <v>-401.7003876305821</v>
+        <v>-375.5729064500288</v>
       </c>
       <c r="D53">
-        <v>647.5487778167544</v>
+        <v>673.6762589973077</v>
       </c>
       <c r="E53">
         <v>-735.2295903317545</v>
@@ -5633,37 +5633,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M53">
-        <v>312.8338543644472</v>
+        <v>300.3083627099738</v>
       </c>
       <c r="N53">
-        <v>-195.9071876977806</v>
+        <v>-183.3816960433072</v>
       </c>
       <c r="O53">
-        <v>-39.18143753955611</v>
+        <v>-36.67633920866143</v>
       </c>
       <c r="P53">
-        <v>-156.7257501582245</v>
+        <v>-146.7053568346457</v>
       </c>
       <c r="Q53">
-        <v>211.7742498417755</v>
+        <v>221.7946431653543</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1226205423144595</v>
+        <v>0.1224537269495352</v>
       </c>
       <c r="T53">
-        <v>1.578691095045068</v>
+        <v>1.576081305527955</v>
       </c>
       <c r="U53">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V53">
-        <v>0.07475320527838313</v>
+        <v>0.07787106933121934</v>
       </c>
       <c r="W53">
-        <v>0.2310875525015738</v>
+        <v>0.2210875525015738</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3737660263919156</v>
+        <v>0.3893553466560967</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5682,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1799782949543047</v>
+        <v>0.1746965554254918</v>
       </c>
       <c r="C54">
-        <v>-436.1032416980834</v>
+        <v>-410.269871626547</v>
       </c>
       <c r="D54">
-        <v>637.705711307044</v>
+        <v>663.5390813785804</v>
       </c>
       <c r="E54">
         <v>-710.6698027739635</v>
@@ -5715,37 +5715,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M54">
-        <v>318.9678515088481</v>
+        <v>306.1967619787969</v>
       </c>
       <c r="N54">
-        <v>-202.0411848421815</v>
+        <v>-189.2700953121302</v>
       </c>
       <c r="O54">
-        <v>-40.40823696843629</v>
+        <v>-37.85401906242604</v>
       </c>
       <c r="P54">
-        <v>-161.6329478737452</v>
+        <v>-151.4160762497042</v>
       </c>
       <c r="Q54">
-        <v>206.8670521262548</v>
+        <v>217.0839237502958</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1242209702793441</v>
+        <v>0.1240506795943172</v>
       </c>
       <c r="T54">
-        <v>1.611580492858507</v>
+        <v>1.608916332726454</v>
       </c>
       <c r="U54">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V54">
-        <v>0.07331564363841424</v>
+        <v>0.07637354876715742</v>
       </c>
       <c r="W54">
-        <v>0.2314465946542684</v>
+        <v>0.2214465946542684</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3665782181920711</v>
+        <v>0.3818677438357871</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5764,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1820178723987216</v>
+        <v>0.1766361328699087</v>
       </c>
       <c r="C55">
-        <v>-470.2113371398104</v>
+        <v>-444.6662800588683</v>
       </c>
       <c r="D55">
-        <v>628.157403423108</v>
+        <v>653.70246050405</v>
       </c>
       <c r="E55">
         <v>-686.1100152161725</v>
@@ -5797,37 +5797,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M55">
-        <v>325.1018486532491</v>
+        <v>312.0851612476199</v>
       </c>
       <c r="N55">
-        <v>-208.1751819865824</v>
+        <v>-195.1584945809532</v>
       </c>
       <c r="O55">
-        <v>-41.63503639731648</v>
+        <v>-39.03169891619065</v>
       </c>
       <c r="P55">
-        <v>-166.5401455892659</v>
+        <v>-156.1267956647626</v>
       </c>
       <c r="Q55">
-        <v>201.9598544107341</v>
+        <v>212.3732043352374</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1258895015618833</v>
+        <v>0.125715587670792</v>
       </c>
       <c r="T55">
-        <v>1.645869439515071</v>
+        <v>1.643148595124889</v>
       </c>
       <c r="U55">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V55">
-        <v>0.07193232960750075</v>
+        <v>0.07493253841306011</v>
       </c>
       <c r="W55">
-        <v>0.2317920880464839</v>
+        <v>0.2217920880464838</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3596616480375038</v>
+        <v>0.3746626920653006</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5846,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1840574498431385</v>
+        <v>0.1785757103143256</v>
       </c>
       <c r="C56">
-        <v>-504.0377188161735</v>
+        <v>-478.7753032769465</v>
       </c>
       <c r="D56">
-        <v>618.8908093045355</v>
+        <v>644.1532248437627</v>
       </c>
       <c r="E56">
         <v>-661.5502276583818</v>
@@ -5879,37 +5879,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M56">
-        <v>331.23584579765</v>
+        <v>317.9735605164429</v>
       </c>
       <c r="N56">
-        <v>-214.3091791309833</v>
+        <v>-201.0468938497762</v>
       </c>
       <c r="O56">
-        <v>-42.86183582619666</v>
+        <v>-40.20937876995524</v>
       </c>
       <c r="P56">
-        <v>-171.4473433047866</v>
+        <v>-160.837515079821</v>
       </c>
       <c r="Q56">
-        <v>197.0526566952134</v>
+        <v>207.662484920179</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1276305776827938</v>
+        <v>0.1274528830549397</v>
       </c>
       <c r="T56">
-        <v>1.681649209939311</v>
+        <v>1.678869216758039</v>
       </c>
       <c r="U56">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V56">
-        <v>0.07060024942958408</v>
+        <v>0.07354489881281827</v>
       </c>
       <c r="W56">
-        <v>0.2321247853871358</v>
+        <v>0.2221247853871358</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3530012471479204</v>
+        <v>0.3677244940640912</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +5928,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1860970272875554</v>
+        <v>0.1805152877587425</v>
       </c>
       <c r="C57">
-        <v>-537.5946730254523</v>
+        <v>-512.6093542568133</v>
       </c>
       <c r="D57">
-        <v>609.8936426530479</v>
+        <v>634.8789614216868</v>
       </c>
       <c r="E57">
         <v>-636.9904401005908</v>
@@ -5961,37 +5961,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M57">
-        <v>337.3698429420509</v>
+        <v>323.8619597852659</v>
       </c>
       <c r="N57">
-        <v>-220.4431762753842</v>
+        <v>-206.9352931185992</v>
       </c>
       <c r="O57">
-        <v>-44.08863525507685</v>
+        <v>-41.38705862371985</v>
       </c>
       <c r="P57">
-        <v>-176.3545410203074</v>
+        <v>-165.5482344948794</v>
       </c>
       <c r="Q57">
-        <v>192.1454589796926</v>
+        <v>202.9517655051206</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1294490349646337</v>
+        <v>0.1292673915672717</v>
       </c>
       <c r="T57">
-        <v>1.719019192382407</v>
+        <v>1.716177421574884</v>
       </c>
       <c r="U57">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V57">
-        <v>0.06931660853086435</v>
+        <v>0.07220771883440338</v>
       </c>
       <c r="W57">
-        <v>0.2324453846426732</v>
+        <v>0.2224453846426732</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3465830426543218</v>
+        <v>0.3610385941720169</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6010,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1881366047319723</v>
+        <v>0.1824548652031594</v>
       </c>
       <c r="C58">
-        <v>-570.8937818519414</v>
+        <v>-546.1801412523312</v>
       </c>
       <c r="D58">
-        <v>601.1543213843496</v>
+        <v>625.8679619839598</v>
       </c>
       <c r="E58">
         <v>-612.4306525427999</v>
@@ -6043,37 +6043,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M58">
-        <v>343.5038400864519</v>
+        <v>329.7503590540889</v>
       </c>
       <c r="N58">
-        <v>-226.5771734197852</v>
+        <v>-212.8236923874222</v>
       </c>
       <c r="O58">
-        <v>-45.31543468395704</v>
+        <v>-42.56473847748445</v>
       </c>
       <c r="P58">
-        <v>-181.2617387358281</v>
+        <v>-170.2589539099378</v>
       </c>
       <c r="Q58">
-        <v>187.2382612641719</v>
+        <v>198.2410460900622</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1313501493956481</v>
+        <v>0.1311643777392551</v>
       </c>
       <c r="T58">
-        <v>1.758087810391098</v>
+        <v>1.755181453883405</v>
       </c>
       <c r="U58">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V58">
-        <v>0.06807881194995606</v>
+        <v>0.07091829528378904</v>
       </c>
       <c r="W58">
-        <v>0.2327545339247985</v>
+        <v>0.2227545339247984</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3403940597497803</v>
+        <v>0.3545914764189452</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6092,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1901761821763892</v>
+        <v>0.1843944426475763</v>
       </c>
       <c r="C59">
-        <v>-603.9459729075011</v>
+        <v>-579.4987171068078</v>
       </c>
       <c r="D59">
-        <v>592.661917886581</v>
+        <v>617.1091736872742</v>
       </c>
       <c r="E59">
         <v>-587.8708649850089</v>
@@ -6125,37 +6125,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M59">
-        <v>349.6378372308528</v>
+        <v>335.6387583229119</v>
       </c>
       <c r="N59">
-        <v>-232.7111705641861</v>
+        <v>-218.7120916562453</v>
       </c>
       <c r="O59">
-        <v>-46.54223411283722</v>
+        <v>-43.74241833124906</v>
       </c>
       <c r="P59">
-        <v>-186.1689364513489</v>
+        <v>-174.9696733249962</v>
       </c>
       <c r="Q59">
-        <v>182.3310635486511</v>
+        <v>193.5303266750038</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1333396877536864</v>
+        <v>0.1331495958262145</v>
       </c>
       <c r="T59">
-        <v>1.798973573423449</v>
+        <v>1.79599962722953</v>
       </c>
       <c r="U59">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V59">
-        <v>0.06688444682802701</v>
+        <v>0.06967411466477519</v>
       </c>
       <c r="W59">
-        <v>0.2330528358636913</v>
+        <v>0.2230528358636913</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3344222341401351</v>
+        <v>0.348370573323876</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6174,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1922157596208061</v>
+        <v>0.1863340200919931</v>
       </c>
       <c r="C60">
-        <v>-636.7615649156928</v>
+        <v>-612.5755244811742</v>
       </c>
       <c r="D60">
-        <v>584.4061134361797</v>
+        <v>608.5921538706983</v>
       </c>
       <c r="E60">
         <v>-563.3110774272184</v>
@@ -6207,37 +6207,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M60">
-        <v>355.7718343752536</v>
+        <v>341.5271575917349</v>
       </c>
       <c r="N60">
-        <v>-238.8451677085869</v>
+        <v>-224.6004909250682</v>
       </c>
       <c r="O60">
-        <v>-47.76903354171739</v>
+        <v>-44.92009818501364</v>
       </c>
       <c r="P60">
-        <v>-191.0761341668695</v>
+        <v>-179.6803927400545</v>
       </c>
       <c r="Q60">
-        <v>177.4238658331305</v>
+        <v>188.8196072599455</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1354239660335361</v>
+        <v>0.135229348107791</v>
       </c>
       <c r="T60">
-        <v>1.841806277552579</v>
+        <v>1.838761523115947</v>
       </c>
       <c r="U60">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V60">
-        <v>0.06573126671030242</v>
+        <v>0.06847283682572737</v>
       </c>
       <c r="W60">
-        <v>0.2333408515288292</v>
+        <v>0.2233408515288292</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3286563335515121</v>
+        <v>0.3423641841286368</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6256,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.194255337065223</v>
+        <v>0.18827359753641</v>
       </c>
       <c r="C61">
-        <v>-669.3503095383287</v>
+        <v>-645.420437387857</v>
       </c>
       <c r="D61">
-        <v>576.3771563713348</v>
+        <v>600.3070285218065</v>
       </c>
       <c r="E61">
         <v>-538.7512898694274</v>
@@ -6289,37 +6289,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M61">
-        <v>361.9058315196546</v>
+        <v>347.4155568605579</v>
       </c>
       <c r="N61">
-        <v>-244.9791648529879</v>
+        <v>-230.4888901938912</v>
       </c>
       <c r="O61">
-        <v>-48.99583297059758</v>
+        <v>-46.09777803877824</v>
       </c>
       <c r="P61">
-        <v>-195.9833318823903</v>
+        <v>-184.391112155113</v>
       </c>
       <c r="Q61">
-        <v>172.5166681176097</v>
+        <v>184.108887844887</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1376099164245979</v>
+        <v>0.1374105517201762</v>
       </c>
       <c r="T61">
-        <v>1.886728381883129</v>
+        <v>1.883609365143165</v>
       </c>
       <c r="U61">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V61">
-        <v>0.06461717744402611</v>
+        <v>0.06731228026935909</v>
       </c>
       <c r="W61">
-        <v>0.233619103951081</v>
+        <v>0.223619103951081</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3230858872201305</v>
+        <v>0.3365614013467955</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6338,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1962949145096398</v>
+        <v>0.190213174980827</v>
       </c>
       <c r="C62">
-        <v>-701.7214298008989</v>
+        <v>-678.0427993776582</v>
       </c>
       <c r="D62">
-        <v>568.5658236665556</v>
+        <v>592.2444540897962</v>
       </c>
       <c r="E62">
         <v>-514.1915023116364</v>
@@ -6371,37 +6371,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M62">
-        <v>368.0398286640555</v>
+        <v>353.3039561293809</v>
       </c>
       <c r="N62">
-        <v>-251.1131619973888</v>
+        <v>-236.3772894627143</v>
       </c>
       <c r="O62">
-        <v>-50.22263239947777</v>
+        <v>-47.27545789254285</v>
       </c>
       <c r="P62">
-        <v>-200.8905295979111</v>
+        <v>-189.1018315701714</v>
       </c>
       <c r="Q62">
-        <v>167.6094704020889</v>
+        <v>179.3981684298286</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1399051643352129</v>
+        <v>0.1397008155131806</v>
       </c>
       <c r="T62">
-        <v>1.933896591430208</v>
+        <v>1.930699599271745</v>
       </c>
       <c r="U62">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V62">
-        <v>0.06354022448662568</v>
+        <v>0.06619040893153644</v>
       </c>
       <c r="W62">
-        <v>0.2338880812925912</v>
+        <v>0.2238880812925912</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3177011224331283</v>
+        <v>0.3309520446576822</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6420,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1983344919540568</v>
+        <v>0.1921527524252438</v>
       </c>
       <c r="C63">
-        <v>-733.8836554352263</v>
+        <v>-710.4514586901521</v>
       </c>
       <c r="D63">
-        <v>560.9633855900192</v>
+        <v>584.3955823350933</v>
       </c>
       <c r="E63">
         <v>-489.6317147538455</v>
@@ -6453,37 +6453,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M63">
-        <v>374.1738258084565</v>
+        <v>359.192355398204</v>
       </c>
       <c r="N63">
-        <v>-257.2471591417898</v>
+        <v>-242.2656887315373</v>
       </c>
       <c r="O63">
-        <v>-51.44943182835796</v>
+        <v>-48.45313774630746</v>
       </c>
       <c r="P63">
-        <v>-205.7977273134318</v>
+        <v>-193.8125509852298</v>
       </c>
       <c r="Q63">
-        <v>162.7022726865682</v>
+        <v>174.6874490147702</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.142318117266885</v>
+        <v>0.1421085287314673</v>
       </c>
       <c r="T63">
-        <v>1.983483683518162</v>
+        <v>1.98020471720179</v>
       </c>
       <c r="U63">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V63">
-        <v>0.06249858146225476</v>
+        <v>0.06510532026052765</v>
       </c>
       <c r="W63">
-        <v>0.2341482397048715</v>
+        <v>0.2241482397048715</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3124929073112738</v>
+        <v>0.3255266013026382</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6502,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.2003740693984737</v>
+        <v>0.1940923298696607</v>
       </c>
       <c r="C64">
-        <v>-765.8452554240771</v>
+        <v>-742.6548006456003</v>
       </c>
       <c r="D64">
-        <v>553.5615731589594</v>
+        <v>576.7520279374362</v>
       </c>
       <c r="E64">
         <v>-465.0719271960545</v>
@@ -6535,37 +6535,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M64">
-        <v>380.3078229528574</v>
+        <v>365.080754667027</v>
       </c>
       <c r="N64">
-        <v>-263.3811562861907</v>
+        <v>-248.1540880003603</v>
       </c>
       <c r="O64">
-        <v>-52.67623125723815</v>
+        <v>-49.63081760007207</v>
       </c>
       <c r="P64">
-        <v>-210.7049250289526</v>
+        <v>-198.5232704002883</v>
       </c>
       <c r="Q64">
-        <v>157.7950749710474</v>
+        <v>169.9767295997117</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1448580677212767</v>
+        <v>0.1446429636980848</v>
       </c>
       <c r="T64">
-        <v>2.035680622558113</v>
+        <v>2.032315367654468</v>
       </c>
       <c r="U64">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V64">
-        <v>0.06149053982576677</v>
+        <v>0.06405523444987397</v>
       </c>
       <c r="W64">
-        <v>0.234400005910304</v>
+        <v>0.224400005910304</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3074526991288339</v>
+        <v>0.3202761722493699</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6584,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.2024136468428905</v>
+        <v>0.1960319073140776</v>
       </c>
       <c r="C65">
-        <v>-797.6140680028075</v>
+        <v>-774.6607775276766</v>
       </c>
       <c r="D65">
-        <v>546.35254813802</v>
+        <v>569.3058386131507</v>
       </c>
       <c r="E65">
         <v>-440.5121396382635</v>
@@ -6617,37 +6617,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M65">
-        <v>386.4418200972583</v>
+        <v>370.96915393585</v>
       </c>
       <c r="N65">
-        <v>-269.5151534305916</v>
+        <v>-254.0424872691834</v>
       </c>
       <c r="O65">
-        <v>-53.90303068611833</v>
+        <v>-50.80849745383668</v>
       </c>
       <c r="P65">
-        <v>-215.6121227444733</v>
+        <v>-203.2339898153467</v>
       </c>
       <c r="Q65">
-        <v>152.8878772555267</v>
+        <v>165.2660101846533</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1475353127948247</v>
+        <v>0.1473143951493844</v>
       </c>
       <c r="T65">
-        <v>2.090699017762387</v>
+        <v>2.087242810023508</v>
       </c>
       <c r="U65">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V65">
-        <v>0.06051449951107207</v>
+        <v>0.06303848469670136</v>
       </c>
       <c r="W65">
-        <v>0.2346437795377863</v>
+        <v>0.2246437795377863</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3025724975553603</v>
+        <v>0.3151924234835068</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.2044532242873074</v>
+        <v>0.1979714847584945</v>
       </c>
       <c r="C66">
-        <v>-829.1975283468762</v>
+        <v>-806.476936180889</v>
       </c>
       <c r="D66">
-        <v>539.3288753517422</v>
+        <v>562.0494675177293</v>
       </c>
       <c r="E66">
         <v>-415.9523520804726</v>
@@ -6699,37 +6699,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M66">
-        <v>392.5758172416593</v>
+        <v>376.8575532046731</v>
       </c>
       <c r="N66">
-        <v>-275.6491505749926</v>
+        <v>-259.9308865380064</v>
       </c>
       <c r="O66">
-        <v>-55.12983011499852</v>
+        <v>-51.98617730760128</v>
       </c>
       <c r="P66">
-        <v>-220.519320459994</v>
+        <v>-207.9447092304051</v>
       </c>
       <c r="Q66">
-        <v>147.980679540006</v>
+        <v>160.5552907695949</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1503612937057921</v>
+        <v>0.1501342394590895</v>
       </c>
       <c r="T66">
-        <v>2.148773990478009</v>
+        <v>2.145221776968605</v>
       </c>
       <c r="U66">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V66">
-        <v>0.05956896045621157</v>
+        <v>0.06205350837331541</v>
       </c>
       <c r="W66">
-        <v>0.2348799352394098</v>
+        <v>0.2248799352394098</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2978448022810578</v>
+        <v>0.310267541866577</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6748,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.2064928017317243</v>
+        <v>0.1999110622029114</v>
       </c>
       <c r="C67">
-        <v>-860.6026941508351</v>
+        <v>-838.1104435240161</v>
       </c>
       <c r="D67">
-        <v>532.4834971055741</v>
+        <v>554.9757477323931</v>
       </c>
       <c r="E67">
         <v>-391.3925645226818</v>
@@ -6781,37 +6781,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M67">
-        <v>398.7098143860601</v>
+        <v>382.7459524734961</v>
       </c>
       <c r="N67">
-        <v>-281.7831477193935</v>
+        <v>-265.8192858068294</v>
       </c>
       <c r="O67">
-        <v>-56.3566295438787</v>
+        <v>-53.16385716136588</v>
       </c>
       <c r="P67">
-        <v>-225.4265181755148</v>
+        <v>-212.6554286454635</v>
       </c>
       <c r="Q67">
-        <v>143.0734818244852</v>
+        <v>155.8445713545365</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1533487592402433</v>
+        <v>0.1531152177293492</v>
       </c>
       <c r="T67">
-        <v>2.210167533063094</v>
+        <v>2.206513827739137</v>
       </c>
       <c r="U67">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V67">
-        <v>0.05865251491073138</v>
+        <v>0.06109883901372594</v>
       </c>
       <c r="W67">
-        <v>0.2351088246117526</v>
+        <v>0.2251088246117526</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2932625745536569</v>
+        <v>0.3054941950686297</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6830,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.2085323791761412</v>
+        <v>0.2018506396473283</v>
       </c>
       <c r="C68">
-        <v>-891.8362692837786</v>
+        <v>-869.5681101608857</v>
       </c>
       <c r="D68">
-        <v>525.8097095304215</v>
+        <v>548.0778686533145</v>
       </c>
       <c r="E68">
         <v>-366.8327769648909</v>
@@ -6863,37 +6863,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M68">
-        <v>404.8438115304611</v>
+        <v>388.634351742319</v>
       </c>
       <c r="N68">
-        <v>-287.9171448637944</v>
+        <v>-271.7076850756524</v>
       </c>
       <c r="O68">
-        <v>-57.58342897275889</v>
+        <v>-54.34153701513048</v>
       </c>
       <c r="P68">
-        <v>-230.3337158910355</v>
+        <v>-217.3661480605219</v>
       </c>
       <c r="Q68">
-        <v>138.1662841089645</v>
+        <v>151.1338519394781</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1565119580414269</v>
+        <v>0.1562715476625654</v>
       </c>
       <c r="T68">
-        <v>2.275172460506127</v>
+        <v>2.271411293260877</v>
       </c>
       <c r="U68">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V68">
-        <v>0.05776384044238697</v>
+        <v>0.0601730990286695</v>
       </c>
       <c r="W68">
-        <v>0.2353307779425092</v>
+        <v>0.2253307779425092</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2888192022119348</v>
+        <v>0.3008654951433475</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +6912,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.2105719566205581</v>
+        <v>0.2037902170917452</v>
       </c>
       <c r="C69">
-        <v>-922.9046256879251</v>
+        <v>-900.8564122519958</v>
       </c>
       <c r="D69">
-        <v>519.3011406840659</v>
+        <v>541.3493541199953</v>
       </c>
       <c r="E69">
         <v>-342.2729894070999</v>
@@ -6945,37 +6945,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M69">
-        <v>410.977808674862</v>
+        <v>394.5227510111421</v>
       </c>
       <c r="N69">
-        <v>-294.0511420081954</v>
+        <v>-277.5960843444754</v>
       </c>
       <c r="O69">
-        <v>-58.81022840163908</v>
+        <v>-55.51921686889509</v>
       </c>
       <c r="P69">
-        <v>-235.2409136065563</v>
+        <v>-222.0768674755803</v>
       </c>
       <c r="Q69">
-        <v>133.2590863934437</v>
+        <v>146.4231325244197</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1598668658608641</v>
+        <v>0.1596191703190068</v>
       </c>
       <c r="T69">
-        <v>2.344117080521464</v>
+        <v>2.340241938511206</v>
       </c>
       <c r="U69">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V69">
-        <v>0.05690169357011254</v>
+        <v>0.0592749930730177</v>
       </c>
       <c r="W69">
-        <v>0.2355461058007059</v>
+        <v>0.2255461058007059</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2845084678505626</v>
+        <v>0.2963749653650886</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +6994,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.212611534064975</v>
+        <v>0.2057297945361621</v>
       </c>
       <c r="C70">
-        <v>-953.8138236706968</v>
+        <v>-931.9815117946241</v>
       </c>
       <c r="D70">
-        <v>512.9517302590853</v>
+        <v>534.784042135158</v>
       </c>
       <c r="E70">
         <v>-317.7132018493089</v>
@@ -7027,37 +7027,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M70">
-        <v>417.1118058192629</v>
+        <v>400.4111502799651</v>
       </c>
       <c r="N70">
-        <v>-300.1851391525963</v>
+        <v>-283.4844836132984</v>
       </c>
       <c r="O70">
-        <v>-60.03702783051926</v>
+        <v>-56.69689672265969</v>
       </c>
       <c r="P70">
-        <v>-240.148111322077</v>
+        <v>-226.7875868906387</v>
       </c>
       <c r="Q70">
-        <v>128.351888677923</v>
+        <v>141.7124131093613</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1634314554190161</v>
+        <v>0.1631760193914757</v>
       </c>
       <c r="T70">
-        <v>2.41737073928776</v>
+        <v>2.413374499089681</v>
       </c>
       <c r="U70">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V70">
-        <v>0.05606490395878735</v>
+        <v>0.05840330199841451</v>
       </c>
       <c r="W70">
-        <v>0.2357551004866027</v>
+        <v>0.2257551004866027</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2803245197939368</v>
+        <v>0.2920165099920725</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7076,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2146511115093919</v>
+        <v>0.207669371980579</v>
       </c>
       <c r="C71">
-        <v>-984.5696307261317</v>
+        <v>-962.9492754449143</v>
       </c>
       <c r="D71">
-        <v>506.7557107614413</v>
+        <v>528.3760660426587</v>
       </c>
       <c r="E71">
         <v>-293.1534142915179</v>
@@ -7109,37 +7109,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M71">
-        <v>423.2458029636639</v>
+        <v>406.2995495487881</v>
       </c>
       <c r="N71">
-        <v>-306.3191362969972</v>
+        <v>-289.3728828821215</v>
       </c>
       <c r="O71">
-        <v>-61.26382725939945</v>
+        <v>-57.8745765764243</v>
       </c>
       <c r="P71">
-        <v>-245.0553090375978</v>
+        <v>-231.4983063056972</v>
       </c>
       <c r="Q71">
-        <v>123.4446909624022</v>
+        <v>137.0016936943028</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1672260184970489</v>
+        <v>0.1669623425976524</v>
       </c>
       <c r="T71">
-        <v>2.495350440555107</v>
+        <v>2.491225289382897</v>
       </c>
       <c r="U71">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V71">
-        <v>0.05525236911880493</v>
+        <v>0.05755687733177081</v>
       </c>
       <c r="W71">
-        <v>0.235958037355517</v>
+        <v>0.225958037355517</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2762618455940246</v>
+        <v>0.2877843866588541</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7158,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2166906889538088</v>
+        <v>0.2096089494249959</v>
       </c>
       <c r="C72">
-        <v>-1015.177539008498</v>
+        <v>-993.7652920027899</v>
       </c>
       <c r="D72">
-        <v>500.7075900368658</v>
+        <v>522.119837042574</v>
       </c>
       <c r="E72">
         <v>-268.593626733727</v>
@@ -7191,37 +7191,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M72">
-        <v>429.3798001080648</v>
+        <v>412.1879488176112</v>
       </c>
       <c r="N72">
-        <v>-312.4531334413982</v>
+        <v>-295.2612821509445</v>
       </c>
       <c r="O72">
-        <v>-62.49062668827963</v>
+        <v>-59.0522564301889</v>
       </c>
       <c r="P72">
-        <v>-249.9625067531185</v>
+        <v>-236.2090257207556</v>
       </c>
       <c r="Q72">
-        <v>118.5374932468815</v>
+        <v>132.2909742792444</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1712735524469505</v>
+        <v>0.1710010873509075</v>
       </c>
       <c r="T72">
-        <v>2.578528788573611</v>
+        <v>2.574266132362327</v>
       </c>
       <c r="U72">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V72">
-        <v>0.05446304955996485</v>
+        <v>0.05673463622703123</v>
       </c>
       <c r="W72">
-        <v>0.2361551760281766</v>
+        <v>0.2261551760281766</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2723152477998242</v>
+        <v>0.2836731811351562</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7240,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2187302663982257</v>
+        <v>0.2115485268694128</v>
       </c>
       <c r="C73">
-        <v>-1045.642781569381</v>
+        <v>-1024.43488866922</v>
       </c>
       <c r="D73">
-        <v>494.8021350337731</v>
+        <v>516.0100279339342</v>
       </c>
       <c r="E73">
         <v>-244.0338391759365</v>
@@ -7273,37 +7273,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M73">
-        <v>435.5137972524657</v>
+        <v>418.0763480864341</v>
       </c>
       <c r="N73">
-        <v>-318.587130585799</v>
+        <v>-301.1496814197674</v>
       </c>
       <c r="O73">
-        <v>-63.7174261171598</v>
+        <v>-60.22993628395349</v>
       </c>
       <c r="P73">
-        <v>-254.8697044686392</v>
+        <v>-240.9197451358139</v>
       </c>
       <c r="Q73">
-        <v>113.6302955313608</v>
+        <v>127.5802548641861</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1756002266692591</v>
+        <v>0.1753183662250767</v>
       </c>
       <c r="T73">
-        <v>2.667443574386493</v>
+        <v>2.663033930029993</v>
       </c>
       <c r="U73">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V73">
-        <v>0.05369596435489493</v>
+        <v>0.05593555684355193</v>
       </c>
       <c r="W73">
-        <v>0.2363467614987895</v>
+        <v>0.2263467614987895</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2684798217744746</v>
+        <v>0.2796777842177596</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7322,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2207698438426426</v>
+        <v>0.2134881043138296</v>
       </c>
       <c r="C74">
-        <v>-1075.970347459145</v>
+        <v>-1054.963146175246</v>
       </c>
       <c r="D74">
-        <v>489.0343567018008</v>
+        <v>510.0415579856992</v>
       </c>
       <c r="E74">
         <v>-219.4740516181455</v>
@@ -7355,37 +7355,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M74">
-        <v>441.6477943968666</v>
+        <v>423.9647473552571</v>
       </c>
       <c r="N74">
-        <v>-324.7211277302</v>
+        <v>-307.0380806885905</v>
       </c>
       <c r="O74">
-        <v>-64.94422554603999</v>
+        <v>-61.40761613771809</v>
       </c>
       <c r="P74">
-        <v>-259.77690218416</v>
+        <v>-245.6304645508724</v>
       </c>
       <c r="Q74">
-        <v>108.72309781584</v>
+        <v>122.8695354491276</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1802359490503041</v>
+        <v>0.1799440221616865</v>
       </c>
       <c r="T74">
-        <v>2.762709416328868</v>
+        <v>2.758142284673921</v>
       </c>
       <c r="U74">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V74">
-        <v>0.05295018707218806</v>
+        <v>0.0551586741096137</v>
       </c>
       <c r="W74">
-        <v>0.2365330251507742</v>
+        <v>0.2265330251507742</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2647509353609403</v>
+        <v>0.2757933705480685</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7404,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2228094212870595</v>
+        <v>0.2154276817582466</v>
       </c>
       <c r="C75">
-        <v>-1106.164995784354</v>
+        <v>-1085.354912873059</v>
       </c>
       <c r="D75">
-        <v>483.3994959343819</v>
+        <v>504.209578845677</v>
       </c>
       <c r="E75">
         <v>-194.9142640603545</v>
@@ -7437,37 +7437,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M75">
-        <v>447.7817915412675</v>
+        <v>429.8531466240802</v>
       </c>
       <c r="N75">
-        <v>-330.8551248746008</v>
+        <v>-312.9264799574135</v>
       </c>
       <c r="O75">
-        <v>-66.17102497492017</v>
+        <v>-62.5852959914827</v>
       </c>
       <c r="P75">
-        <v>-264.6840998996807</v>
+        <v>-250.3411839659308</v>
       </c>
       <c r="Q75">
-        <v>103.8159001003193</v>
+        <v>118.1588160340692</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1852150582743894</v>
+        <v>0.184912319278786</v>
       </c>
       <c r="T75">
-        <v>2.865031987304011</v>
+        <v>2.860295702624807</v>
       </c>
       <c r="U75">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V75">
-        <v>0.05222484204380193</v>
+        <v>0.05440307583413954</v>
       </c>
       <c r="W75">
-        <v>0.2367141856890059</v>
+        <v>0.2267141856890059</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2611242102190096</v>
+        <v>0.2720153791706977</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2248489987314764</v>
+        <v>0.2173672592026635</v>
       </c>
       <c r="C76">
-        <v>-1136.231268804423</v>
+        <v>-1115.614817871281</v>
       </c>
       <c r="D76">
-        <v>477.8930104721041</v>
+        <v>498.5094614052467</v>
       </c>
       <c r="E76">
         <v>-170.3544765025636</v>
@@ -7519,37 +7519,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M76">
-        <v>453.9157886856685</v>
+        <v>435.7415458929032</v>
       </c>
       <c r="N76">
-        <v>-336.9891220190018</v>
+        <v>-318.8148792262365</v>
       </c>
       <c r="O76">
-        <v>-67.39782440380036</v>
+        <v>-63.76297584524731</v>
       </c>
       <c r="P76">
-        <v>-269.5912976152014</v>
+        <v>-255.0519033809892</v>
       </c>
       <c r="Q76">
-        <v>98.90870238479857</v>
+        <v>113.4480966190108</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1905771759003275</v>
+        <v>0.1902627930972009</v>
       </c>
       <c r="T76">
-        <v>2.975225525277242</v>
+        <v>2.970307075802684</v>
       </c>
       <c r="U76">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V76">
-        <v>0.0515191009351019</v>
+        <v>0.05366789913367819</v>
       </c>
       <c r="W76">
-        <v>0.2368904499964746</v>
+        <v>0.2268904499964746</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2575955046755095</v>
+        <v>0.268339495668391</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7568,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2268885761758933</v>
+        <v>0.2193068366470803</v>
       </c>
       <c r="C77">
-        <v>-1166.173504143219</v>
+        <v>-1145.747283289234</v>
       </c>
       <c r="D77">
-        <v>472.510562691099</v>
+        <v>492.9367835450842</v>
       </c>
       <c r="E77">
         <v>-145.7946889447728</v>
@@ -7601,37 +7601,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M77">
-        <v>460.0497858300694</v>
+        <v>441.6299451617262</v>
       </c>
       <c r="N77">
-        <v>-343.1231191634027</v>
+        <v>-324.7032784950595</v>
       </c>
       <c r="O77">
-        <v>-68.62462383268054</v>
+        <v>-64.94065569901191</v>
       </c>
       <c r="P77">
-        <v>-274.4984953307222</v>
+        <v>-259.7626227960476</v>
       </c>
       <c r="Q77">
-        <v>94.00150466927784</v>
+        <v>108.7373772039524</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1963682629363406</v>
+        <v>0.1960413048210889</v>
       </c>
       <c r="T77">
-        <v>3.094234546288332</v>
+        <v>3.089119358834791</v>
       </c>
       <c r="U77">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V77">
-        <v>0.05083217958930054</v>
+        <v>0.05295232714522916</v>
       </c>
       <c r="W77">
-        <v>0.2370620139224108</v>
+        <v>0.2270620139224108</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2541608979465027</v>
+        <v>0.2647616357261457</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7650,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2289281536203102</v>
+        <v>0.2212464140914973</v>
       </c>
       <c r="C78">
-        <v>-1195.995846184641</v>
+        <v>-1175.756535698378</v>
       </c>
       <c r="D78">
-        <v>467.2480082074682</v>
+        <v>487.4873186937311</v>
       </c>
       <c r="E78">
         <v>-121.2349013869818</v>
@@ -7683,37 +7683,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M78">
-        <v>466.1837829744703</v>
+        <v>447.5183444305492</v>
       </c>
       <c r="N78">
-        <v>-349.2571163078036</v>
+        <v>-330.5916777638826</v>
       </c>
       <c r="O78">
-        <v>-69.85142326156073</v>
+        <v>-66.11833555277651</v>
       </c>
       <c r="P78">
-        <v>-279.4056930462429</v>
+        <v>-264.4733422111061</v>
       </c>
       <c r="Q78">
-        <v>89.0943069537571</v>
+        <v>104.0266577888939</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2026419405586881</v>
+        <v>0.2023013591886343</v>
       </c>
       <c r="T78">
-        <v>3.223160985717013</v>
+        <v>3.217832665452908</v>
       </c>
       <c r="U78">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V78">
-        <v>0.05016333512102026</v>
+        <v>0.05225558599858141</v>
       </c>
       <c r="W78">
-        <v>0.2372290630081908</v>
+        <v>0.2272290630081908</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2508166756051013</v>
+        <v>0.261277929992907</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7732,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.230967731064727</v>
+        <v>0.2231859915359141</v>
       </c>
       <c r="C79">
-        <v>-1225.702256715068</v>
+        <v>-1205.646616813122</v>
       </c>
       <c r="D79">
-        <v>462.1013852348319</v>
+        <v>482.1570251367781</v>
       </c>
       <c r="E79">
         <v>-96.67511382919088</v>
@@ -7765,37 +7765,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M79">
-        <v>472.3177801188713</v>
+        <v>453.4067436993722</v>
       </c>
       <c r="N79">
-        <v>-355.3911134522046</v>
+        <v>-336.4800770327055</v>
       </c>
       <c r="O79">
-        <v>-71.07822269044092</v>
+        <v>-67.29601540654112</v>
       </c>
       <c r="P79">
-        <v>-284.3128907617637</v>
+        <v>-269.1840616261644</v>
       </c>
       <c r="Q79">
-        <v>84.1871092382363</v>
+        <v>99.31593837383559</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2094611553655876</v>
+        <v>0.2091057661098793</v>
       </c>
       <c r="T79">
-        <v>3.363298419878622</v>
+        <v>3.357738433516078</v>
       </c>
       <c r="U79">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V79">
-        <v>0.04951186323633169</v>
+        <v>0.05157694202457385</v>
       </c>
       <c r="W79">
-        <v>0.2373917731566778</v>
+        <v>0.2273917731566778</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2475593161816584</v>
+        <v>0.2578847101228693</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7814,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.233007308509144</v>
+        <v>0.225125568980331</v>
       </c>
       <c r="C80">
-        <v>-1255.296524870141</v>
+        <v>-1235.421393487858</v>
       </c>
       <c r="D80">
-        <v>457.0669046375497</v>
+        <v>476.9420360198333</v>
       </c>
       <c r="E80">
         <v>-72.11532627139991</v>
@@ -7847,37 +7847,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M80">
-        <v>478.4517772632722</v>
+        <v>459.2951429681953</v>
       </c>
       <c r="N80">
-        <v>-361.5251105966055</v>
+        <v>-342.3684763015286</v>
       </c>
       <c r="O80">
-        <v>-72.30502211932111</v>
+        <v>-68.47369526030572</v>
       </c>
       <c r="P80">
-        <v>-289.2200884772844</v>
+        <v>-273.8947810412229</v>
       </c>
       <c r="Q80">
-        <v>79.27991152271557</v>
+        <v>94.60521895877713</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2169002987912962</v>
+        <v>0.2165287554785102</v>
       </c>
       <c r="T80">
-        <v>3.516175620782196</v>
+        <v>3.510362907766809</v>
       </c>
       <c r="U80">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V80">
-        <v>0.04887709575894282</v>
+        <v>0.05091569917810496</v>
       </c>
       <c r="W80">
-        <v>0.2375503112500754</v>
+        <v>0.2275503112500754</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2443854787947141</v>
+        <v>0.2545784958905247</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +7896,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2350468859535608</v>
+        <v>0.227065146424748</v>
       </c>
       <c r="C81">
-        <v>-1284.782276438336</v>
+        <v>-1265.084567072164</v>
       </c>
       <c r="D81">
-        <v>452.1409406271462</v>
+        <v>471.8386499933175</v>
       </c>
       <c r="E81">
         <v>-47.55553871360894</v>
@@ -7929,37 +7929,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M81">
-        <v>484.5857744076731</v>
+        <v>465.1835422370183</v>
       </c>
       <c r="N81">
-        <v>-367.6591077410064</v>
+        <v>-348.2568755703516</v>
       </c>
       <c r="O81">
-        <v>-73.53182154820129</v>
+        <v>-69.65137511407032</v>
       </c>
       <c r="P81">
-        <v>-294.1272861928052</v>
+        <v>-278.6055004562813</v>
       </c>
       <c r="Q81">
-        <v>74.37271380719483</v>
+        <v>89.89449954371872</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2250479320670722</v>
+        <v>0.2246586962155821</v>
       </c>
       <c r="T81">
-        <v>3.683612555105158</v>
+        <v>3.677523046231896</v>
       </c>
       <c r="U81">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V81">
-        <v>0.04825839834427266</v>
+        <v>0.05027119665686312</v>
       </c>
       <c r="W81">
-        <v>0.2377048357208553</v>
+        <v>0.2277048357208553</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2412919917213633</v>
+        <v>0.2513559832843155</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +7978,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2370864633979778</v>
+        <v>0.2290047238691648</v>
       </c>
       <c r="C82">
-        <v>-1314.162982569346</v>
+        <v>-1294.639682171753</v>
       </c>
       <c r="D82">
-        <v>447.3200220539273</v>
+        <v>466.8433224515197</v>
       </c>
       <c r="E82">
         <v>-22.99575115581797</v>
@@ -8011,37 +8011,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M82">
-        <v>490.7197715520741</v>
+        <v>471.0719415058413</v>
       </c>
       <c r="N82">
-        <v>-373.7931048854074</v>
+        <v>-354.1452748391746</v>
       </c>
       <c r="O82">
-        <v>-74.75862097708148</v>
+        <v>-70.82905496783494</v>
       </c>
       <c r="P82">
-        <v>-299.0344839083259</v>
+        <v>-283.3162198713397</v>
       </c>
       <c r="Q82">
-        <v>69.46551609167409</v>
+        <v>85.18378012866026</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2340103286704258</v>
+        <v>0.2336016310263612</v>
       </c>
       <c r="T82">
-        <v>3.867793182860416</v>
+        <v>3.86139919854349</v>
       </c>
       <c r="U82">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V82">
-        <v>0.04765516836496925</v>
+        <v>0.04964280669865233</v>
       </c>
       <c r="W82">
-        <v>0.2378554970798657</v>
+        <v>0.2278554970798657</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2382758418248462</v>
+        <v>0.2482140334932617</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8060,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2391260408423947</v>
+        <v>0.2309443013135817</v>
       </c>
       <c r="C83">
-        <v>-1343.441967931229</v>
+        <v>-1324.09013485874</v>
       </c>
       <c r="D83">
-        <v>442.6008242498353</v>
+        <v>461.952657322324</v>
       </c>
       <c r="E83">
         <v>1.564036401972999</v>
@@ -8093,37 +8093,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M83">
-        <v>496.853768696475</v>
+        <v>476.9603407746644</v>
       </c>
       <c r="N83">
-        <v>-379.9271020298083</v>
+        <v>-360.0336741079977</v>
       </c>
       <c r="O83">
-        <v>-75.98542040596168</v>
+        <v>-72.00673482159954</v>
       </c>
       <c r="P83">
-        <v>-303.9416816238466</v>
+        <v>-288.0269392863981</v>
       </c>
       <c r="Q83">
-        <v>64.55831837615335</v>
+        <v>80.47306071360185</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2439161354425535</v>
+        <v>0.2434859273961697</v>
       </c>
       <c r="T83">
-        <v>4.071361245116228</v>
+        <v>4.064630735308937</v>
       </c>
       <c r="U83">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V83">
-        <v>0.04706683295305605</v>
+        <v>0.04902993254187884</v>
       </c>
       <c r="W83">
-        <v>0.2380024384053204</v>
+        <v>0.2280024384053204</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2353341647652802</v>
+        <v>0.2451496627093942</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8142,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2411656182868115</v>
+        <v>0.2328838787579986</v>
       </c>
       <c r="C84">
-        <v>-1372.622418356602</v>
+        <v>-1353.439180371193</v>
       </c>
       <c r="D84">
-        <v>437.9801613822526</v>
+        <v>457.1633993676618</v>
       </c>
       <c r="E84">
         <v>26.12382395976374</v>
@@ -8175,37 +8175,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M84">
-        <v>502.9877658408759</v>
+        <v>482.8487400434873</v>
       </c>
       <c r="N84">
-        <v>-386.0610991742092</v>
+        <v>-365.9220733768207</v>
       </c>
       <c r="O84">
-        <v>-77.21221983484185</v>
+        <v>-73.18441467536414</v>
       </c>
       <c r="P84">
-        <v>-308.8488793393674</v>
+        <v>-292.7376587014566</v>
       </c>
       <c r="Q84">
-        <v>59.65112066063261</v>
+        <v>75.76234129854345</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2549225874115842</v>
+        <v>0.2544684789181791</v>
       </c>
       <c r="T84">
-        <v>4.297547980956018</v>
+        <v>4.290443553937211</v>
       </c>
       <c r="U84">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V84">
-        <v>0.04649284718533585</v>
+        <v>0.04843200653527056</v>
       </c>
       <c r="W84">
-        <v>0.2381457957960078</v>
+        <v>0.2281457957960078</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2324642359266792</v>
+        <v>0.2421600326763528</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8224,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2432051957312284</v>
+        <v>0.2348234562024155</v>
       </c>
       <c r="C85">
-        <v>-1401.707388014836</v>
+        <v>-1382.689940338656</v>
       </c>
       <c r="D85">
-        <v>433.4549792818096</v>
+        <v>452.4724269579892</v>
       </c>
       <c r="E85">
         <v>50.68361151755471</v>
@@ -8257,37 +8257,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M85">
-        <v>509.1217629852769</v>
+        <v>488.7371393123104</v>
       </c>
       <c r="N85">
-        <v>-392.1950963186102</v>
+        <v>-371.8104726456437</v>
       </c>
       <c r="O85">
-        <v>-78.43901926372205</v>
+        <v>-74.36209452912874</v>
       </c>
       <c r="P85">
-        <v>-313.7560770548881</v>
+        <v>-297.448378116515</v>
       </c>
       <c r="Q85">
-        <v>54.74392294511188</v>
+        <v>71.05162188348504</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.267223916082854</v>
+        <v>0.2667430953251309</v>
       </c>
       <c r="T85">
-        <v>4.550344921012256</v>
+        <v>4.542822586521754</v>
       </c>
       <c r="U85">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V85">
-        <v>0.04593269239997036</v>
+        <v>0.04784848838424321</v>
       </c>
       <c r="W85">
-        <v>0.2382856987917389</v>
+        <v>0.2282856987917389</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2296634619998518</v>
+        <v>0.239242441921216</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8306,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2452447731756453</v>
+        <v>0.2367630336468324</v>
       </c>
       <c r="C86">
-        <v>-1430.699806144172</v>
+        <v>-1411.845409567337</v>
       </c>
       <c r="D86">
-        <v>429.0223487102642</v>
+        <v>447.8767452870994</v>
       </c>
       <c r="E86">
         <v>75.24339907534545</v>
@@ -8339,37 +8339,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M86">
-        <v>515.2557601296777</v>
+        <v>494.6255385811334</v>
       </c>
       <c r="N86">
-        <v>-398.329093463011</v>
+        <v>-377.6988719144667</v>
       </c>
       <c r="O86">
-        <v>-79.66581869260222</v>
+        <v>-75.53977438289334</v>
       </c>
       <c r="P86">
-        <v>-318.6632747704088</v>
+        <v>-302.1590975315734</v>
       </c>
       <c r="Q86">
-        <v>49.8367252295912</v>
+        <v>66.34090246842663</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2810629108380321</v>
+        <v>0.2805520387829514</v>
       </c>
       <c r="T86">
-        <v>4.834741478575519</v>
+        <v>4.826748998179361</v>
       </c>
       <c r="U86">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V86">
-        <v>0.04538587463330405</v>
+        <v>0.04727886352252603</v>
       </c>
       <c r="W86">
-        <v>0.2384222707637621</v>
+        <v>0.2284222707637621</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2269293731665203</v>
+        <v>0.2363943176126301</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8388,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2472843506200622</v>
+        <v>0.2387026110912493</v>
       </c>
       <c r="C87">
-        <v>-1459.602483374969</v>
+        <v>-1440.908462415958</v>
       </c>
       <c r="D87">
-        <v>424.6794590372581</v>
+        <v>443.3734799962691</v>
       </c>
       <c r="E87">
         <v>99.80318663313642</v>
@@ -8421,37 +8421,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M87">
-        <v>521.3897572740786</v>
+        <v>500.5139378499564</v>
       </c>
       <c r="N87">
-        <v>-404.463090607412</v>
+        <v>-383.5872711832897</v>
       </c>
       <c r="O87">
-        <v>-80.8926181214824</v>
+        <v>-76.71745423665794</v>
       </c>
       <c r="P87">
-        <v>-323.5704724859296</v>
+        <v>-306.8698169466318</v>
       </c>
       <c r="Q87">
-        <v>44.9295275140704</v>
+        <v>61.63018305336823</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.296747104893901</v>
+        <v>0.2962021747018149</v>
       </c>
       <c r="T87">
-        <v>5.15705757714722</v>
+        <v>5.148532264724652</v>
       </c>
       <c r="U87">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V87">
-        <v>0.04485192316702988</v>
+        <v>0.0467226415987316</v>
       </c>
       <c r="W87">
-        <v>0.2385556292776201</v>
+        <v>0.22855562927762</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2242596158351494</v>
+        <v>0.233613207993658</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8470,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2493239280644791</v>
+        <v>0.2406421885356662</v>
       </c>
       <c r="C88">
-        <v>-1488.418117672733</v>
+        <v>-1469.881858790794</v>
       </c>
       <c r="D88">
-        <v>420.4236122972856</v>
+        <v>438.9598711792243</v>
       </c>
       <c r="E88">
         <v>124.3629741909274</v>
@@ -8503,37 +8503,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M88">
-        <v>527.5237544184796</v>
+        <v>506.4023371187794</v>
       </c>
       <c r="N88">
-        <v>-410.5970877518129</v>
+        <v>-389.4756704521128</v>
       </c>
       <c r="O88">
-        <v>-82.11941755036258</v>
+        <v>-77.89513409042256</v>
       </c>
       <c r="P88">
-        <v>-328.4776702014503</v>
+        <v>-311.5805363616902</v>
       </c>
       <c r="Q88">
-        <v>40.02232979854966</v>
+        <v>56.91946363830982</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3146718981006082</v>
+        <v>0.3140880443233731</v>
       </c>
       <c r="T88">
-        <v>5.525418832657736</v>
+        <v>5.516284569347842</v>
       </c>
       <c r="U88">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V88">
-        <v>0.04433038917671558</v>
+        <v>0.04617935506851379</v>
       </c>
       <c r="W88">
-        <v>0.2386858864306906</v>
+        <v>0.2286858864306906</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2216519458835779</v>
+        <v>0.2308967753425689</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8552,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.251363505508896</v>
+        <v>0.2425817659800831</v>
       </c>
       <c r="C89">
-        <v>-1517.149299927355</v>
+        <v>-1498.76824978617</v>
       </c>
       <c r="D89">
-        <v>416.2522176004546</v>
+        <v>434.6332677416397</v>
       </c>
       <c r="E89">
         <v>148.9227617487184</v>
@@ -8585,37 +8585,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M89">
-        <v>533.6577515628805</v>
+        <v>512.2907363876025</v>
       </c>
       <c r="N89">
-        <v>-416.7310848962139</v>
+        <v>-395.3640697209358</v>
       </c>
       <c r="O89">
-        <v>-83.34621697924278</v>
+        <v>-79.07281394418716</v>
       </c>
       <c r="P89">
-        <v>-333.3848679169711</v>
+        <v>-316.2912557767486</v>
       </c>
       <c r="Q89">
-        <v>35.11513208302893</v>
+        <v>52.20874422325136</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.335354351800655</v>
+        <v>0.3347255861944018</v>
       </c>
       <c r="T89">
-        <v>5.950451050554485</v>
+        <v>5.940614151605367</v>
       </c>
       <c r="U89">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V89">
-        <v>0.04382084447353494</v>
+        <v>0.04564855788381823</v>
       </c>
       <c r="W89">
-        <v>0.2388131491664492</v>
+        <v>0.2288131491664492</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2191042223676747</v>
+        <v>0.2282427894190912</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2534030829533129</v>
+        <v>0.2445213434245</v>
       </c>
       <c r="C90">
-        <v>-1545.798519212888</v>
+        <v>-1527.570182994638</v>
       </c>
       <c r="D90">
-        <v>412.1627858727124</v>
+        <v>430.3911220909626</v>
       </c>
       <c r="E90">
         <v>173.4825493065093</v>
@@ -8667,37 +8667,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M90">
-        <v>539.7917487072815</v>
+        <v>518.1791356564255</v>
       </c>
       <c r="N90">
-        <v>-422.8650820406148</v>
+        <v>-401.2524689897588</v>
       </c>
       <c r="O90">
-        <v>-84.57301640812297</v>
+        <v>-80.25049379795178</v>
       </c>
       <c r="P90">
-        <v>-338.2920656324919</v>
+        <v>-321.001975191807</v>
       </c>
       <c r="Q90">
-        <v>30.20793436750813</v>
+        <v>47.49802480819295</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3594838811173763</v>
+        <v>0.3588027183772686</v>
       </c>
       <c r="T90">
-        <v>6.446321971434027</v>
+        <v>6.435665330905815</v>
       </c>
       <c r="U90">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V90">
-        <v>0.04332288033179022</v>
+        <v>0.04512982427150211</v>
       </c>
       <c r="W90">
-        <v>0.2389375195673042</v>
+        <v>0.2289375195673042</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2166144016589511</v>
+        <v>0.2256491213575106</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8716,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2554426603977298</v>
+        <v>0.2464609208689169</v>
       </c>
       <c r="C91">
-        <v>-1574.368167740289</v>
+        <v>-1556.290107509192</v>
       </c>
       <c r="D91">
-        <v>408.1529249031026</v>
+        <v>426.2309851341994</v>
       </c>
       <c r="E91">
         <v>198.0423368643003</v>
@@ -8749,37 +8749,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M91">
-        <v>545.9257458516824</v>
+        <v>524.0675349252485</v>
       </c>
       <c r="N91">
-        <v>-428.9990791850158</v>
+        <v>-407.1408682585819</v>
       </c>
       <c r="O91">
-        <v>-85.79981583700317</v>
+        <v>-81.42817365171638</v>
       </c>
       <c r="P91">
-        <v>-343.1992633480126</v>
+        <v>-325.7126946068655</v>
       </c>
       <c r="Q91">
-        <v>25.30073665198739</v>
+        <v>42.78730539313449</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3880005975825923</v>
+        <v>0.3872575109570204</v>
       </c>
       <c r="T91">
-        <v>7.032351241564393</v>
+        <v>7.020725815533618</v>
       </c>
       <c r="U91">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V91">
-        <v>0.04283610639547797</v>
+        <v>0.04462274759429422</v>
       </c>
       <c r="W91">
-        <v>0.2390590951276906</v>
+        <v>0.2290590951276906</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2141805319773898</v>
+        <v>0.223113737971471</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2574822378421467</v>
+        <v>0.2484004983133338</v>
       </c>
       <c r="C92">
-        <v>-1602.86054552384</v>
+        <v>-1584.930378638149</v>
       </c>
       <c r="D92">
-        <v>404.2203346773422</v>
+        <v>422.1505015630322</v>
       </c>
       <c r="E92">
         <v>222.6021244220908</v>
@@ -8831,37 +8831,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M92">
-        <v>552.0597429960833</v>
+        <v>529.9559341940715</v>
       </c>
       <c r="N92">
-        <v>-435.1330763294166</v>
+        <v>-413.0292675274048</v>
       </c>
       <c r="O92">
-        <v>-87.02661526588332</v>
+        <v>-82.60585350548097</v>
       </c>
       <c r="P92">
-        <v>-348.1064610635333</v>
+        <v>-330.4234140219238</v>
       </c>
       <c r="Q92">
-        <v>20.39353893646671</v>
+        <v>38.0765859780762</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4222206573408516</v>
+        <v>0.4214032620527224</v>
       </c>
       <c r="T92">
-        <v>7.735586365720832</v>
+        <v>7.72279839708698</v>
       </c>
       <c r="U92">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V92">
-        <v>0.04236014965775045</v>
+        <v>0.04412693928769096</v>
       </c>
       <c r="W92">
-        <v>0.2391779690089572</v>
+        <v>0.2291779690089573</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2118007482887522</v>
+        <v>0.2206346964384548</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +8880,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2595218152865636</v>
+        <v>0.2503400757577506</v>
       </c>
       <c r="C93">
-        <v>-1631.277864780382</v>
+        <v>-1613.49326235178</v>
       </c>
       <c r="D93">
-        <v>400.3628029785909</v>
+        <v>418.1474054071929</v>
       </c>
       <c r="E93">
         <v>247.1619119798818</v>
@@ -8913,37 +8913,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M93">
-        <v>558.1937401404842</v>
+        <v>535.8443334628945</v>
       </c>
       <c r="N93">
-        <v>-441.2670734738176</v>
+        <v>-418.9176667962278</v>
       </c>
       <c r="O93">
-        <v>-88.25341469476352</v>
+        <v>-83.78353335924557</v>
       </c>
       <c r="P93">
-        <v>-353.013658779054</v>
+        <v>-335.1341334369823</v>
       </c>
       <c r="Q93">
-        <v>15.48634122094597</v>
+        <v>33.36586656301773</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4640451748231685</v>
+        <v>0.4631369578363583</v>
       </c>
       <c r="T93">
-        <v>8.595095961912037</v>
+        <v>8.580887107874423</v>
       </c>
       <c r="U93">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V93">
-        <v>0.04189465350766527</v>
+        <v>0.0436420278669471</v>
       </c>
       <c r="W93">
-        <v>0.2392942302774488</v>
+        <v>0.2292942302774488</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2094732675383264</v>
+        <v>0.2182101393347355</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +8962,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2615613927309805</v>
+        <v>0.2522796532021676</v>
       </c>
       <c r="C94">
-        <v>-1659.622254079026</v>
+        <v>-1641.980939478308</v>
       </c>
       <c r="D94">
-        <v>396.5782012377374</v>
+        <v>414.2195158384559</v>
       </c>
       <c r="E94">
         <v>271.7216995376727</v>
@@ -8995,37 +8995,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M94">
-        <v>564.3277372848851</v>
+        <v>541.7327327317174</v>
       </c>
       <c r="N94">
-        <v>-447.4010706182184</v>
+        <v>-424.8060660650507</v>
       </c>
       <c r="O94">
-        <v>-89.48021412364369</v>
+        <v>-84.96121321301015</v>
       </c>
       <c r="P94">
-        <v>-357.9208564945747</v>
+        <v>-339.8448528520406</v>
       </c>
       <c r="Q94">
-        <v>10.57914350542529</v>
+        <v>28.65514714795938</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.5163258216760647</v>
+        <v>0.5153040775659031</v>
       </c>
       <c r="T94">
-        <v>9.669482957151045</v>
+        <v>9.653497996358729</v>
       </c>
       <c r="U94">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V94">
-        <v>0.0414392768391037</v>
+        <v>0.04316765799882812</v>
       </c>
       <c r="W94">
-        <v>0.2394079641270601</v>
+        <v>0.2294079641270601</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2071963841955184</v>
+        <v>0.2158382899941406</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9044,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2636009701753974</v>
+        <v>0.2542192306465845</v>
       </c>
       <c r="C95">
-        <v>-1687.895762257715</v>
+        <v>-1670.395509665634</v>
       </c>
       <c r="D95">
-        <v>392.8644806168396</v>
+        <v>410.3647332089205</v>
       </c>
       <c r="E95">
         <v>296.2814870954637</v>
@@ -9077,37 +9077,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M95">
-        <v>570.461734429286</v>
+        <v>547.6211320005405</v>
       </c>
       <c r="N95">
-        <v>-453.5350677626193</v>
+        <v>-430.6944653338738</v>
       </c>
       <c r="O95">
-        <v>-90.70701355252388</v>
+        <v>-86.13889306677476</v>
       </c>
       <c r="P95">
-        <v>-362.8280542100955</v>
+        <v>-344.555572267099</v>
       </c>
       <c r="Q95">
-        <v>5.671945789904498</v>
+        <v>23.94442773290098</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5835437962012168</v>
+        <v>0.5823760886467465</v>
       </c>
       <c r="T95">
-        <v>11.05083766531548</v>
+        <v>11.03256913869569</v>
       </c>
       <c r="U95">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V95">
-        <v>0.04099369321717786</v>
+        <v>0.04270348963324933</v>
       </c>
       <c r="W95">
-        <v>0.2395192520874325</v>
+        <v>0.2295192520874325</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2049684660858893</v>
+        <v>0.2135174481662466</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9126,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2656405476198143</v>
+        <v>0.2561588080910013</v>
       </c>
       <c r="C96">
-        <v>-1716.100362121762</v>
+        <v>-1698.73899512388</v>
       </c>
       <c r="D96">
-        <v>389.2196683105839</v>
+        <v>406.5810353084655</v>
       </c>
       <c r="E96">
         <v>320.8412746532547</v>
@@ -9159,37 +9159,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M96">
-        <v>576.595731573687</v>
+        <v>553.5095312693635</v>
       </c>
       <c r="N96">
-        <v>-459.6690649070203</v>
+        <v>-436.5828646026968</v>
       </c>
       <c r="O96">
-        <v>-91.93381298140406</v>
+        <v>-87.31657292053937</v>
       </c>
       <c r="P96">
-        <v>-367.7352519256162</v>
+        <v>-349.2662916821574</v>
       </c>
       <c r="Q96">
-        <v>0.7647480743837605</v>
+        <v>19.23370831784257</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.6731677622347529</v>
+        <v>0.6718054367545379</v>
       </c>
       <c r="T96">
-        <v>12.89264394286806</v>
+        <v>12.87133066181164</v>
       </c>
       <c r="U96">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V96">
-        <v>0.04055759009784617</v>
+        <v>0.04224919719034241</v>
       </c>
       <c r="W96">
-        <v>0.2396281722188607</v>
+        <v>0.2296281722188608</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2027879504892308</v>
+        <v>0.2112459859517121</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9208,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2676801250642312</v>
+        <v>0.2580983855354183</v>
       </c>
       <c r="C97">
-        <v>-1744.237953938406</v>
+        <v>-1727.013344162782</v>
       </c>
       <c r="D97">
-        <v>385.6418640517306</v>
+        <v>402.8664738273542</v>
       </c>
       <c r="E97">
         <v>345.4010622110457</v>
@@ -9241,37 +9241,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M97">
-        <v>582.7297287180879</v>
+        <v>559.3979305381865</v>
       </c>
       <c r="N97">
-        <v>-465.8030620514213</v>
+        <v>-442.4712638715199</v>
       </c>
       <c r="O97">
-        <v>-93.16061241028426</v>
+        <v>-88.49425277430397</v>
       </c>
       <c r="P97">
-        <v>-372.642449641137</v>
+        <v>-353.9770110972159</v>
       </c>
       <c r="Q97">
-        <v>-4.142449641136977</v>
+        <v>14.52298890278411</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.798641314681704</v>
+        <v>0.7970065241054456</v>
       </c>
       <c r="T97">
-        <v>15.47117273144168</v>
+        <v>15.44559679417398</v>
       </c>
       <c r="U97">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V97">
-        <v>0.04013066809681621</v>
+        <v>0.04180446879886512</v>
       </c>
       <c r="W97">
-        <v>0.2397347992948905</v>
+        <v>0.2297347992948905</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.200653340484081</v>
+        <v>0.2090223439943256</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9290,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.269719702508648</v>
+        <v>0.2600379629798351</v>
       </c>
       <c r="C98">
-        <v>-1772.310368740386</v>
+        <v>-1755.220434536932</v>
       </c>
       <c r="D98">
-        <v>382.1292368075407</v>
+        <v>399.2191710109955</v>
       </c>
       <c r="E98">
         <v>369.9608497688362</v>
@@ -9323,37 +9323,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M98">
-        <v>588.8637258624888</v>
+        <v>565.2863298070095</v>
       </c>
       <c r="N98">
-        <v>-471.9370591958221</v>
+        <v>-448.3596631403428</v>
       </c>
       <c r="O98">
-        <v>-94.38741183916443</v>
+        <v>-89.67193262806856</v>
       </c>
       <c r="P98">
-        <v>-377.5496473566577</v>
+        <v>-358.6877305122742</v>
       </c>
       <c r="Q98">
-        <v>-9.049647356657658</v>
+        <v>9.812269487725757</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.9868516433521279</v>
+        <v>0.9848081551318051</v>
       </c>
       <c r="T98">
-        <v>19.33896591430206</v>
+        <v>19.30699599271743</v>
       </c>
       <c r="U98">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V98">
-        <v>0.03971264030414105</v>
+        <v>0.04136900558221028</v>
       </c>
       <c r="W98">
-        <v>0.239839204973503</v>
+        <v>0.229839204973503</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1985632015207053</v>
+        <v>0.2068450279110514</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9372,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2717592799530649</v>
+        <v>0.261977540424252</v>
       </c>
       <c r="C99">
-        <v>-1800.319371450601</v>
+        <v>-1783.362076610932</v>
       </c>
       <c r="D99">
-        <v>378.6800216551169</v>
+        <v>395.6373164947856</v>
       </c>
       <c r="E99">
         <v>394.5206373266271</v>
@@ -9405,37 +9405,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M99">
-        <v>594.9977230068897</v>
+        <v>571.1747290758325</v>
       </c>
       <c r="N99">
-        <v>-478.071056340223</v>
+        <v>-454.2480624091658</v>
       </c>
       <c r="O99">
-        <v>-95.61421126804461</v>
+        <v>-90.84961248183316</v>
       </c>
       <c r="P99">
-        <v>-382.4568450721785</v>
+        <v>-363.3984499273326</v>
       </c>
       <c r="Q99">
-        <v>-13.95684507217845</v>
+        <v>5.101550072667351</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.300535524469504</v>
+        <v>1.297810873509073</v>
       </c>
       <c r="T99">
-        <v>25.78528788573608</v>
+        <v>25.74266132362324</v>
       </c>
       <c r="U99">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V99">
-        <v>0.03930323164121176</v>
+        <v>0.04094252098857925</v>
       </c>
       <c r="W99">
-        <v>0.2399414579577111</v>
+        <v>0.2299414579577111</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1965161582060587</v>
+        <v>0.2047126049428962</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9454,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2737988573974819</v>
+        <v>0.2639171178686689</v>
       </c>
       <c r="C100">
-        <v>-1828.266663839053</v>
+        <v>-1811.440016355683</v>
       </c>
       <c r="D100">
-        <v>375.2925168244563</v>
+        <v>392.1191643078264</v>
       </c>
       <c r="E100">
         <v>419.0804248844181</v>
@@ -9487,37 +9487,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M100">
-        <v>601.1317201512907</v>
+        <v>577.0631283446555</v>
       </c>
       <c r="N100">
-        <v>-484.205053484624</v>
+        <v>-460.1364616779888</v>
       </c>
       <c r="O100">
-        <v>-96.8410106969248</v>
+        <v>-92.02729233559778</v>
       </c>
       <c r="P100">
-        <v>-387.3640427876992</v>
+        <v>-368.1091693423911</v>
       </c>
       <c r="Q100">
-        <v>-18.86404278769919</v>
+        <v>0.3908306576089444</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.927903286704256</v>
+        <v>1.92381631026361</v>
       </c>
       <c r="T100">
-        <v>38.67793182860412</v>
+        <v>38.61399198543486</v>
       </c>
       <c r="U100">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V100">
-        <v>0.03890217825711775</v>
+        <v>0.04052474016216517</v>
       </c>
       <c r="W100">
-        <v>0.2400416241463232</v>
+        <v>0.2300416241463231</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1945108912855887</v>
+        <v>0.2026237008108258</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9536,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2758384348418987</v>
+        <v>0.2658566953130858</v>
       </c>
       <c r="C101">
-        <v>-1856.153887322495</v>
+        <v>-1839.455938186203</v>
       </c>
       <c r="D101">
-        <v>371.9650808988047</v>
+        <v>388.6630300350974</v>
       </c>
       <c r="E101">
         <v>443.6402124422091</v>
@@ -9569,37 +9569,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M101">
-        <v>607.2657172956916</v>
+        <v>582.9515276134786</v>
       </c>
       <c r="N101">
-        <v>-490.3390506290249</v>
+        <v>-466.0248609468119</v>
       </c>
       <c r="O101">
-        <v>-98.067810125805</v>
+        <v>-93.20497218936238</v>
       </c>
       <c r="P101">
-        <v>-392.2712405032199</v>
+        <v>-372.8198887574495</v>
       </c>
       <c r="Q101">
-        <v>-23.77124050321993</v>
+        <v>-4.319888757449519</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.810006573408512</v>
+        <v>3.80183262052722</v>
       </c>
       <c r="T101">
-        <v>77.35586365720825</v>
+        <v>77.22798397086973</v>
       </c>
       <c r="U101">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V101">
-        <v>0.03850922696159131</v>
+        <v>0.04011539935244633</v>
       </c>
       <c r="W101">
-        <v>0.2401397667755693</v>
+        <v>0.2301397667755693</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.1925461348079566</v>
+        <v>0.2005769967622316</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/finland/finland_air_transport.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_air_transport.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08491369717164138</v>
+        <v>0.0848115317328316</v>
       </c>
       <c r="C2">
-        <v>2389.948365266387</v>
+        <v>2371.115086764689</v>
       </c>
       <c r="D2">
-        <v>2186.648365266386</v>
+        <v>2192.37487432248</v>
       </c>
       <c r="E2">
-        <v>-1987.778755779091</v>
+        <v>-1963.2189682213</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>24.55978755779091</v>
       </c>
       <c r="G2">
         <v>203.3</v>
@@ -1451,28 +1451,28 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.332558676852802</v>
       </c>
       <c r="N2">
-        <v>116.9266666666667</v>
+        <v>115.5941079898139</v>
       </c>
       <c r="O2">
-        <v>23.38533333333334</v>
+        <v>23.11882159796278</v>
       </c>
       <c r="P2">
-        <v>93.54133333333334</v>
+        <v>92.4752863918511</v>
       </c>
       <c r="Q2">
-        <v>462.0413333333333</v>
+        <v>460.9752863918511</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08491369717164138</v>
+        <v>0.08522976745181625</v>
       </c>
       <c r="T2">
-        <v>0.8042187817285175</v>
+        <v>0.8107175193586469</v>
       </c>
       <c r="U2">
         <v>0.05425774444168939</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>87.74597974388688</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0848115317328316</v>
+        <v>0.08470936629402183</v>
       </c>
       <c r="C3">
-        <v>2371.115086764689</v>
+        <v>2352.311880781065</v>
       </c>
       <c r="D3">
-        <v>2192.37487432248</v>
+        <v>2198.131455896646</v>
       </c>
       <c r="E3">
-        <v>-1963.2189682213</v>
+        <v>-1938.659180663509</v>
       </c>
       <c r="F3">
-        <v>24.55978755779091</v>
+        <v>49.11957511558182</v>
       </c>
       <c r="G3">
         <v>203.3</v>
@@ -1533,28 +1533,28 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M3">
-        <v>1.332558676852802</v>
+        <v>2.665117353705604</v>
       </c>
       <c r="N3">
-        <v>115.5941079898139</v>
+        <v>114.2615493129611</v>
       </c>
       <c r="O3">
-        <v>23.11882159796278</v>
+        <v>22.85230986259221</v>
       </c>
       <c r="P3">
-        <v>92.4752863918511</v>
+        <v>91.40923945036886</v>
       </c>
       <c r="Q3">
-        <v>460.9752863918511</v>
+        <v>459.9092394503689</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08522976745181625</v>
+        <v>0.08555228814587225</v>
       </c>
       <c r="T3">
-        <v>0.8107175193586469</v>
+        <v>0.8173488842873504</v>
       </c>
       <c r="U3">
         <v>0.05425774444168939</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>87.74597974388688</v>
+        <v>43.87298987194344</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08470936629402183</v>
+        <v>0.08460720085521205</v>
       </c>
       <c r="C4">
-        <v>2352.311880781065</v>
+        <v>2333.538984825972</v>
       </c>
       <c r="D4">
-        <v>2198.131455896646</v>
+        <v>2203.918347499345</v>
       </c>
       <c r="E4">
-        <v>-1938.659180663509</v>
+        <v>-1914.099393105718</v>
       </c>
       <c r="F4">
-        <v>49.11957511558182</v>
+        <v>73.67936267337272</v>
       </c>
       <c r="G4">
         <v>203.3</v>
@@ -1615,28 +1615,28 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M4">
-        <v>2.665117353705604</v>
+        <v>3.997676030558405</v>
       </c>
       <c r="N4">
-        <v>114.2615493129611</v>
+        <v>112.9289906361083</v>
       </c>
       <c r="O4">
-        <v>22.85230986259221</v>
+        <v>22.58579812722165</v>
       </c>
       <c r="P4">
-        <v>91.40923945036886</v>
+        <v>90.34319250888662</v>
       </c>
       <c r="Q4">
-        <v>459.9092394503689</v>
+        <v>458.8431925088866</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08555228814587225</v>
+        <v>0.08588145875114589</v>
       </c>
       <c r="T4">
-        <v>0.8173488842873504</v>
+        <v>0.8241169783898415</v>
       </c>
       <c r="U4">
         <v>0.05425774444168939</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>43.87298987194344</v>
+        <v>29.24865991462897</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08460720085521205</v>
+        <v>0.08450503541640231</v>
       </c>
       <c r="C5">
-        <v>2333.538984825972</v>
+        <v>2314.796638917587</v>
       </c>
       <c r="D5">
-        <v>2203.918347499345</v>
+        <v>2209.735789148751</v>
       </c>
       <c r="E5">
-        <v>-1914.099393105718</v>
+        <v>-1889.539605547927</v>
       </c>
       <c r="F5">
-        <v>73.67936267337272</v>
+        <v>98.23915023116365</v>
       </c>
       <c r="G5">
         <v>203.3</v>
@@ -1697,28 +1697,28 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M5">
-        <v>3.997676030558405</v>
+        <v>5.330234707411209</v>
       </c>
       <c r="N5">
-        <v>112.9289906361083</v>
+        <v>111.5964319592555</v>
       </c>
       <c r="O5">
-        <v>22.58579812722165</v>
+        <v>22.31928639185109</v>
       </c>
       <c r="P5">
-        <v>90.34319250888662</v>
+        <v>89.27714556740438</v>
       </c>
       <c r="Q5">
-        <v>458.8431925088866</v>
+        <v>457.7771455674044</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08588145875114589</v>
+        <v>0.08621748707736275</v>
       </c>
       <c r="T5">
-        <v>0.8241169783898415</v>
+        <v>0.8310260744528014</v>
       </c>
       <c r="U5">
         <v>0.05425774444168939</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>29.24865991462897</v>
+        <v>21.93649493597172</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08450503541640231</v>
+        <v>0.08440286997759253</v>
       </c>
       <c r="C6">
-        <v>2314.796638917587</v>
+        <v>2296.085085614999</v>
       </c>
       <c r="D6">
-        <v>2209.735789148751</v>
+        <v>2215.584023403953</v>
       </c>
       <c r="E6">
-        <v>-1889.539605547927</v>
+        <v>-1864.979817990136</v>
       </c>
       <c r="F6">
-        <v>98.23915023116365</v>
+        <v>122.7989377889546</v>
       </c>
       <c r="G6">
         <v>203.3</v>
@@ -1779,28 +1779,28 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M6">
-        <v>5.330234707411209</v>
+        <v>6.662793384264011</v>
       </c>
       <c r="N6">
-        <v>111.5964319592555</v>
+        <v>110.2638732824027</v>
       </c>
       <c r="O6">
-        <v>22.31928639185109</v>
+        <v>22.05277465648054</v>
       </c>
       <c r="P6">
-        <v>89.27714556740438</v>
+        <v>88.21109862592213</v>
       </c>
       <c r="Q6">
-        <v>457.7771455674044</v>
+        <v>456.7110986259221</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08621748707736275</v>
+        <v>0.08656058968413152</v>
       </c>
       <c r="T6">
-        <v>0.8310260744528014</v>
+        <v>0.8380806251697182</v>
       </c>
       <c r="U6">
         <v>0.05425774444168939</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>21.93649493597172</v>
+        <v>17.54919594877738</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08440286997759253</v>
+        <v>0.08430070453878276</v>
       </c>
       <c r="C7">
-        <v>2296.085085614999</v>
+        <v>2277.404570051905</v>
       </c>
       <c r="D7">
-        <v>2215.584023403953</v>
+        <v>2221.46329539865</v>
       </c>
       <c r="E7">
-        <v>-1864.979817990136</v>
+        <v>-1840.420030432345</v>
       </c>
       <c r="F7">
-        <v>122.7989377889546</v>
+        <v>147.3587253467455</v>
       </c>
       <c r="G7">
         <v>203.3</v>
@@ -1861,28 +1861,28 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M7">
-        <v>6.662793384264011</v>
+        <v>7.995352061116813</v>
       </c>
       <c r="N7">
-        <v>110.2638732824027</v>
+        <v>108.9313146055499</v>
       </c>
       <c r="O7">
-        <v>22.05277465648054</v>
+        <v>21.78626292110997</v>
       </c>
       <c r="P7">
-        <v>88.21109862592213</v>
+        <v>87.14505168443989</v>
       </c>
       <c r="Q7">
-        <v>456.7110986259221</v>
+        <v>455.6450516844399</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08656058968413152</v>
+        <v>0.08691099234636349</v>
       </c>
       <c r="T7">
-        <v>0.8380806251697182</v>
+        <v>0.8452852727103992</v>
       </c>
       <c r="U7">
         <v>0.05425774444168939</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>17.54919594877738</v>
+        <v>14.62432995731448</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08430070453878276</v>
+        <v>0.08428253909997301</v>
       </c>
       <c r="C8">
-        <v>2277.404570051905</v>
+        <v>2253.893410170574</v>
       </c>
       <c r="D8">
-        <v>2221.46329539865</v>
+        <v>2222.51192307511</v>
       </c>
       <c r="E8">
-        <v>-1840.420030432346</v>
+        <v>-1815.860242874555</v>
       </c>
       <c r="F8">
-        <v>147.3587253467454</v>
+        <v>171.9185129045364</v>
       </c>
       <c r="G8">
         <v>203.3</v>
@@ -1943,45 +1943,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M8">
-        <v>7.995352061116811</v>
+        <v>9.585788507326416</v>
       </c>
       <c r="N8">
-        <v>108.9313146055499</v>
+        <v>107.3408781593403</v>
       </c>
       <c r="O8">
-        <v>21.78626292110998</v>
+        <v>21.46817563186805</v>
       </c>
       <c r="P8">
-        <v>87.14505168443989</v>
+        <v>85.87270252747221</v>
       </c>
       <c r="Q8">
-        <v>455.6450516844399</v>
+        <v>454.3727025274722</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08691099234636349</v>
+        <v>0.08726893054971871</v>
       </c>
       <c r="T8">
-        <v>0.8452852727103992</v>
+        <v>0.8526448589078691</v>
       </c>
       <c r="U8">
-        <v>0.05425774444168939</v>
+        <v>0.05575774444168938</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.04340619555335151</v>
+        <v>0.04460619555335151</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>14.62432995731448</v>
+        <v>12.1979184682929</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08428253909997301</v>
+        <v>0.08419237366116322</v>
       </c>
       <c r="C9">
-        <v>2253.893410170574</v>
+        <v>2234.553246816606</v>
       </c>
       <c r="D9">
-        <v>2222.51192307511</v>
+        <v>2227.731547278933</v>
       </c>
       <c r="E9">
-        <v>-1815.860242874555</v>
+        <v>-1791.300455316764</v>
       </c>
       <c r="F9">
-        <v>171.9185129045364</v>
+        <v>196.4783004623273</v>
       </c>
       <c r="G9">
         <v>203.3</v>
@@ -2025,28 +2025,28 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M9">
-        <v>9.585788507326418</v>
+        <v>10.95518686551591</v>
       </c>
       <c r="N9">
-        <v>107.3408781593403</v>
+        <v>105.9714798011508</v>
       </c>
       <c r="O9">
-        <v>21.46817563186805</v>
+        <v>21.19429596023015</v>
       </c>
       <c r="P9">
-        <v>85.87270252747221</v>
+        <v>84.77718384092061</v>
       </c>
       <c r="Q9">
-        <v>454.3727025274722</v>
+        <v>453.2771838409206</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08726893054971871</v>
+        <v>0.08763465001836425</v>
       </c>
       <c r="T9">
-        <v>0.8526448589078691</v>
+        <v>0.8601644361096318</v>
       </c>
       <c r="U9">
         <v>0.05575774444168938</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>12.19791846829289</v>
+        <v>10.67317865975628</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08419237366116322</v>
+        <v>0.08422460822235346</v>
       </c>
       <c r="C10">
-        <v>2234.553246816606</v>
+        <v>2208.124606141026</v>
       </c>
       <c r="D10">
-        <v>2227.731547278933</v>
+        <v>2225.862694161144</v>
       </c>
       <c r="E10">
-        <v>-1791.300455316764</v>
+        <v>-1766.740667758973</v>
       </c>
       <c r="F10">
-        <v>196.4783004623273</v>
+        <v>221.0380880201182</v>
       </c>
       <c r="G10">
         <v>203.3</v>
@@ -2107,45 +2107,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M10">
-        <v>10.95518686551591</v>
+        <v>12.70034997333959</v>
       </c>
       <c r="N10">
-        <v>105.9714798011508</v>
+        <v>104.2263166933271</v>
       </c>
       <c r="O10">
-        <v>21.19429596023015</v>
+        <v>20.84526333866542</v>
       </c>
       <c r="P10">
-        <v>84.77718384092061</v>
+        <v>83.38105335466166</v>
       </c>
       <c r="Q10">
-        <v>453.2771838409206</v>
+        <v>451.8810533546617</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08763465001836425</v>
+        <v>0.08800840727752948</v>
       </c>
       <c r="T10">
-        <v>0.8601644361096318</v>
+        <v>0.8678492787444001</v>
       </c>
       <c r="U10">
-        <v>0.05575774444168938</v>
+        <v>0.05745774444168938</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.04460619555335151</v>
+        <v>0.04596619555335151</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>10.67317865975628</v>
+        <v>9.206570441926212</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08422460822235346</v>
+        <v>0.08414804278354369</v>
       </c>
       <c r="C11">
-        <v>2208.124606141026</v>
+        <v>2188.008960748995</v>
       </c>
       <c r="D11">
-        <v>2225.862694161144</v>
+        <v>2230.306836326904</v>
       </c>
       <c r="E11">
-        <v>-1766.740667758973</v>
+        <v>-1742.180880201182</v>
       </c>
       <c r="F11">
-        <v>221.0380880201182</v>
+        <v>245.5978755779091</v>
       </c>
       <c r="G11">
         <v>203.3</v>
@@ -2189,28 +2189,28 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M11">
-        <v>12.70034997333959</v>
+        <v>14.11149997037733</v>
       </c>
       <c r="N11">
-        <v>104.2263166933271</v>
+        <v>102.8151666962894</v>
       </c>
       <c r="O11">
-        <v>20.84526333866542</v>
+        <v>20.56303333925787</v>
       </c>
       <c r="P11">
-        <v>83.38105335466166</v>
+        <v>82.25213335703148</v>
       </c>
       <c r="Q11">
-        <v>451.8810533546617</v>
+        <v>450.7521333570315</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08800840727752948</v>
+        <v>0.08839047025356504</v>
       </c>
       <c r="T11">
-        <v>0.8678492787444001</v>
+        <v>0.8757048956599411</v>
       </c>
       <c r="U11">
         <v>0.05745774444168938</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>9.206570441926212</v>
+        <v>8.285913397733593</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08414804278354371</v>
+        <v>0.08414187734473391</v>
       </c>
       <c r="C12">
-        <v>2188.008960748994</v>
+        <v>2163.807810307555</v>
       </c>
       <c r="D12">
-        <v>2230.306836326904</v>
+        <v>2230.665473443255</v>
       </c>
       <c r="E12">
-        <v>-1742.180880201182</v>
+        <v>-1717.621092643391</v>
       </c>
       <c r="F12">
-        <v>245.5978755779091</v>
+        <v>270.1576631357</v>
       </c>
       <c r="G12">
         <v>203.3</v>
@@ -2271,45 +2271,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M12">
-        <v>14.11149997037733</v>
+        <v>15.73877609792362</v>
       </c>
       <c r="N12">
-        <v>102.8151666962894</v>
+        <v>101.1878905687431</v>
       </c>
       <c r="O12">
-        <v>20.56303333925787</v>
+        <v>20.23757811374861</v>
       </c>
       <c r="P12">
-        <v>82.25213335703148</v>
+        <v>80.95031245499445</v>
       </c>
       <c r="Q12">
-        <v>450.7521333570315</v>
+        <v>449.4503124549944</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08839047025356506</v>
+        <v>0.08878111891445534</v>
       </c>
       <c r="T12">
-        <v>0.8757048956599414</v>
+        <v>0.8837370432926854</v>
       </c>
       <c r="U12">
-        <v>0.05745774444168938</v>
+        <v>0.05825774444168939</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.04596619555335151</v>
+        <v>0.04660619555335151</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>8.285913397733591</v>
+        <v>7.429209611927354</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08414187734473391</v>
+        <v>0.08407171190592415</v>
       </c>
       <c r="C13">
-        <v>2163.807810307555</v>
+        <v>2143.33761304995</v>
       </c>
       <c r="D13">
-        <v>2230.665473443255</v>
+        <v>2234.755063743441</v>
       </c>
       <c r="E13">
-        <v>-1717.621092643391</v>
+        <v>-1693.0613050856</v>
       </c>
       <c r="F13">
-        <v>270.1576631357</v>
+        <v>294.7174506934909</v>
       </c>
       <c r="G13">
         <v>203.3</v>
@@ -2353,28 +2353,28 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M13">
-        <v>15.73877609792362</v>
+        <v>17.16957392500758</v>
       </c>
       <c r="N13">
-        <v>101.1878905687431</v>
+        <v>99.75709274165909</v>
       </c>
       <c r="O13">
-        <v>20.23757811374861</v>
+        <v>19.95141854833182</v>
       </c>
       <c r="P13">
-        <v>80.95031245499445</v>
+        <v>79.80567419332728</v>
       </c>
       <c r="Q13">
-        <v>449.4503124549944</v>
+        <v>448.3056741933273</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08878111891445534</v>
+        <v>0.08918064595400224</v>
       </c>
       <c r="T13">
-        <v>0.8837370432926854</v>
+        <v>0.8919517397352649</v>
       </c>
       <c r="U13">
         <v>0.05825774444168939</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>7.429209611927354</v>
+        <v>6.81010881093341</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08407171190592415</v>
+        <v>0.08400154646711439</v>
       </c>
       <c r="C14">
-        <v>2143.33761304995</v>
+        <v>2122.882438634323</v>
       </c>
       <c r="D14">
-        <v>2234.755063743441</v>
+        <v>2238.859676885604</v>
       </c>
       <c r="E14">
-        <v>-1693.0613050856</v>
+        <v>-1668.501517527809</v>
       </c>
       <c r="F14">
-        <v>294.7174506934909</v>
+        <v>319.2772382512819</v>
       </c>
       <c r="G14">
         <v>203.3</v>
@@ -2435,28 +2435,28 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M14">
-        <v>17.16957392500758</v>
+        <v>18.60037175209155</v>
       </c>
       <c r="N14">
-        <v>99.75709274165909</v>
+        <v>98.32629491457513</v>
       </c>
       <c r="O14">
-        <v>19.95141854833182</v>
+        <v>19.66525898291503</v>
       </c>
       <c r="P14">
-        <v>79.80567419332728</v>
+        <v>78.66103593166011</v>
       </c>
       <c r="Q14">
-        <v>448.3056741933273</v>
+        <v>447.1610359316601</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08918064595400224</v>
+        <v>0.0895893575231939</v>
       </c>
       <c r="T14">
-        <v>0.8919517397352649</v>
+        <v>0.9003552797742252</v>
       </c>
       <c r="U14">
         <v>0.05825774444168939</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>6.81010881093341</v>
+        <v>6.286254287015454</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08400154646711439</v>
+        <v>0.08404338102830462</v>
       </c>
       <c r="C15">
-        <v>2122.882438634323</v>
+        <v>2095.873555059637</v>
       </c>
       <c r="D15">
-        <v>2238.859676885604</v>
+        <v>2236.410580868709</v>
       </c>
       <c r="E15">
-        <v>-1668.501517527809</v>
+        <v>-1643.941729970018</v>
       </c>
       <c r="F15">
-        <v>319.2772382512819</v>
+        <v>343.8370258090728</v>
       </c>
       <c r="G15">
         <v>203.3</v>
@@ -2517,45 +2517,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M15">
-        <v>18.60037175209155</v>
+        <v>20.37500660498459</v>
       </c>
       <c r="N15">
-        <v>98.32629491457513</v>
+        <v>96.55166006168209</v>
       </c>
       <c r="O15">
-        <v>19.66525898291503</v>
+        <v>19.31033201233642</v>
       </c>
       <c r="P15">
-        <v>78.66103593166011</v>
+        <v>77.24132804934567</v>
       </c>
       <c r="Q15">
-        <v>447.1610359316601</v>
+        <v>445.7413280493457</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0895893575231939</v>
+        <v>0.09000757401259932</v>
       </c>
       <c r="T15">
-        <v>0.9003552797742252</v>
+        <v>0.9089542509768825</v>
       </c>
       <c r="U15">
-        <v>0.05825774444168939</v>
+        <v>0.05925774444168939</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.04660619555335151</v>
+        <v>0.04740619555335152</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y15">
-        <v>6.286254287015454</v>
+        <v>5.738730246009415</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08404338102830462</v>
+        <v>0.08398121558949485</v>
       </c>
       <c r="C16">
-        <v>2095.873555059637</v>
+        <v>2074.955019959946</v>
       </c>
       <c r="D16">
-        <v>2236.410580868709</v>
+        <v>2240.05183332681</v>
       </c>
       <c r="E16">
-        <v>-1643.941729970018</v>
+        <v>-1619.381942412227</v>
       </c>
       <c r="F16">
-        <v>343.8370258090728</v>
+        <v>368.3968133668637</v>
       </c>
       <c r="G16">
         <v>203.3</v>
@@ -2599,28 +2599,28 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M16">
-        <v>20.37500660498459</v>
+        <v>21.83036421962635</v>
       </c>
       <c r="N16">
-        <v>96.55166006168209</v>
+        <v>95.09630244704033</v>
       </c>
       <c r="O16">
-        <v>19.31033201233642</v>
+        <v>19.01926048940807</v>
       </c>
       <c r="P16">
-        <v>77.24132804934567</v>
+        <v>76.07704195763226</v>
       </c>
       <c r="Q16">
-        <v>445.7413280493457</v>
+        <v>444.5770419576323</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09000757401259932</v>
+        <v>0.09043563088999074</v>
       </c>
       <c r="T16">
-        <v>0.9089542509768825</v>
+        <v>0.9177555509137199</v>
       </c>
       <c r="U16">
         <v>0.05925774444168939</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.738730246009415</v>
+        <v>5.356148229608786</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08398121558949485</v>
+        <v>0.0839190501506851</v>
       </c>
       <c r="C17">
-        <v>2074.955019959946</v>
+        <v>2054.048361339652</v>
       </c>
       <c r="D17">
-        <v>2240.05183332681</v>
+        <v>2243.704962264306</v>
       </c>
       <c r="E17">
-        <v>-1619.381942412227</v>
+        <v>-1594.822154854436</v>
       </c>
       <c r="F17">
-        <v>368.3968133668636</v>
+        <v>392.9566009246546</v>
       </c>
       <c r="G17">
         <v>203.3</v>
@@ -2681,28 +2681,28 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M17">
-        <v>21.83036421962635</v>
+        <v>23.28572183426811</v>
       </c>
       <c r="N17">
-        <v>95.09630244704033</v>
+        <v>93.64094483239857</v>
       </c>
       <c r="O17">
-        <v>19.01926048940807</v>
+        <v>18.72818896647972</v>
       </c>
       <c r="P17">
-        <v>76.07704195763226</v>
+        <v>74.91275586591885</v>
       </c>
       <c r="Q17">
-        <v>444.5770419576323</v>
+        <v>443.4127558659188</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09043563088999074</v>
+        <v>0.09087387959779625</v>
       </c>
       <c r="T17">
-        <v>0.9177555509137199</v>
+        <v>0.9267664056109581</v>
       </c>
       <c r="U17">
         <v>0.05925774444168939</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.356148229608787</v>
+        <v>5.021388965258238</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0839190501506851</v>
+        <v>0.08385688471187532</v>
       </c>
       <c r="C18">
-        <v>2054.048361339652</v>
+        <v>2033.153637398992</v>
       </c>
       <c r="D18">
-        <v>2243.704962264306</v>
+        <v>2247.370025881437</v>
       </c>
       <c r="E18">
-        <v>-1594.822154854436</v>
+        <v>-1570.262367296645</v>
       </c>
       <c r="F18">
-        <v>392.9566009246546</v>
+        <v>417.5163884824455</v>
       </c>
       <c r="G18">
         <v>203.3</v>
@@ -2763,28 +2763,28 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M18">
-        <v>23.28572183426811</v>
+        <v>24.74107944890986</v>
       </c>
       <c r="N18">
-        <v>93.64094483239857</v>
+        <v>92.18558721775682</v>
       </c>
       <c r="O18">
-        <v>18.72818896647972</v>
+        <v>18.43711744355137</v>
       </c>
       <c r="P18">
-        <v>74.91275586591885</v>
+        <v>73.74846977420546</v>
       </c>
       <c r="Q18">
-        <v>443.4127558659188</v>
+        <v>442.2484697742054</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09087387959779625</v>
+        <v>0.09132268851542838</v>
       </c>
       <c r="T18">
-        <v>0.9267664056109581</v>
+        <v>0.9359943893370456</v>
       </c>
       <c r="U18">
         <v>0.05925774444168939</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.021388965258238</v>
+        <v>4.726013143772459</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08385688471187532</v>
+        <v>0.08415471927306555</v>
       </c>
       <c r="C19">
-        <v>2033.153637398992</v>
+        <v>1991.142425917978</v>
       </c>
       <c r="D19">
-        <v>2247.370025881437</v>
+        <v>2229.918601958214</v>
       </c>
       <c r="E19">
-        <v>-1570.262367296645</v>
+        <v>-1545.702579738855</v>
       </c>
       <c r="F19">
-        <v>417.5163884824455</v>
+        <v>442.0761760402364</v>
       </c>
       <c r="G19">
         <v>203.3</v>
@@ -2845,45 +2845,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M19">
-        <v>24.74107944890986</v>
+        <v>27.30162750365221</v>
       </c>
       <c r="N19">
-        <v>92.18558721775682</v>
+        <v>89.62503916301446</v>
       </c>
       <c r="O19">
-        <v>18.43711744355137</v>
+        <v>17.92500783260289</v>
       </c>
       <c r="P19">
-        <v>73.74846977420546</v>
+        <v>71.70003133041158</v>
       </c>
       <c r="Q19">
-        <v>442.2484697742054</v>
+        <v>440.2000313304115</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09132268851542838</v>
+        <v>0.09178244399202717</v>
       </c>
       <c r="T19">
-        <v>0.9359943893370456</v>
+        <v>0.9454474458369402</v>
       </c>
       <c r="U19">
-        <v>0.05925774444168939</v>
+        <v>0.06175774444168938</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.04740619555335152</v>
+        <v>0.04940619555335151</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.726013143772459</v>
+        <v>4.282772763309627</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08415471927306556</v>
+        <v>0.0841125538342558</v>
       </c>
       <c r="C20">
-        <v>1991.142425917978</v>
+        <v>1969.036807736846</v>
       </c>
       <c r="D20">
-        <v>2229.918601958214</v>
+        <v>2232.372771334873</v>
       </c>
       <c r="E20">
-        <v>-1545.702579738855</v>
+        <v>-1521.142792181064</v>
       </c>
       <c r="F20">
-        <v>442.0761760402364</v>
+        <v>466.6359635980273</v>
       </c>
       <c r="G20">
         <v>203.3</v>
@@ -2927,28 +2927,28 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M20">
-        <v>27.30162750365221</v>
+        <v>28.81838458718844</v>
       </c>
       <c r="N20">
-        <v>89.62503916301446</v>
+        <v>88.10828207947824</v>
       </c>
       <c r="O20">
-        <v>17.92500783260289</v>
+        <v>17.62165641589565</v>
       </c>
       <c r="P20">
-        <v>71.70003133041158</v>
+        <v>70.4866256635826</v>
       </c>
       <c r="Q20">
-        <v>440.2000313304115</v>
+        <v>438.9866256635826</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09178244399202717</v>
+        <v>0.09225355145570246</v>
       </c>
       <c r="T20">
-        <v>0.94544744583694</v>
+        <v>0.9551339111393011</v>
       </c>
       <c r="U20">
         <v>0.06175774444168938</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>4.282772763309627</v>
+        <v>4.057363670503857</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0841125538342558</v>
+        <v>0.08463038839544601</v>
       </c>
       <c r="C21">
-        <v>1969.036807736846</v>
+        <v>1914.706527989161</v>
       </c>
       <c r="D21">
-        <v>2232.372771334873</v>
+        <v>2202.602279144979</v>
       </c>
       <c r="E21">
-        <v>-1521.142792181064</v>
+        <v>-1496.583004623273</v>
       </c>
       <c r="F21">
-        <v>466.6359635980273</v>
+        <v>491.1957511558182</v>
       </c>
       <c r="G21">
         <v>203.3</v>
@@ -3009,45 +3009,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M21">
-        <v>28.81838458718844</v>
+        <v>32.05432679977004</v>
       </c>
       <c r="N21">
-        <v>88.10828207947824</v>
+        <v>84.87233986689664</v>
       </c>
       <c r="O21">
-        <v>17.62165641589565</v>
+        <v>16.97446797337933</v>
       </c>
       <c r="P21">
-        <v>70.4866256635826</v>
+        <v>67.8978718935173</v>
       </c>
       <c r="Q21">
-        <v>438.9866256635826</v>
+        <v>436.3978718935173</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09225355145570246</v>
+        <v>0.09273643660596964</v>
       </c>
       <c r="T21">
-        <v>0.9551339111393011</v>
+        <v>0.9650625380742209</v>
       </c>
       <c r="U21">
-        <v>0.06175774444168938</v>
+        <v>0.06525774444168939</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.04940619555335151</v>
+        <v>0.05220619555335151</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>4.057363670503857</v>
+        <v>3.647765476313342</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08463038839544601</v>
+        <v>0.08508662295663624</v>
       </c>
       <c r="C22">
-        <v>1914.706527989161</v>
+        <v>1864.567975735521</v>
       </c>
       <c r="D22">
-        <v>2202.602279144979</v>
+        <v>2177.02351444913</v>
       </c>
       <c r="E22">
-        <v>-1496.583004623273</v>
+        <v>-1472.023217065482</v>
       </c>
       <c r="F22">
-        <v>491.1957511558182</v>
+        <v>515.7555387136092</v>
       </c>
       <c r="G22">
         <v>203.3</v>
@@ -3091,45 +3091,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M22">
-        <v>32.05432679977004</v>
+        <v>35.10115864815665</v>
       </c>
       <c r="N22">
-        <v>84.87233986689664</v>
+        <v>81.82550801851002</v>
       </c>
       <c r="O22">
-        <v>16.97446797337933</v>
+        <v>16.365101603702</v>
       </c>
       <c r="P22">
-        <v>67.8978718935173</v>
+        <v>65.46040641480802</v>
       </c>
       <c r="Q22">
-        <v>436.3978718935173</v>
+        <v>433.960406414808</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09273643660596964</v>
+        <v>0.09323154669674991</v>
       </c>
       <c r="T22">
-        <v>0.9650625380742209</v>
+        <v>0.975242522653063</v>
       </c>
       <c r="U22">
-        <v>0.06525774444168939</v>
+        <v>0.06805774444168938</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.05220619555335151</v>
+        <v>0.05444619555335151</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.647765476313342</v>
+        <v>3.331134104110467</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08508662295663624</v>
+        <v>0.08509485751782649</v>
       </c>
       <c r="C23">
-        <v>1864.567975735521</v>
+        <v>1839.551974961174</v>
       </c>
       <c r="D23">
-        <v>2177.02351444913</v>
+        <v>2176.567301232574</v>
       </c>
       <c r="E23">
-        <v>-1472.023217065482</v>
+        <v>-1447.463429507691</v>
       </c>
       <c r="F23">
-        <v>515.7555387136091</v>
+        <v>540.3153262714001</v>
       </c>
       <c r="G23">
         <v>203.3</v>
@@ -3173,28 +3173,28 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M23">
-        <v>35.10115864815664</v>
+        <v>36.77264239330697</v>
       </c>
       <c r="N23">
-        <v>81.82550801851004</v>
+        <v>80.15402427335971</v>
       </c>
       <c r="O23">
-        <v>16.36510160370201</v>
+        <v>16.03080485467194</v>
       </c>
       <c r="P23">
-        <v>65.46040641480803</v>
+        <v>64.12321941868777</v>
       </c>
       <c r="Q23">
-        <v>433.9604064148081</v>
+        <v>432.6232194186878</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09323154669674991</v>
+        <v>0.09373935191806301</v>
       </c>
       <c r="T23">
-        <v>0.975242522653063</v>
+        <v>0.9856835324775164</v>
       </c>
       <c r="U23">
         <v>0.06805774444168938</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.331134104110468</v>
+        <v>3.179718917559991</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08509485751782649</v>
+        <v>0.08510309207901672</v>
       </c>
       <c r="C24">
-        <v>1839.551974961174</v>
+        <v>1814.536165353245</v>
       </c>
       <c r="D24">
-        <v>2176.567301232574</v>
+        <v>2176.111279182435</v>
       </c>
       <c r="E24">
-        <v>-1447.463429507691</v>
+        <v>-1422.9036419499</v>
       </c>
       <c r="F24">
-        <v>540.3153262714001</v>
+        <v>564.8751138291909</v>
       </c>
       <c r="G24">
         <v>203.3</v>
@@ -3255,28 +3255,28 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M24">
-        <v>36.77264239330697</v>
+        <v>38.44412613845728</v>
       </c>
       <c r="N24">
-        <v>80.15402427335971</v>
+        <v>78.4825405282094</v>
       </c>
       <c r="O24">
-        <v>16.03080485467194</v>
+        <v>15.69650810564188</v>
       </c>
       <c r="P24">
-        <v>64.12321941868777</v>
+        <v>62.78603242256752</v>
       </c>
       <c r="Q24">
-        <v>432.6232194186878</v>
+        <v>431.2860324225675</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09373935191806301</v>
+        <v>0.09426034688538425</v>
       </c>
       <c r="T24">
-        <v>0.9856835324775164</v>
+        <v>0.9963957373623451</v>
       </c>
       <c r="U24">
         <v>0.06805774444168938</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.179718917559991</v>
+        <v>3.041470268970427</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08510309207901672</v>
+        <v>0.08660892664020696</v>
       </c>
       <c r="C25">
-        <v>1814.536165353245</v>
+        <v>1709.678662492148</v>
       </c>
       <c r="D25">
-        <v>2176.111279182435</v>
+        <v>2095.81356387913</v>
       </c>
       <c r="E25">
-        <v>-1422.9036419499</v>
+        <v>-1398.343854392109</v>
       </c>
       <c r="F25">
-        <v>564.8751138291909</v>
+        <v>589.4349013869819</v>
       </c>
       <c r="G25">
         <v>203.3</v>
@@ -3337,45 +3337,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M25">
-        <v>38.44412613845728</v>
+        <v>44.71320211442605</v>
       </c>
       <c r="N25">
-        <v>78.4825405282094</v>
+        <v>72.21346455224062</v>
       </c>
       <c r="O25">
-        <v>15.69650810564188</v>
+        <v>14.44269291044812</v>
       </c>
       <c r="P25">
-        <v>62.78603242256752</v>
+        <v>57.7707716417925</v>
       </c>
       <c r="Q25">
-        <v>431.2860324225675</v>
+        <v>426.2707716417925</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09426034688538425</v>
+        <v>0.09479505224658236</v>
       </c>
       <c r="T25">
-        <v>0.9963957373623451</v>
+        <v>1.007389842375722</v>
       </c>
       <c r="U25">
-        <v>0.06805774444168938</v>
+        <v>0.07585774444168938</v>
       </c>
       <c r="V25">
         <v>0.2</v>
       </c>
       <c r="W25">
-        <v>0.05444619555335151</v>
+        <v>0.06068619555335151</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>3.041470268970427</v>
+        <v>2.615036748373296</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08660892664020695</v>
+        <v>0.08667956120139718</v>
       </c>
       <c r="C26">
-        <v>1709.678662492149</v>
+        <v>1681.49758187077</v>
       </c>
       <c r="D26">
-        <v>2095.81356387913</v>
+        <v>2092.192270815543</v>
       </c>
       <c r="E26">
-        <v>-1398.343854392109</v>
+        <v>-1373.784066834318</v>
       </c>
       <c r="F26">
-        <v>589.4349013869818</v>
+        <v>613.9946889447727</v>
       </c>
       <c r="G26">
         <v>203.3</v>
@@ -3419,28 +3419,28 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M26">
-        <v>44.71320211442605</v>
+        <v>46.57625220252714</v>
       </c>
       <c r="N26">
-        <v>72.21346455224062</v>
+        <v>70.35041446413953</v>
       </c>
       <c r="O26">
-        <v>14.44269291044812</v>
+        <v>14.07008289282791</v>
       </c>
       <c r="P26">
-        <v>57.7707716417925</v>
+        <v>56.28033157131163</v>
       </c>
       <c r="Q26">
-        <v>426.2707716417925</v>
+        <v>424.7803315713116</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09479505224658233</v>
+        <v>0.0953440164174124</v>
       </c>
       <c r="T26">
-        <v>1.007389842375722</v>
+        <v>1.018677123522789</v>
       </c>
       <c r="U26">
         <v>0.07585774444168938</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.615036748373296</v>
+        <v>2.510435278438364</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08667956120139718</v>
+        <v>0.08756139576258741</v>
       </c>
       <c r="C27">
-        <v>1681.49758187077</v>
+        <v>1612.759015817432</v>
       </c>
       <c r="D27">
-        <v>2092.192270815543</v>
+        <v>2048.013492319996</v>
       </c>
       <c r="E27">
-        <v>-1373.784066834318</v>
+        <v>-1349.224279276527</v>
       </c>
       <c r="F27">
-        <v>613.9946889447727</v>
+        <v>638.5544765025637</v>
       </c>
       <c r="G27">
         <v>203.3</v>
@@ -3501,45 +3501,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M27">
-        <v>46.57625220252714</v>
+        <v>50.92966474898822</v>
       </c>
       <c r="N27">
-        <v>70.35041446413953</v>
+        <v>65.99700191767846</v>
       </c>
       <c r="O27">
-        <v>14.07008289282791</v>
+        <v>13.19940038353569</v>
       </c>
       <c r="P27">
-        <v>56.28033157131163</v>
+        <v>52.79760153414277</v>
       </c>
       <c r="Q27">
-        <v>424.7803315713116</v>
+        <v>421.2976015341428</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0953440164174124</v>
+        <v>0.09590781745772435</v>
       </c>
       <c r="T27">
-        <v>1.018677123522789</v>
+        <v>1.030269466322479</v>
       </c>
       <c r="U27">
-        <v>0.07585774444168938</v>
+        <v>0.07975774444168938</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.06068619555335151</v>
+        <v>0.06380619555335151</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.510435278438364</v>
+        <v>2.295845991583708</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08756139576258741</v>
+        <v>0.08766323032377765</v>
       </c>
       <c r="C28">
-        <v>1612.759015817432</v>
+        <v>1583.217325198432</v>
       </c>
       <c r="D28">
-        <v>2048.013492319996</v>
+        <v>2043.031589258787</v>
       </c>
       <c r="E28">
-        <v>-1349.224279276527</v>
+        <v>-1324.664491718736</v>
       </c>
       <c r="F28">
-        <v>638.5544765025637</v>
+        <v>663.1142640603546</v>
       </c>
       <c r="G28">
         <v>203.3</v>
@@ -3583,28 +3583,28 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M28">
-        <v>50.92966474898822</v>
+        <v>52.88849800856469</v>
       </c>
       <c r="N28">
-        <v>65.99700191767846</v>
+        <v>64.03816865810199</v>
       </c>
       <c r="O28">
-        <v>13.19940038353569</v>
+        <v>12.8076337316204</v>
       </c>
       <c r="P28">
-        <v>52.79760153414277</v>
+        <v>51.2305349264816</v>
       </c>
       <c r="Q28">
-        <v>421.2976015341428</v>
+        <v>419.7305349264816</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09590781745772435</v>
+        <v>0.09648706510188046</v>
       </c>
       <c r="T28">
-        <v>1.030269466322479</v>
+        <v>1.042179407555038</v>
       </c>
       <c r="U28">
         <v>0.07975774444168938</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.295845991583708</v>
+        <v>2.210814658562089</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08766323032377765</v>
+        <v>0.08776506488496788</v>
       </c>
       <c r="C29">
-        <v>1583.217325198432</v>
+        <v>1553.699813258224</v>
       </c>
       <c r="D29">
-        <v>2043.031589258787</v>
+        <v>2038.07386487637</v>
       </c>
       <c r="E29">
-        <v>-1324.664491718736</v>
+        <v>-1300.104704160945</v>
       </c>
       <c r="F29">
-        <v>663.1142640603546</v>
+        <v>687.6740516181455</v>
       </c>
       <c r="G29">
         <v>203.3</v>
@@ -3665,28 +3665,28 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M29">
-        <v>52.88849800856469</v>
+        <v>54.84733126814117</v>
       </c>
       <c r="N29">
-        <v>64.03816865810199</v>
+        <v>62.07933539852551</v>
       </c>
       <c r="O29">
-        <v>12.8076337316204</v>
+        <v>12.4158670797051</v>
       </c>
       <c r="P29">
-        <v>51.2305349264816</v>
+        <v>49.66346831882041</v>
       </c>
       <c r="Q29">
-        <v>419.7305349264816</v>
+        <v>418.1634683188204</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09648706510188046</v>
+        <v>0.09708240295837424</v>
       </c>
       <c r="T29">
-        <v>1.042179407555038</v>
+        <v>1.054420180488501</v>
       </c>
       <c r="U29">
         <v>0.07975774444168938</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.210814658562089</v>
+        <v>2.131856992184871</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08776506488496788</v>
+        <v>0.08786689944615811</v>
       </c>
       <c r="C30">
-        <v>1553.699813258224</v>
+        <v>1524.206304403274</v>
       </c>
       <c r="D30">
-        <v>2038.07386487637</v>
+        <v>2033.14014357921</v>
       </c>
       <c r="E30">
-        <v>-1300.104704160945</v>
+        <v>-1275.544916603154</v>
       </c>
       <c r="F30">
-        <v>687.6740516181455</v>
+        <v>712.2338391759365</v>
       </c>
       <c r="G30">
         <v>203.3</v>
@@ -3747,28 +3747,28 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M30">
-        <v>54.84733126814117</v>
+        <v>56.80616452771764</v>
       </c>
       <c r="N30">
-        <v>62.07933539852551</v>
+        <v>60.12050213894904</v>
       </c>
       <c r="O30">
-        <v>12.4158670797051</v>
+        <v>12.02410042778981</v>
       </c>
       <c r="P30">
-        <v>49.66346831882041</v>
+        <v>48.09640171115923</v>
       </c>
       <c r="Q30">
-        <v>418.1634683188204</v>
+        <v>416.5964017111592</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09708240295837424</v>
+        <v>0.09769451089533263</v>
       </c>
       <c r="T30">
-        <v>1.054420180488501</v>
+        <v>1.067005763927132</v>
       </c>
       <c r="U30">
         <v>0.07975774444168938</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.131856992184871</v>
+        <v>2.058344682109531</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08786689944615809</v>
+        <v>0.09137673400734835</v>
       </c>
       <c r="C31">
-        <v>1524.206304403275</v>
+        <v>1343.075720383256</v>
       </c>
       <c r="D31">
-        <v>2033.140143579211</v>
+        <v>1876.569347116984</v>
       </c>
       <c r="E31">
-        <v>-1275.544916603155</v>
+        <v>-1250.985129045364</v>
       </c>
       <c r="F31">
-        <v>712.2338391759363</v>
+        <v>736.7936267337273</v>
       </c>
       <c r="G31">
         <v>203.3</v>
@@ -3829,45 +3829,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M31">
-        <v>56.80616452771763</v>
+        <v>69.22746728691303</v>
       </c>
       <c r="N31">
-        <v>60.12050213894905</v>
+        <v>47.69919937975365</v>
       </c>
       <c r="O31">
-        <v>12.02410042778981</v>
+        <v>9.539839875950731</v>
       </c>
       <c r="P31">
-        <v>48.09640171115924</v>
+        <v>38.15935950380292</v>
       </c>
       <c r="Q31">
-        <v>416.5964017111592</v>
+        <v>406.6593595038029</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09769451089533263</v>
+        <v>0.09832410763048985</v>
       </c>
       <c r="T31">
-        <v>1.067005763927132</v>
+        <v>1.079950935464009</v>
       </c>
       <c r="U31">
-        <v>0.07975774444168938</v>
+        <v>0.09395774444168939</v>
       </c>
       <c r="V31">
         <v>0.2</v>
       </c>
       <c r="W31">
-        <v>0.06380619555335151</v>
+        <v>0.07516619555335152</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>2.058344682109531</v>
+        <v>1.689021298180164</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09137673400734835</v>
+        <v>0.09159216856853858</v>
       </c>
       <c r="C32">
-        <v>1343.075720383256</v>
+        <v>1309.687394966768</v>
       </c>
       <c r="D32">
-        <v>1876.569347116984</v>
+        <v>1867.740809258286</v>
       </c>
       <c r="E32">
-        <v>-1250.985129045364</v>
+        <v>-1226.425341487573</v>
       </c>
       <c r="F32">
-        <v>736.7936267337273</v>
+        <v>761.3534142915182</v>
       </c>
       <c r="G32">
         <v>203.3</v>
@@ -3911,28 +3911,28 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M32">
-        <v>69.22746728691303</v>
+        <v>71.53504952981014</v>
       </c>
       <c r="N32">
-        <v>47.69919937975365</v>
+        <v>45.39161713685654</v>
       </c>
       <c r="O32">
-        <v>9.539839875950731</v>
+        <v>9.078323427371307</v>
       </c>
       <c r="P32">
-        <v>38.15935950380292</v>
+        <v>36.31329370948523</v>
       </c>
       <c r="Q32">
-        <v>406.6593595038029</v>
+        <v>404.8132937094852</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09832410763048985</v>
+        <v>0.09897195354637624</v>
       </c>
       <c r="T32">
-        <v>1.079950935464009</v>
+        <v>1.093271329364274</v>
       </c>
       <c r="U32">
         <v>0.09395774444168939</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>1.689021298180164</v>
+        <v>1.634536740174352</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09159216856853858</v>
+        <v>0.0918076031297288</v>
       </c>
       <c r="C33">
-        <v>1309.687394966768</v>
+        <v>1276.381750326942</v>
       </c>
       <c r="D33">
-        <v>1867.740809258286</v>
+        <v>1858.994952176251</v>
       </c>
       <c r="E33">
-        <v>-1226.425341487573</v>
+        <v>-1201.865553929782</v>
       </c>
       <c r="F33">
-        <v>761.3534142915182</v>
+        <v>785.9132018493092</v>
       </c>
       <c r="G33">
         <v>203.3</v>
@@ -3993,28 +3993,28 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M33">
-        <v>71.53504952981014</v>
+        <v>73.84263177270724</v>
       </c>
       <c r="N33">
-        <v>45.39161713685654</v>
+        <v>43.08403489395944</v>
       </c>
       <c r="O33">
-        <v>9.078323427371307</v>
+        <v>8.616806978791889</v>
       </c>
       <c r="P33">
-        <v>36.31329370948523</v>
+        <v>34.46722791516756</v>
       </c>
       <c r="Q33">
-        <v>404.8132937094852</v>
+        <v>402.9672279151675</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09897195354637624</v>
+        <v>0.09963885375390635</v>
       </c>
       <c r="T33">
-        <v>1.093271329364274</v>
+        <v>1.106983499555724</v>
       </c>
       <c r="U33">
         <v>0.09395774444168939</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.634536740174352</v>
+        <v>1.583457467043904</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0918076031297288</v>
+        <v>0.09202303769091903</v>
       </c>
       <c r="C34">
-        <v>1276.381750326942</v>
+        <v>1243.157630397598</v>
       </c>
       <c r="D34">
-        <v>1858.994952176251</v>
+        <v>1850.330619804698</v>
       </c>
       <c r="E34">
-        <v>-1201.865553929782</v>
+        <v>-1177.305766371991</v>
       </c>
       <c r="F34">
-        <v>785.9132018493092</v>
+        <v>810.4729894071</v>
       </c>
       <c r="G34">
         <v>203.3</v>
@@ -4075,28 +4075,28 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M34">
-        <v>73.84263177270724</v>
+        <v>76.15021401560433</v>
       </c>
       <c r="N34">
-        <v>43.08403489395944</v>
+        <v>40.77645265106234</v>
       </c>
       <c r="O34">
-        <v>8.616806978791889</v>
+        <v>8.155290530212469</v>
       </c>
       <c r="P34">
-        <v>34.46722791516756</v>
+        <v>32.62116212084987</v>
       </c>
       <c r="Q34">
-        <v>402.9672279151675</v>
+        <v>401.1211621208499</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09963885375390635</v>
+        <v>0.100325661430318</v>
       </c>
       <c r="T34">
-        <v>1.106983499555724</v>
+        <v>1.121104988260351</v>
       </c>
       <c r="U34">
         <v>0.09395774444168939</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.583457467043904</v>
+        <v>1.535473907436513</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09202303769091903</v>
+        <v>0.1086071271700107</v>
       </c>
       <c r="C35">
-        <v>1243.157630397598</v>
+        <v>730.0219447306455</v>
       </c>
       <c r="D35">
-        <v>1850.330619804698</v>
+        <v>1361.754721695537</v>
       </c>
       <c r="E35">
-        <v>-1177.305766371991</v>
+        <v>-1152.7459788142</v>
       </c>
       <c r="F35">
-        <v>810.4729894071</v>
+        <v>835.032776964891</v>
       </c>
       <c r="G35">
         <v>203.3</v>
@@ -4157,45 +4157,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M35">
-        <v>76.15021401560433</v>
+        <v>125.8876579901073</v>
       </c>
       <c r="N35">
-        <v>40.77645265106234</v>
+        <v>-8.960991323440595</v>
       </c>
       <c r="O35">
-        <v>8.155290530212469</v>
+        <v>-1.792198264688119</v>
       </c>
       <c r="P35">
-        <v>32.62116212084987</v>
+        <v>-7.168793058752476</v>
       </c>
       <c r="Q35">
-        <v>401.1211621208499</v>
+        <v>361.3312069412475</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.100325661430318</v>
+        <v>0.101320139317114</v>
       </c>
       <c r="T35">
-        <v>1.121104988260351</v>
+        <v>1.14155250031899</v>
       </c>
       <c r="U35">
-        <v>0.09395774444168939</v>
+        <v>0.1507577444416894</v>
       </c>
       <c r="V35">
-        <v>0.2</v>
+        <v>0.1857635109485558</v>
       </c>
       <c r="W35">
-        <v>0.07516619555335152</v>
+        <v>0.1227524565315161</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y35">
-        <v>1.535473907436513</v>
+        <v>0.9288175547427788</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1086071271700107</v>
+        <v>0.1096567046144276</v>
       </c>
       <c r="C36">
-        <v>730.0219447306455</v>
+        <v>683.0797456571044</v>
       </c>
       <c r="D36">
-        <v>1361.754721695537</v>
+        <v>1339.372310179786</v>
       </c>
       <c r="E36">
-        <v>-1152.7459788142</v>
+        <v>-1128.186191256409</v>
       </c>
       <c r="F36">
-        <v>835.032776964891</v>
+        <v>859.592564522682</v>
       </c>
       <c r="G36">
         <v>203.3</v>
@@ -4239,37 +4239,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M36">
-        <v>125.8876579901073</v>
+        <v>129.5902361662869</v>
       </c>
       <c r="N36">
-        <v>-8.960991323440595</v>
+        <v>-12.66356949962022</v>
       </c>
       <c r="O36">
-        <v>-1.792198264688119</v>
+        <v>-2.532713899924045</v>
       </c>
       <c r="P36">
-        <v>-7.168793058752476</v>
+        <v>-10.13085559969618</v>
       </c>
       <c r="Q36">
-        <v>361.3312069412475</v>
+        <v>358.3691444003038</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.101320139317114</v>
+        <v>0.1021742953066081</v>
       </c>
       <c r="T36">
-        <v>1.14155250031899</v>
+        <v>1.159114846477743</v>
       </c>
       <c r="U36">
         <v>0.1507577444416894</v>
       </c>
       <c r="V36">
-        <v>0.1857635109485558</v>
+        <v>0.1804559820643113</v>
       </c>
       <c r="W36">
-        <v>0.1227524565315161</v>
+        <v>0.1235526076146639</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.9288175547427788</v>
+        <v>0.9022799103215565</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1096567046144276</v>
+        <v>0.1107062820588445</v>
       </c>
       <c r="C37">
-        <v>683.0797456571044</v>
+        <v>636.8614233342689</v>
       </c>
       <c r="D37">
-        <v>1339.372310179786</v>
+        <v>1317.713775414742</v>
       </c>
       <c r="E37">
-        <v>-1128.186191256409</v>
+        <v>-1103.626403698618</v>
       </c>
       <c r="F37">
-        <v>859.592564522682</v>
+        <v>884.1523520804728</v>
       </c>
       <c r="G37">
         <v>203.3</v>
@@ -4321,37 +4321,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M37">
-        <v>129.5902361662869</v>
+        <v>133.2928143424665</v>
       </c>
       <c r="N37">
-        <v>-12.66356949962022</v>
+        <v>-16.36614767579985</v>
       </c>
       <c r="O37">
-        <v>-2.532713899924045</v>
+        <v>-3.27322953515997</v>
       </c>
       <c r="P37">
-        <v>-10.13085559969618</v>
+        <v>-13.09291814063988</v>
       </c>
       <c r="Q37">
-        <v>358.3691444003038</v>
+        <v>355.4070818593601</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1021742953066081</v>
+        <v>0.1030551436707738</v>
       </c>
       <c r="T37">
-        <v>1.159114846477743</v>
+        <v>1.177226015953958</v>
       </c>
       <c r="U37">
         <v>0.1507577444416894</v>
       </c>
       <c r="V37">
-        <v>0.1804559820643113</v>
+        <v>0.1754433158958582</v>
       </c>
       <c r="W37">
-        <v>0.1235526076146639</v>
+        <v>0.124308305859859</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.9022799103215565</v>
+        <v>0.8772165794792911</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1107062820588445</v>
+        <v>0.1117558595032614</v>
       </c>
       <c r="C38">
-        <v>636.861423334269</v>
+        <v>591.3324198904453</v>
       </c>
       <c r="D38">
-        <v>1317.713775414742</v>
+        <v>1296.744559528709</v>
       </c>
       <c r="E38">
-        <v>-1103.626403698618</v>
+        <v>-1079.066616140827</v>
       </c>
       <c r="F38">
-        <v>884.1523520804727</v>
+        <v>908.7121396382637</v>
       </c>
       <c r="G38">
         <v>203.3</v>
@@ -4403,37 +4403,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M38">
-        <v>133.2928143424665</v>
+        <v>136.9953925186461</v>
       </c>
       <c r="N38">
-        <v>-16.36614767579982</v>
+        <v>-20.06872585197945</v>
       </c>
       <c r="O38">
-        <v>-3.273229535159965</v>
+        <v>-4.01374517039589</v>
       </c>
       <c r="P38">
-        <v>-13.09291814063986</v>
+        <v>-16.05498068158356</v>
       </c>
       <c r="Q38">
-        <v>355.4070818593601</v>
+        <v>352.4450193184164</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1030551436707738</v>
+        <v>0.1039639554750718</v>
       </c>
       <c r="T38">
-        <v>1.177226015953958</v>
+        <v>1.195912143191322</v>
       </c>
       <c r="U38">
         <v>0.1507577444416894</v>
       </c>
       <c r="V38">
-        <v>0.1754433158958583</v>
+        <v>0.1707016046554297</v>
       </c>
       <c r="W38">
-        <v>0.124308305859859</v>
+        <v>0.1250231555512598</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.8772165794792912</v>
+        <v>0.8535080232771483</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1117558595032614</v>
+        <v>0.1128054369476783</v>
       </c>
       <c r="C39">
-        <v>591.3324198904453</v>
+        <v>546.4603427207767</v>
       </c>
       <c r="D39">
-        <v>1296.744559528709</v>
+        <v>1276.432269916831</v>
       </c>
       <c r="E39">
-        <v>-1079.066616140827</v>
+        <v>-1054.506828583036</v>
       </c>
       <c r="F39">
-        <v>908.7121396382637</v>
+        <v>933.2719271960545</v>
       </c>
       <c r="G39">
         <v>203.3</v>
@@ -4485,37 +4485,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M39">
-        <v>136.9953925186461</v>
+        <v>140.6979706948258</v>
       </c>
       <c r="N39">
-        <v>-20.06872585197945</v>
+        <v>-23.77130402815908</v>
       </c>
       <c r="O39">
-        <v>-4.01374517039589</v>
+        <v>-4.754260805631816</v>
       </c>
       <c r="P39">
-        <v>-16.05498068158356</v>
+        <v>-19.01704322252726</v>
       </c>
       <c r="Q39">
-        <v>352.4450193184164</v>
+        <v>349.4829567774727</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1039639554750718</v>
+        <v>0.1049020837891859</v>
       </c>
       <c r="T39">
-        <v>1.195912143191322</v>
+        <v>1.215201048726666</v>
       </c>
       <c r="U39">
         <v>0.1507577444416894</v>
       </c>
       <c r="V39">
-        <v>0.1707016046554297</v>
+        <v>0.1662094571644973</v>
       </c>
       <c r="W39">
-        <v>0.1250231555512598</v>
+        <v>0.1257003815746922</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.8535080232771483</v>
+        <v>0.8310472858224864</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1128054369476783</v>
+        <v>0.1138550143920952</v>
       </c>
       <c r="C40">
-        <v>546.4603427207767</v>
+        <v>502.2147975182677</v>
       </c>
       <c r="D40">
-        <v>1276.432269916831</v>
+        <v>1256.746512272113</v>
       </c>
       <c r="E40">
-        <v>-1054.506828583036</v>
+        <v>-1029.947041025245</v>
       </c>
       <c r="F40">
-        <v>933.2719271960545</v>
+        <v>957.8317147538455</v>
       </c>
       <c r="G40">
         <v>203.3</v>
@@ -4567,37 +4567,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M40">
-        <v>140.6979706948258</v>
+        <v>144.4005488710054</v>
       </c>
       <c r="N40">
-        <v>-23.77130402815908</v>
+        <v>-27.47388220433871</v>
       </c>
       <c r="O40">
-        <v>-4.754260805631816</v>
+        <v>-5.494776440867742</v>
       </c>
       <c r="P40">
-        <v>-19.01704322252726</v>
+        <v>-21.97910576347097</v>
       </c>
       <c r="Q40">
-        <v>349.4829567774727</v>
+        <v>346.520894236529</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1049020837891859</v>
+        <v>0.1058709704086807</v>
       </c>
       <c r="T40">
-        <v>1.215201048726666</v>
+        <v>1.235122377394317</v>
       </c>
       <c r="U40">
         <v>0.1507577444416894</v>
       </c>
       <c r="V40">
-        <v>0.1662094571644973</v>
+        <v>0.1619476762115615</v>
       </c>
       <c r="W40">
-        <v>0.1257003815746922</v>
+        <v>0.1263428780584614</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8310472858224864</v>
+        <v>0.8097383810578073</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1138550143920952</v>
+        <v>0.1371561026370947</v>
       </c>
       <c r="C41">
-        <v>502.2147975182677</v>
+        <v>157.1119861367199</v>
       </c>
       <c r="D41">
-        <v>1256.746512272113</v>
+        <v>936.2034884483563</v>
       </c>
       <c r="E41">
-        <v>-1029.947041025245</v>
+        <v>-1005.387253467454</v>
       </c>
       <c r="F41">
-        <v>957.8317147538455</v>
+        <v>982.3915023116365</v>
       </c>
       <c r="G41">
         <v>203.3</v>
@@ -4649,45 +4649,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M41">
-        <v>144.4005488710054</v>
+        <v>201.1522681720134</v>
       </c>
       <c r="N41">
-        <v>-27.47388220433871</v>
+        <v>-84.2256015053467</v>
       </c>
       <c r="O41">
-        <v>-5.494776440867742</v>
+        <v>-16.84512030106934</v>
       </c>
       <c r="P41">
-        <v>-21.97910576347097</v>
+        <v>-67.38048120427736</v>
       </c>
       <c r="Q41">
-        <v>346.520894236529</v>
+        <v>301.1195187957226</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1058709704086807</v>
+        <v>0.1079580045831297</v>
       </c>
       <c r="T41">
-        <v>1.235122377394317</v>
+        <v>1.278033996662517</v>
       </c>
       <c r="U41">
-        <v>0.1507577444416894</v>
+        <v>0.2047577444416894</v>
       </c>
       <c r="V41">
-        <v>0.1619476762115615</v>
+        <v>0.1162568712043336</v>
       </c>
       <c r="W41">
-        <v>0.1263428780584614</v>
+        <v>0.1809532497180421</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y41">
-        <v>0.8097383810578073</v>
+        <v>0.5812843560216681</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1371561026370947</v>
+        <v>0.1387456800815116</v>
       </c>
       <c r="C42">
-        <v>157.1119861367199</v>
+        <v>116.5410408003553</v>
       </c>
       <c r="D42">
-        <v>936.2034884483563</v>
+        <v>920.1923306697826</v>
       </c>
       <c r="E42">
-        <v>-1005.387253467454</v>
+        <v>-980.8274659096636</v>
       </c>
       <c r="F42">
-        <v>982.3915023116365</v>
+        <v>1006.951289869427</v>
       </c>
       <c r="G42">
         <v>203.3</v>
@@ -4731,37 +4731,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M42">
-        <v>201.1522681720134</v>
+        <v>206.1810748763137</v>
       </c>
       <c r="N42">
-        <v>-84.2256015053467</v>
+        <v>-89.25440820964704</v>
       </c>
       <c r="O42">
-        <v>-16.84512030106934</v>
+        <v>-17.85088164192941</v>
       </c>
       <c r="P42">
-        <v>-67.38048120427736</v>
+        <v>-71.40352656771763</v>
       </c>
       <c r="Q42">
-        <v>301.1195187957226</v>
+        <v>297.0964734322824</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1079580045831297</v>
+        <v>0.1090115300845387</v>
       </c>
       <c r="T42">
-        <v>1.278033996662517</v>
+        <v>1.299695589826288</v>
       </c>
       <c r="U42">
         <v>0.2047577444416894</v>
       </c>
       <c r="V42">
-        <v>0.1162568712043336</v>
+        <v>0.1134213377603255</v>
       </c>
       <c r="W42">
-        <v>0.1809532497180421</v>
+        <v>0.1815338471503261</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5812843560216681</v>
+        <v>0.5671066888016274</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1387456800815116</v>
+        <v>0.1403352575259285</v>
       </c>
       <c r="C43">
-        <v>116.5410408003553</v>
+        <v>76.50853955204593</v>
       </c>
       <c r="D43">
-        <v>920.1923306697826</v>
+        <v>904.7196169792643</v>
       </c>
       <c r="E43">
-        <v>-980.8274659096636</v>
+        <v>-956.2676783518725</v>
       </c>
       <c r="F43">
-        <v>1006.951289869427</v>
+        <v>1031.511077427218</v>
       </c>
       <c r="G43">
         <v>203.3</v>
@@ -4813,37 +4813,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M43">
-        <v>206.1810748763137</v>
+        <v>211.2098815806141</v>
       </c>
       <c r="N43">
-        <v>-89.25440820964704</v>
+        <v>-94.2832149139474</v>
       </c>
       <c r="O43">
-        <v>-17.85088164192941</v>
+        <v>-18.85664298278948</v>
       </c>
       <c r="P43">
-        <v>-71.40352656771763</v>
+        <v>-75.42657193115792</v>
       </c>
       <c r="Q43">
-        <v>297.0964734322824</v>
+        <v>293.0734280688421</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1090115300845387</v>
+        <v>0.1101013840515135</v>
       </c>
       <c r="T43">
-        <v>1.299695589826288</v>
+        <v>1.322104134478466</v>
       </c>
       <c r="U43">
         <v>0.2047577444416894</v>
       </c>
       <c r="V43">
-        <v>0.1134213377603255</v>
+        <v>0.110720829718413</v>
       </c>
       <c r="W43">
-        <v>0.1815338471503261</v>
+        <v>0.1820867970858348</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5671066888016274</v>
+        <v>0.5536041485920647</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1403352575259285</v>
+        <v>0.1419248349703454</v>
       </c>
       <c r="C44">
-        <v>76.50853955204616</v>
+        <v>36.98777029670123</v>
       </c>
       <c r="D44">
-        <v>904.7196169792643</v>
+        <v>889.7586352817103</v>
       </c>
       <c r="E44">
-        <v>-956.2676783518727</v>
+        <v>-931.7078907940818</v>
       </c>
       <c r="F44">
-        <v>1031.511077427218</v>
+        <v>1056.070864985009</v>
       </c>
       <c r="G44">
         <v>203.3</v>
@@ -4895,37 +4895,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M44">
-        <v>211.209881580614</v>
+        <v>216.2386882849144</v>
       </c>
       <c r="N44">
-        <v>-94.28321491394735</v>
+        <v>-99.31202161824771</v>
       </c>
       <c r="O44">
-        <v>-18.85664298278947</v>
+        <v>-19.86240432364954</v>
       </c>
       <c r="P44">
-        <v>-75.42657193115788</v>
+        <v>-79.44961729459817</v>
       </c>
       <c r="Q44">
-        <v>293.0734280688421</v>
+        <v>289.0503827054018</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1101013840515135</v>
+        <v>0.1112294785085576</v>
       </c>
       <c r="T44">
-        <v>1.322104134478466</v>
+        <v>1.345298943855281</v>
       </c>
       <c r="U44">
         <v>0.2047577444416894</v>
       </c>
       <c r="V44">
-        <v>0.110720829718413</v>
+        <v>0.1081459267017057</v>
       </c>
       <c r="W44">
-        <v>0.1820867970858348</v>
+        <v>0.1826140284196918</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5536041485920649</v>
+        <v>0.5407296335085284</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1419248349703454</v>
+        <v>0.1435144124147623</v>
       </c>
       <c r="C45">
-        <v>36.98777029670123</v>
+        <v>-2.046240895732581</v>
       </c>
       <c r="D45">
-        <v>889.7586352817103</v>
+        <v>875.2844116470676</v>
       </c>
       <c r="E45">
-        <v>-931.7078907940818</v>
+        <v>-907.1481032362908</v>
       </c>
       <c r="F45">
-        <v>1056.070864985009</v>
+        <v>1080.6306525428</v>
       </c>
       <c r="G45">
         <v>203.3</v>
@@ -4977,37 +4977,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M45">
-        <v>216.2386882849144</v>
+        <v>221.2674949892147</v>
       </c>
       <c r="N45">
-        <v>-99.31202161824771</v>
+        <v>-104.340828322548</v>
       </c>
       <c r="O45">
-        <v>-19.86240432364954</v>
+        <v>-20.86816566450961</v>
       </c>
       <c r="P45">
-        <v>-79.44961729459817</v>
+        <v>-83.47266265803844</v>
       </c>
       <c r="Q45">
-        <v>289.0503827054018</v>
+        <v>285.0273373419616</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1112294785085576</v>
+        <v>0.1123978620533533</v>
       </c>
       <c r="T45">
-        <v>1.345298943855281</v>
+        <v>1.369322139281268</v>
       </c>
       <c r="U45">
         <v>0.2047577444416894</v>
       </c>
       <c r="V45">
-        <v>0.1081459267017057</v>
+        <v>0.1056880647312124</v>
       </c>
       <c r="W45">
-        <v>0.1826140284196918</v>
+        <v>0.1831172946929191</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5407296335085284</v>
+        <v>0.5284403236560619</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1435144124147623</v>
+        <v>0.1451039898591791</v>
       </c>
       <c r="C46">
-        <v>-2.046240895732581</v>
+        <v>-40.616868905925</v>
       </c>
       <c r="D46">
-        <v>875.2844116470676</v>
+        <v>861.2735711946659</v>
       </c>
       <c r="E46">
-        <v>-907.1481032362908</v>
+        <v>-882.5883156785001</v>
       </c>
       <c r="F46">
-        <v>1080.6306525428</v>
+        <v>1105.190440100591</v>
       </c>
       <c r="G46">
         <v>203.3</v>
@@ -5059,37 +5059,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M46">
-        <v>221.2674949892147</v>
+        <v>226.296301693515</v>
       </c>
       <c r="N46">
-        <v>-104.340828322548</v>
+        <v>-109.3696350268484</v>
       </c>
       <c r="O46">
-        <v>-20.86816566450961</v>
+        <v>-21.87392700536967</v>
       </c>
       <c r="P46">
-        <v>-83.47266265803844</v>
+        <v>-87.49570802147869</v>
       </c>
       <c r="Q46">
-        <v>285.0273373419616</v>
+        <v>281.0042919785213</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1123978620533533</v>
+        <v>0.1136087322725051</v>
       </c>
       <c r="T46">
-        <v>1.369322139281268</v>
+        <v>1.394218905450018</v>
       </c>
       <c r="U46">
         <v>0.2047577444416894</v>
       </c>
       <c r="V46">
-        <v>0.1056880647312124</v>
+        <v>0.1033394410705188</v>
       </c>
       <c r="W46">
-        <v>0.1831172946929191</v>
+        <v>0.1835981935762251</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5284403236560619</v>
+        <v>0.5166972053525939</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1451039898591791</v>
+        <v>0.146693567303596</v>
       </c>
       <c r="C47">
-        <v>-40.616868905925</v>
+        <v>-78.74601553022444</v>
       </c>
       <c r="D47">
-        <v>861.2735711946659</v>
+        <v>847.7042121281575</v>
       </c>
       <c r="E47">
-        <v>-882.5883156785001</v>
+        <v>-858.0285281207091</v>
       </c>
       <c r="F47">
-        <v>1105.190440100591</v>
+        <v>1129.750227658382</v>
       </c>
       <c r="G47">
         <v>203.3</v>
@@ -5141,37 +5141,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M47">
-        <v>226.296301693515</v>
+        <v>231.3251083978154</v>
       </c>
       <c r="N47">
-        <v>-109.3696350268484</v>
+        <v>-114.3984417311487</v>
       </c>
       <c r="O47">
-        <v>-21.87392700536967</v>
+        <v>-22.87968834622974</v>
       </c>
       <c r="P47">
-        <v>-87.49570802147869</v>
+        <v>-91.51875338491895</v>
       </c>
       <c r="Q47">
-        <v>281.0042919785213</v>
+        <v>276.981246615081</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1136087322725051</v>
+        <v>0.1148644495368108</v>
       </c>
       <c r="T47">
-        <v>1.394218905450018</v>
+        <v>1.420037774069463</v>
       </c>
       <c r="U47">
         <v>0.2047577444416894</v>
       </c>
       <c r="V47">
-        <v>0.1033394410705188</v>
+        <v>0.1010929314820292</v>
       </c>
       <c r="W47">
-        <v>0.1835981935762251</v>
+        <v>0.1840581838124308</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5166972053525939</v>
+        <v>0.5054646574101462</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.146693567303596</v>
+        <v>0.1649986682034073</v>
       </c>
       <c r="C48">
-        <v>-78.74601553022444</v>
+        <v>-233.4860422641891</v>
       </c>
       <c r="D48">
-        <v>847.7042121281575</v>
+        <v>717.5239729519838</v>
       </c>
       <c r="E48">
-        <v>-858.0285281207091</v>
+        <v>-833.4687405629181</v>
       </c>
       <c r="F48">
-        <v>1129.750227658382</v>
+        <v>1154.310015216173</v>
       </c>
       <c r="G48">
         <v>203.3</v>
@@ -5223,45 +5223,45 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M48">
-        <v>231.3251083978154</v>
+        <v>276.7547656346817</v>
       </c>
       <c r="N48">
-        <v>-114.3984417311487</v>
+        <v>-159.8280989680151</v>
       </c>
       <c r="O48">
-        <v>-22.87968834622974</v>
+        <v>-31.96561979360301</v>
       </c>
       <c r="P48">
-        <v>-91.51875338491895</v>
+        <v>-127.8624791744121</v>
       </c>
       <c r="Q48">
-        <v>276.981246615081</v>
+        <v>240.637520825588</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1148644495368108</v>
+        <v>0.1166685400099476</v>
       </c>
       <c r="T48">
-        <v>1.420037774069463</v>
+        <v>1.457131773035279</v>
       </c>
       <c r="U48">
-        <v>0.2047577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V48">
-        <v>0.1010929314820292</v>
+        <v>0.08449839438068482</v>
       </c>
       <c r="W48">
-        <v>0.1840581838124308</v>
+        <v>0.2194985999960321</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.5054646574101462</v>
+        <v>0.4224919719034241</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1649986682034073</v>
+        <v>0.1669382456478242</v>
       </c>
       <c r="C49">
-        <v>-233.4860422641891</v>
+        <v>-269.5343015785552</v>
       </c>
       <c r="D49">
-        <v>717.5239729519838</v>
+        <v>706.0355011954085</v>
       </c>
       <c r="E49">
-        <v>-833.4687405629181</v>
+        <v>-808.9089530051272</v>
       </c>
       <c r="F49">
-        <v>1154.310015216173</v>
+        <v>1178.869802773964</v>
       </c>
       <c r="G49">
         <v>203.3</v>
@@ -5305,37 +5305,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M49">
-        <v>276.7547656346817</v>
+        <v>282.6431649035048</v>
       </c>
       <c r="N49">
-        <v>-159.8280989680151</v>
+        <v>-165.7164982368381</v>
       </c>
       <c r="O49">
-        <v>-31.96561979360301</v>
+        <v>-33.14329964736762</v>
       </c>
       <c r="P49">
-        <v>-127.8624791744121</v>
+        <v>-132.5731985894705</v>
       </c>
       <c r="Q49">
-        <v>240.637520825588</v>
+        <v>235.9268014105295</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1166685400099476</v>
+        <v>0.1180313965486005</v>
       </c>
       <c r="T49">
-        <v>1.457131773035279</v>
+        <v>1.485153537901342</v>
       </c>
       <c r="U49">
         <v>0.2397577444416894</v>
       </c>
       <c r="V49">
-        <v>0.08449839438068482</v>
+        <v>0.08273801116442055</v>
       </c>
       <c r="W49">
-        <v>0.2194985999960321</v>
+        <v>0.2199206655053166</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.4224919719034241</v>
+        <v>0.4136900558221027</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1669382456478242</v>
+        <v>0.1688778230922411</v>
       </c>
       <c r="C50">
-        <v>-269.534301578555</v>
+        <v>-305.2204683545569</v>
       </c>
       <c r="D50">
-        <v>706.0355011954085</v>
+        <v>694.9091219771975</v>
       </c>
       <c r="E50">
-        <v>-808.9089530051274</v>
+        <v>-784.3491654473364</v>
       </c>
       <c r="F50">
-        <v>1178.869802773964</v>
+        <v>1203.429590331755</v>
       </c>
       <c r="G50">
         <v>203.3</v>
@@ -5387,37 +5387,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M50">
-        <v>282.6431649035047</v>
+        <v>288.5315641723278</v>
       </c>
       <c r="N50">
-        <v>-165.716498236838</v>
+        <v>-171.6048975056611</v>
       </c>
       <c r="O50">
-        <v>-33.14329964736761</v>
+        <v>-34.32097950113222</v>
       </c>
       <c r="P50">
-        <v>-132.5731985894705</v>
+        <v>-137.2839180045289</v>
       </c>
       <c r="Q50">
-        <v>235.9268014105295</v>
+        <v>231.2160819954711</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1180313965486005</v>
+        <v>0.1194476984417103</v>
       </c>
       <c r="T50">
-        <v>1.485153537901342</v>
+        <v>1.514274195507251</v>
       </c>
       <c r="U50">
         <v>0.2397577444416894</v>
       </c>
       <c r="V50">
-        <v>0.08273801116442056</v>
+        <v>0.08104948032433035</v>
       </c>
       <c r="W50">
-        <v>0.2199206655053166</v>
+        <v>0.2203255038509569</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4136900558221028</v>
+        <v>0.4052474016216517</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1688778230922411</v>
+        <v>0.170817400536658</v>
       </c>
       <c r="C51">
-        <v>-305.2204683545569</v>
+        <v>-340.5613956026691</v>
       </c>
       <c r="D51">
-        <v>694.9091219771975</v>
+        <v>684.1279822868763</v>
       </c>
       <c r="E51">
-        <v>-784.3491654473364</v>
+        <v>-759.7893778895454</v>
       </c>
       <c r="F51">
-        <v>1203.429590331755</v>
+        <v>1227.989377889545</v>
       </c>
       <c r="G51">
         <v>203.3</v>
@@ -5469,37 +5469,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M51">
-        <v>288.5315641723278</v>
+        <v>294.4199634411508</v>
       </c>
       <c r="N51">
-        <v>-171.6048975056611</v>
+        <v>-177.4932967744841</v>
       </c>
       <c r="O51">
-        <v>-34.32097950113222</v>
+        <v>-35.49865935489682</v>
       </c>
       <c r="P51">
-        <v>-137.2839180045289</v>
+        <v>-141.9946374195873</v>
       </c>
       <c r="Q51">
-        <v>231.2160819954711</v>
+        <v>226.5053625804127</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1194476984417103</v>
+        <v>0.1209206524105445</v>
       </c>
       <c r="T51">
-        <v>1.514274195507251</v>
+        <v>1.544559679417396</v>
       </c>
       <c r="U51">
         <v>0.2397577444416894</v>
       </c>
       <c r="V51">
-        <v>0.08104948032433035</v>
+        <v>0.07942849071784373</v>
       </c>
       <c r="W51">
-        <v>0.2203255038509569</v>
+        <v>0.2207141486627715</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.4052474016216517</v>
+        <v>0.3971424535892186</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.170817400536658</v>
+        <v>0.1727569779810749</v>
       </c>
       <c r="C52">
-        <v>-340.5613956026691</v>
+        <v>-375.5729064500288</v>
       </c>
       <c r="D52">
-        <v>684.1279822868763</v>
+        <v>673.6762589973077</v>
       </c>
       <c r="E52">
-        <v>-759.7893778895454</v>
+        <v>-735.2295903317545</v>
       </c>
       <c r="F52">
-        <v>1227.989377889545</v>
+        <v>1252.549165447336</v>
       </c>
       <c r="G52">
         <v>203.3</v>
@@ -5551,37 +5551,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M52">
-        <v>294.4199634411508</v>
+        <v>300.3083627099738</v>
       </c>
       <c r="N52">
-        <v>-177.4932967744841</v>
+        <v>-183.3816960433072</v>
       </c>
       <c r="O52">
-        <v>-35.49865935489682</v>
+        <v>-36.67633920866143</v>
       </c>
       <c r="P52">
-        <v>-141.9946374195873</v>
+        <v>-146.7053568346457</v>
       </c>
       <c r="Q52">
-        <v>226.5053625804127</v>
+        <v>221.7946431653543</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1209206524105445</v>
+        <v>0.1224537269495352</v>
       </c>
       <c r="T52">
-        <v>1.544559679417396</v>
+        <v>1.576081305527955</v>
       </c>
       <c r="U52">
         <v>0.2397577444416894</v>
       </c>
       <c r="V52">
-        <v>0.07942849071784373</v>
+        <v>0.07787106933121934</v>
       </c>
       <c r="W52">
-        <v>0.2207141486627715</v>
+        <v>0.2210875525015738</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3971424535892186</v>
+        <v>0.3893553466560967</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1727569779810749</v>
+        <v>0.1746965554254918</v>
       </c>
       <c r="C53">
-        <v>-375.5729064500288</v>
+        <v>-410.269871626547</v>
       </c>
       <c r="D53">
-        <v>673.6762589973077</v>
+        <v>663.5390813785804</v>
       </c>
       <c r="E53">
-        <v>-735.2295903317545</v>
+        <v>-710.6698027739635</v>
       </c>
       <c r="F53">
-        <v>1252.549165447336</v>
+        <v>1277.108953005127</v>
       </c>
       <c r="G53">
         <v>203.3</v>
@@ -5633,37 +5633,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M53">
-        <v>300.3083627099738</v>
+        <v>306.1967619787969</v>
       </c>
       <c r="N53">
-        <v>-183.3816960433072</v>
+        <v>-189.2700953121302</v>
       </c>
       <c r="O53">
-        <v>-36.67633920866143</v>
+        <v>-37.85401906242604</v>
       </c>
       <c r="P53">
-        <v>-146.7053568346457</v>
+        <v>-151.4160762497042</v>
       </c>
       <c r="Q53">
-        <v>221.7946431653543</v>
+        <v>217.0839237502958</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1224537269495352</v>
+        <v>0.1240506795943172</v>
       </c>
       <c r="T53">
-        <v>1.576081305527955</v>
+        <v>1.608916332726454</v>
       </c>
       <c r="U53">
         <v>0.2397577444416894</v>
       </c>
       <c r="V53">
-        <v>0.07787106933121934</v>
+        <v>0.07637354876715742</v>
       </c>
       <c r="W53">
-        <v>0.2210875525015738</v>
+        <v>0.2214465946542684</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3893553466560967</v>
+        <v>0.3818677438357871</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1746965554254918</v>
+        <v>0.1766361328699087</v>
       </c>
       <c r="C54">
-        <v>-410.269871626547</v>
+        <v>-444.6662800588683</v>
       </c>
       <c r="D54">
-        <v>663.5390813785804</v>
+        <v>653.70246050405</v>
       </c>
       <c r="E54">
-        <v>-710.6698027739635</v>
+        <v>-686.1100152161725</v>
       </c>
       <c r="F54">
-        <v>1277.108953005127</v>
+        <v>1301.668740562918</v>
       </c>
       <c r="G54">
         <v>203.3</v>
@@ -5715,37 +5715,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M54">
-        <v>306.1967619787969</v>
+        <v>312.0851612476199</v>
       </c>
       <c r="N54">
-        <v>-189.2700953121302</v>
+        <v>-195.1584945809532</v>
       </c>
       <c r="O54">
-        <v>-37.85401906242604</v>
+        <v>-39.03169891619065</v>
       </c>
       <c r="P54">
-        <v>-151.4160762497042</v>
+        <v>-156.1267956647626</v>
       </c>
       <c r="Q54">
-        <v>217.0839237502958</v>
+        <v>212.3732043352374</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1240506795943172</v>
+        <v>0.125715587670792</v>
       </c>
       <c r="T54">
-        <v>1.608916332726454</v>
+        <v>1.643148595124889</v>
       </c>
       <c r="U54">
         <v>0.2397577444416894</v>
       </c>
       <c r="V54">
-        <v>0.07637354876715742</v>
+        <v>0.07493253841306011</v>
       </c>
       <c r="W54">
-        <v>0.2214465946542684</v>
+        <v>0.2217920880464838</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3818677438357871</v>
+        <v>0.3746626920653006</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1766361328699087</v>
+        <v>0.1785757103143256</v>
       </c>
       <c r="C55">
-        <v>-444.6662800588683</v>
+        <v>-478.7753032769465</v>
       </c>
       <c r="D55">
-        <v>653.70246050405</v>
+        <v>644.1532248437627</v>
       </c>
       <c r="E55">
-        <v>-686.1100152161725</v>
+        <v>-661.5502276583818</v>
       </c>
       <c r="F55">
-        <v>1301.668740562918</v>
+        <v>1326.228528120709</v>
       </c>
       <c r="G55">
         <v>203.3</v>
@@ -5797,37 +5797,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M55">
-        <v>312.0851612476199</v>
+        <v>317.9735605164429</v>
       </c>
       <c r="N55">
-        <v>-195.1584945809532</v>
+        <v>-201.0468938497762</v>
       </c>
       <c r="O55">
-        <v>-39.03169891619065</v>
+        <v>-40.20937876995524</v>
       </c>
       <c r="P55">
-        <v>-156.1267956647626</v>
+        <v>-160.837515079821</v>
       </c>
       <c r="Q55">
-        <v>212.3732043352374</v>
+        <v>207.662484920179</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.125715587670792</v>
+        <v>0.1274528830549397</v>
       </c>
       <c r="T55">
-        <v>1.643148595124889</v>
+        <v>1.678869216758039</v>
       </c>
       <c r="U55">
         <v>0.2397577444416894</v>
       </c>
       <c r="V55">
-        <v>0.07493253841306011</v>
+        <v>0.07354489881281827</v>
       </c>
       <c r="W55">
-        <v>0.2217920880464838</v>
+        <v>0.2221247853871358</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3746626920653006</v>
+        <v>0.3677244940640912</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1785757103143256</v>
+        <v>0.1805152877587425</v>
       </c>
       <c r="C56">
-        <v>-478.7753032769465</v>
+        <v>-512.6093542568133</v>
       </c>
       <c r="D56">
-        <v>644.1532248437627</v>
+        <v>634.8789614216868</v>
       </c>
       <c r="E56">
-        <v>-661.5502276583818</v>
+        <v>-636.9904401005908</v>
       </c>
       <c r="F56">
-        <v>1326.228528120709</v>
+        <v>1350.7883156785</v>
       </c>
       <c r="G56">
         <v>203.3</v>
@@ -5879,37 +5879,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M56">
-        <v>317.9735605164429</v>
+        <v>323.8619597852659</v>
       </c>
       <c r="N56">
-        <v>-201.0468938497762</v>
+        <v>-206.9352931185992</v>
       </c>
       <c r="O56">
-        <v>-40.20937876995524</v>
+        <v>-41.38705862371985</v>
       </c>
       <c r="P56">
-        <v>-160.837515079821</v>
+        <v>-165.5482344948794</v>
       </c>
       <c r="Q56">
-        <v>207.662484920179</v>
+        <v>202.9517655051206</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1274528830549397</v>
+        <v>0.1292673915672717</v>
       </c>
       <c r="T56">
-        <v>1.678869216758039</v>
+        <v>1.716177421574884</v>
       </c>
       <c r="U56">
         <v>0.2397577444416894</v>
       </c>
       <c r="V56">
-        <v>0.07354489881281827</v>
+        <v>0.07220771883440338</v>
       </c>
       <c r="W56">
-        <v>0.2221247853871358</v>
+        <v>0.2224453846426732</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3677244940640912</v>
+        <v>0.3610385941720169</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1805152877587425</v>
+        <v>0.1824548652031594</v>
       </c>
       <c r="C57">
-        <v>-512.6093542568133</v>
+        <v>-546.1801412523312</v>
       </c>
       <c r="D57">
-        <v>634.8789614216868</v>
+        <v>625.8679619839598</v>
       </c>
       <c r="E57">
-        <v>-636.9904401005908</v>
+        <v>-612.4306525427999</v>
       </c>
       <c r="F57">
-        <v>1350.7883156785</v>
+        <v>1375.348103236291</v>
       </c>
       <c r="G57">
         <v>203.3</v>
@@ -5961,37 +5961,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M57">
-        <v>323.8619597852659</v>
+        <v>329.7503590540889</v>
       </c>
       <c r="N57">
-        <v>-206.9352931185992</v>
+        <v>-212.8236923874222</v>
       </c>
       <c r="O57">
-        <v>-41.38705862371985</v>
+        <v>-42.56473847748445</v>
       </c>
       <c r="P57">
-        <v>-165.5482344948794</v>
+        <v>-170.2589539099378</v>
       </c>
       <c r="Q57">
-        <v>202.9517655051206</v>
+        <v>198.2410460900622</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1292673915672717</v>
+        <v>0.1311643777392551</v>
       </c>
       <c r="T57">
-        <v>1.716177421574884</v>
+        <v>1.755181453883405</v>
       </c>
       <c r="U57">
         <v>0.2397577444416894</v>
       </c>
       <c r="V57">
-        <v>0.07220771883440338</v>
+        <v>0.07091829528378904</v>
       </c>
       <c r="W57">
-        <v>0.2224453846426732</v>
+        <v>0.2227545339247984</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3610385941720169</v>
+        <v>0.3545914764189452</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1824548652031594</v>
+        <v>0.1843944426475763</v>
       </c>
       <c r="C58">
-        <v>-546.1801412523312</v>
+        <v>-579.4987171068078</v>
       </c>
       <c r="D58">
-        <v>625.8679619839598</v>
+        <v>617.1091736872742</v>
       </c>
       <c r="E58">
-        <v>-612.4306525427999</v>
+        <v>-587.8708649850089</v>
       </c>
       <c r="F58">
-        <v>1375.348103236291</v>
+        <v>1399.907890794082</v>
       </c>
       <c r="G58">
         <v>203.3</v>
@@ -6043,37 +6043,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M58">
-        <v>329.7503590540889</v>
+        <v>335.6387583229119</v>
       </c>
       <c r="N58">
-        <v>-212.8236923874222</v>
+        <v>-218.7120916562453</v>
       </c>
       <c r="O58">
-        <v>-42.56473847748445</v>
+        <v>-43.74241833124906</v>
       </c>
       <c r="P58">
-        <v>-170.2589539099378</v>
+        <v>-174.9696733249962</v>
       </c>
       <c r="Q58">
-        <v>198.2410460900622</v>
+        <v>193.5303266750038</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1311643777392551</v>
+        <v>0.1331495958262145</v>
       </c>
       <c r="T58">
-        <v>1.755181453883405</v>
+        <v>1.79599962722953</v>
       </c>
       <c r="U58">
         <v>0.2397577444416894</v>
       </c>
       <c r="V58">
-        <v>0.07091829528378904</v>
+        <v>0.06967411466477519</v>
       </c>
       <c r="W58">
-        <v>0.2227545339247984</v>
+        <v>0.2230528358636913</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3545914764189452</v>
+        <v>0.348370573323876</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1843944426475763</v>
+        <v>0.1863340200919932</v>
       </c>
       <c r="C59">
-        <v>-579.4987171068078</v>
+        <v>-612.5755244811746</v>
       </c>
       <c r="D59">
-        <v>617.1091736872742</v>
+        <v>608.5921538706983</v>
       </c>
       <c r="E59">
-        <v>-587.8708649850089</v>
+        <v>-563.3110774272179</v>
       </c>
       <c r="F59">
-        <v>1399.907890794082</v>
+        <v>1424.467678351873</v>
       </c>
       <c r="G59">
         <v>203.3</v>
@@ -6125,37 +6125,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M59">
-        <v>335.6387583229119</v>
+        <v>341.527157591735</v>
       </c>
       <c r="N59">
-        <v>-218.7120916562453</v>
+        <v>-224.6004909250683</v>
       </c>
       <c r="O59">
-        <v>-43.74241833124906</v>
+        <v>-44.92009818501366</v>
       </c>
       <c r="P59">
-        <v>-174.9696733249962</v>
+        <v>-179.6803927400546</v>
       </c>
       <c r="Q59">
-        <v>193.5303266750038</v>
+        <v>188.8196072599454</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1331495958262145</v>
+        <v>0.1352293481077911</v>
       </c>
       <c r="T59">
-        <v>1.79599962722953</v>
+        <v>1.838761523115948</v>
       </c>
       <c r="U59">
         <v>0.2397577444416894</v>
       </c>
       <c r="V59">
-        <v>0.06967411466477519</v>
+        <v>0.06847283682572734</v>
       </c>
       <c r="W59">
-        <v>0.2230528358636913</v>
+        <v>0.2233408515288292</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.348370573323876</v>
+        <v>0.3423641841286367</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1863340200919931</v>
+        <v>0.18827359753641</v>
       </c>
       <c r="C60">
-        <v>-612.5755244811742</v>
+        <v>-645.420437387857</v>
       </c>
       <c r="D60">
-        <v>608.5921538706983</v>
+        <v>600.3070285218065</v>
       </c>
       <c r="E60">
-        <v>-563.3110774272184</v>
+        <v>-538.7512898694274</v>
       </c>
       <c r="F60">
-        <v>1424.467678351873</v>
+        <v>1449.027465909664</v>
       </c>
       <c r="G60">
         <v>203.3</v>
@@ -6207,37 +6207,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M60">
-        <v>341.5271575917349</v>
+        <v>347.4155568605579</v>
       </c>
       <c r="N60">
-        <v>-224.6004909250682</v>
+        <v>-230.4888901938912</v>
       </c>
       <c r="O60">
-        <v>-44.92009818501364</v>
+        <v>-46.09777803877824</v>
       </c>
       <c r="P60">
-        <v>-179.6803927400545</v>
+        <v>-184.391112155113</v>
       </c>
       <c r="Q60">
-        <v>188.8196072599455</v>
+        <v>184.108887844887</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.135229348107791</v>
+        <v>0.1374105517201762</v>
       </c>
       <c r="T60">
-        <v>1.838761523115947</v>
+        <v>1.883609365143165</v>
       </c>
       <c r="U60">
         <v>0.2397577444416894</v>
       </c>
       <c r="V60">
-        <v>0.06847283682572737</v>
+        <v>0.06731228026935909</v>
       </c>
       <c r="W60">
-        <v>0.2233408515288292</v>
+        <v>0.223619103951081</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3423641841286368</v>
+        <v>0.3365614013467955</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.18827359753641</v>
+        <v>0.190213174980827</v>
       </c>
       <c r="C61">
-        <v>-645.420437387857</v>
+        <v>-678.0427993776582</v>
       </c>
       <c r="D61">
-        <v>600.3070285218065</v>
+        <v>592.2444540897962</v>
       </c>
       <c r="E61">
-        <v>-538.7512898694274</v>
+        <v>-514.1915023116364</v>
       </c>
       <c r="F61">
-        <v>1449.027465909664</v>
+        <v>1473.587253467455</v>
       </c>
       <c r="G61">
         <v>203.3</v>
@@ -6289,37 +6289,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M61">
-        <v>347.4155568605579</v>
+        <v>353.3039561293809</v>
       </c>
       <c r="N61">
-        <v>-230.4888901938912</v>
+        <v>-236.3772894627143</v>
       </c>
       <c r="O61">
-        <v>-46.09777803877824</v>
+        <v>-47.27545789254285</v>
       </c>
       <c r="P61">
-        <v>-184.391112155113</v>
+        <v>-189.1018315701714</v>
       </c>
       <c r="Q61">
-        <v>184.108887844887</v>
+        <v>179.3981684298286</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1374105517201762</v>
+        <v>0.1397008155131806</v>
       </c>
       <c r="T61">
-        <v>1.883609365143165</v>
+        <v>1.930699599271745</v>
       </c>
       <c r="U61">
         <v>0.2397577444416894</v>
       </c>
       <c r="V61">
-        <v>0.06731228026935909</v>
+        <v>0.06619040893153644</v>
       </c>
       <c r="W61">
-        <v>0.223619103951081</v>
+        <v>0.2238880812925912</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3365614013467955</v>
+        <v>0.3309520446576822</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.190213174980827</v>
+        <v>0.1921527524252438</v>
       </c>
       <c r="C62">
-        <v>-678.0427993776582</v>
+        <v>-710.4514586901521</v>
       </c>
       <c r="D62">
-        <v>592.2444540897962</v>
+        <v>584.3955823350933</v>
       </c>
       <c r="E62">
-        <v>-514.1915023116364</v>
+        <v>-489.6317147538455</v>
       </c>
       <c r="F62">
-        <v>1473.587253467455</v>
+        <v>1498.147041025245</v>
       </c>
       <c r="G62">
         <v>203.3</v>
@@ -6371,37 +6371,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M62">
-        <v>353.3039561293809</v>
+        <v>359.192355398204</v>
       </c>
       <c r="N62">
-        <v>-236.3772894627143</v>
+        <v>-242.2656887315373</v>
       </c>
       <c r="O62">
-        <v>-47.27545789254285</v>
+        <v>-48.45313774630746</v>
       </c>
       <c r="P62">
-        <v>-189.1018315701714</v>
+        <v>-193.8125509852298</v>
       </c>
       <c r="Q62">
-        <v>179.3981684298286</v>
+        <v>174.6874490147702</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1397008155131806</v>
+        <v>0.1421085287314673</v>
       </c>
       <c r="T62">
-        <v>1.930699599271745</v>
+        <v>1.98020471720179</v>
       </c>
       <c r="U62">
         <v>0.2397577444416894</v>
       </c>
       <c r="V62">
-        <v>0.06619040893153644</v>
+        <v>0.06510532026052765</v>
       </c>
       <c r="W62">
-        <v>0.2238880812925912</v>
+        <v>0.2241482397048715</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3309520446576822</v>
+        <v>0.3255266013026382</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1921527524252438</v>
+        <v>0.1940923298696607</v>
       </c>
       <c r="C63">
-        <v>-710.4514586901521</v>
+        <v>-742.6548006456003</v>
       </c>
       <c r="D63">
-        <v>584.3955823350933</v>
+        <v>576.7520279374362</v>
       </c>
       <c r="E63">
-        <v>-489.6317147538455</v>
+        <v>-465.0719271960545</v>
       </c>
       <c r="F63">
-        <v>1498.147041025245</v>
+        <v>1522.706828583036</v>
       </c>
       <c r="G63">
         <v>203.3</v>
@@ -6453,37 +6453,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M63">
-        <v>359.192355398204</v>
+        <v>365.080754667027</v>
       </c>
       <c r="N63">
-        <v>-242.2656887315373</v>
+        <v>-248.1540880003603</v>
       </c>
       <c r="O63">
-        <v>-48.45313774630746</v>
+        <v>-49.63081760007207</v>
       </c>
       <c r="P63">
-        <v>-193.8125509852298</v>
+        <v>-198.5232704002883</v>
       </c>
       <c r="Q63">
-        <v>174.6874490147702</v>
+        <v>169.9767295997117</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1421085287314673</v>
+        <v>0.1446429636980848</v>
       </c>
       <c r="T63">
-        <v>1.98020471720179</v>
+        <v>2.032315367654468</v>
       </c>
       <c r="U63">
         <v>0.2397577444416894</v>
       </c>
       <c r="V63">
-        <v>0.06510532026052765</v>
+        <v>0.06405523444987397</v>
       </c>
       <c r="W63">
-        <v>0.2241482397048715</v>
+        <v>0.224400005910304</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3255266013026382</v>
+        <v>0.3202761722493699</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1940923298696607</v>
+        <v>0.1960319073140776</v>
       </c>
       <c r="C64">
-        <v>-742.6548006456003</v>
+        <v>-774.6607775276766</v>
       </c>
       <c r="D64">
-        <v>576.7520279374362</v>
+        <v>569.3058386131507</v>
       </c>
       <c r="E64">
-        <v>-465.0719271960545</v>
+        <v>-440.5121396382635</v>
       </c>
       <c r="F64">
-        <v>1522.706828583036</v>
+        <v>1547.266616140827</v>
       </c>
       <c r="G64">
         <v>203.3</v>
@@ -6535,37 +6535,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M64">
-        <v>365.080754667027</v>
+        <v>370.96915393585</v>
       </c>
       <c r="N64">
-        <v>-248.1540880003603</v>
+        <v>-254.0424872691834</v>
       </c>
       <c r="O64">
-        <v>-49.63081760007207</v>
+        <v>-50.80849745383668</v>
       </c>
       <c r="P64">
-        <v>-198.5232704002883</v>
+        <v>-203.2339898153467</v>
       </c>
       <c r="Q64">
-        <v>169.9767295997117</v>
+        <v>165.2660101846533</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1446429636980848</v>
+        <v>0.1473143951493844</v>
       </c>
       <c r="T64">
-        <v>2.032315367654468</v>
+        <v>2.087242810023508</v>
       </c>
       <c r="U64">
         <v>0.2397577444416894</v>
       </c>
       <c r="V64">
-        <v>0.06405523444987397</v>
+        <v>0.06303848469670136</v>
       </c>
       <c r="W64">
-        <v>0.224400005910304</v>
+        <v>0.2246437795377863</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3202761722493699</v>
+        <v>0.3151924234835068</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1960319073140776</v>
+        <v>0.1979714847584945</v>
       </c>
       <c r="C65">
-        <v>-774.6607775276766</v>
+        <v>-806.476936180889</v>
       </c>
       <c r="D65">
-        <v>569.3058386131507</v>
+        <v>562.0494675177293</v>
       </c>
       <c r="E65">
-        <v>-440.5121396382635</v>
+        <v>-415.9523520804726</v>
       </c>
       <c r="F65">
-        <v>1547.266616140827</v>
+        <v>1571.826403698618</v>
       </c>
       <c r="G65">
         <v>203.3</v>
@@ -6617,37 +6617,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M65">
-        <v>370.96915393585</v>
+        <v>376.8575532046731</v>
       </c>
       <c r="N65">
-        <v>-254.0424872691834</v>
+        <v>-259.9308865380064</v>
       </c>
       <c r="O65">
-        <v>-50.80849745383668</v>
+        <v>-51.98617730760128</v>
       </c>
       <c r="P65">
-        <v>-203.2339898153467</v>
+        <v>-207.9447092304051</v>
       </c>
       <c r="Q65">
-        <v>165.2660101846533</v>
+        <v>160.5552907695949</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1473143951493844</v>
+        <v>0.1501342394590895</v>
       </c>
       <c r="T65">
-        <v>2.087242810023508</v>
+        <v>2.145221776968605</v>
       </c>
       <c r="U65">
         <v>0.2397577444416894</v>
       </c>
       <c r="V65">
-        <v>0.06303848469670136</v>
+        <v>0.06205350837331541</v>
       </c>
       <c r="W65">
-        <v>0.2246437795377863</v>
+        <v>0.2248799352394098</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3151924234835068</v>
+        <v>0.310267541866577</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1979714847584945</v>
+        <v>0.1999110622029114</v>
       </c>
       <c r="C66">
-        <v>-806.476936180889</v>
+        <v>-838.1104435240161</v>
       </c>
       <c r="D66">
-        <v>562.0494675177293</v>
+        <v>554.9757477323931</v>
       </c>
       <c r="E66">
-        <v>-415.9523520804726</v>
+        <v>-391.3925645226818</v>
       </c>
       <c r="F66">
-        <v>1571.826403698618</v>
+        <v>1596.386191256409</v>
       </c>
       <c r="G66">
         <v>203.3</v>
@@ -6699,37 +6699,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M66">
-        <v>376.8575532046731</v>
+        <v>382.7459524734961</v>
       </c>
       <c r="N66">
-        <v>-259.9308865380064</v>
+        <v>-265.8192858068294</v>
       </c>
       <c r="O66">
-        <v>-51.98617730760128</v>
+        <v>-53.16385716136588</v>
       </c>
       <c r="P66">
-        <v>-207.9447092304051</v>
+        <v>-212.6554286454635</v>
       </c>
       <c r="Q66">
-        <v>160.5552907695949</v>
+        <v>155.8445713545365</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1501342394590895</v>
+        <v>0.1531152177293492</v>
       </c>
       <c r="T66">
-        <v>2.145221776968605</v>
+        <v>2.206513827739137</v>
       </c>
       <c r="U66">
         <v>0.2397577444416894</v>
       </c>
       <c r="V66">
-        <v>0.06205350837331541</v>
+        <v>0.06109883901372594</v>
       </c>
       <c r="W66">
-        <v>0.2248799352394098</v>
+        <v>0.2251088246117526</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.310267541866577</v>
+        <v>0.3054941950686297</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1999110622029114</v>
+        <v>0.2018506396473283</v>
       </c>
       <c r="C67">
-        <v>-838.1104435240161</v>
+        <v>-869.5681101608857</v>
       </c>
       <c r="D67">
-        <v>554.9757477323931</v>
+        <v>548.0778686533145</v>
       </c>
       <c r="E67">
-        <v>-391.3925645226818</v>
+        <v>-366.8327769648909</v>
       </c>
       <c r="F67">
-        <v>1596.386191256409</v>
+        <v>1620.9459788142</v>
       </c>
       <c r="G67">
         <v>203.3</v>
@@ -6781,37 +6781,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M67">
-        <v>382.7459524734961</v>
+        <v>388.634351742319</v>
       </c>
       <c r="N67">
-        <v>-265.8192858068294</v>
+        <v>-271.7076850756524</v>
       </c>
       <c r="O67">
-        <v>-53.16385716136588</v>
+        <v>-54.34153701513048</v>
       </c>
       <c r="P67">
-        <v>-212.6554286454635</v>
+        <v>-217.3661480605219</v>
       </c>
       <c r="Q67">
-        <v>155.8445713545365</v>
+        <v>151.1338519394781</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1531152177293492</v>
+        <v>0.1562715476625654</v>
       </c>
       <c r="T67">
-        <v>2.206513827739137</v>
+        <v>2.271411293260877</v>
       </c>
       <c r="U67">
         <v>0.2397577444416894</v>
       </c>
       <c r="V67">
-        <v>0.06109883901372594</v>
+        <v>0.0601730990286695</v>
       </c>
       <c r="W67">
-        <v>0.2251088246117526</v>
+        <v>0.2253307779425092</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3054941950686297</v>
+        <v>0.3008654951433475</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2018506396473283</v>
+        <v>0.2037902170917452</v>
       </c>
       <c r="C68">
-        <v>-869.5681101608857</v>
+        <v>-900.8564122519958</v>
       </c>
       <c r="D68">
-        <v>548.0778686533145</v>
+        <v>541.3493541199953</v>
       </c>
       <c r="E68">
-        <v>-366.8327769648909</v>
+        <v>-342.2729894070999</v>
       </c>
       <c r="F68">
-        <v>1620.9459788142</v>
+        <v>1645.505766371991</v>
       </c>
       <c r="G68">
         <v>203.3</v>
@@ -6863,37 +6863,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M68">
-        <v>388.634351742319</v>
+        <v>394.5227510111421</v>
       </c>
       <c r="N68">
-        <v>-271.7076850756524</v>
+        <v>-277.5960843444754</v>
       </c>
       <c r="O68">
-        <v>-54.34153701513048</v>
+        <v>-55.51921686889509</v>
       </c>
       <c r="P68">
-        <v>-217.3661480605219</v>
+        <v>-222.0768674755803</v>
       </c>
       <c r="Q68">
-        <v>151.1338519394781</v>
+        <v>146.4231325244197</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1562715476625654</v>
+        <v>0.1596191703190068</v>
       </c>
       <c r="T68">
-        <v>2.271411293260877</v>
+        <v>2.340241938511206</v>
       </c>
       <c r="U68">
         <v>0.2397577444416894</v>
       </c>
       <c r="V68">
-        <v>0.0601730990286695</v>
+        <v>0.0592749930730177</v>
       </c>
       <c r="W68">
-        <v>0.2253307779425092</v>
+        <v>0.2255461058007059</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3008654951433475</v>
+        <v>0.2963749653650886</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2037902170917452</v>
+        <v>0.2057297945361621</v>
       </c>
       <c r="C69">
-        <v>-900.8564122519958</v>
+        <v>-931.9815117946241</v>
       </c>
       <c r="D69">
-        <v>541.3493541199953</v>
+        <v>534.784042135158</v>
       </c>
       <c r="E69">
-        <v>-342.2729894070999</v>
+        <v>-317.7132018493089</v>
       </c>
       <c r="F69">
-        <v>1645.505766371991</v>
+        <v>1670.065553929782</v>
       </c>
       <c r="G69">
         <v>203.3</v>
@@ -6945,37 +6945,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M69">
-        <v>394.5227510111421</v>
+        <v>400.4111502799651</v>
       </c>
       <c r="N69">
-        <v>-277.5960843444754</v>
+        <v>-283.4844836132984</v>
       </c>
       <c r="O69">
-        <v>-55.51921686889509</v>
+        <v>-56.69689672265969</v>
       </c>
       <c r="P69">
-        <v>-222.0768674755803</v>
+        <v>-226.7875868906387</v>
       </c>
       <c r="Q69">
-        <v>146.4231325244197</v>
+        <v>141.7124131093613</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1596191703190068</v>
+        <v>0.1631760193914757</v>
       </c>
       <c r="T69">
-        <v>2.340241938511206</v>
+        <v>2.413374499089681</v>
       </c>
       <c r="U69">
         <v>0.2397577444416894</v>
       </c>
       <c r="V69">
-        <v>0.0592749930730177</v>
+        <v>0.05840330199841451</v>
       </c>
       <c r="W69">
-        <v>0.2255461058007059</v>
+        <v>0.2257551004866027</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2963749653650886</v>
+        <v>0.2920165099920725</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2057297945361621</v>
+        <v>0.207669371980579</v>
       </c>
       <c r="C70">
-        <v>-931.9815117946241</v>
+        <v>-962.9492754449143</v>
       </c>
       <c r="D70">
-        <v>534.784042135158</v>
+        <v>528.3760660426587</v>
       </c>
       <c r="E70">
-        <v>-317.7132018493089</v>
+        <v>-293.1534142915179</v>
       </c>
       <c r="F70">
-        <v>1670.065553929782</v>
+        <v>1694.625341487573</v>
       </c>
       <c r="G70">
         <v>203.3</v>
@@ -7027,37 +7027,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M70">
-        <v>400.4111502799651</v>
+        <v>406.2995495487881</v>
       </c>
       <c r="N70">
-        <v>-283.4844836132984</v>
+        <v>-289.3728828821215</v>
       </c>
       <c r="O70">
-        <v>-56.69689672265969</v>
+        <v>-57.8745765764243</v>
       </c>
       <c r="P70">
-        <v>-226.7875868906387</v>
+        <v>-231.4983063056972</v>
       </c>
       <c r="Q70">
-        <v>141.7124131093613</v>
+        <v>137.0016936943028</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1631760193914757</v>
+        <v>0.1669623425976524</v>
       </c>
       <c r="T70">
-        <v>2.413374499089681</v>
+        <v>2.491225289382897</v>
       </c>
       <c r="U70">
         <v>0.2397577444416894</v>
       </c>
       <c r="V70">
-        <v>0.05840330199841451</v>
+        <v>0.05755687733177081</v>
       </c>
       <c r="W70">
-        <v>0.2257551004866027</v>
+        <v>0.225958037355517</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2920165099920725</v>
+        <v>0.2877843866588541</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.207669371980579</v>
+        <v>0.2096089494249959</v>
       </c>
       <c r="C71">
-        <v>-962.9492754449143</v>
+        <v>-993.7652920027899</v>
       </c>
       <c r="D71">
-        <v>528.3760660426587</v>
+        <v>522.119837042574</v>
       </c>
       <c r="E71">
-        <v>-293.1534142915179</v>
+        <v>-268.593626733727</v>
       </c>
       <c r="F71">
-        <v>1694.625341487573</v>
+        <v>1719.185129045364</v>
       </c>
       <c r="G71">
         <v>203.3</v>
@@ -7109,37 +7109,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M71">
-        <v>406.2995495487881</v>
+        <v>412.1879488176112</v>
       </c>
       <c r="N71">
-        <v>-289.3728828821215</v>
+        <v>-295.2612821509445</v>
       </c>
       <c r="O71">
-        <v>-57.8745765764243</v>
+        <v>-59.0522564301889</v>
       </c>
       <c r="P71">
-        <v>-231.4983063056972</v>
+        <v>-236.2090257207556</v>
       </c>
       <c r="Q71">
-        <v>137.0016936943028</v>
+        <v>132.2909742792444</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1669623425976524</v>
+        <v>0.1710010873509075</v>
       </c>
       <c r="T71">
-        <v>2.491225289382897</v>
+        <v>2.574266132362327</v>
       </c>
       <c r="U71">
         <v>0.2397577444416894</v>
       </c>
       <c r="V71">
-        <v>0.05755687733177081</v>
+        <v>0.05673463622703123</v>
       </c>
       <c r="W71">
-        <v>0.225958037355517</v>
+        <v>0.2261551760281766</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2877843866588541</v>
+        <v>0.2836731811351562</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2096089494249959</v>
+        <v>0.2115485268694128</v>
       </c>
       <c r="C72">
-        <v>-993.7652920027899</v>
+        <v>-1024.434888669221</v>
       </c>
       <c r="D72">
-        <v>522.119837042574</v>
+        <v>516.0100279339342</v>
       </c>
       <c r="E72">
-        <v>-268.593626733727</v>
+        <v>-244.0338391759362</v>
       </c>
       <c r="F72">
-        <v>1719.185129045364</v>
+        <v>1743.744916603155</v>
       </c>
       <c r="G72">
         <v>203.3</v>
@@ -7191,37 +7191,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M72">
-        <v>412.1879488176112</v>
+        <v>418.0763480864342</v>
       </c>
       <c r="N72">
-        <v>-295.2612821509445</v>
+        <v>-301.1496814197675</v>
       </c>
       <c r="O72">
-        <v>-59.0522564301889</v>
+        <v>-60.2299362839535</v>
       </c>
       <c r="P72">
-        <v>-236.2090257207556</v>
+        <v>-240.919745135814</v>
       </c>
       <c r="Q72">
-        <v>132.2909742792444</v>
+        <v>127.580254864186</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1710010873509075</v>
+        <v>0.1753183662250767</v>
       </c>
       <c r="T72">
-        <v>2.574266132362327</v>
+        <v>2.663033930029994</v>
       </c>
       <c r="U72">
         <v>0.2397577444416894</v>
       </c>
       <c r="V72">
-        <v>0.05673463622703123</v>
+        <v>0.05593555684355192</v>
       </c>
       <c r="W72">
-        <v>0.2261551760281766</v>
+        <v>0.2263467614987895</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2836731811351562</v>
+        <v>0.2796777842177596</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2115485268694128</v>
+        <v>0.2134881043138296</v>
       </c>
       <c r="C73">
-        <v>-1024.43488866922</v>
+        <v>-1054.963146175246</v>
       </c>
       <c r="D73">
-        <v>516.0100279339342</v>
+        <v>510.0415579856992</v>
       </c>
       <c r="E73">
-        <v>-244.0338391759365</v>
+        <v>-219.4740516181455</v>
       </c>
       <c r="F73">
-        <v>1743.744916603154</v>
+        <v>1768.304704160945</v>
       </c>
       <c r="G73">
         <v>203.3</v>
@@ -7273,37 +7273,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M73">
-        <v>418.0763480864341</v>
+        <v>423.9647473552571</v>
       </c>
       <c r="N73">
-        <v>-301.1496814197674</v>
+        <v>-307.0380806885905</v>
       </c>
       <c r="O73">
-        <v>-60.22993628395349</v>
+        <v>-61.40761613771809</v>
       </c>
       <c r="P73">
-        <v>-240.9197451358139</v>
+        <v>-245.6304645508724</v>
       </c>
       <c r="Q73">
-        <v>127.5802548641861</v>
+        <v>122.8695354491276</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1753183662250767</v>
+        <v>0.1799440221616865</v>
       </c>
       <c r="T73">
-        <v>2.663033930029993</v>
+        <v>2.758142284673921</v>
       </c>
       <c r="U73">
         <v>0.2397577444416894</v>
       </c>
       <c r="V73">
-        <v>0.05593555684355193</v>
+        <v>0.0551586741096137</v>
       </c>
       <c r="W73">
-        <v>0.2263467614987895</v>
+        <v>0.2265330251507742</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2796777842177596</v>
+        <v>0.2757933705480685</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2134881043138296</v>
+        <v>0.2154276817582466</v>
       </c>
       <c r="C74">
-        <v>-1054.963146175246</v>
+        <v>-1085.354912873059</v>
       </c>
       <c r="D74">
-        <v>510.0415579856992</v>
+        <v>504.209578845677</v>
       </c>
       <c r="E74">
-        <v>-219.4740516181455</v>
+        <v>-194.9142640603545</v>
       </c>
       <c r="F74">
-        <v>1768.304704160945</v>
+        <v>1792.864491718736</v>
       </c>
       <c r="G74">
         <v>203.3</v>
@@ -7355,37 +7355,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M74">
-        <v>423.9647473552571</v>
+        <v>429.8531466240802</v>
       </c>
       <c r="N74">
-        <v>-307.0380806885905</v>
+        <v>-312.9264799574135</v>
       </c>
       <c r="O74">
-        <v>-61.40761613771809</v>
+        <v>-62.5852959914827</v>
       </c>
       <c r="P74">
-        <v>-245.6304645508724</v>
+        <v>-250.3411839659308</v>
       </c>
       <c r="Q74">
-        <v>122.8695354491276</v>
+        <v>118.1588160340692</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1799440221616865</v>
+        <v>0.184912319278786</v>
       </c>
       <c r="T74">
-        <v>2.758142284673921</v>
+        <v>2.860295702624807</v>
       </c>
       <c r="U74">
         <v>0.2397577444416894</v>
       </c>
       <c r="V74">
-        <v>0.0551586741096137</v>
+        <v>0.05440307583413954</v>
       </c>
       <c r="W74">
-        <v>0.2265330251507742</v>
+        <v>0.2267141856890059</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2757933705480685</v>
+        <v>0.2720153791706977</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2154276817582466</v>
+        <v>0.2173672592026635</v>
       </c>
       <c r="C75">
-        <v>-1085.354912873059</v>
+        <v>-1115.614817871281</v>
       </c>
       <c r="D75">
-        <v>504.209578845677</v>
+        <v>498.5094614052467</v>
       </c>
       <c r="E75">
-        <v>-194.9142640603545</v>
+        <v>-170.3544765025636</v>
       </c>
       <c r="F75">
-        <v>1792.864491718736</v>
+        <v>1817.424279276527</v>
       </c>
       <c r="G75">
         <v>203.3</v>
@@ -7437,37 +7437,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M75">
-        <v>429.8531466240802</v>
+        <v>435.7415458929032</v>
       </c>
       <c r="N75">
-        <v>-312.9264799574135</v>
+        <v>-318.8148792262365</v>
       </c>
       <c r="O75">
-        <v>-62.5852959914827</v>
+        <v>-63.76297584524731</v>
       </c>
       <c r="P75">
-        <v>-250.3411839659308</v>
+        <v>-255.0519033809892</v>
       </c>
       <c r="Q75">
-        <v>118.1588160340692</v>
+        <v>113.4480966190108</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.184912319278786</v>
+        <v>0.1902627930972009</v>
       </c>
       <c r="T75">
-        <v>2.860295702624807</v>
+        <v>2.970307075802684</v>
       </c>
       <c r="U75">
         <v>0.2397577444416894</v>
       </c>
       <c r="V75">
-        <v>0.05440307583413954</v>
+        <v>0.05366789913367819</v>
       </c>
       <c r="W75">
-        <v>0.2267141856890059</v>
+        <v>0.2268904499964746</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2720153791706977</v>
+        <v>0.268339495668391</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2173672592026635</v>
+        <v>0.2193068366470803</v>
       </c>
       <c r="C76">
-        <v>-1115.614817871281</v>
+        <v>-1145.747283289234</v>
       </c>
       <c r="D76">
-        <v>498.5094614052467</v>
+        <v>492.9367835450842</v>
       </c>
       <c r="E76">
-        <v>-170.3544765025636</v>
+        <v>-145.7946889447728</v>
       </c>
       <c r="F76">
-        <v>1817.424279276527</v>
+        <v>1841.984066834318</v>
       </c>
       <c r="G76">
         <v>203.3</v>
@@ -7519,37 +7519,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M76">
-        <v>435.7415458929032</v>
+        <v>441.6299451617262</v>
       </c>
       <c r="N76">
-        <v>-318.8148792262365</v>
+        <v>-324.7032784950595</v>
       </c>
       <c r="O76">
-        <v>-63.76297584524731</v>
+        <v>-64.94065569901191</v>
       </c>
       <c r="P76">
-        <v>-255.0519033809892</v>
+        <v>-259.7626227960476</v>
       </c>
       <c r="Q76">
-        <v>113.4480966190108</v>
+        <v>108.7373772039524</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1902627930972009</v>
+        <v>0.1960413048210889</v>
       </c>
       <c r="T76">
-        <v>2.970307075802684</v>
+        <v>3.089119358834791</v>
       </c>
       <c r="U76">
         <v>0.2397577444416894</v>
       </c>
       <c r="V76">
-        <v>0.05366789913367819</v>
+        <v>0.05295232714522916</v>
       </c>
       <c r="W76">
-        <v>0.2268904499964746</v>
+        <v>0.2270620139224108</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.268339495668391</v>
+        <v>0.2647616357261457</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2193068366470803</v>
+        <v>0.2212464140914973</v>
       </c>
       <c r="C77">
-        <v>-1145.747283289234</v>
+        <v>-1175.756535698378</v>
       </c>
       <c r="D77">
-        <v>492.9367835450842</v>
+        <v>487.4873186937311</v>
       </c>
       <c r="E77">
-        <v>-145.7946889447728</v>
+        <v>-121.2349013869818</v>
       </c>
       <c r="F77">
-        <v>1841.984066834318</v>
+        <v>1866.543854392109</v>
       </c>
       <c r="G77">
         <v>203.3</v>
@@ -7601,37 +7601,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M77">
-        <v>441.6299451617262</v>
+        <v>447.5183444305492</v>
       </c>
       <c r="N77">
-        <v>-324.7032784950595</v>
+        <v>-330.5916777638826</v>
       </c>
       <c r="O77">
-        <v>-64.94065569901191</v>
+        <v>-66.11833555277651</v>
       </c>
       <c r="P77">
-        <v>-259.7626227960476</v>
+        <v>-264.4733422111061</v>
       </c>
       <c r="Q77">
-        <v>108.7373772039524</v>
+        <v>104.0266577888939</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1960413048210889</v>
+        <v>0.2023013591886343</v>
       </c>
       <c r="T77">
-        <v>3.089119358834791</v>
+        <v>3.217832665452908</v>
       </c>
       <c r="U77">
         <v>0.2397577444416894</v>
       </c>
       <c r="V77">
-        <v>0.05295232714522916</v>
+        <v>0.05225558599858141</v>
       </c>
       <c r="W77">
-        <v>0.2270620139224108</v>
+        <v>0.2272290630081908</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2647616357261457</v>
+        <v>0.261277929992907</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2212464140914973</v>
+        <v>0.2231859915359141</v>
       </c>
       <c r="C78">
-        <v>-1175.756535698378</v>
+        <v>-1205.646616813122</v>
       </c>
       <c r="D78">
-        <v>487.4873186937311</v>
+        <v>482.1570251367781</v>
       </c>
       <c r="E78">
-        <v>-121.2349013869818</v>
+        <v>-96.67511382919088</v>
       </c>
       <c r="F78">
-        <v>1866.543854392109</v>
+        <v>1891.1036419499</v>
       </c>
       <c r="G78">
         <v>203.3</v>
@@ -7683,37 +7683,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M78">
-        <v>447.5183444305492</v>
+        <v>453.4067436993722</v>
       </c>
       <c r="N78">
-        <v>-330.5916777638826</v>
+        <v>-336.4800770327055</v>
       </c>
       <c r="O78">
-        <v>-66.11833555277651</v>
+        <v>-67.29601540654112</v>
       </c>
       <c r="P78">
-        <v>-264.4733422111061</v>
+        <v>-269.1840616261644</v>
       </c>
       <c r="Q78">
-        <v>104.0266577888939</v>
+        <v>99.31593837383559</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2023013591886343</v>
+        <v>0.2091057661098793</v>
       </c>
       <c r="T78">
-        <v>3.217832665452908</v>
+        <v>3.357738433516078</v>
       </c>
       <c r="U78">
         <v>0.2397577444416894</v>
       </c>
       <c r="V78">
-        <v>0.05225558599858141</v>
+        <v>0.05157694202457385</v>
       </c>
       <c r="W78">
-        <v>0.2272290630081908</v>
+        <v>0.2273917731566778</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.261277929992907</v>
+        <v>0.2578847101228693</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2231859915359141</v>
+        <v>0.225125568980331</v>
       </c>
       <c r="C79">
-        <v>-1205.646616813122</v>
+        <v>-1235.421393487858</v>
       </c>
       <c r="D79">
-        <v>482.1570251367781</v>
+        <v>476.9420360198333</v>
       </c>
       <c r="E79">
-        <v>-96.67511382919088</v>
+        <v>-72.11532627139991</v>
       </c>
       <c r="F79">
-        <v>1891.1036419499</v>
+        <v>1915.663429507691</v>
       </c>
       <c r="G79">
         <v>203.3</v>
@@ -7765,37 +7765,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M79">
-        <v>453.4067436993722</v>
+        <v>459.2951429681953</v>
       </c>
       <c r="N79">
-        <v>-336.4800770327055</v>
+        <v>-342.3684763015286</v>
       </c>
       <c r="O79">
-        <v>-67.29601540654112</v>
+        <v>-68.47369526030572</v>
       </c>
       <c r="P79">
-        <v>-269.1840616261644</v>
+        <v>-273.8947810412229</v>
       </c>
       <c r="Q79">
-        <v>99.31593837383559</v>
+        <v>94.60521895877713</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2091057661098793</v>
+        <v>0.2165287554785102</v>
       </c>
       <c r="T79">
-        <v>3.357738433516078</v>
+        <v>3.510362907766809</v>
       </c>
       <c r="U79">
         <v>0.2397577444416894</v>
       </c>
       <c r="V79">
-        <v>0.05157694202457385</v>
+        <v>0.05091569917810496</v>
       </c>
       <c r="W79">
-        <v>0.2273917731566778</v>
+        <v>0.2275503112500754</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2578847101228693</v>
+        <v>0.2545784958905247</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.225125568980331</v>
+        <v>0.227065146424748</v>
       </c>
       <c r="C80">
-        <v>-1235.421393487858</v>
+        <v>-1265.084567072164</v>
       </c>
       <c r="D80">
-        <v>476.9420360198333</v>
+        <v>471.8386499933175</v>
       </c>
       <c r="E80">
-        <v>-72.11532627139991</v>
+        <v>-47.55553871360894</v>
       </c>
       <c r="F80">
-        <v>1915.663429507691</v>
+        <v>1940.223217065482</v>
       </c>
       <c r="G80">
         <v>203.3</v>
@@ -7847,37 +7847,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M80">
-        <v>459.2951429681953</v>
+        <v>465.1835422370183</v>
       </c>
       <c r="N80">
-        <v>-342.3684763015286</v>
+        <v>-348.2568755703516</v>
       </c>
       <c r="O80">
-        <v>-68.47369526030572</v>
+        <v>-69.65137511407032</v>
       </c>
       <c r="P80">
-        <v>-273.8947810412229</v>
+        <v>-278.6055004562813</v>
       </c>
       <c r="Q80">
-        <v>94.60521895877713</v>
+        <v>89.89449954371872</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2165287554785102</v>
+        <v>0.2246586962155821</v>
       </c>
       <c r="T80">
-        <v>3.510362907766809</v>
+        <v>3.677523046231896</v>
       </c>
       <c r="U80">
         <v>0.2397577444416894</v>
       </c>
       <c r="V80">
-        <v>0.05091569917810496</v>
+        <v>0.05027119665686312</v>
       </c>
       <c r="W80">
-        <v>0.2275503112500754</v>
+        <v>0.2277048357208553</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2545784958905247</v>
+        <v>0.2513559832843155</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.227065146424748</v>
+        <v>0.2290047238691648</v>
       </c>
       <c r="C81">
-        <v>-1265.084567072164</v>
+        <v>-1294.639682171753</v>
       </c>
       <c r="D81">
-        <v>471.8386499933175</v>
+        <v>466.8433224515197</v>
       </c>
       <c r="E81">
-        <v>-47.55553871360894</v>
+        <v>-22.99575115581797</v>
       </c>
       <c r="F81">
-        <v>1940.223217065482</v>
+        <v>1964.783004623273</v>
       </c>
       <c r="G81">
         <v>203.3</v>
@@ -7929,37 +7929,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M81">
-        <v>465.1835422370183</v>
+        <v>471.0719415058413</v>
       </c>
       <c r="N81">
-        <v>-348.2568755703516</v>
+        <v>-354.1452748391746</v>
       </c>
       <c r="O81">
-        <v>-69.65137511407032</v>
+        <v>-70.82905496783494</v>
       </c>
       <c r="P81">
-        <v>-278.6055004562813</v>
+        <v>-283.3162198713397</v>
       </c>
       <c r="Q81">
-        <v>89.89449954371872</v>
+        <v>85.18378012866026</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2246586962155821</v>
+        <v>0.2336016310263612</v>
       </c>
       <c r="T81">
-        <v>3.677523046231896</v>
+        <v>3.86139919854349</v>
       </c>
       <c r="U81">
         <v>0.2397577444416894</v>
       </c>
       <c r="V81">
-        <v>0.05027119665686312</v>
+        <v>0.04964280669865233</v>
       </c>
       <c r="W81">
-        <v>0.2277048357208553</v>
+        <v>0.2278554970798657</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2513559832843155</v>
+        <v>0.2482140334932617</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2290047238691648</v>
+        <v>0.2309443013135817</v>
       </c>
       <c r="C82">
-        <v>-1294.639682171753</v>
+        <v>-1324.09013485874</v>
       </c>
       <c r="D82">
-        <v>466.8433224515197</v>
+        <v>461.952657322324</v>
       </c>
       <c r="E82">
-        <v>-22.99575115581797</v>
+        <v>1.564036401972999</v>
       </c>
       <c r="F82">
-        <v>1964.783004623273</v>
+        <v>1989.342792181064</v>
       </c>
       <c r="G82">
         <v>203.3</v>
@@ -8011,37 +8011,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M82">
-        <v>471.0719415058413</v>
+        <v>476.9603407746644</v>
       </c>
       <c r="N82">
-        <v>-354.1452748391746</v>
+        <v>-360.0336741079977</v>
       </c>
       <c r="O82">
-        <v>-70.82905496783494</v>
+        <v>-72.00673482159954</v>
       </c>
       <c r="P82">
-        <v>-283.3162198713397</v>
+        <v>-288.0269392863981</v>
       </c>
       <c r="Q82">
-        <v>85.18378012866026</v>
+        <v>80.47306071360185</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2336016310263612</v>
+        <v>0.2434859273961697</v>
       </c>
       <c r="T82">
-        <v>3.86139919854349</v>
+        <v>4.064630735308937</v>
       </c>
       <c r="U82">
         <v>0.2397577444416894</v>
       </c>
       <c r="V82">
-        <v>0.04964280669865233</v>
+        <v>0.04902993254187884</v>
       </c>
       <c r="W82">
-        <v>0.2278554970798657</v>
+        <v>0.2280024384053204</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2482140334932617</v>
+        <v>0.2451496627093942</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2309443013135817</v>
+        <v>0.2328838787579986</v>
       </c>
       <c r="C83">
-        <v>-1324.09013485874</v>
+        <v>-1353.439180371193</v>
       </c>
       <c r="D83">
-        <v>461.952657322324</v>
+        <v>457.1633993676618</v>
       </c>
       <c r="E83">
-        <v>1.564036401972999</v>
+        <v>26.12382395976374</v>
       </c>
       <c r="F83">
-        <v>1989.342792181064</v>
+        <v>2013.902579738855</v>
       </c>
       <c r="G83">
         <v>203.3</v>
@@ -8093,37 +8093,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M83">
-        <v>476.9603407746644</v>
+        <v>482.8487400434873</v>
       </c>
       <c r="N83">
-        <v>-360.0336741079977</v>
+        <v>-365.9220733768207</v>
       </c>
       <c r="O83">
-        <v>-72.00673482159954</v>
+        <v>-73.18441467536414</v>
       </c>
       <c r="P83">
-        <v>-288.0269392863981</v>
+        <v>-292.7376587014566</v>
       </c>
       <c r="Q83">
-        <v>80.47306071360185</v>
+        <v>75.76234129854345</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2434859273961697</v>
+        <v>0.2544684789181791</v>
       </c>
       <c r="T83">
-        <v>4.064630735308937</v>
+        <v>4.290443553937211</v>
       </c>
       <c r="U83">
         <v>0.2397577444416894</v>
       </c>
       <c r="V83">
-        <v>0.04902993254187884</v>
+        <v>0.04843200653527056</v>
       </c>
       <c r="W83">
-        <v>0.2280024384053204</v>
+        <v>0.2281457957960078</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2451496627093942</v>
+        <v>0.2421600326763528</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2328838787579986</v>
+        <v>0.2348234562024155</v>
       </c>
       <c r="C84">
-        <v>-1353.439180371193</v>
+        <v>-1382.689940338656</v>
       </c>
       <c r="D84">
-        <v>457.1633993676618</v>
+        <v>452.4724269579892</v>
       </c>
       <c r="E84">
-        <v>26.12382395976374</v>
+        <v>50.68361151755471</v>
       </c>
       <c r="F84">
-        <v>2013.902579738855</v>
+        <v>2038.462367296646</v>
       </c>
       <c r="G84">
         <v>203.3</v>
@@ -8175,37 +8175,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M84">
-        <v>482.8487400434873</v>
+        <v>488.7371393123104</v>
       </c>
       <c r="N84">
-        <v>-365.9220733768207</v>
+        <v>-371.8104726456437</v>
       </c>
       <c r="O84">
-        <v>-73.18441467536414</v>
+        <v>-74.36209452912874</v>
       </c>
       <c r="P84">
-        <v>-292.7376587014566</v>
+        <v>-297.448378116515</v>
       </c>
       <c r="Q84">
-        <v>75.76234129854345</v>
+        <v>71.05162188348504</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2544684789181791</v>
+        <v>0.2667430953251309</v>
       </c>
       <c r="T84">
-        <v>4.290443553937211</v>
+        <v>4.542822586521754</v>
       </c>
       <c r="U84">
         <v>0.2397577444416894</v>
       </c>
       <c r="V84">
-        <v>0.04843200653527056</v>
+        <v>0.04784848838424321</v>
       </c>
       <c r="W84">
-        <v>0.2281457957960078</v>
+        <v>0.2282856987917389</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2421600326763528</v>
+        <v>0.239242441921216</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2348234562024155</v>
+        <v>0.2367630336468325</v>
       </c>
       <c r="C85">
-        <v>-1382.689940338656</v>
+        <v>-1411.845409567338</v>
       </c>
       <c r="D85">
-        <v>452.4724269579892</v>
+        <v>447.8767452870989</v>
       </c>
       <c r="E85">
-        <v>50.68361151755471</v>
+        <v>75.24339907534591</v>
       </c>
       <c r="F85">
-        <v>2038.462367296646</v>
+        <v>2063.022154854437</v>
       </c>
       <c r="G85">
         <v>203.3</v>
@@ -8257,37 +8257,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M85">
-        <v>488.7371393123104</v>
+        <v>494.6255385811335</v>
       </c>
       <c r="N85">
-        <v>-371.8104726456437</v>
+        <v>-377.6988719144668</v>
       </c>
       <c r="O85">
-        <v>-74.36209452912874</v>
+        <v>-75.53977438289336</v>
       </c>
       <c r="P85">
-        <v>-297.448378116515</v>
+        <v>-302.1590975315734</v>
       </c>
       <c r="Q85">
-        <v>71.05162188348504</v>
+        <v>66.34090246842658</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2667430953251309</v>
+        <v>0.2805520387829517</v>
       </c>
       <c r="T85">
-        <v>4.542822586521754</v>
+        <v>4.826748998179365</v>
       </c>
       <c r="U85">
         <v>0.2397577444416894</v>
       </c>
       <c r="V85">
-        <v>0.04784848838424321</v>
+        <v>0.04727886352252602</v>
       </c>
       <c r="W85">
-        <v>0.2282856987917389</v>
+        <v>0.2284222707637621</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.239242441921216</v>
+        <v>0.2363943176126301</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2367630336468324</v>
+        <v>0.2387026110912493</v>
       </c>
       <c r="C86">
-        <v>-1411.845409567337</v>
+        <v>-1440.908462415958</v>
       </c>
       <c r="D86">
-        <v>447.8767452870994</v>
+        <v>443.3734799962691</v>
       </c>
       <c r="E86">
-        <v>75.24339907534545</v>
+        <v>99.80318663313642</v>
       </c>
       <c r="F86">
-        <v>2063.022154854436</v>
+        <v>2087.581942412227</v>
       </c>
       <c r="G86">
         <v>203.3</v>
@@ -8339,37 +8339,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M86">
-        <v>494.6255385811334</v>
+        <v>500.5139378499564</v>
       </c>
       <c r="N86">
-        <v>-377.6988719144667</v>
+        <v>-383.5872711832897</v>
       </c>
       <c r="O86">
-        <v>-75.53977438289334</v>
+        <v>-76.71745423665794</v>
       </c>
       <c r="P86">
-        <v>-302.1590975315734</v>
+        <v>-306.8698169466318</v>
       </c>
       <c r="Q86">
-        <v>66.34090246842663</v>
+        <v>61.63018305336823</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2805520387829514</v>
+        <v>0.2962021747018149</v>
       </c>
       <c r="T86">
-        <v>4.826748998179361</v>
+        <v>5.148532264724652</v>
       </c>
       <c r="U86">
         <v>0.2397577444416894</v>
       </c>
       <c r="V86">
-        <v>0.04727886352252603</v>
+        <v>0.0467226415987316</v>
       </c>
       <c r="W86">
-        <v>0.2284222707637621</v>
+        <v>0.22855562927762</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2363943176126301</v>
+        <v>0.233613207993658</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2387026110912493</v>
+        <v>0.2406421885356662</v>
       </c>
       <c r="C87">
-        <v>-1440.908462415958</v>
+        <v>-1469.881858790794</v>
       </c>
       <c r="D87">
-        <v>443.3734799962691</v>
+        <v>438.9598711792243</v>
       </c>
       <c r="E87">
-        <v>99.80318663313642</v>
+        <v>124.3629741909274</v>
       </c>
       <c r="F87">
-        <v>2087.581942412227</v>
+        <v>2112.141729970018</v>
       </c>
       <c r="G87">
         <v>203.3</v>
@@ -8421,37 +8421,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M87">
-        <v>500.5139378499564</v>
+        <v>506.4023371187794</v>
       </c>
       <c r="N87">
-        <v>-383.5872711832897</v>
+        <v>-389.4756704521128</v>
       </c>
       <c r="O87">
-        <v>-76.71745423665794</v>
+        <v>-77.89513409042256</v>
       </c>
       <c r="P87">
-        <v>-306.8698169466318</v>
+        <v>-311.5805363616902</v>
       </c>
       <c r="Q87">
-        <v>61.63018305336823</v>
+        <v>56.91946363830982</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2962021747018149</v>
+        <v>0.3140880443233731</v>
       </c>
       <c r="T87">
-        <v>5.148532264724652</v>
+        <v>5.516284569347842</v>
       </c>
       <c r="U87">
         <v>0.2397577444416894</v>
       </c>
       <c r="V87">
-        <v>0.0467226415987316</v>
+        <v>0.04617935506851379</v>
       </c>
       <c r="W87">
-        <v>0.22855562927762</v>
+        <v>0.2286858864306906</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.233613207993658</v>
+        <v>0.2308967753425689</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2406421885356662</v>
+        <v>0.2425817659800831</v>
       </c>
       <c r="C88">
-        <v>-1469.881858790794</v>
+        <v>-1498.76824978617</v>
       </c>
       <c r="D88">
-        <v>438.9598711792243</v>
+        <v>434.6332677416397</v>
       </c>
       <c r="E88">
-        <v>124.3629741909274</v>
+        <v>148.9227617487184</v>
       </c>
       <c r="F88">
-        <v>2112.141729970018</v>
+        <v>2136.701517527809</v>
       </c>
       <c r="G88">
         <v>203.3</v>
@@ -8503,37 +8503,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M88">
-        <v>506.4023371187794</v>
+        <v>512.2907363876025</v>
       </c>
       <c r="N88">
-        <v>-389.4756704521128</v>
+        <v>-395.3640697209358</v>
       </c>
       <c r="O88">
-        <v>-77.89513409042256</v>
+        <v>-79.07281394418716</v>
       </c>
       <c r="P88">
-        <v>-311.5805363616902</v>
+        <v>-316.2912557767486</v>
       </c>
       <c r="Q88">
-        <v>56.91946363830982</v>
+        <v>52.20874422325136</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3140880443233731</v>
+        <v>0.3347255861944018</v>
       </c>
       <c r="T88">
-        <v>5.516284569347842</v>
+        <v>5.940614151605367</v>
       </c>
       <c r="U88">
         <v>0.2397577444416894</v>
       </c>
       <c r="V88">
-        <v>0.04617935506851379</v>
+        <v>0.04564855788381823</v>
       </c>
       <c r="W88">
-        <v>0.2286858864306906</v>
+        <v>0.2288131491664492</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2308967753425689</v>
+        <v>0.2282427894190912</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2425817659800831</v>
+        <v>0.2445213434245</v>
       </c>
       <c r="C89">
-        <v>-1498.76824978617</v>
+        <v>-1527.570182994638</v>
       </c>
       <c r="D89">
-        <v>434.6332677416397</v>
+        <v>430.3911220909626</v>
       </c>
       <c r="E89">
-        <v>148.9227617487184</v>
+        <v>173.4825493065093</v>
       </c>
       <c r="F89">
-        <v>2136.701517527809</v>
+        <v>2161.2613050856</v>
       </c>
       <c r="G89">
         <v>203.3</v>
@@ -8585,37 +8585,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M89">
-        <v>512.2907363876025</v>
+        <v>518.1791356564255</v>
       </c>
       <c r="N89">
-        <v>-395.3640697209358</v>
+        <v>-401.2524689897588</v>
       </c>
       <c r="O89">
-        <v>-79.07281394418716</v>
+        <v>-80.25049379795178</v>
       </c>
       <c r="P89">
-        <v>-316.2912557767486</v>
+        <v>-321.001975191807</v>
       </c>
       <c r="Q89">
-        <v>52.20874422325136</v>
+        <v>47.49802480819295</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3347255861944018</v>
+        <v>0.3588027183772686</v>
       </c>
       <c r="T89">
-        <v>5.940614151605367</v>
+        <v>6.435665330905815</v>
       </c>
       <c r="U89">
         <v>0.2397577444416894</v>
       </c>
       <c r="V89">
-        <v>0.04564855788381823</v>
+        <v>0.04512982427150211</v>
       </c>
       <c r="W89">
-        <v>0.2288131491664492</v>
+        <v>0.2289375195673042</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2282427894190912</v>
+        <v>0.2256491213575106</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2445213434245</v>
+        <v>0.2464609208689169</v>
       </c>
       <c r="C90">
-        <v>-1527.570182994638</v>
+        <v>-1556.290107509192</v>
       </c>
       <c r="D90">
-        <v>430.3911220909626</v>
+        <v>426.2309851341994</v>
       </c>
       <c r="E90">
-        <v>173.4825493065093</v>
+        <v>198.0423368643003</v>
       </c>
       <c r="F90">
-        <v>2161.2613050856</v>
+        <v>2185.821092643391</v>
       </c>
       <c r="G90">
         <v>203.3</v>
@@ -8667,37 +8667,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M90">
-        <v>518.1791356564255</v>
+        <v>524.0675349252485</v>
       </c>
       <c r="N90">
-        <v>-401.2524689897588</v>
+        <v>-407.1408682585819</v>
       </c>
       <c r="O90">
-        <v>-80.25049379795178</v>
+        <v>-81.42817365171638</v>
       </c>
       <c r="P90">
-        <v>-321.001975191807</v>
+        <v>-325.7126946068655</v>
       </c>
       <c r="Q90">
-        <v>47.49802480819295</v>
+        <v>42.78730539313449</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3588027183772686</v>
+        <v>0.3872575109570204</v>
       </c>
       <c r="T90">
-        <v>6.435665330905815</v>
+        <v>7.020725815533618</v>
       </c>
       <c r="U90">
         <v>0.2397577444416894</v>
       </c>
       <c r="V90">
-        <v>0.04512982427150211</v>
+        <v>0.04462274759429422</v>
       </c>
       <c r="W90">
-        <v>0.2289375195673042</v>
+        <v>0.2290590951276906</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2256491213575106</v>
+        <v>0.223113737971471</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2464609208689169</v>
+        <v>0.2484004983133338</v>
       </c>
       <c r="C91">
-        <v>-1556.290107509192</v>
+        <v>-1584.930378638149</v>
       </c>
       <c r="D91">
-        <v>426.2309851341994</v>
+        <v>422.1505015630322</v>
       </c>
       <c r="E91">
-        <v>198.0423368643003</v>
+        <v>222.6021244220908</v>
       </c>
       <c r="F91">
-        <v>2185.821092643391</v>
+        <v>2210.380880201182</v>
       </c>
       <c r="G91">
         <v>203.3</v>
@@ -8749,37 +8749,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M91">
-        <v>524.0675349252485</v>
+        <v>529.9559341940715</v>
       </c>
       <c r="N91">
-        <v>-407.1408682585819</v>
+        <v>-413.0292675274048</v>
       </c>
       <c r="O91">
-        <v>-81.42817365171638</v>
+        <v>-82.60585350548097</v>
       </c>
       <c r="P91">
-        <v>-325.7126946068655</v>
+        <v>-330.4234140219238</v>
       </c>
       <c r="Q91">
-        <v>42.78730539313449</v>
+        <v>38.0765859780762</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3872575109570204</v>
+        <v>0.4214032620527224</v>
       </c>
       <c r="T91">
-        <v>7.020725815533618</v>
+        <v>7.72279839708698</v>
       </c>
       <c r="U91">
         <v>0.2397577444416894</v>
       </c>
       <c r="V91">
-        <v>0.04462274759429422</v>
+        <v>0.04412693928769096</v>
       </c>
       <c r="W91">
-        <v>0.2290590951276906</v>
+        <v>0.2291779690089573</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.223113737971471</v>
+        <v>0.2206346964384548</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2484004983133338</v>
+        <v>0.2503400757577506</v>
       </c>
       <c r="C92">
-        <v>-1584.930378638149</v>
+        <v>-1613.49326235178</v>
       </c>
       <c r="D92">
-        <v>422.1505015630322</v>
+        <v>418.1474054071929</v>
       </c>
       <c r="E92">
-        <v>222.6021244220908</v>
+        <v>247.1619119798818</v>
       </c>
       <c r="F92">
-        <v>2210.380880201182</v>
+        <v>2234.940667758973</v>
       </c>
       <c r="G92">
         <v>203.3</v>
@@ -8831,37 +8831,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M92">
-        <v>529.9559341940715</v>
+        <v>535.8443334628945</v>
       </c>
       <c r="N92">
-        <v>-413.0292675274048</v>
+        <v>-418.9176667962278</v>
       </c>
       <c r="O92">
-        <v>-82.60585350548097</v>
+        <v>-83.78353335924557</v>
       </c>
       <c r="P92">
-        <v>-330.4234140219238</v>
+        <v>-335.1341334369823</v>
       </c>
       <c r="Q92">
-        <v>38.0765859780762</v>
+        <v>33.36586656301773</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4214032620527224</v>
+        <v>0.4631369578363583</v>
       </c>
       <c r="T92">
-        <v>7.72279839708698</v>
+        <v>8.580887107874423</v>
       </c>
       <c r="U92">
         <v>0.2397577444416894</v>
       </c>
       <c r="V92">
-        <v>0.04412693928769096</v>
+        <v>0.0436420278669471</v>
       </c>
       <c r="W92">
-        <v>0.2291779690089573</v>
+        <v>0.2292942302774488</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2206346964384548</v>
+        <v>0.2182101393347355</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2503400757577506</v>
+        <v>0.2522796532021676</v>
       </c>
       <c r="C93">
-        <v>-1613.49326235178</v>
+        <v>-1641.980939478308</v>
       </c>
       <c r="D93">
-        <v>418.1474054071929</v>
+        <v>414.2195158384559</v>
       </c>
       <c r="E93">
-        <v>247.1619119798818</v>
+        <v>271.7216995376727</v>
       </c>
       <c r="F93">
-        <v>2234.940667758973</v>
+        <v>2259.500455316764</v>
       </c>
       <c r="G93">
         <v>203.3</v>
@@ -8913,37 +8913,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M93">
-        <v>535.8443334628945</v>
+        <v>541.7327327317174</v>
       </c>
       <c r="N93">
-        <v>-418.9176667962278</v>
+        <v>-424.8060660650507</v>
       </c>
       <c r="O93">
-        <v>-83.78353335924557</v>
+        <v>-84.96121321301015</v>
       </c>
       <c r="P93">
-        <v>-335.1341334369823</v>
+        <v>-339.8448528520406</v>
       </c>
       <c r="Q93">
-        <v>33.36586656301773</v>
+        <v>28.65514714795938</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4631369578363583</v>
+        <v>0.5153040775659031</v>
       </c>
       <c r="T93">
-        <v>8.580887107874423</v>
+        <v>9.653497996358729</v>
       </c>
       <c r="U93">
         <v>0.2397577444416894</v>
       </c>
       <c r="V93">
-        <v>0.0436420278669471</v>
+        <v>0.04316765799882812</v>
       </c>
       <c r="W93">
-        <v>0.2292942302774488</v>
+        <v>0.2294079641270601</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2182101393347355</v>
+        <v>0.2158382899941406</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2522796532021676</v>
+        <v>0.2542192306465845</v>
       </c>
       <c r="C94">
-        <v>-1641.980939478308</v>
+        <v>-1670.395509665634</v>
       </c>
       <c r="D94">
-        <v>414.2195158384559</v>
+        <v>410.3647332089205</v>
       </c>
       <c r="E94">
-        <v>271.7216995376727</v>
+        <v>296.2814870954637</v>
       </c>
       <c r="F94">
-        <v>2259.500455316764</v>
+        <v>2284.060242874555</v>
       </c>
       <c r="G94">
         <v>203.3</v>
@@ -8995,37 +8995,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M94">
-        <v>541.7327327317174</v>
+        <v>547.6211320005405</v>
       </c>
       <c r="N94">
-        <v>-424.8060660650507</v>
+        <v>-430.6944653338738</v>
       </c>
       <c r="O94">
-        <v>-84.96121321301015</v>
+        <v>-86.13889306677476</v>
       </c>
       <c r="P94">
-        <v>-339.8448528520406</v>
+        <v>-344.555572267099</v>
       </c>
       <c r="Q94">
-        <v>28.65514714795938</v>
+        <v>23.94442773290098</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5153040775659031</v>
+        <v>0.5823760886467465</v>
       </c>
       <c r="T94">
-        <v>9.653497996358729</v>
+        <v>11.03256913869569</v>
       </c>
       <c r="U94">
         <v>0.2397577444416894</v>
       </c>
       <c r="V94">
-        <v>0.04316765799882812</v>
+        <v>0.04270348963324933</v>
       </c>
       <c r="W94">
-        <v>0.2294079641270601</v>
+        <v>0.2295192520874325</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2158382899941406</v>
+        <v>0.2135174481662466</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2542192306465845</v>
+        <v>0.2561588080910013</v>
       </c>
       <c r="C95">
-        <v>-1670.395509665634</v>
+        <v>-1698.73899512388</v>
       </c>
       <c r="D95">
-        <v>410.3647332089205</v>
+        <v>406.5810353084655</v>
       </c>
       <c r="E95">
-        <v>296.2814870954637</v>
+        <v>320.8412746532547</v>
       </c>
       <c r="F95">
-        <v>2284.060242874555</v>
+        <v>2308.620030432346</v>
       </c>
       <c r="G95">
         <v>203.3</v>
@@ -9077,37 +9077,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M95">
-        <v>547.6211320005405</v>
+        <v>553.5095312693635</v>
       </c>
       <c r="N95">
-        <v>-430.6944653338738</v>
+        <v>-436.5828646026968</v>
       </c>
       <c r="O95">
-        <v>-86.13889306677476</v>
+        <v>-87.31657292053937</v>
       </c>
       <c r="P95">
-        <v>-344.555572267099</v>
+        <v>-349.2662916821574</v>
       </c>
       <c r="Q95">
-        <v>23.94442773290098</v>
+        <v>19.23370831784257</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5823760886467465</v>
+        <v>0.6718054367545379</v>
       </c>
       <c r="T95">
-        <v>11.03256913869569</v>
+        <v>12.87133066181164</v>
       </c>
       <c r="U95">
         <v>0.2397577444416894</v>
       </c>
       <c r="V95">
-        <v>0.04270348963324933</v>
+        <v>0.04224919719034241</v>
       </c>
       <c r="W95">
-        <v>0.2295192520874325</v>
+        <v>0.2296281722188608</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2135174481662466</v>
+        <v>0.2112459859517121</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2561588080910013</v>
+        <v>0.2580983855354183</v>
       </c>
       <c r="C96">
-        <v>-1698.73899512388</v>
+        <v>-1727.013344162782</v>
       </c>
       <c r="D96">
-        <v>406.5810353084655</v>
+        <v>402.8664738273542</v>
       </c>
       <c r="E96">
-        <v>320.8412746532547</v>
+        <v>345.4010622110457</v>
       </c>
       <c r="F96">
-        <v>2308.620030432346</v>
+        <v>2333.179817990137</v>
       </c>
       <c r="G96">
         <v>203.3</v>
@@ -9159,37 +9159,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M96">
-        <v>553.5095312693635</v>
+        <v>559.3979305381865</v>
       </c>
       <c r="N96">
-        <v>-436.5828646026968</v>
+        <v>-442.4712638715199</v>
       </c>
       <c r="O96">
-        <v>-87.31657292053937</v>
+        <v>-88.49425277430397</v>
       </c>
       <c r="P96">
-        <v>-349.2662916821574</v>
+        <v>-353.9770110972159</v>
       </c>
       <c r="Q96">
-        <v>19.23370831784257</v>
+        <v>14.52298890278411</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6718054367545379</v>
+        <v>0.7970065241054456</v>
       </c>
       <c r="T96">
-        <v>12.87133066181164</v>
+        <v>15.44559679417398</v>
       </c>
       <c r="U96">
         <v>0.2397577444416894</v>
       </c>
       <c r="V96">
-        <v>0.04224919719034241</v>
+        <v>0.04180446879886512</v>
       </c>
       <c r="W96">
-        <v>0.2296281722188608</v>
+        <v>0.2297347992948905</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2112459859517121</v>
+        <v>0.2090223439943256</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2580983855354183</v>
+        <v>0.2600379629798352</v>
       </c>
       <c r="C97">
-        <v>-1727.013344162782</v>
+        <v>-1755.220434536932</v>
       </c>
       <c r="D97">
-        <v>402.8664738273542</v>
+        <v>399.2191710109955</v>
       </c>
       <c r="E97">
-        <v>345.4010622110457</v>
+        <v>369.9608497688366</v>
       </c>
       <c r="F97">
-        <v>2333.179817990137</v>
+        <v>2357.739605547928</v>
       </c>
       <c r="G97">
         <v>203.3</v>
@@ -9241,37 +9241,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M97">
-        <v>559.3979305381865</v>
+        <v>565.2863298070096</v>
       </c>
       <c r="N97">
-        <v>-442.4712638715199</v>
+        <v>-448.3596631403429</v>
       </c>
       <c r="O97">
-        <v>-88.49425277430397</v>
+        <v>-89.67193262806859</v>
       </c>
       <c r="P97">
-        <v>-353.9770110972159</v>
+        <v>-358.6877305122743</v>
       </c>
       <c r="Q97">
-        <v>14.52298890278411</v>
+        <v>9.8122694877257</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7970065241054456</v>
+        <v>0.9848081551318075</v>
       </c>
       <c r="T97">
-        <v>15.44559679417398</v>
+        <v>19.30699599271748</v>
       </c>
       <c r="U97">
         <v>0.2397577444416894</v>
       </c>
       <c r="V97">
-        <v>0.04180446879886512</v>
+        <v>0.04136900558221027</v>
       </c>
       <c r="W97">
-        <v>0.2297347992948905</v>
+        <v>0.229839204973503</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2090223439943256</v>
+        <v>0.2068450279110513</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2600379629798351</v>
+        <v>0.261977540424252</v>
       </c>
       <c r="C98">
-        <v>-1755.220434536932</v>
+        <v>-1783.362076610932</v>
       </c>
       <c r="D98">
-        <v>399.2191710109955</v>
+        <v>395.6373164947856</v>
       </c>
       <c r="E98">
-        <v>369.9608497688362</v>
+        <v>394.5206373266271</v>
       </c>
       <c r="F98">
-        <v>2357.739605547927</v>
+        <v>2382.299393105718</v>
       </c>
       <c r="G98">
         <v>203.3</v>
@@ -9323,37 +9323,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M98">
-        <v>565.2863298070095</v>
+        <v>571.1747290758325</v>
       </c>
       <c r="N98">
-        <v>-448.3596631403428</v>
+        <v>-454.2480624091658</v>
       </c>
       <c r="O98">
-        <v>-89.67193262806856</v>
+        <v>-90.84961248183316</v>
       </c>
       <c r="P98">
-        <v>-358.6877305122742</v>
+        <v>-363.3984499273326</v>
       </c>
       <c r="Q98">
-        <v>9.812269487725757</v>
+        <v>5.101550072667351</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9848081551318051</v>
+        <v>1.297810873509073</v>
       </c>
       <c r="T98">
-        <v>19.30699599271743</v>
+        <v>25.74266132362324</v>
       </c>
       <c r="U98">
         <v>0.2397577444416894</v>
       </c>
       <c r="V98">
-        <v>0.04136900558221028</v>
+        <v>0.04094252098857925</v>
       </c>
       <c r="W98">
-        <v>0.229839204973503</v>
+        <v>0.2299414579577111</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2068450279110514</v>
+        <v>0.2047126049428962</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.261977540424252</v>
+        <v>0.2639171178686689</v>
       </c>
       <c r="C99">
-        <v>-1783.362076610932</v>
+        <v>-1811.440016355683</v>
       </c>
       <c r="D99">
-        <v>395.6373164947856</v>
+        <v>392.1191643078264</v>
       </c>
       <c r="E99">
-        <v>394.5206373266271</v>
+        <v>419.0804248844181</v>
       </c>
       <c r="F99">
-        <v>2382.299393105718</v>
+        <v>2406.859180663509</v>
       </c>
       <c r="G99">
         <v>203.3</v>
@@ -9405,37 +9405,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M99">
-        <v>571.1747290758325</v>
+        <v>577.0631283446555</v>
       </c>
       <c r="N99">
-        <v>-454.2480624091658</v>
+        <v>-460.1364616779888</v>
       </c>
       <c r="O99">
-        <v>-90.84961248183316</v>
+        <v>-92.02729233559778</v>
       </c>
       <c r="P99">
-        <v>-363.3984499273326</v>
+        <v>-368.1091693423911</v>
       </c>
       <c r="Q99">
-        <v>5.101550072667351</v>
+        <v>0.3908306576089444</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.297810873509073</v>
+        <v>1.92381631026361</v>
       </c>
       <c r="T99">
-        <v>25.74266132362324</v>
+        <v>38.61399198543486</v>
       </c>
       <c r="U99">
         <v>0.2397577444416894</v>
       </c>
       <c r="V99">
-        <v>0.04094252098857925</v>
+        <v>0.04052474016216517</v>
       </c>
       <c r="W99">
-        <v>0.2299414579577111</v>
+        <v>0.2300416241463231</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2047126049428962</v>
+        <v>0.2026237008108258</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2639171178686689</v>
+        <v>0.2658566953130858</v>
       </c>
       <c r="C100">
-        <v>-1811.440016355683</v>
+        <v>-1839.455938186203</v>
       </c>
       <c r="D100">
-        <v>392.1191643078264</v>
+        <v>388.6630300350974</v>
       </c>
       <c r="E100">
-        <v>419.0804248844181</v>
+        <v>443.6402124422091</v>
       </c>
       <c r="F100">
-        <v>2406.859180663509</v>
+        <v>2431.4189682213</v>
       </c>
       <c r="G100">
         <v>203.3</v>
@@ -9487,37 +9487,37 @@
         <v>116.9266666666667</v>
       </c>
       <c r="M100">
-        <v>577.0631283446555</v>
+        <v>582.9515276134786</v>
       </c>
       <c r="N100">
-        <v>-460.1364616779888</v>
+        <v>-466.0248609468119</v>
       </c>
       <c r="O100">
-        <v>-92.02729233559778</v>
+        <v>-93.20497218936238</v>
       </c>
       <c r="P100">
-        <v>-368.1091693423911</v>
+        <v>-372.8198887574495</v>
       </c>
       <c r="Q100">
-        <v>0.3908306576089444</v>
+        <v>-4.319888757449519</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.92381631026361</v>
+        <v>3.80183262052722</v>
       </c>
       <c r="T100">
-        <v>38.61399198543486</v>
+        <v>77.22798397086973</v>
       </c>
       <c r="U100">
         <v>0.2397577444416894</v>
       </c>
       <c r="V100">
-        <v>0.04052474016216517</v>
+        <v>0.04011539935244633</v>
       </c>
       <c r="W100">
-        <v>0.2300416241463231</v>
+        <v>0.2301397667755693</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2026237008108258</v>
+        <v>0.2005769967622316</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2658566953130858</v>
-      </c>
-      <c r="C101">
-        <v>-1839.455938186203</v>
-      </c>
-      <c r="D101">
-        <v>388.6630300350974</v>
-      </c>
-      <c r="E101">
-        <v>443.6402124422091</v>
-      </c>
-      <c r="F101">
-        <v>2431.4189682213</v>
-      </c>
-      <c r="G101">
-        <v>203.3</v>
-      </c>
-      <c r="H101">
-        <v>468.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>485.4266666666667</v>
-      </c>
-      <c r="K101">
-        <v>368.5</v>
-      </c>
-      <c r="L101">
-        <v>116.9266666666667</v>
-      </c>
-      <c r="M101">
-        <v>582.9515276134786</v>
-      </c>
-      <c r="N101">
-        <v>-466.0248609468119</v>
-      </c>
-      <c r="O101">
-        <v>-93.20497218936238</v>
-      </c>
-      <c r="P101">
-        <v>-372.8198887574495</v>
-      </c>
-      <c r="Q101">
-        <v>-4.319888757449519</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.80183262052722</v>
-      </c>
-      <c r="T101">
-        <v>77.22798397086973</v>
-      </c>
-      <c r="U101">
-        <v>0.2397577444416894</v>
-      </c>
-      <c r="V101">
-        <v>0.04011539935244633</v>
-      </c>
-      <c r="W101">
-        <v>0.2301397667755693</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2005769967622316</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
